--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,88 +852,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9513670599526608</v>
+        <v>0.9478296079490753</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9213215134648567</v>
+        <v>0.9193366363418792</v>
       </c>
       <c r="E2" t="n">
-        <v>107.8296407911593</v>
+        <v>107.599071801667</v>
       </c>
       <c r="F2" t="n">
-        <v>101.7138406744517</v>
+        <v>101.4931685599083</v>
       </c>
       <c r="G2" t="n">
-        <v>6.115800116707605</v>
+        <v>6.105903241758648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.306750052550015</v>
+        <v>0.3090341636641471</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7508789930976755</v>
+        <v>0.7516400885914124</v>
       </c>
       <c r="J2" t="n">
-        <v>0.525500538861946</v>
+        <v>0.5268391794824828</v>
       </c>
       <c r="K2" t="n">
-        <v>5225</v>
+        <v>5425</v>
       </c>
       <c r="L2" t="n">
-        <v>2163</v>
+        <v>2239</v>
       </c>
       <c r="M2" t="n">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="N2" t="n">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="O2" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="P2" t="n">
-        <v>852</v>
+        <v>880</v>
       </c>
       <c r="Q2" t="n">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="R2" t="n">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="S2" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="T2" t="n">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="U2" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="V2" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="W2" t="n">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="X2" t="n">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="Y2" t="n">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="Z2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA2" t="n">
-        <v>2048</v>
+        <v>2122</v>
       </c>
       <c r="AB2" t="n">
-        <v>2281.28</v>
+        <v>2370.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2009.28</v>
+        <v>2084.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
         <v>2825</v>
@@ -1014,82 +1014,82 @@
         <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF2" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="BG2" t="n">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="BH2" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="BI2" t="n">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="BJ2" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="BK2" t="n">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="BL2" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="BM2" t="n">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="BN2" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="BO2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BP2" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="BQ2" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="BR2" t="n">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BT2" t="n">
-        <v>1030.08</v>
+        <v>1118.88</v>
       </c>
       <c r="BU2" t="n">
-        <v>923.08</v>
+        <v>997.88</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9753838449447071</v>
+        <v>0.9661893842455647</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9119867787118268</v>
+        <v>0.9085823981297221</v>
       </c>
       <c r="BX2" t="n">
-        <v>108.7646349275893</v>
+        <v>108.2138382466106</v>
       </c>
       <c r="BY2" t="n">
-        <v>100.4824077811239</v>
+        <v>100.1188143811745</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.282227146465344</v>
+        <v>8.095023865436145</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2769908188711299</v>
+        <v>0.2840239137757798</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7498216817295763</v>
+        <v>0.7514837501679607</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.5187050668526008</v>
+        <v>0.5220080490652037</v>
       </c>
       <c r="CD2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1104,88 +1104,88 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9451462608068156</v>
+        <v>0.9448071580071298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9652789106172202</v>
+        <v>0.9634181368605332</v>
       </c>
       <c r="E3" t="n">
-        <v>106.6574808032636</v>
+        <v>106.4779154352175</v>
       </c>
       <c r="F3" t="n">
-        <v>111.3589823186588</v>
+        <v>110.9143244493264</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.70150151539512</v>
+        <v>-4.43640901410892</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3153302198611653</v>
+        <v>0.3118869980054629</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659169145206523</v>
+        <v>0.6638645626985797</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4943916704434566</v>
+        <v>0.4949126257316508</v>
       </c>
       <c r="K3" t="n">
-        <v>5022.766666666666</v>
+        <v>5222.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2099</v>
+        <v>2179</v>
       </c>
       <c r="M3" t="n">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="N3" t="n">
-        <v>1044</v>
+        <v>1087</v>
       </c>
       <c r="O3" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="P3" t="n">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="Q3" t="n">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="R3" t="n">
-        <v>624</v>
+        <v>650</v>
       </c>
       <c r="S3" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="T3" t="n">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="U3" t="n">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="V3" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="W3" t="n">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="X3" t="n">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="Y3" t="n">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="Z3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA3" t="n">
-        <v>2177</v>
+        <v>2256</v>
       </c>
       <c r="AB3" t="n">
-        <v>2220.56</v>
+        <v>2306</v>
       </c>
       <c r="AC3" t="n">
-        <v>1965.56</v>
+        <v>2044</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>2600</v>
@@ -1266,82 +1266,82 @@
         <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>2422.766666666666</v>
+        <v>2622.766666666666</v>
       </c>
       <c r="BF3" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="BG3" t="n">
-        <v>515</v>
+        <v>558</v>
       </c>
       <c r="BH3" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="BI3" t="n">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="BJ3" t="n">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="BK3" t="n">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="BL3" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="BM3" t="n">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="BN3" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="BO3" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="BP3" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="BQ3" t="n">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="BR3" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="BS3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BT3" t="n">
-        <v>1097.28</v>
+        <v>1182.72</v>
       </c>
       <c r="BU3" t="n">
-        <v>966.28</v>
+        <v>1044.72</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9221935179855261</v>
+        <v>0.9232809079877918</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.9650702186512353</v>
+        <v>0.9613647243660142</v>
       </c>
       <c r="BX3" t="n">
-        <v>104.5273310547558</v>
+        <v>104.3320579916257</v>
       </c>
       <c r="BY3" t="n">
-        <v>110.8174417883001</v>
+        <v>109.9697830135092</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-6.29011073354435</v>
+        <v>-5.637725021883549</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.3046222764795947</v>
+        <v>0.2985595207206184</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6632347093661144</v>
+        <v>0.672312808645644</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.483702261069576</v>
+        <v>0.4855664339054939</v>
       </c>
       <c r="CD3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1356,166 +1356,166 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9102302420787259</v>
+        <v>0.8912543118697351</v>
       </c>
       <c r="D4" t="n">
-        <v>1.001898562194691</v>
+        <v>0.9933287096910387</v>
       </c>
       <c r="E4" t="n">
-        <v>106.7337395527079</v>
+        <v>104.6747312859054</v>
       </c>
       <c r="F4" t="n">
-        <v>111.8994828137643</v>
+        <v>110.8904447187794</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.1657432610564</v>
+        <v>-6.215713432873981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3721297357183876</v>
+        <v>0.3674149295227593</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7098974497146971</v>
+        <v>0.7138123377602861</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5266028018987361</v>
+        <v>0.5242723091641447</v>
       </c>
       <c r="K4" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="L4" t="n">
-        <v>1034</v>
+        <v>1090</v>
       </c>
       <c r="M4" t="n">
+        <v>264</v>
+      </c>
+      <c r="N4" t="n">
+        <v>595</v>
+      </c>
+      <c r="O4" t="n">
+        <v>114</v>
+      </c>
+      <c r="P4" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>220</v>
+      </c>
+      <c r="R4" t="n">
+        <v>309</v>
+      </c>
+      <c r="S4" t="n">
+        <v>186</v>
+      </c>
+      <c r="T4" t="n">
+        <v>297</v>
+      </c>
+      <c r="U4" t="n">
+        <v>212</v>
+      </c>
+      <c r="V4" t="n">
+        <v>84</v>
+      </c>
+      <c r="W4" t="n">
+        <v>163</v>
+      </c>
+      <c r="X4" t="n">
+        <v>325</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>312</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1149</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1227.96</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1041.96</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AG4" t="n">
         <v>252</v>
       </c>
-      <c r="N4" t="n">
-        <v>548</v>
-      </c>
-      <c r="O4" t="n">
-        <v>109</v>
-      </c>
-      <c r="P4" t="n">
-        <v>317</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>203</v>
-      </c>
-      <c r="R4" t="n">
-        <v>282</v>
-      </c>
-      <c r="S4" t="n">
-        <v>171</v>
-      </c>
-      <c r="T4" t="n">
-        <v>271</v>
-      </c>
-      <c r="U4" t="n">
-        <v>202</v>
-      </c>
-      <c r="V4" t="n">
-        <v>77</v>
-      </c>
-      <c r="W4" t="n">
-        <v>152</v>
-      </c>
-      <c r="X4" t="n">
-        <v>300</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>288</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1077</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1141.08</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>970.08</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>138</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>90</v>
       </c>
-      <c r="AG4" t="n">
-        <v>205</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>43</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>121</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
+        <v>131</v>
+      </c>
+      <c r="AL4" t="n">
         <v>73</v>
       </c>
-      <c r="AK4" t="n">
-        <v>104</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>58</v>
-      </c>
       <c r="AM4" t="n">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="AN4" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="AQ4" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="AR4" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>426.76</v>
+        <v>513.64</v>
       </c>
       <c r="AU4" t="n">
-        <v>368.76</v>
+        <v>440.64</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.8989491706217176</v>
+        <v>0.8565521787102405</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.011121276035282</v>
+        <v>0.9895878345533277</v>
       </c>
       <c r="AX4" t="n">
-        <v>104.0680646041733</v>
+        <v>99.70799113972332</v>
       </c>
       <c r="AY4" t="n">
-        <v>114.7939083022978</v>
+        <v>111.9570818325775</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-10.72584369812456</v>
+        <v>-12.24909069285422</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.349263231360418</v>
+        <v>0.3420731009636137</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.6862519644957648</v>
+        <v>0.6993276174719608</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.5114083139083139</v>
+        <v>0.5085029121926712</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
         <v>1600</v>
@@ -2112,166 +2112,166 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9541817439874302</v>
+        <v>0.952800893948761</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9553313539133701</v>
+        <v>0.9546275848060224</v>
       </c>
       <c r="E7" t="n">
-        <v>105.0516767509059</v>
+        <v>104.8570916014656</v>
       </c>
       <c r="F7" t="n">
-        <v>107.4146540648682</v>
+        <v>107.2136958118755</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.362977313962327</v>
+        <v>-2.356604210409873</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2478907648670726</v>
+        <v>0.2468114772794032</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7243566706475588</v>
+        <v>0.7262024809342082</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4970642783908503</v>
+        <v>0.4968790640824296</v>
       </c>
       <c r="K7" t="n">
-        <v>5225</v>
+        <v>5425</v>
       </c>
       <c r="L7" t="n">
-        <v>2069</v>
+        <v>2148</v>
       </c>
       <c r="M7" t="n">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="N7" t="n">
-        <v>919</v>
+        <v>954</v>
       </c>
       <c r="O7" t="n">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="P7" t="n">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="Q7" t="n">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="R7" t="n">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="S7" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="T7" t="n">
-        <v>649</v>
+        <v>673</v>
       </c>
       <c r="U7" t="n">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="V7" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="W7" t="n">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="X7" t="n">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="Y7" t="n">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="Z7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AA7" t="n">
-        <v>2131</v>
+        <v>2211</v>
       </c>
       <c r="AB7" t="n">
-        <v>2172.84</v>
+        <v>2259</v>
       </c>
       <c r="AC7" t="n">
-        <v>1973.84</v>
+        <v>2053</v>
       </c>
       <c r="AD7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2825</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>262</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>510</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>358</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>193</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>293</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>113</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>337</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>228</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>196</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>280</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>291</v>
+      </c>
+      <c r="AS7" t="n">
         <v>26</v>
       </c>
-      <c r="AE7" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>241</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>475</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>327</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>279</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>106</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>313</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>209</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>182</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>258</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>270</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>20</v>
-      </c>
       <c r="AT7" t="n">
-        <v>1106.76</v>
+        <v>1192.92</v>
       </c>
       <c r="AU7" t="n">
-        <v>1000.76</v>
+        <v>1079.92</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.9246022212041622</v>
+        <v>0.9240519763283908</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.001551034889766</v>
+        <v>0.9968923601129954</v>
       </c>
       <c r="AX7" t="n">
-        <v>102.2095324590962</v>
+        <v>102.0372714060191</v>
       </c>
       <c r="AY7" t="n">
-        <v>113.6530859517258</v>
+        <v>112.8199213290357</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-11.44355349262961</v>
+        <v>-10.7826499230165</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.2586343838141796</v>
+        <v>0.255785499256024</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.6969338358176095</v>
+        <v>0.7024523867154299</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.4839808717710026</v>
+        <v>0.4845582017918947</v>
       </c>
       <c r="BD7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE7" t="n">
         <v>2600</v>
@@ -2364,88 +2364,88 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9459419347929299</v>
+        <v>0.9458353590186224</v>
       </c>
       <c r="D8" t="n">
-        <v>1.001979567531668</v>
+        <v>1.001694778211526</v>
       </c>
       <c r="E8" t="n">
-        <v>103.3401279584083</v>
+        <v>103.3238994429118</v>
       </c>
       <c r="F8" t="n">
-        <v>112.0248759185563</v>
+        <v>112.2605546973642</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.684747960147986</v>
+        <v>-8.93665525445245</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2394475217963702</v>
+        <v>0.2383965098857872</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7199870869801822</v>
+        <v>0.7157995494467564</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4858848540797874</v>
+        <v>0.4833619695025826</v>
       </c>
       <c r="K8" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="L8" t="n">
-        <v>1952</v>
+        <v>2031</v>
       </c>
       <c r="M8" t="n">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="N8" t="n">
-        <v>820</v>
+        <v>858</v>
       </c>
       <c r="O8" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P8" t="n">
-        <v>653</v>
+        <v>676</v>
       </c>
       <c r="Q8" t="n">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="R8" t="n">
-        <v>552</v>
+        <v>581</v>
       </c>
       <c r="S8" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="T8" t="n">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="U8" t="n">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="V8" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="W8" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="X8" t="n">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="Y8" t="n">
-        <v>551</v>
+        <v>574</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA8" t="n">
-        <v>2101</v>
+        <v>2189</v>
       </c>
       <c r="AB8" t="n">
-        <v>2069.88</v>
+        <v>2153.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>1892.88</v>
+        <v>1969.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
         <v>2600</v>
@@ -2526,82 +2526,82 @@
         <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF8" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="BG8" t="n">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="BH8" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="BI8" t="n">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="BJ8" t="n">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="BK8" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="BL8" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="BM8" t="n">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="BN8" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="BO8" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="BP8" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="BQ8" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="BR8" t="n">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="BS8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BT8" t="n">
-        <v>972.28</v>
+        <v>1056.04</v>
       </c>
       <c r="BU8" t="n">
-        <v>884.28</v>
+        <v>961.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9694003411994768</v>
+        <v>0.9673826968503583</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9810781454135754</v>
+        <v>0.9821163684746815</v>
       </c>
       <c r="BX8" t="n">
-        <v>106.3750076991478</v>
+        <v>106.1090983804054</v>
       </c>
       <c r="BY8" t="n">
-        <v>110.1937029097644</v>
+        <v>110.8059199295949</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-3.818695210616629</v>
+        <v>-4.69682154918951</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2380648191902935</v>
+        <v>0.2360691571080565</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.7055283080103313</v>
+        <v>0.6982654467103913</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.4756588647029859</v>
+        <v>0.4713997101160227</v>
       </c>
       <c r="CD8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -2616,166 +2616,166 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8723044961578448</v>
+        <v>0.8788980760961078</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9853653904493135</v>
+        <v>0.9901385468020822</v>
       </c>
       <c r="E9" t="n">
-        <v>96.00194118830481</v>
+        <v>96.76702190164306</v>
       </c>
       <c r="F9" t="n">
-        <v>111.5058390920437</v>
+        <v>111.9512044795993</v>
       </c>
       <c r="G9" t="n">
-        <v>-15.50389790373888</v>
+        <v>-15.18418257795627</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2355802557542776</v>
+        <v>0.2367758869432156</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6965921489168726</v>
+        <v>0.6959539893431467</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4623154498926504</v>
+        <v>0.4620166039177583</v>
       </c>
       <c r="K9" t="n">
-        <v>5050</v>
+        <v>5250</v>
       </c>
       <c r="L9" t="n">
-        <v>1826</v>
+        <v>1910</v>
       </c>
       <c r="M9" t="n">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="N9" t="n">
-        <v>867</v>
+        <v>902</v>
       </c>
       <c r="O9" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="P9" t="n">
-        <v>676</v>
+        <v>702</v>
       </c>
       <c r="Q9" t="n">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="R9" t="n">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="S9" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="T9" t="n">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="U9" t="n">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="V9" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="W9" t="n">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="X9" t="n">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="Y9" t="n">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="Z9" t="n">
         <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>2118</v>
+        <v>2208</v>
       </c>
       <c r="AB9" t="n">
-        <v>2093.2</v>
+        <v>2173.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>1902.2</v>
+        <v>1974.68</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF9" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="AG9" t="n">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AI9" t="n">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="AK9" t="n">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AL9" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AM9" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="AN9" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AP9" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AQ9" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="AR9" t="n">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="AS9" t="n">
         <v>20</v>
       </c>
       <c r="AT9" t="n">
-        <v>983.36</v>
+        <v>1063.84</v>
       </c>
       <c r="AU9" t="n">
-        <v>904.36</v>
+        <v>976.84</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.867140907857443</v>
+        <v>0.880725266834</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.035799638762833</v>
+        <v>1.041466393905793</v>
       </c>
       <c r="AX9" t="n">
-        <v>94.1427952507713</v>
+        <v>95.8159679034119</v>
       </c>
       <c r="AY9" t="n">
-        <v>117.5835699025132</v>
+        <v>118.006782922973</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-23.4407746517419</v>
+        <v>-22.19081501956105</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2023663101604278</v>
+        <v>0.2073124914301385</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6957926034538938</v>
+        <v>0.6945777878035942</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4431361193957445</v>
+        <v>0.4440137605611068</v>
       </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
         <v>2650</v>
@@ -2868,166 +2868,166 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9309111154602038</v>
+        <v>0.9278659108749586</v>
       </c>
       <c r="D10" t="n">
-        <v>1.01327207159717</v>
+        <v>1.019597879733606</v>
       </c>
       <c r="E10" t="n">
-        <v>106.0387469668643</v>
+        <v>105.8972980483962</v>
       </c>
       <c r="F10" t="n">
-        <v>113.9117954482826</v>
+        <v>114.607284058986</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.873048481418281</v>
+        <v>-8.709986010589809</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3233664377143212</v>
+        <v>0.3257931951652311</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6985995075245754</v>
+        <v>0.6968800410623125</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5028829305041638</v>
+        <v>0.5024622821050767</v>
       </c>
       <c r="K10" t="n">
-        <v>5250</v>
+        <v>5450</v>
       </c>
       <c r="L10" t="n">
-        <v>2137</v>
+        <v>2207</v>
       </c>
       <c r="M10" t="n">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="N10" t="n">
-        <v>925</v>
+        <v>959</v>
       </c>
       <c r="O10" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="P10" t="n">
-        <v>765</v>
+        <v>793</v>
       </c>
       <c r="Q10" t="n">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="R10" t="n">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="S10" t="n">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="T10" t="n">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="U10" t="n">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="V10" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="W10" t="n">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="X10" t="n">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="Y10" t="n">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="Z10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AA10" t="n">
-        <v>2314</v>
+        <v>2402</v>
       </c>
       <c r="AB10" t="n">
-        <v>2298.16</v>
+        <v>2380.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>2017.16</v>
+        <v>2085.64</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE10" t="n">
-        <v>2650</v>
+        <v>2850</v>
       </c>
       <c r="AF10" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="AG10" t="n">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="AH10" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="AI10" t="n">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="AJ10" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="AK10" t="n">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="AL10" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="AM10" t="n">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="AN10" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AP10" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="AQ10" t="n">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="AR10" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>1166.92</v>
+        <v>1249.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1021.92</v>
+        <v>1090.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.887353442635865</v>
+        <v>0.8845918104232021</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.0290983253107</v>
+        <v>1.040167651451432</v>
       </c>
       <c r="AX10" t="n">
-        <v>101.4187448389346</v>
+        <v>101.4759506481696</v>
       </c>
       <c r="AY10" t="n">
-        <v>115.051534451985</v>
+        <v>116.3114239866485</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-13.63278961305036</v>
+        <v>-14.83547333847888</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.322843520260875</v>
+        <v>0.3275610465914474</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.6947198965222865</v>
+        <v>0.6916808977023716</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.4924235969899657</v>
+        <v>0.4923594417570263</v>
       </c>
       <c r="BD10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE10" t="n">
         <v>2600</v>
@@ -3120,88 +3120,88 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9835297833947405</v>
+        <v>0.9912428260057484</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9574052460631601</v>
+        <v>0.9532239132014457</v>
       </c>
       <c r="E11" t="n">
-        <v>111.2268249738531</v>
+        <v>112.052331241677</v>
       </c>
       <c r="F11" t="n">
-        <v>107.1693098803709</v>
+        <v>106.9789374299037</v>
       </c>
       <c r="G11" t="n">
-        <v>4.057515093482283</v>
+        <v>5.073393811773331</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3072742872857415</v>
+        <v>0.3088339718884638</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7094697893236824</v>
+        <v>0.7056867632385835</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5046662654850583</v>
+        <v>0.5048127389768325</v>
       </c>
       <c r="K11" t="n">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="L11" t="n">
-        <v>2023</v>
+        <v>2111</v>
       </c>
       <c r="M11" t="n">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="N11" t="n">
-        <v>810</v>
+        <v>839</v>
       </c>
       <c r="O11" t="n">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="P11" t="n">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="Q11" t="n">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="R11" t="n">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="S11" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="T11" t="n">
-        <v>521</v>
+        <v>543</v>
       </c>
       <c r="U11" t="n">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="V11" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="W11" t="n">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="X11" t="n">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="Y11" t="n">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="Z11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA11" t="n">
-        <v>1928</v>
+        <v>1998</v>
       </c>
       <c r="AB11" t="n">
-        <v>2067.6</v>
+        <v>2141.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>1820.6</v>
+        <v>1886.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
         <v>2625</v>
@@ -3282,82 +3282,82 @@
         <v>13</v>
       </c>
       <c r="BE11" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF11" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="BG11" t="n">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="BH11" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="BI11" t="n">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="BJ11" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="BK11" t="n">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="BL11" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="BM11" t="n">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="BN11" t="n">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="BO11" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="BP11" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="BQ11" t="n">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="BR11" t="n">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="BS11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000.12</v>
+        <v>1074.44</v>
       </c>
       <c r="BU11" t="n">
-        <v>868.12</v>
+        <v>934.4399999999999</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9994787008426725</v>
+        <v>1.013677946261001</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9455934717970034</v>
+        <v>0.9381394040940479</v>
       </c>
       <c r="BX11" t="n">
-        <v>114.63664688545</v>
+        <v>116.025365427898</v>
       </c>
       <c r="BY11" t="n">
-        <v>106.0445443587693</v>
+        <v>105.7503198825735</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.592102526680669</v>
+        <v>10.27504554532443</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3548420736354028</v>
+        <v>0.3543023823524119</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7024979814092718</v>
+        <v>0.695468222155567</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.5307470176676962</v>
+        <v>0.5290337529448877</v>
       </c>
       <c r="CD11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -3372,166 +3372,166 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.004732132916311</v>
+        <v>0.9996579735914274</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9783666965370409</v>
+        <v>0.9738292579932933</v>
       </c>
       <c r="E12" t="n">
-        <v>111.8733182421374</v>
+        <v>111.2763691806427</v>
       </c>
       <c r="F12" t="n">
-        <v>109.7216528852768</v>
+        <v>109.4210093737802</v>
       </c>
       <c r="G12" t="n">
-        <v>2.151665356860573</v>
+        <v>1.85535980686256</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2632112790867055</v>
+        <v>0.2619283216602137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7161188109373329</v>
+        <v>0.712987704879225</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4915199927464975</v>
+        <v>0.4895509620663888</v>
       </c>
       <c r="K12" t="n">
-        <v>5250</v>
+        <v>5450</v>
       </c>
       <c r="L12" t="n">
-        <v>2166</v>
+        <v>2240</v>
       </c>
       <c r="M12" t="n">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="N12" t="n">
-        <v>904</v>
+        <v>948</v>
       </c>
       <c r="O12" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="P12" t="n">
-        <v>697</v>
+        <v>720</v>
       </c>
       <c r="Q12" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="R12" t="n">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="S12" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="T12" t="n">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="U12" t="n">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="V12" t="n">
+        <v>153</v>
+      </c>
+      <c r="W12" t="n">
+        <v>303</v>
+      </c>
+      <c r="X12" t="n">
+        <v>577</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>566</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2210</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2239.84</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2008.84</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2650</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>228</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>482</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>122</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>334</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>221</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>281</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>123</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>313</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>157</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>61</v>
+      </c>
+      <c r="AP12" t="n">
         <v>148</v>
       </c>
-      <c r="W12" t="n">
-        <v>290</v>
-      </c>
-      <c r="X12" t="n">
-        <v>557</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>547</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2134</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2154.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1931.56</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2450</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>438</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>112</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>311</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>269</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>289</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>147</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>56</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>135</v>
-      </c>
       <c r="AQ12" t="n">
+        <v>283</v>
+      </c>
+      <c r="AR12" t="n">
         <v>263</v>
       </c>
-      <c r="AR12" t="n">
-        <v>244</v>
-      </c>
       <c r="AS12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT12" t="n">
-        <v>1002.36</v>
+        <v>1087.64</v>
       </c>
       <c r="AU12" t="n">
-        <v>887.36</v>
+        <v>964.64</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.9674384813015685</v>
+        <v>0.9597685851356376</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.9690199491248445</v>
+        <v>0.9603150188733838</v>
       </c>
       <c r="AX12" t="n">
-        <v>109.1605693359916</v>
+        <v>108.1294250472061</v>
       </c>
       <c r="AY12" t="n">
-        <v>109.2877208455712</v>
+        <v>108.6966867862862</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.1271515095796675</v>
+        <v>-0.5672617390801378</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2763681123334968</v>
+        <v>0.2726914443517993</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.715386390490225</v>
+        <v>0.7089396640962401</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4935295664432309</v>
+        <v>0.4892854585924872</v>
       </c>
       <c r="BD12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE12" t="n">
         <v>2800</v>
@@ -3624,166 +3624,166 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9515919644242917</v>
+        <v>0.9389420322132526</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9016632170157765</v>
+        <v>0.9019054086307456</v>
       </c>
       <c r="E13" t="n">
-        <v>109.5877821991982</v>
+        <v>108.1524754715565</v>
       </c>
       <c r="F13" t="n">
-        <v>101.5542176600192</v>
+        <v>101.6939523609695</v>
       </c>
       <c r="G13" t="n">
-        <v>8.033564539178935</v>
+        <v>6.458523110586963</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3505430557519366</v>
+        <v>0.3492063795185625</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7160438771005349</v>
+        <v>0.716388343365899</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5368214122666169</v>
+        <v>0.536391397396402</v>
       </c>
       <c r="K13" t="n">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="L13" t="n">
-        <v>1991</v>
+        <v>2045</v>
       </c>
       <c r="M13" t="n">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="N13" t="n">
-        <v>906</v>
+        <v>945</v>
       </c>
       <c r="O13" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P13" t="n">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="Q13" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="R13" t="n">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="S13" t="n">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="T13" t="n">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="U13" t="n">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="V13" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="W13" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="X13" t="n">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="Y13" t="n">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="Z13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA13" t="n">
-        <v>1868</v>
+        <v>1941</v>
       </c>
       <c r="AB13" t="n">
-        <v>2095.04</v>
+        <v>2181.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>1816.04</v>
+        <v>1890.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="AF13" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="AG13" t="n">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="AH13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AI13" t="n">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="AJ13" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="AK13" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="AL13" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="AM13" t="n">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="AN13" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="AO13" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AP13" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AQ13" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="AR13" t="n">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="AS13" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AT13" t="n">
-        <v>920.8</v>
+        <v>1007.52</v>
       </c>
       <c r="AU13" t="n">
-        <v>808.8</v>
+        <v>883.52</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9714552370892989</v>
+        <v>0.9423917779099632</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8856373843129653</v>
+        <v>0.8874976188706328</v>
       </c>
       <c r="AX13" t="n">
-        <v>110.5164153930311</v>
+        <v>107.3291980503213</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.876174900982</v>
+        <v>102.1521036496273</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.640240492049131</v>
+        <v>5.177094400694011</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.353111873344149</v>
+        <v>0.3500016733724874</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.686351863531231</v>
+        <v>0.689572541570295</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5404371619712222</v>
+        <v>0.5392041506103724</v>
       </c>
       <c r="BD13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE13" t="n">
         <v>2825</v>
@@ -3876,166 +3876,166 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.028670537269259</v>
+        <v>1.027407741266988</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9190865287410088</v>
+        <v>0.9199785448861912</v>
       </c>
       <c r="E14" t="n">
-        <v>117.7476046919323</v>
+        <v>117.7626017095482</v>
       </c>
       <c r="F14" t="n">
-        <v>102.7277481173657</v>
+        <v>102.734801392852</v>
       </c>
       <c r="G14" t="n">
-        <v>15.01985657456663</v>
+        <v>15.02780031669616</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3481326878394413</v>
+        <v>0.3496421767671987</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7337456576911964</v>
+        <v>0.735750588438885</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5442575441697856</v>
+        <v>0.5455706034571096</v>
       </c>
       <c r="K14" t="n">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="L14" t="n">
-        <v>2383</v>
+        <v>2471</v>
       </c>
       <c r="M14" t="n">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="N14" t="n">
-        <v>1032</v>
+        <v>1080</v>
       </c>
       <c r="O14" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="P14" t="n">
-        <v>732</v>
+        <v>758</v>
       </c>
       <c r="Q14" t="n">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="R14" t="n">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="S14" t="n">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="T14" t="n">
-        <v>641</v>
+        <v>667</v>
       </c>
       <c r="U14" t="n">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="V14" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="W14" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="X14" t="n">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="Y14" t="n">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
-        <v>2027</v>
+        <v>2106</v>
       </c>
       <c r="AB14" t="n">
-        <v>2321.76</v>
+        <v>2410.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>2024.76</v>
+        <v>2099.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AF14" t="n">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="AG14" t="n">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="AH14" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="AI14" t="n">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="AJ14" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="AK14" t="n">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="AL14" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="AM14" t="n">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="AN14" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="AO14" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="AP14" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="AQ14" t="n">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="AR14" t="n">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="AS14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT14" t="n">
-        <v>1151.2</v>
+        <v>1239.68</v>
       </c>
       <c r="AU14" t="n">
-        <v>1003.2</v>
+        <v>1077.68</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.021584059554004</v>
+        <v>1.019654844243572</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.9151161035642108</v>
+        <v>0.9171200222139769</v>
       </c>
       <c r="AX14" t="n">
-        <v>117.0203084119286</v>
+        <v>117.1011809659024</v>
       </c>
       <c r="AY14" t="n">
-        <v>104.4034877105762</v>
+        <v>104.2973947709277</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.61682070135243</v>
+        <v>12.80378619497469</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3568654736194627</v>
+        <v>0.3591528604244217</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6709071649833965</v>
+        <v>0.6792622809044958</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5161060537516851</v>
+        <v>0.5206492031213887</v>
       </c>
       <c r="BD14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE14" t="n">
         <v>2600</v>
@@ -4128,88 +4128,88 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8696020133271409</v>
+        <v>0.8710773281609038</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9988797880295546</v>
+        <v>0.9844110933721589</v>
       </c>
       <c r="E15" t="n">
-        <v>98.42777545090779</v>
+        <v>98.68775792913159</v>
       </c>
       <c r="F15" t="n">
-        <v>113.0500217719582</v>
+        <v>111.4815519838257</v>
       </c>
       <c r="G15" t="n">
-        <v>-14.62224632105038</v>
+        <v>-12.79379405469412</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2897070823085149</v>
+        <v>0.289141425296649</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6961633251289732</v>
+        <v>0.6957036020976969</v>
       </c>
       <c r="J15" t="n">
-        <v>0.489443645147027</v>
+        <v>0.4888634655013326</v>
       </c>
       <c r="K15" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="L15" t="n">
-        <v>1886</v>
+        <v>1959</v>
       </c>
       <c r="M15" t="n">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="N15" t="n">
-        <v>889</v>
+        <v>917</v>
       </c>
       <c r="O15" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="P15" t="n">
-        <v>715</v>
+        <v>753</v>
       </c>
       <c r="Q15" t="n">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="R15" t="n">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="S15" t="n">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="T15" t="n">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="U15" t="n">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="V15" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="W15" t="n">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="X15" t="n">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="Y15" t="n">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="Z15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>2176</v>
+        <v>2230</v>
       </c>
       <c r="AB15" t="n">
-        <v>2175.36</v>
+        <v>2255.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>1918.36</v>
+        <v>1987.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
         <v>2600</v>
@@ -4290,82 +4290,82 @@
         <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF15" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="BG15" t="n">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="BH15" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="BI15" t="n">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="BJ15" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="BK15" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="BL15" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="BM15" t="n">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="BN15" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="BO15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="BP15" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="BQ15" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="BR15" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="BS15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BT15" t="n">
-        <v>1025.44</v>
+        <v>1105.84</v>
       </c>
       <c r="BU15" t="n">
-        <v>908.4400000000001</v>
+        <v>977.84</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.9087490283477585</v>
+        <v>0.9086883491675444</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9840924569471531</v>
+        <v>0.9562925546387006</v>
       </c>
       <c r="BX15" t="n">
-        <v>102.3805000016416</v>
+        <v>102.5964092234174</v>
       </c>
       <c r="BY15" t="n">
-        <v>110.5866434434876</v>
+        <v>107.6391945078743</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-8.206143441846001</v>
+        <v>-5.042785284456899</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2783497136320031</v>
+        <v>0.2780920433526182</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.7117141358523394</v>
+        <v>0.7095984735802972</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.4979077965273281</v>
+        <v>0.496096348668224</v>
       </c>
       <c r="CD15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -4380,88 +4380,88 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.066378724431395</v>
+        <v>1.063190586171518</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8926546426226705</v>
+        <v>0.8818932511519842</v>
       </c>
       <c r="E16" t="n">
-        <v>119.72513940432</v>
+        <v>119.6119420010929</v>
       </c>
       <c r="F16" t="n">
-        <v>100.4061841698055</v>
+        <v>99.20976028557901</v>
       </c>
       <c r="G16" t="n">
-        <v>19.31895523451453</v>
+        <v>20.40218171551393</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3201634994321476</v>
+        <v>0.3230010338362724</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7036812862599849</v>
+        <v>0.7043943991816094</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5196219946664736</v>
+        <v>0.5213756637679303</v>
       </c>
       <c r="K16" t="n">
-        <v>5050</v>
+        <v>5250</v>
       </c>
       <c r="L16" t="n">
-        <v>2313</v>
+        <v>2394</v>
       </c>
       <c r="M16" t="n">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="N16" t="n">
-        <v>965</v>
+        <v>995</v>
       </c>
       <c r="O16" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="P16" t="n">
-        <v>661</v>
+        <v>695</v>
       </c>
       <c r="Q16" t="n">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="R16" t="n">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="S16" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="T16" t="n">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="U16" t="n">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="V16" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="W16" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="X16" t="n">
-        <v>525</v>
+        <v>548</v>
       </c>
       <c r="Y16" t="n">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="Z16" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AA16" t="n">
-        <v>1915</v>
+        <v>1968</v>
       </c>
       <c r="AB16" t="n">
-        <v>2168.76</v>
+        <v>2251.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>1933.76</v>
+        <v>2003.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>2625</v>
@@ -4542,82 +4542,82 @@
         <v>13</v>
       </c>
       <c r="BE16" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="BF16" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="BG16" t="n">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="BH16" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="BI16" t="n">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="BJ16" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="BK16" t="n">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="BL16" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="BM16" t="n">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="BN16" t="n">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BO16" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="BP16" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="BQ16" t="n">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="BR16" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="BS16" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BT16" t="n">
-        <v>1059.24</v>
+        <v>1141.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>939.24</v>
+        <v>1008.6</v>
       </c>
       <c r="BV16" t="n">
-        <v>1.059226337924005</v>
+        <v>1.053400244981743</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8746854514345053</v>
+        <v>0.8545449139691456</v>
       </c>
       <c r="BX16" t="n">
-        <v>119.5986315857444</v>
+        <v>119.3819681499499</v>
       </c>
       <c r="BY16" t="n">
-        <v>96.75229666304953</v>
+        <v>94.64051716434697</v>
       </c>
       <c r="BZ16" t="n">
-        <v>22.8463349226949</v>
+        <v>24.7414509856029</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.327982843172208</v>
+        <v>0.3330564240004531</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.7441418047363652</v>
+        <v>0.7424556830045079</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.5421192194577145</v>
+        <v>0.5438960019074555</v>
       </c>
       <c r="CD16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -4632,88 +4632,88 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.018305301051677</v>
+        <v>1.021811537765894</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9694079712113691</v>
+        <v>0.972266802109112</v>
       </c>
       <c r="E17" t="n">
-        <v>114.3791303056464</v>
+        <v>114.7139844926788</v>
       </c>
       <c r="F17" t="n">
-        <v>108.7815540913745</v>
+        <v>109.0551112315178</v>
       </c>
       <c r="G17" t="n">
-        <v>5.597576214271908</v>
+        <v>5.658873261161097</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2992750500995604</v>
+        <v>0.3000721635572696</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7132392231574252</v>
+        <v>0.7140120735488064</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5107044931473004</v>
+        <v>0.5120410336206559</v>
       </c>
       <c r="K17" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="L17" t="n">
-        <v>2113</v>
+        <v>2203</v>
       </c>
       <c r="M17" t="n">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="N17" t="n">
-        <v>821</v>
+        <v>848</v>
       </c>
       <c r="O17" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="P17" t="n">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="Q17" t="n">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="R17" t="n">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="S17" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="T17" t="n">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="U17" t="n">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="V17" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="W17" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="X17" t="n">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="Y17" t="n">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="Z17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA17" t="n">
-        <v>2023</v>
+        <v>2107</v>
       </c>
       <c r="AB17" t="n">
-        <v>2073.84</v>
+        <v>2154.96</v>
       </c>
       <c r="AC17" t="n">
-        <v>1848.84</v>
+        <v>1921.96</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>2600</v>
@@ -4794,82 +4794,82 @@
         <v>13</v>
       </c>
       <c r="BE17" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF17" t="n">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="BG17" t="n">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="BH17" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="BI17" t="n">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="BJ17" t="n">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="BK17" t="n">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="BL17" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="BM17" t="n">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="BN17" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="BO17" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="BP17" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="BQ17" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="BR17" t="n">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="BS17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BT17" t="n">
-        <v>1005.84</v>
+        <v>1086.96</v>
       </c>
       <c r="BU17" t="n">
-        <v>889.84</v>
+        <v>962.96</v>
       </c>
       <c r="BV17" t="n">
-        <v>1.0491216061048</v>
+        <v>1.053763594529146</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.9599593069310303</v>
+        <v>0.9664037890557728</v>
       </c>
       <c r="BX17" t="n">
-        <v>118.8410977577682</v>
+        <v>119.1675778662853</v>
       </c>
       <c r="BY17" t="n">
-        <v>108.1008513352918</v>
+        <v>108.7003273660462</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.74024642247644</v>
+        <v>10.46725050023908</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.3207939503033441</v>
+        <v>0.3207328772030869</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.700010979444062</v>
+        <v>0.7025742374355443</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.5129757497576845</v>
+        <v>0.515474118657443</v>
       </c>
       <c r="CD17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -4884,88 +4884,88 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8694043673832872</v>
+        <v>0.8698857619894513</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9784362771082007</v>
+        <v>0.9655951594945336</v>
       </c>
       <c r="E18" t="n">
-        <v>98.21758340793994</v>
+        <v>98.20048210317212</v>
       </c>
       <c r="F18" t="n">
-        <v>112.0074210073753</v>
+        <v>110.6958903462252</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.78983759943529</v>
+        <v>-12.49540824305307</v>
       </c>
       <c r="H18" t="n">
-        <v>0.281766605714072</v>
+        <v>0.2799792023268792</v>
       </c>
       <c r="I18" t="n">
-        <v>0.643490846029693</v>
+        <v>0.6454287962216435</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4502452252408753</v>
+        <v>0.4523905664387471</v>
       </c>
       <c r="K18" t="n">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="L18" t="n">
-        <v>1824</v>
+        <v>1896</v>
       </c>
       <c r="M18" t="n">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="N18" t="n">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="O18" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="P18" t="n">
-        <v>691</v>
+        <v>715</v>
       </c>
       <c r="Q18" t="n">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="R18" t="n">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="S18" t="n">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="T18" t="n">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="U18" t="n">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="V18" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W18" t="n">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="X18" t="n">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="Y18" t="n">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="Z18" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AA18" t="n">
-        <v>2118</v>
+        <v>2174</v>
       </c>
       <c r="AB18" t="n">
-        <v>2105.32</v>
+        <v>2186.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>1862.32</v>
+        <v>1935.96</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>2600</v>
@@ -5046,82 +5046,82 @@
         <v>13</v>
       </c>
       <c r="BE18" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="BF18" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="BG18" t="n">
-        <v>423</v>
+        <v>456</v>
       </c>
       <c r="BH18" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="BI18" t="n">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="BJ18" t="n">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="BK18" t="n">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="BL18" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="BM18" t="n">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="BN18" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="BO18" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="BP18" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="BQ18" t="n">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="BR18" t="n">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="BS18" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="BT18" t="n">
-        <v>1034.8</v>
+        <v>1116.44</v>
       </c>
       <c r="BU18" t="n">
-        <v>904.8</v>
+        <v>978.4400000000001</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8391979749083278</v>
+        <v>0.8424843327725763</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9390689527303638</v>
+        <v>0.9164149732244016</v>
       </c>
       <c r="BX18" t="n">
-        <v>95.94883713386052</v>
+        <v>96.0891534684848</v>
       </c>
       <c r="BY18" t="n">
-        <v>107.6727528860883</v>
+        <v>105.383127573118</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-11.72391575222783</v>
+        <v>-9.293974104633186</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.3097573787445323</v>
+        <v>0.3040294355831882</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.6369722391274116</v>
+        <v>0.6413495708114882</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.4627838534682442</v>
+        <v>0.4661100260003441</v>
       </c>
       <c r="CD18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -5136,166 +5136,166 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.992032740863957</v>
+        <v>0.9779892491425078</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8695293686756513</v>
+        <v>0.8737500264904272</v>
       </c>
       <c r="E19" t="n">
-        <v>113.0043073993123</v>
+        <v>111.3855983541495</v>
       </c>
       <c r="F19" t="n">
-        <v>97.74287415486252</v>
+        <v>98.44802722025337</v>
       </c>
       <c r="G19" t="n">
-        <v>15.26143324444977</v>
+        <v>12.93757113389612</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3248090494829252</v>
+        <v>0.3230671505308827</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7171648285413645</v>
+        <v>0.7130498573383734</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5271472881554786</v>
+        <v>0.523726374101411</v>
       </c>
       <c r="K19" t="n">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="L19" t="n">
-        <v>2183</v>
+        <v>2236</v>
       </c>
       <c r="M19" t="n">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="N19" t="n">
-        <v>989</v>
+        <v>1030</v>
       </c>
       <c r="O19" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P19" t="n">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="Q19" t="n">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="R19" t="n">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="S19" t="n">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="T19" t="n">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="U19" t="n">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="V19" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="W19" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="X19" t="n">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="Y19" t="n">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="Z19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>1874</v>
+        <v>1955</v>
       </c>
       <c r="AB19" t="n">
-        <v>2205.6</v>
+        <v>2292.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>1930.6</v>
+        <v>2007.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF19" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="AG19" t="n">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="AH19" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AI19" t="n">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="AJ19" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="AK19" t="n">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="AL19" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="AM19" t="n">
+        <v>304</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>188</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>136</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>284</v>
       </c>
-      <c r="AN19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>91</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>121</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>263</v>
-      </c>
       <c r="AR19" t="n">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>1018.84</v>
+        <v>1105.32</v>
       </c>
       <c r="AU19" t="n">
-        <v>889.84</v>
+        <v>966.3200000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.9936248790724237</v>
+        <v>0.9643351548656856</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.8659893271862308</v>
+        <v>0.8750276196853359</v>
       </c>
       <c r="AX19" t="n">
-        <v>113.5978811475987</v>
+        <v>110.190287457777</v>
       </c>
       <c r="AY19" t="n">
-        <v>95.98630174244708</v>
+        <v>97.58597137152154</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.61157940515162</v>
+        <v>12.60431608625542</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.315133038938186</v>
+        <v>0.3122595573104623</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.7487721713529848</v>
+        <v>0.7377943586381863</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.5325416686012221</v>
+        <v>0.5250217409161783</v>
       </c>
       <c r="BD19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE19" t="n">
         <v>2800</v>

--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,88 +852,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9513670599526608</v>
+        <v>0.9432599401720271</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9213215134648567</v>
+        <v>0.9196898303741848</v>
       </c>
       <c r="E2" t="n">
-        <v>107.8296407911593</v>
+        <v>107.1070396266322</v>
       </c>
       <c r="F2" t="n">
-        <v>101.7138406744517</v>
+        <v>101.4614980651912</v>
       </c>
       <c r="G2" t="n">
-        <v>6.115800116707605</v>
+        <v>5.645541561441012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.306750052550015</v>
+        <v>0.3088197400700812</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7508789930976755</v>
+        <v>0.7528570242029435</v>
       </c>
       <c r="J2" t="n">
-        <v>0.525500538861946</v>
+        <v>0.5267588574986236</v>
       </c>
       <c r="K2" t="n">
-        <v>5225</v>
+        <v>5625</v>
       </c>
       <c r="L2" t="n">
-        <v>2163</v>
+        <v>2304</v>
       </c>
       <c r="M2" t="n">
-        <v>450</v>
+        <v>481</v>
       </c>
       <c r="N2" t="n">
-        <v>840</v>
+        <v>901</v>
       </c>
       <c r="O2" t="n">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="P2" t="n">
-        <v>852</v>
+        <v>912</v>
       </c>
       <c r="Q2" t="n">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="R2" t="n">
-        <v>562</v>
+        <v>594</v>
       </c>
       <c r="S2" t="n">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="T2" t="n">
-        <v>625</v>
+        <v>674</v>
       </c>
       <c r="U2" t="n">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="V2" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="W2" t="n">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="X2" t="n">
-        <v>540</v>
+        <v>581</v>
       </c>
       <c r="Y2" t="n">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="Z2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA2" t="n">
-        <v>2048</v>
+        <v>2195</v>
       </c>
       <c r="AB2" t="n">
-        <v>2281.28</v>
+        <v>2449.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>2009.28</v>
+        <v>2153.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>2825</v>
@@ -1014,82 +1014,82 @@
         <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="BF2" t="n">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="BG2" t="n">
-        <v>364</v>
+        <v>425</v>
       </c>
       <c r="BH2" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="BI2" t="n">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="BJ2" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="BK2" t="n">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="BL2" t="n">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="BM2" t="n">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="BN2" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="BO2" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="BP2" t="n">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="BQ2" t="n">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="BR2" t="n">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BT2" t="n">
-        <v>1030.08</v>
+        <v>1198.16</v>
       </c>
       <c r="BU2" t="n">
-        <v>923.08</v>
+        <v>1067.16</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9753838449447071</v>
+        <v>0.9557386360988619</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9119867787118268</v>
+        <v>0.9100569460666302</v>
       </c>
       <c r="BX2" t="n">
-        <v>108.7646349275893</v>
+        <v>107.1858620076165</v>
       </c>
       <c r="BY2" t="n">
-        <v>100.4824077811239</v>
+        <v>100.153641547364</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.282227146465344</v>
+        <v>7.032220460252481</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2769908188711299</v>
+        <v>0.2853815130082458</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7498216817295763</v>
+        <v>0.7539287884212696</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.5187050668526008</v>
+        <v>0.5221924858415766</v>
       </c>
       <c r="CD2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1104,88 +1104,88 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9451462608068156</v>
+        <v>0.9438279057453388</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9652789106172202</v>
+        <v>0.9638406964510521</v>
       </c>
       <c r="E3" t="n">
-        <v>106.6574808032636</v>
+        <v>106.577415622253</v>
       </c>
       <c r="F3" t="n">
-        <v>111.3589823186588</v>
+        <v>110.8123091873803</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.70150151539512</v>
+        <v>-4.234893565127281</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3153302198611653</v>
+        <v>0.3155861723712737</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659169145206523</v>
+        <v>0.6634315756743168</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4943916704434566</v>
+        <v>0.4954259332906475</v>
       </c>
       <c r="K3" t="n">
-        <v>5022.766666666666</v>
+        <v>5422.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2099</v>
+        <v>2260</v>
       </c>
       <c r="M3" t="n">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="N3" t="n">
-        <v>1044</v>
+        <v>1119</v>
       </c>
       <c r="O3" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="P3" t="n">
-        <v>543</v>
+        <v>592</v>
       </c>
       <c r="Q3" t="n">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="R3" t="n">
+        <v>680</v>
+      </c>
+      <c r="S3" t="n">
+        <v>276</v>
+      </c>
+      <c r="T3" t="n">
         <v>624</v>
       </c>
-      <c r="S3" t="n">
-        <v>255</v>
-      </c>
-      <c r="T3" t="n">
-        <v>584</v>
-      </c>
       <c r="U3" t="n">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="V3" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="W3" t="n">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="X3" t="n">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="Y3" t="n">
-        <v>550</v>
+        <v>594</v>
       </c>
       <c r="Z3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AA3" t="n">
-        <v>2177</v>
+        <v>2335</v>
       </c>
       <c r="AB3" t="n">
-        <v>2220.56</v>
+        <v>2394.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1965.56</v>
+        <v>2118.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>2600</v>
@@ -1266,82 +1266,82 @@
         <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>2422.766666666666</v>
+        <v>2822.766666666666</v>
       </c>
       <c r="BF3" t="n">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="BG3" t="n">
-        <v>515</v>
+        <v>590</v>
       </c>
       <c r="BH3" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="BI3" t="n">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="BJ3" t="n">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="BK3" t="n">
-        <v>312</v>
+        <v>368</v>
       </c>
       <c r="BL3" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="BM3" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="BN3" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="BO3" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="BP3" t="n">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="BQ3" t="n">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="BR3" t="n">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="BS3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="BT3" t="n">
-        <v>1097.28</v>
+        <v>1270.92</v>
       </c>
       <c r="BU3" t="n">
-        <v>966.28</v>
+        <v>1118.92</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9221935179855261</v>
+        <v>0.9229299393414335</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.9650702186512353</v>
+        <v>0.9623263330401947</v>
       </c>
       <c r="BX3" t="n">
-        <v>104.5273310547558</v>
+        <v>104.6772267411649</v>
       </c>
       <c r="BY3" t="n">
-        <v>110.8174417883001</v>
+        <v>109.8405065394571</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-6.29011073354435</v>
+        <v>-5.1632797982922</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.3046222764795947</v>
+        <v>0.306645605375028</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6632347093661144</v>
+        <v>0.6708743161026323</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.483702261069576</v>
+        <v>0.4872239693282844</v>
       </c>
       <c r="CD3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -1356,244 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9102302420787259</v>
+        <v>0.8815775210709956</v>
       </c>
       <c r="D4" t="n">
-        <v>1.001898562194691</v>
+        <v>0.9895742605736871</v>
       </c>
       <c r="E4" t="n">
-        <v>106.7337395527079</v>
+        <v>104.0052670909505</v>
       </c>
       <c r="F4" t="n">
-        <v>111.8994828137643</v>
+        <v>110.4704387005334</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.1657432610564</v>
+        <v>-6.465171609582924</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3721297357183876</v>
+        <v>0.3717084796757875</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7098974497146971</v>
+        <v>0.7145007106452325</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5266028018987361</v>
+        <v>0.5258505022518318</v>
       </c>
       <c r="K4" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="L4" t="n">
-        <v>1034</v>
+        <v>1157</v>
       </c>
       <c r="M4" t="n">
+        <v>281</v>
+      </c>
+      <c r="N4" t="n">
+        <v>636</v>
+      </c>
+      <c r="O4" t="n">
+        <v>121</v>
+      </c>
+      <c r="P4" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>232</v>
+      </c>
+      <c r="R4" t="n">
+        <v>329</v>
+      </c>
+      <c r="S4" t="n">
+        <v>205</v>
+      </c>
+      <c r="T4" t="n">
+        <v>318</v>
+      </c>
+      <c r="U4" t="n">
+        <v>225</v>
+      </c>
+      <c r="V4" t="n">
+        <v>91</v>
+      </c>
+      <c r="W4" t="n">
+        <v>176</v>
+      </c>
+      <c r="X4" t="n">
+        <v>352</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>331</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1317.76</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1112.76</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AG4" t="n">
         <v>252</v>
       </c>
-      <c r="N4" t="n">
-        <v>548</v>
-      </c>
-      <c r="O4" t="n">
-        <v>109</v>
-      </c>
-      <c r="P4" t="n">
-        <v>317</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="AH4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>138</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>131</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>134</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>78</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>66</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>143</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>513.64</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>440.64</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8565521787102405</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.9895878345533277</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>99.70799113972332</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>111.9570818325775</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-12.24909069285422</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.3420731009636137</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.6993276174719608</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.5085029121926712</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>179</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>384</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>73</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>223</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>142</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>198</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>132</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>184</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>147</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>61</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>110</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>209</v>
+      </c>
+      <c r="BR4" t="n">
         <v>203</v>
       </c>
-      <c r="R4" t="n">
-        <v>282</v>
-      </c>
-      <c r="S4" t="n">
-        <v>171</v>
-      </c>
-      <c r="T4" t="n">
-        <v>271</v>
-      </c>
-      <c r="U4" t="n">
-        <v>202</v>
-      </c>
-      <c r="V4" t="n">
-        <v>77</v>
-      </c>
-      <c r="W4" t="n">
-        <v>152</v>
-      </c>
-      <c r="X4" t="n">
-        <v>300</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>288</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1077</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1141.08</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>970.08</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="BS4" t="n">
         <v>13</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>205</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>43</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>121</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>73</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>104</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>58</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>68</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>118</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>104</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>426.76</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>368.76</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8989491706217176</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.011121276035282</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>104.0680646041733</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>114.7939083022978</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-10.72584369812456</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.349263231360418</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.6862519644957648</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.5114083139083139</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>162</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>343</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>66</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>196</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>130</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>178</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>113</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>163</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>134</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>54</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>97</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>182</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>184</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>12</v>
-      </c>
       <c r="BT4" t="n">
-        <v>714.3199999999999</v>
+        <v>804.12</v>
       </c>
       <c r="BU4" t="n">
-        <v>601.3199999999999</v>
+        <v>672.12</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.9172809117393561</v>
+        <v>0.8982610826448324</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.9961343660443216</v>
+        <v>0.9895652112539265</v>
       </c>
       <c r="BX4" t="n">
-        <v>108.399786395542</v>
+        <v>106.870117725102</v>
       </c>
       <c r="BY4" t="n">
-        <v>110.0904668834308</v>
+        <v>109.4793432791707</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-1.690680487888798</v>
+        <v>-2.609225554068724</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3864213009421186</v>
+        <v>0.3914653988172367</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.72467587797653</v>
+        <v>0.7246161060940803</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5360993568927498</v>
+        <v>0.5374155622912722</v>
       </c>
       <c r="CD4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1860,166 +1860,166 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9087129240726243</v>
+        <v>0.9111616026552879</v>
       </c>
       <c r="D6" t="n">
-        <v>0.94514919170816</v>
+        <v>0.9441572715315162</v>
       </c>
       <c r="E6" t="n">
-        <v>100.9504844798601</v>
+        <v>101.2175003278942</v>
       </c>
       <c r="F6" t="n">
-        <v>109.0257007240447</v>
+        <v>109.0308384929754</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.07521624418459</v>
+        <v>-7.813338165081285</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2657710606894645</v>
+        <v>0.2688101357363925</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6142560244749703</v>
+        <v>0.6132922937209954</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4357171089844654</v>
+        <v>0.4377730705100569</v>
       </c>
       <c r="K6" t="n">
-        <v>5250</v>
+        <v>5450</v>
       </c>
       <c r="L6" t="n">
-        <v>1987</v>
+        <v>2066</v>
       </c>
       <c r="M6" t="n">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="N6" t="n">
-        <v>933</v>
+        <v>959</v>
       </c>
       <c r="O6" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="P6" t="n">
-        <v>682</v>
+        <v>714</v>
       </c>
       <c r="Q6" t="n">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="R6" t="n">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="S6" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="T6" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="U6" t="n">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="V6" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="W6" t="n">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="X6" t="n">
-        <v>577</v>
+        <v>599</v>
       </c>
       <c r="Y6" t="n">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="Z6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA6" t="n">
-        <v>2150</v>
+        <v>2231</v>
       </c>
       <c r="AB6" t="n">
-        <v>2190.8</v>
+        <v>2271.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>1970.8</v>
+        <v>2043.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AF6" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="AG6" t="n">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="AH6" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AI6" t="n">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="AJ6" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="AK6" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AL6" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="AM6" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="AN6" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="AO6" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="AQ6" t="n">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="AR6" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="AS6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>1084.04</v>
+        <v>1165.08</v>
       </c>
       <c r="AU6" t="n">
-        <v>986.04</v>
+        <v>1059.08</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8765458236953942</v>
+        <v>0.883565925274619</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9357182380057207</v>
+        <v>0.9344788886437961</v>
       </c>
       <c r="AX6" t="n">
-        <v>96.30846684824357</v>
+        <v>97.15499867171044</v>
       </c>
       <c r="AY6" t="n">
-        <v>107.9108809128095</v>
+        <v>108.0004194536928</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-11.60241406456598</v>
+        <v>-10.84542078198236</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2520816829007047</v>
+        <v>0.2589205689046916</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6215065918760251</v>
+        <v>0.6191300706075695</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4326764491428264</v>
+        <v>0.4368587077880129</v>
       </c>
       <c r="BD6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE6" t="n">
         <v>2650</v>
@@ -2112,166 +2112,166 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9541817439874302</v>
+        <v>0.9519589359236779</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9553313539133701</v>
+        <v>0.949815132141226</v>
       </c>
       <c r="E7" t="n">
-        <v>105.0516767509059</v>
+        <v>104.7052809981214</v>
       </c>
       <c r="F7" t="n">
-        <v>107.4146540648682</v>
+        <v>106.7354270650476</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.362977313962327</v>
+        <v>-2.030146066926122</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2478907648670726</v>
+        <v>0.2456498428867715</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7243566706475588</v>
+        <v>0.7251584529354757</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4970642783908503</v>
+        <v>0.4961123059389704</v>
       </c>
       <c r="K7" t="n">
-        <v>5225</v>
+        <v>5625</v>
       </c>
       <c r="L7" t="n">
-        <v>2069</v>
+        <v>2221</v>
       </c>
       <c r="M7" t="n">
-        <v>472</v>
+        <v>514</v>
       </c>
       <c r="N7" t="n">
-        <v>919</v>
+        <v>992</v>
       </c>
       <c r="O7" t="n">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="P7" t="n">
-        <v>653</v>
+        <v>701</v>
       </c>
       <c r="Q7" t="n">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="R7" t="n">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="S7" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="T7" t="n">
-        <v>649</v>
+        <v>696</v>
       </c>
       <c r="U7" t="n">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="V7" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="W7" t="n">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="X7" t="n">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="Y7" t="n">
-        <v>553</v>
+        <v>596</v>
       </c>
       <c r="Z7" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>2131</v>
+        <v>2276</v>
       </c>
       <c r="AB7" t="n">
-        <v>2172.84</v>
+        <v>2337.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>1973.84</v>
+        <v>2125.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE7" t="n">
-        <v>2625</v>
+        <v>3025</v>
       </c>
       <c r="AF7" t="n">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="AG7" t="n">
-        <v>475</v>
+        <v>548</v>
       </c>
       <c r="AH7" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AI7" t="n">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="AJ7" t="n">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="AK7" t="n">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="AL7" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="AM7" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>242</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>209</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>299</v>
+      </c>
+      <c r="AR7" t="n">
         <v>313</v>
       </c>
-      <c r="AN7" t="n">
-        <v>209</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>182</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>258</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>270</v>
-      </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>1106.76</v>
+        <v>1271.48</v>
       </c>
       <c r="AU7" t="n">
-        <v>1000.76</v>
+        <v>1152.48</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.9246022212041622</v>
+        <v>0.9243969158562604</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.001551034889766</v>
+        <v>0.9850914634515775</v>
       </c>
       <c r="AX7" t="n">
-        <v>102.2095324590962</v>
+        <v>101.9418796261397</v>
       </c>
       <c r="AY7" t="n">
-        <v>113.6530859517258</v>
+        <v>111.5534046338128</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-11.44355349262961</v>
+        <v>-9.611525007673057</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.2586343838141796</v>
+        <v>0.25301884692467</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.6969338358176095</v>
+        <v>0.7020868740657144</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.4839808717710026</v>
+        <v>0.4839483107434733</v>
       </c>
       <c r="BD7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE7" t="n">
         <v>2600</v>
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9459419347929299</v>
+        <v>0.9455085669412943</v>
       </c>
       <c r="D8" t="n">
-        <v>1.001979567531668</v>
+        <v>0.9922283956810483</v>
       </c>
       <c r="E8" t="n">
-        <v>103.3401279584083</v>
+        <v>103.3708051837332</v>
       </c>
       <c r="F8" t="n">
-        <v>112.0248759185563</v>
+        <v>111.6076737219649</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.684747960147986</v>
+        <v>-8.23686853823169</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2394475217963702</v>
+        <v>0.2397841231850364</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7199870869801822</v>
+        <v>0.7103322260665734</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4858848540797874</v>
+        <v>0.482202444503248</v>
       </c>
       <c r="K8" t="n">
-        <v>5000</v>
+        <v>5400</v>
       </c>
       <c r="L8" t="n">
-        <v>1952</v>
+        <v>2103</v>
       </c>
       <c r="M8" t="n">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="N8" t="n">
-        <v>820</v>
+        <v>882</v>
       </c>
       <c r="O8" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="P8" t="n">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="Q8" t="n">
-        <v>429</v>
+        <v>485</v>
       </c>
       <c r="R8" t="n">
-        <v>552</v>
+        <v>617</v>
       </c>
       <c r="S8" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="T8" t="n">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="U8" t="n">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="V8" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="W8" t="n">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="X8" t="n">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="Y8" t="n">
-        <v>551</v>
+        <v>601</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA8" t="n">
-        <v>2101</v>
+        <v>2256</v>
       </c>
       <c r="AB8" t="n">
-        <v>2069.88</v>
+        <v>2230.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>1892.88</v>
+        <v>2038.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AF8" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AG8" t="n">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="AH8" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="AI8" t="n">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="AJ8" t="n">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="AK8" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="AL8" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AM8" t="n">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="AN8" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="AO8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AP8" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="AQ8" t="n">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="AR8" t="n">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="AS8" t="n">
         <v>20</v>
       </c>
       <c r="AT8" t="n">
-        <v>1097.6</v>
+        <v>1174.44</v>
       </c>
       <c r="AU8" t="n">
-        <v>1008.6</v>
+        <v>1077.44</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9242880211868864</v>
+        <v>0.9251968748828777</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.021273187948369</v>
+        <v>1.001618135229817</v>
       </c>
       <c r="AX8" t="n">
-        <v>100.5387005054181</v>
+        <v>100.8281043582518</v>
       </c>
       <c r="AY8" t="n">
-        <v>113.7151894651335</v>
+        <v>112.3521593863083</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-13.1764889597154</v>
+        <v>-11.52405502805657</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.2407238626635178</v>
+        <v>0.2432337345422321</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.7333336521831216</v>
+        <v>0.7215370926115999</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.4953242288891429</v>
+        <v>0.4922335550056718</v>
       </c>
       <c r="BD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>230</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>435</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>112</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>338</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>221</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>291</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>95</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>285</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>198</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>69</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>155</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>272</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>290</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1056.04</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>961.04</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.9673826968503583</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.9821163684746815</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>106.1090983804054</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>110.8059199295949</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-4.69682154918951</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.2360691571080565</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.6982654467103913</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.4713997101160227</v>
+      </c>
+      <c r="CD8" t="n">
         <v>13</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>212</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>397</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>106</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>315</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>196</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>262</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>88</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>263</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>180</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>145</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>252</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>267</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>972.28</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>884.28</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0.9694003411994768</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0.9810781454135754</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>106.3750076991478</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>110.1937029097644</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>-3.818695210616629</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.2380648191902935</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.7055283080103313</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0.4756588647029859</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2616,244 +2616,244 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8723044961578448</v>
+        <v>0.8832711557463706</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9853653904493135</v>
+        <v>0.9910471164260928</v>
       </c>
       <c r="E9" t="n">
-        <v>96.00194118830481</v>
+        <v>97.40883213953286</v>
       </c>
       <c r="F9" t="n">
-        <v>111.5058390920437</v>
+        <v>112.1467761069504</v>
       </c>
       <c r="G9" t="n">
-        <v>-15.50389790373888</v>
+        <v>-14.73794396741756</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2355802557542776</v>
+        <v>0.2403520886613681</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6965921489168726</v>
+        <v>0.6921257894634965</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4623154498926504</v>
+        <v>0.4617989649162559</v>
       </c>
       <c r="K9" t="n">
-        <v>5050</v>
+        <v>5450</v>
       </c>
       <c r="L9" t="n">
-        <v>1826</v>
+        <v>1989</v>
       </c>
       <c r="M9" t="n">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="N9" t="n">
-        <v>867</v>
+        <v>936</v>
       </c>
       <c r="O9" t="n">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="P9" t="n">
-        <v>676</v>
+        <v>727</v>
       </c>
       <c r="Q9" t="n">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="R9" t="n">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="S9" t="n">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="T9" t="n">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="U9" t="n">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="V9" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="W9" t="n">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="X9" t="n">
-        <v>567</v>
+        <v>610</v>
       </c>
       <c r="Y9" t="n">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA9" t="n">
-        <v>2118</v>
+        <v>2291</v>
       </c>
       <c r="AB9" t="n">
-        <v>2093.2</v>
+        <v>2252.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>1902.2</v>
+        <v>2043.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF9" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="AG9" t="n">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AI9" t="n">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="AK9" t="n">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AL9" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AM9" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="AN9" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AP9" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AQ9" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="AR9" t="n">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="AS9" t="n">
         <v>20</v>
       </c>
       <c r="AT9" t="n">
-        <v>983.36</v>
+        <v>1063.84</v>
       </c>
       <c r="AU9" t="n">
-        <v>904.36</v>
+        <v>976.84</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.867140907857443</v>
+        <v>0.880725266834</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.035799638762833</v>
+        <v>1.041466393905793</v>
       </c>
       <c r="AX9" t="n">
-        <v>94.1427952507713</v>
+        <v>95.8159679034119</v>
       </c>
       <c r="AY9" t="n">
-        <v>117.5835699025132</v>
+        <v>118.006782922973</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-23.4407746517419</v>
+        <v>-22.19081501956105</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2023663101604278</v>
+        <v>0.2073124914301385</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6957926034538938</v>
+        <v>0.6945777878035942</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4431361193957445</v>
+        <v>0.4440137605611068</v>
       </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>2650</v>
+        <v>2850</v>
       </c>
       <c r="BF9" t="n">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="BG9" t="n">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="BH9" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="BI9" t="n">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="BJ9" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="BK9" t="n">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="BL9" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="BM9" t="n">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="BN9" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="BO9" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="BP9" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="BQ9" t="n">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="BR9" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="BS9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BT9" t="n">
-        <v>1109.84</v>
+        <v>1189.08</v>
       </c>
       <c r="BU9" t="n">
-        <v>997.84</v>
+        <v>1067.08</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8770708853582156</v>
+        <v>0.8856351954507149</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.9388106996983723</v>
+        <v>0.944229215909229</v>
       </c>
       <c r="BX9" t="n">
-        <v>97.71807589987421</v>
+        <v>98.88792035878804</v>
       </c>
       <c r="BY9" t="n">
-        <v>105.8956260362257</v>
+        <v>106.7053412063581</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-8.177550136351487</v>
+        <v>-7.817420847570044</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.2662392824562929</v>
+        <v>0.2710317146617958</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.697330190882699</v>
+        <v>0.689848933861977</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.4800194472744096</v>
+        <v>0.4783137975317512</v>
       </c>
       <c r="CD9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -2868,244 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9309111154602038</v>
+        <v>0.9254185449619178</v>
       </c>
       <c r="D10" t="n">
-        <v>1.01327207159717</v>
+        <v>1.024995516433016</v>
       </c>
       <c r="E10" t="n">
-        <v>106.0387469668643</v>
+        <v>105.71319139563</v>
       </c>
       <c r="F10" t="n">
-        <v>113.9117954482826</v>
+        <v>115.0254449666538</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.873048481418281</v>
+        <v>-9.312253571023758</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3233664377143212</v>
+        <v>0.3270545493061554</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6985995075245754</v>
+        <v>0.6958009919767537</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5028829305041638</v>
+        <v>0.5010515921357155</v>
       </c>
       <c r="K10" t="n">
-        <v>5250</v>
+        <v>5650</v>
       </c>
       <c r="L10" t="n">
-        <v>2137</v>
+        <v>2283</v>
       </c>
       <c r="M10" t="n">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="N10" t="n">
-        <v>925</v>
+        <v>989</v>
       </c>
       <c r="O10" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="P10" t="n">
-        <v>765</v>
+        <v>828</v>
       </c>
       <c r="Q10" t="n">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="R10" t="n">
-        <v>564</v>
+        <v>607</v>
       </c>
       <c r="S10" t="n">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="T10" t="n">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="U10" t="n">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="V10" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="W10" t="n">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="X10" t="n">
-        <v>644</v>
+        <v>689</v>
       </c>
       <c r="Y10" t="n">
-        <v>561</v>
+        <v>605</v>
       </c>
       <c r="Z10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA10" t="n">
-        <v>2314</v>
+        <v>2498</v>
       </c>
       <c r="AB10" t="n">
-        <v>2298.16</v>
+        <v>2469.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>2017.16</v>
+        <v>2161.08</v>
       </c>
       <c r="AD10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>255</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>510</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>126</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>408</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>217</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>310</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>159</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>286</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>98</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>195</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>346</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>304</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1249.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1090.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.8845918104232021</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.040167651451432</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>101.4759506481696</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>116.3114239866485</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-14.83547333847888</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.3275610465914474</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.6916808977023716</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.4923594417570263</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2800</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>248</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>479</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>151</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>420</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>229</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>297</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>149</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>310</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>203</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>102</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>190</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>343</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>301</v>
+      </c>
+      <c r="BS10" t="n">
         <v>26</v>
       </c>
-      <c r="AE10" t="n">
-        <v>2650</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>236</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>476</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>119</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>206</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>293</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>145</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>271</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>205</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>182</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>323</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>283</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1166.92</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1021.92</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.887353442635865</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.0290983253107</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>101.4187448389346</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>115.051534451985</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-13.63278961305036</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.322843520260875</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0.6947198965222865</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.4924235969899657</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2600</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>235</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>449</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>142</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>385</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>206</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>271</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>136</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>298</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>191</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>92</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>178</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>321</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>278</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>25</v>
-      </c>
       <c r="BT10" t="n">
-        <v>1131.24</v>
+        <v>1219.68</v>
       </c>
       <c r="BU10" t="n">
-        <v>995.24</v>
+        <v>1070.68</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9744687882845425</v>
+        <v>0.9662452795006333</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.9974458178836401</v>
+        <v>1.0098233814146</v>
       </c>
       <c r="BX10" t="n">
-        <v>110.658749094794</v>
+        <v>109.9504321430904</v>
       </c>
       <c r="BY10" t="n">
-        <v>112.7720564445802</v>
+        <v>113.739465946659</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-2.113307349786196</v>
+        <v>-3.78903380356864</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3238893551677674</v>
+        <v>0.3265480520208633</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7024791185268638</v>
+        <v>0.6999210862511355</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.5133422640183615</v>
+        <v>0.5097437425144044</v>
       </c>
       <c r="CD10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -3120,244 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9835297833947405</v>
+        <v>0.9921104963999936</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9574052460631601</v>
+        <v>0.9548441840700294</v>
       </c>
       <c r="E11" t="n">
-        <v>111.2268249738531</v>
+        <v>112.2441574333956</v>
       </c>
       <c r="F11" t="n">
-        <v>107.1693098803709</v>
+        <v>107.2425285741542</v>
       </c>
       <c r="G11" t="n">
-        <v>4.057515093482283</v>
+        <v>5.001628859241404</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3072742872857415</v>
+        <v>0.3124848398706469</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7094697893236824</v>
+        <v>0.7042415744766607</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5046662654850583</v>
+        <v>0.5062589208340909</v>
       </c>
       <c r="K11" t="n">
-        <v>5025</v>
+        <v>5425</v>
       </c>
       <c r="L11" t="n">
-        <v>2023</v>
+        <v>2194</v>
       </c>
       <c r="M11" t="n">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="N11" t="n">
-        <v>810</v>
+        <v>871</v>
       </c>
       <c r="O11" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="P11" t="n">
-        <v>763</v>
+        <v>816</v>
       </c>
       <c r="Q11" t="n">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="R11" t="n">
-        <v>490</v>
+        <v>538</v>
       </c>
       <c r="S11" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="T11" t="n">
-        <v>521</v>
+        <v>563</v>
       </c>
       <c r="U11" t="n">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="V11" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="W11" t="n">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="X11" t="n">
-        <v>573</v>
+        <v>615</v>
       </c>
       <c r="Y11" t="n">
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="Z11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA11" t="n">
-        <v>1928</v>
+        <v>2077</v>
       </c>
       <c r="AB11" t="n">
-        <v>2067.6</v>
+        <v>2223.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>1820.6</v>
+        <v>1957.72</v>
       </c>
       <c r="AD11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2825</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>251</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>463</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>137</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>426</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>262</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>126</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>296</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>191</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>145</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>327</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>278</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1149.28</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1023.28</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.972083578671915</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.9703557654762979</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>108.7330357242149</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>108.628150930622</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.1048847935928835</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.2736542647090081</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.7123882587748193</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.4851108624454937</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>221</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>408</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>144</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>390</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>207</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>276</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>267</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>235</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>88</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>155</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>288</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>277</v>
+      </c>
+      <c r="BS11" t="n">
         <v>25</v>
       </c>
-      <c r="AE11" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>232</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>431</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>128</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>395</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>242</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>276</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>172</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>81</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>135</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>306</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>259</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1067.48</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>952.48</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.9688077057504956</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.9683084223088435</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>108.0792970554561</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>108.2075549772338</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-0.1282579217777639</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.2633655614245158</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.7159053043216003</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.4805917250087773</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="BT11" t="n">
+        <v>1074.44</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>934.4399999999999</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1.013677946261001</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.9381394040940479</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>116.025365427898</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>105.7503198825735</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>10.27504554532443</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.3543023823524119</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.695468222155567</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.5290337529448877</v>
+      </c>
+      <c r="CD11" t="n">
         <v>13</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>203</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>379</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>135</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>368</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>182</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>248</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>132</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>245</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>208</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>80</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>144</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>267</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>254</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000.12</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>868.12</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>0.9994787008426725</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>0.9455934717970034</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>114.63664688545</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>106.0445443587693</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>8.592102526680669</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0.3548420736354028</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>0.7024979814092718</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>0.5307470176676962</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -3372,244 +3372,244 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.004732132916311</v>
+        <v>0.9925706404691326</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9783666965370409</v>
+        <v>0.9757770985766129</v>
       </c>
       <c r="E12" t="n">
-        <v>111.8733182421374</v>
+        <v>110.5505626257644</v>
       </c>
       <c r="F12" t="n">
-        <v>109.7216528852768</v>
+        <v>109.6230935061225</v>
       </c>
       <c r="G12" t="n">
-        <v>2.151665356860573</v>
+        <v>0.9274691196419705</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2632112790867055</v>
+        <v>0.2605912314551478</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7161188109373329</v>
+        <v>0.7108755066280439</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4915199927464975</v>
+        <v>0.4854003324687796</v>
       </c>
       <c r="K12" t="n">
-        <v>5250</v>
+        <v>5650</v>
       </c>
       <c r="L12" t="n">
-        <v>2166</v>
+        <v>2314</v>
       </c>
       <c r="M12" t="n">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="N12" t="n">
-        <v>904</v>
+        <v>990</v>
       </c>
       <c r="O12" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="P12" t="n">
-        <v>697</v>
+        <v>755</v>
       </c>
       <c r="Q12" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="R12" t="n">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="S12" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="T12" t="n">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="U12" t="n">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="V12" t="n">
+        <v>161</v>
+      </c>
+      <c r="W12" t="n">
+        <v>310</v>
+      </c>
+      <c r="X12" t="n">
+        <v>595</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>587</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2297</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2332.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2090.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2650</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>228</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>482</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>122</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>334</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>221</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>281</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>123</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>313</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>157</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>61</v>
+      </c>
+      <c r="AP12" t="n">
         <v>148</v>
       </c>
-      <c r="W12" t="n">
-        <v>290</v>
-      </c>
-      <c r="X12" t="n">
-        <v>557</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>547</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2134</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2154.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1931.56</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2450</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>438</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>112</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>311</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>269</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="AQ12" t="n">
+        <v>283</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>263</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1087.64</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>964.64</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.9597685851356376</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.9603150188733838</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>108.1294250472061</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>108.6966867862862</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.5672617390801378</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.2726914443517993</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.7089396640962401</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.4892854585924872</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>254</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>508</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>158</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>421</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>289</v>
       </c>
-      <c r="AN12" t="n">
-        <v>147</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>56</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>135</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>263</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>244</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1002.36</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>887.36</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.9674384813015685</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.9690199491248445</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>109.1605693359916</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>109.2877208455712</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.1271515095796675</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.2763681123334968</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.715386390490225</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.4935295664432309</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>239</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>466</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>148</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>386</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>275</v>
-      </c>
       <c r="BK12" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="BL12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="BM12" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="BN12" t="n">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="BO12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="BP12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="BQ12" t="n">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="BR12" t="n">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="BS12" t="n">
         <v>30</v>
       </c>
       <c r="BT12" t="n">
-        <v>1152.2</v>
+        <v>1244.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>1044.2</v>
+        <v>1125.56</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.036698120014661</v>
+        <v>1.020999088424828</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.9863781943189237</v>
+        <v>0.9891775676527448</v>
       </c>
       <c r="BX12" t="n">
-        <v>114.1985315902624</v>
+        <v>112.648881860515</v>
       </c>
       <c r="BY12" t="n">
-        <v>110.0935946335959</v>
+        <v>110.4259793299805</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.104936956666495</v>
+        <v>2.222902530534465</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2519339934465984</v>
+        <v>0.2501043802780497</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.7167465998919967</v>
+        <v>0.7125532368222738</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.4897975010064402</v>
+        <v>0.4820332231615664</v>
       </c>
       <c r="CD12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -3624,166 +3624,166 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9515919644242917</v>
+        <v>0.9422541345137335</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9016632170157765</v>
+        <v>0.8981760470580207</v>
       </c>
       <c r="E13" t="n">
-        <v>109.5877821991982</v>
+        <v>108.4090269385123</v>
       </c>
       <c r="F13" t="n">
-        <v>101.5542176600192</v>
+        <v>101.296168408491</v>
       </c>
       <c r="G13" t="n">
-        <v>8.033564539178935</v>
+        <v>7.112858530021297</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3505430557519366</v>
+        <v>0.3490933227272767</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7160438771005349</v>
+        <v>0.7185780419109262</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5368214122666169</v>
+        <v>0.5397349258878932</v>
       </c>
       <c r="K13" t="n">
-        <v>5025</v>
+        <v>5425</v>
       </c>
       <c r="L13" t="n">
-        <v>1991</v>
+        <v>2132</v>
       </c>
       <c r="M13" t="n">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="N13" t="n">
-        <v>906</v>
+        <v>979</v>
       </c>
       <c r="O13" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="P13" t="n">
-        <v>669</v>
+        <v>725</v>
       </c>
       <c r="Q13" t="n">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="R13" t="n">
-        <v>491</v>
+        <v>519</v>
       </c>
       <c r="S13" t="n">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="T13" t="n">
+        <v>649</v>
+      </c>
+      <c r="U13" t="n">
+        <v>427</v>
+      </c>
+      <c r="V13" t="n">
+        <v>177</v>
+      </c>
+      <c r="W13" t="n">
+        <v>334</v>
+      </c>
+      <c r="X13" t="n">
         <v>582</v>
       </c>
-      <c r="U13" t="n">
-        <v>394</v>
-      </c>
-      <c r="V13" t="n">
-        <v>166</v>
-      </c>
-      <c r="W13" t="n">
-        <v>304</v>
-      </c>
-      <c r="X13" t="n">
-        <v>544</v>
-      </c>
       <c r="Y13" t="n">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="Z13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AA13" t="n">
-        <v>1868</v>
+        <v>2015</v>
       </c>
       <c r="AB13" t="n">
-        <v>2095.04</v>
+        <v>2266.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>1816.04</v>
+        <v>1966.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="AF13" t="n">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="AG13" t="n">
-        <v>407</v>
+        <v>480</v>
       </c>
       <c r="AH13" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="AI13" t="n">
-        <v>265</v>
+        <v>321</v>
       </c>
       <c r="AJ13" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="AK13" t="n">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="AL13" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="AM13" t="n">
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="AN13" t="n">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="AO13" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AP13" t="n">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="AQ13" t="n">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="AR13" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="AS13" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AT13" t="n">
-        <v>920.8</v>
+        <v>1092.12</v>
       </c>
       <c r="AU13" t="n">
-        <v>808.8</v>
+        <v>959.12</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9714552370892989</v>
+        <v>0.9490053945573691</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8856373843129653</v>
+        <v>0.880860313278059</v>
       </c>
       <c r="AX13" t="n">
-        <v>110.5164153930311</v>
+        <v>107.9253647448632</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.876174900982</v>
+        <v>101.2906945722753</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.640240492049131</v>
+        <v>6.634670172587852</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.353111873344149</v>
+        <v>0.3497056866633611</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.686351863531231</v>
+        <v>0.6961831309942441</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5404371619712222</v>
+        <v>0.5459320364608566</v>
       </c>
       <c r="BD13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE13" t="n">
         <v>2825</v>
@@ -3876,244 +3876,244 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.028670537269259</v>
+        <v>1.026720368572058</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9190865287410088</v>
+        <v>0.9281116179551975</v>
       </c>
       <c r="E14" t="n">
-        <v>117.7476046919323</v>
+        <v>117.7050245941314</v>
       </c>
       <c r="F14" t="n">
-        <v>102.7277481173657</v>
+        <v>103.6190747989198</v>
       </c>
       <c r="G14" t="n">
-        <v>15.01985657456663</v>
+        <v>14.08594979521154</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3481326878394413</v>
+        <v>0.3507017541979268</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7337456576911964</v>
+        <v>0.7332833055184487</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5442575441697856</v>
+        <v>0.5442800091287897</v>
       </c>
       <c r="K14" t="n">
-        <v>5200</v>
+        <v>5600</v>
       </c>
       <c r="L14" t="n">
-        <v>2383</v>
+        <v>2555</v>
       </c>
       <c r="M14" t="n">
-        <v>560</v>
+        <v>598</v>
       </c>
       <c r="N14" t="n">
-        <v>1032</v>
+        <v>1105</v>
       </c>
       <c r="O14" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="P14" t="n">
-        <v>732</v>
+        <v>791</v>
       </c>
       <c r="Q14" t="n">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="R14" t="n">
-        <v>604</v>
+        <v>649</v>
       </c>
       <c r="S14" t="n">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="T14" t="n">
-        <v>641</v>
+        <v>683</v>
       </c>
       <c r="U14" t="n">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="V14" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="W14" t="n">
+        <v>312</v>
+      </c>
+      <c r="X14" t="n">
+        <v>609</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>623</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2198</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2493.56</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2171.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2800</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>309</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>569</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>365</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>255</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>322</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>162</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>313</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>247</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>118</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>164</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>317</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>311</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1239.68</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1077.68</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.019654844243572</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.9171200222139769</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>117.1011809659024</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>104.2973947709277</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>12.80378619497469</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.3591528604244217</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.6792622809044958</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.5206492031213887</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2800</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>289</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>536</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>157</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>426</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>243</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>327</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>370</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>294</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>103</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>148</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>292</v>
       </c>
-      <c r="X14" t="n">
-        <v>557</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>579</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2321.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2024.76</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>285</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>521</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>121</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>339</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>242</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>305</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>148</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>287</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>233</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>112</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>157</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>294</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>291</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1151.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1003.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.021584059554004</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.9151161035642108</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>117.0203084119286</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>104.4034877105762</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>12.61682070135243</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0.3568654736194627</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0.6709071649833965</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0.5161060537516851</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2600</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>275</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>511</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>146</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>393</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>220</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>299</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>149</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>354</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>282</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>97</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>135</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>263</v>
-      </c>
       <c r="BR14" t="n">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="BS14" t="n">
         <v>19</v>
       </c>
       <c r="BT14" t="n">
-        <v>1170.56</v>
+        <v>1253.88</v>
       </c>
       <c r="BU14" t="n">
-        <v>1021.56</v>
+        <v>1093.88</v>
       </c>
       <c r="BV14" t="n">
-        <v>1.035757014984514</v>
+        <v>1.033785892900543</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.9230569539178066</v>
+        <v>0.9391032136964179</v>
       </c>
       <c r="BX14" t="n">
-        <v>118.474900971936</v>
+        <v>118.3088682223603</v>
       </c>
       <c r="BY14" t="n">
-        <v>101.0520085241552</v>
+        <v>102.9407548269119</v>
       </c>
       <c r="BZ14" t="n">
-        <v>17.42289244778084</v>
+        <v>15.3681133954484</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3393999020594199</v>
+        <v>0.3422506479714318</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7965841503989961</v>
+        <v>0.7873043301324011</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5724090345878862</v>
+        <v>0.5679108151361908</v>
       </c>
       <c r="CD14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4128,244 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8696020133271409</v>
+        <v>0.8739823776265447</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9988797880295546</v>
+        <v>0.979909289995743</v>
       </c>
       <c r="E15" t="n">
-        <v>98.42777545090779</v>
+        <v>98.9585051075961</v>
       </c>
       <c r="F15" t="n">
-        <v>113.0500217719582</v>
+        <v>110.9175154931327</v>
       </c>
       <c r="G15" t="n">
-        <v>-14.62224632105038</v>
+        <v>-11.95901038553655</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2897070823085149</v>
+        <v>0.2872044134435567</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6961633251289732</v>
+        <v>0.698426830510033</v>
       </c>
       <c r="J15" t="n">
-        <v>0.489443645147027</v>
+        <v>0.4895164299825243</v>
       </c>
       <c r="K15" t="n">
-        <v>5000</v>
+        <v>5400</v>
       </c>
       <c r="L15" t="n">
-        <v>1886</v>
+        <v>2041</v>
       </c>
       <c r="M15" t="n">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="N15" t="n">
-        <v>889</v>
+        <v>944</v>
       </c>
       <c r="O15" t="n">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="P15" t="n">
-        <v>715</v>
+        <v>790</v>
       </c>
       <c r="Q15" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="R15" t="n">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="S15" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="T15" t="n">
-        <v>585</v>
+        <v>641</v>
       </c>
       <c r="U15" t="n">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="V15" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="W15" t="n">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="X15" t="n">
-        <v>525</v>
+        <v>561</v>
       </c>
       <c r="Y15" t="n">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="Z15" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2176</v>
+        <v>2305</v>
       </c>
       <c r="AB15" t="n">
-        <v>2175.36</v>
+        <v>2342.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1918.36</v>
+        <v>2065.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
+        <v>2800</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>226</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>499</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>136</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>420</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>237</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>149</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>217</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>213</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>298</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>285</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1236.28</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1087.28</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.8417554040527594</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.001839115684425</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>95.58045128576205</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>113.9616706937297</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-18.38121940796766</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.2956658999565711</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.6880531619447876</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.4834065054886604</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE15" t="n">
         <v>2600</v>
       </c>
-      <c r="AF15" t="n">
-        <v>214</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>472</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>122</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>383</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>164</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>218</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>196</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>79</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>199</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>280</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>266</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1149.92</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1009.92</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.8334663071542632</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.012529632105617</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>94.77910663484582</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>115.3239094597772</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-20.54480282493135</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0.3001908072406798</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0.6818087306150967</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.4816305823344414</v>
-      </c>
-      <c r="BD15" t="n">
+      <c r="BF15" t="n">
+        <v>225</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>445</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>125</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>370</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>176</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>236</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>128</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>321</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>219</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>91</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>187</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>263</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>263</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1105.84</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>977.84</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.9086883491675444</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.9562925546387006</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>102.5964092234174</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>107.6391945078743</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-5.042785284456899</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.2780920433526182</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.7095984735802972</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.496096348668224</v>
+      </c>
+      <c r="CD15" t="n">
         <v>13</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>212</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>417</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>112</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>332</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>168</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>226</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>117</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>295</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>201</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>81</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>177</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>245</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>246</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1025.44</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>908.4400000000001</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>0.9087490283477585</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0.9840924569471531</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>102.3805000016416</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>110.5866434434876</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>-8.206143441846001</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.2783497136320031</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.7117141358523394</v>
-      </c>
-      <c r="CC15" t="n">
-        <v>0.4979077965273281</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -4380,244 +4380,244 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.066378724431395</v>
+        <v>1.066320734491772</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8926546426226705</v>
+        <v>0.8865698457689081</v>
       </c>
       <c r="E16" t="n">
-        <v>119.72513940432</v>
+        <v>119.9038869922654</v>
       </c>
       <c r="F16" t="n">
-        <v>100.4061841698055</v>
+        <v>99.83719295936778</v>
       </c>
       <c r="G16" t="n">
-        <v>19.31895523451453</v>
+        <v>20.06669403289761</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3201634994321476</v>
+        <v>0.3233837115954228</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7036812862599849</v>
+        <v>0.7012942234775651</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5196219946664736</v>
+        <v>0.5202345665074829</v>
       </c>
       <c r="K16" t="n">
-        <v>5050</v>
+        <v>5450</v>
       </c>
       <c r="L16" t="n">
-        <v>2313</v>
+        <v>2486</v>
       </c>
       <c r="M16" t="n">
-        <v>557</v>
+        <v>595</v>
       </c>
       <c r="N16" t="n">
-        <v>965</v>
+        <v>1021</v>
       </c>
       <c r="O16" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="P16" t="n">
-        <v>661</v>
+        <v>721</v>
       </c>
       <c r="Q16" t="n">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="R16" t="n">
-        <v>579</v>
+        <v>637</v>
       </c>
       <c r="S16" t="n">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="T16" t="n">
-        <v>575</v>
+        <v>619</v>
       </c>
       <c r="U16" t="n">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="V16" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="W16" t="n">
+        <v>309</v>
+      </c>
+      <c r="X16" t="n">
+        <v>572</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>616</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2052</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2331.28</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2075.28</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2825</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>307</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>524</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>138</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>352</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>255</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>347</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>123</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>294</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>262</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>161</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>299</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>319</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1189.68</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1066.68</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.078318331893942</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.9163072824401171</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>120.3885259172726</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>104.6626776261728</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15.72584829109983</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.3144019072193234</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.6630728682025467</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.4982632336360799</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2625</v>
+      </c>
+      <c r="BF16" t="n">
         <v>288</v>
       </c>
-      <c r="X16" t="n">
-        <v>525</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>566</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1915</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2168.76</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1933.76</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>289</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>498</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>128</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>326</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>229</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>308</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>276</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>247</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>115</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>275</v>
-      </c>
-      <c r="AR16" t="n">
+      <c r="BG16" t="n">
+        <v>497</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>135</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>369</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>222</v>
+      </c>
+      <c r="BK16" t="n">
         <v>290</v>
       </c>
-      <c r="AS16" t="n">
-        <v>33</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1109.52</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>994.52</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.072980927361294</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.9092415883348237</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>119.841915852236</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>103.779003406811</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16.06291244542495</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0.3129456436720919</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0.6663331153587108</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.4988553256284053</v>
-      </c>
-      <c r="BD16" t="n">
+      <c r="BL16" t="n">
+        <v>133</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>325</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>278</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>122</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>148</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>273</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>297</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1141.6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1008.6</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1.053400244981743</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0.8545449139691456</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>119.3819681499499</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>94.64051716434697</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>24.7414509856029</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.3330564240004531</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0.7424556830045079</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.5438960019074555</v>
+      </c>
+      <c r="CD16" t="n">
         <v>13</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2425</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>268</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>467</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>125</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>335</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>211</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>271</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>299</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>260</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>114</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>138</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>250</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>276</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1059.24</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>939.24</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1.059226337924005</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0.8746854514345053</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>119.5986315857444</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>96.75229666304953</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>22.8463349226949</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0.327982843172208</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>0.7441418047363652</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>0.5421192194577145</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -4632,244 +4632,244 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.018305301051677</v>
+        <v>1.027327099601123</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9694079712113691</v>
+        <v>0.9680843155609898</v>
       </c>
       <c r="E17" t="n">
-        <v>114.3791303056464</v>
+        <v>115.1436809734568</v>
       </c>
       <c r="F17" t="n">
-        <v>108.7815540913745</v>
+        <v>108.747229770015</v>
       </c>
       <c r="G17" t="n">
-        <v>5.597576214271908</v>
+        <v>6.396451203441813</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2992750500995604</v>
+        <v>0.3013040587341609</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7132392231574252</v>
+        <v>0.7112297333762169</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5107044931473004</v>
+        <v>0.5129668115249663</v>
       </c>
       <c r="K17" t="n">
-        <v>5000</v>
+        <v>5400</v>
       </c>
       <c r="L17" t="n">
-        <v>2113</v>
+        <v>2299</v>
       </c>
       <c r="M17" t="n">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="N17" t="n">
-        <v>821</v>
+        <v>872</v>
       </c>
       <c r="O17" t="n">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="P17" t="n">
-        <v>716</v>
+        <v>776</v>
       </c>
       <c r="Q17" t="n">
-        <v>425</v>
+        <v>464</v>
       </c>
       <c r="R17" t="n">
-        <v>561</v>
+        <v>609</v>
       </c>
       <c r="S17" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="T17" t="n">
-        <v>567</v>
+        <v>612</v>
       </c>
       <c r="U17" t="n">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="V17" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="W17" t="n">
+        <v>321</v>
+      </c>
+      <c r="X17" t="n">
+        <v>587</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>630</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2183</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2236.96</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1997.96</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2800</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>263</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>470</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>381</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>275</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>115</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>322</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>224</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>306</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>297</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1035</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.002778925739386</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.9696448044586913</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>111.407205287259</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>108.7907820022718</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.616423284987204</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.2832630130130154</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.7192669796068415</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.510638597759095</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>230</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>402</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>143</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>395</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>254</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>334</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>124</v>
+      </c>
+      <c r="BM17" t="n">
         <v>290</v>
       </c>
-      <c r="X17" t="n">
-        <v>546</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>584</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2073.84</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1848.84</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>246</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>446</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>126</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>353</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>250</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>109</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>299</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>211</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>87</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>159</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>283</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>275</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1068</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>959</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.9898594810026412</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.978129815162451</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>110.2603911190724</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>109.4098950969893</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.850496022083112</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0.2794114499114524</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0.7254499096620687</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0.5086079485838687</v>
-      </c>
-      <c r="BD17" t="n">
+      <c r="BN17" t="n">
+        <v>192</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>76</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>143</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>281</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>333</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>39</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1086.96</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>962.96</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1.053763594529146</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0.9664037890557728</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>119.1675778662853</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>108.7003273660462</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>10.46725050023908</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.3207328772030869</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0.7025742374355443</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0.515474118657443</v>
+      </c>
+      <c r="CD17" t="n">
         <v>13</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>211</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>375</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>132</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>363</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>235</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>311</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>116</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>268</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>176</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>68</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>131</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>263</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>309</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1005.84</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>889.84</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1.0491216061048</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0.9599593069310303</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>118.8410977577682</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>108.1008513352918</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>10.74024642247644</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0.3207939503033441</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>0.700010979444062</v>
-      </c>
-      <c r="CC17" t="n">
-        <v>0.5129757497576845</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -4884,88 +4884,88 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8694043673832872</v>
+        <v>0.8696256375531357</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9784362771082007</v>
+        <v>0.9649995485404105</v>
       </c>
       <c r="E18" t="n">
-        <v>98.21758340793994</v>
+        <v>98.1283370895403</v>
       </c>
       <c r="F18" t="n">
-        <v>112.0074210073753</v>
+        <v>110.5218918796121</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.78983759943529</v>
+        <v>-12.39355479007186</v>
       </c>
       <c r="H18" t="n">
-        <v>0.281766605714072</v>
+        <v>0.278156610787707</v>
       </c>
       <c r="I18" t="n">
-        <v>0.643490846029693</v>
+        <v>0.6497891332036879</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4502452252408753</v>
+        <v>0.4539133785523674</v>
       </c>
       <c r="K18" t="n">
-        <v>5025</v>
+        <v>5425</v>
       </c>
       <c r="L18" t="n">
-        <v>1824</v>
+        <v>1971</v>
       </c>
       <c r="M18" t="n">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="N18" t="n">
-        <v>853</v>
+        <v>933</v>
       </c>
       <c r="O18" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="P18" t="n">
-        <v>691</v>
+        <v>738</v>
       </c>
       <c r="Q18" t="n">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="R18" t="n">
-        <v>553</v>
+        <v>602</v>
       </c>
       <c r="S18" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="T18" t="n">
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="U18" t="n">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="V18" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="W18" t="n">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="X18" t="n">
-        <v>496</v>
+        <v>540</v>
       </c>
       <c r="Y18" t="n">
-        <v>529</v>
+        <v>571</v>
       </c>
       <c r="Z18" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2118</v>
+        <v>2256</v>
       </c>
       <c r="AB18" t="n">
-        <v>2105.32</v>
+        <v>2273.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>1862.32</v>
+        <v>2013.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>2600</v>
@@ -5046,82 +5046,82 @@
         <v>13</v>
       </c>
       <c r="BE18" t="n">
-        <v>2425</v>
+        <v>2825</v>
       </c>
       <c r="BF18" t="n">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="BG18" t="n">
-        <v>423</v>
+        <v>503</v>
       </c>
       <c r="BH18" t="n">
+        <v>112</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>374</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>229</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>319</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>147</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>300</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>196</v>
+      </c>
+      <c r="BO18" t="n">
         <v>99</v>
       </c>
-      <c r="BI18" t="n">
-        <v>327</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>193</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>270</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>130</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>237</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>167</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>85</v>
-      </c>
       <c r="BP18" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="BQ18" t="n">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="BR18" t="n">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="BS18" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="BT18" t="n">
-        <v>1034.8</v>
+        <v>1203.36</v>
       </c>
       <c r="BU18" t="n">
-        <v>904.8</v>
+        <v>1056.36</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8391979749083278</v>
+        <v>0.8439399091608871</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9390689527303638</v>
+        <v>0.9187791654036023</v>
       </c>
       <c r="BX18" t="n">
-        <v>95.94883713386052</v>
+        <v>96.10082584467253</v>
       </c>
       <c r="BY18" t="n">
-        <v>107.6727528860883</v>
+        <v>105.4270421570148</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-11.72391575222783</v>
+        <v>-9.326216312342265</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.3097573787445323</v>
+        <v>0.2987965638107627</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.6369722391274116</v>
+        <v>0.650050165377585</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.4627838534682442</v>
+        <v>0.4680669165364976</v>
       </c>
       <c r="CD18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -5136,166 +5136,166 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.992032740863957</v>
+        <v>0.9779892491425078</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8695293686756513</v>
+        <v>0.8737500264904272</v>
       </c>
       <c r="E19" t="n">
-        <v>113.0043073993123</v>
+        <v>111.3855983541495</v>
       </c>
       <c r="F19" t="n">
-        <v>97.74287415486252</v>
+        <v>98.44802722025337</v>
       </c>
       <c r="G19" t="n">
-        <v>15.26143324444977</v>
+        <v>12.93757113389612</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3248090494829252</v>
+        <v>0.3230671505308827</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7171648285413645</v>
+        <v>0.7130498573383734</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5271472881554786</v>
+        <v>0.523726374101411</v>
       </c>
       <c r="K19" t="n">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="L19" t="n">
-        <v>2183</v>
+        <v>2236</v>
       </c>
       <c r="M19" t="n">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="N19" t="n">
-        <v>989</v>
+        <v>1030</v>
       </c>
       <c r="O19" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P19" t="n">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="Q19" t="n">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="R19" t="n">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="S19" t="n">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="T19" t="n">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="U19" t="n">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="V19" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="W19" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="X19" t="n">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="Y19" t="n">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="Z19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>1874</v>
+        <v>1955</v>
       </c>
       <c r="AB19" t="n">
-        <v>2205.6</v>
+        <v>2292.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>1930.6</v>
+        <v>2007.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF19" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="AG19" t="n">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="AH19" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AI19" t="n">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="AJ19" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="AK19" t="n">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="AL19" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="AM19" t="n">
+        <v>304</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>188</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>136</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>284</v>
       </c>
-      <c r="AN19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>91</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>121</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>263</v>
-      </c>
       <c r="AR19" t="n">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>1018.84</v>
+        <v>1105.32</v>
       </c>
       <c r="AU19" t="n">
-        <v>889.84</v>
+        <v>966.3200000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.9936248790724237</v>
+        <v>0.9643351548656856</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.8659893271862308</v>
+        <v>0.8750276196853359</v>
       </c>
       <c r="AX19" t="n">
-        <v>113.5978811475987</v>
+        <v>110.190287457777</v>
       </c>
       <c r="AY19" t="n">
-        <v>95.98630174244708</v>
+        <v>97.58597137152154</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.61157940515162</v>
+        <v>12.60431608625542</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.315133038938186</v>
+        <v>0.3122595573104623</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.7487721713529848</v>
+        <v>0.7377943586381863</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.5325416686012221</v>
+        <v>0.5250217409161783</v>
       </c>
       <c r="BD19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE19" t="n">
         <v>2800</v>

--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,166 +852,166 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9432599401720271</v>
+        <v>0.9382211469007501</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9196898303741848</v>
+        <v>0.9180905809674205</v>
       </c>
       <c r="E2" t="n">
-        <v>107.1070396266322</v>
+        <v>106.5214655653528</v>
       </c>
       <c r="F2" t="n">
-        <v>101.4614980651912</v>
+        <v>101.3711110324959</v>
       </c>
       <c r="G2" t="n">
-        <v>5.645541561441012</v>
+        <v>5.150354532856938</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3088197400700812</v>
+        <v>0.308023000264709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7528570242029435</v>
+        <v>0.7481165963126565</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5267588574986236</v>
+        <v>0.5232923282123512</v>
       </c>
       <c r="K2" t="n">
-        <v>5625</v>
+        <v>5825</v>
       </c>
       <c r="L2" t="n">
-        <v>2304</v>
+        <v>2373</v>
       </c>
       <c r="M2" t="n">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="N2" t="n">
-        <v>901</v>
+        <v>929</v>
       </c>
       <c r="O2" t="n">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="P2" t="n">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="Q2" t="n">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="R2" t="n">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="S2" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="T2" t="n">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="U2" t="n">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="V2" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="W2" t="n">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="X2" t="n">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="Y2" t="n">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="Z2" t="n">
         <v>47</v>
       </c>
       <c r="AA2" t="n">
-        <v>2195</v>
+        <v>2270</v>
       </c>
       <c r="AB2" t="n">
-        <v>2449.36</v>
+        <v>2535.92</v>
       </c>
       <c r="AC2" t="n">
-        <v>2153.36</v>
+        <v>2229.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="AF2" t="n">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="AG2" t="n">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="AH2" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="AI2" t="n">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="AJ2" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="AK2" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="AL2" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AM2" t="n">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="AN2" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AO2" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="AQ2" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="AR2" t="n">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1251.2</v>
+        <v>1337.76</v>
       </c>
       <c r="AU2" t="n">
-        <v>1086.2</v>
+        <v>1162.76</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.9307812442451924</v>
+        <v>0.9218714903158456</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9293227146817394</v>
+        <v>0.9255886402081579</v>
       </c>
       <c r="AX2" t="n">
-        <v>107.028217245648</v>
+        <v>105.9013622192401</v>
       </c>
       <c r="AY2" t="n">
-        <v>102.7693545830184</v>
+        <v>102.5074158852856</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.258862662629544</v>
+        <v>3.393946333954433</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.3322579671319167</v>
+        <v>0.329155055037408</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.7517852599846179</v>
+        <v>0.742691883677951</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.5313252291556706</v>
+        <v>0.5243188477584073</v>
       </c>
       <c r="BD2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE2" t="n">
         <v>2800</v>
@@ -1104,166 +1104,166 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9438279057453388</v>
+        <v>0.9417478490836568</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9638406964510521</v>
+        <v>0.9630565204183384</v>
       </c>
       <c r="E3" t="n">
-        <v>106.577415622253</v>
+        <v>106.2528620227581</v>
       </c>
       <c r="F3" t="n">
-        <v>110.8123091873803</v>
+        <v>110.6352929969687</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.234893565127281</v>
+        <v>-4.382430974210579</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3155861723712737</v>
+        <v>0.3117903207002066</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6634315756743168</v>
+        <v>0.6665233051145197</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4954259332906475</v>
+        <v>0.4949735292691835</v>
       </c>
       <c r="K3" t="n">
-        <v>5422.766666666666</v>
+        <v>5647.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2260</v>
+        <v>2347</v>
       </c>
       <c r="M3" t="n">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="N3" t="n">
-        <v>1119</v>
+        <v>1161</v>
       </c>
       <c r="O3" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="P3" t="n">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="Q3" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="R3" t="n">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="S3" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="T3" t="n">
-        <v>624</v>
+        <v>657</v>
       </c>
       <c r="U3" t="n">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="V3" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="W3" t="n">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="X3" t="n">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="Y3" t="n">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="Z3" t="n">
         <v>67</v>
       </c>
       <c r="AA3" t="n">
-        <v>2335</v>
+        <v>2429</v>
       </c>
       <c r="AB3" t="n">
-        <v>2394.2</v>
+        <v>2492.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>2118.2</v>
+        <v>2207.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2600</v>
+        <v>2825</v>
       </c>
       <c r="AF3" t="n">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="AG3" t="n">
-        <v>529</v>
+        <v>571</v>
       </c>
       <c r="AH3" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="AI3" t="n">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="AJ3" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AK3" t="n">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="AL3" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="AM3" t="n">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="AN3" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="AO3" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AP3" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AQ3" t="n">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="AR3" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="AS3" t="n">
         <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>1123.28</v>
+        <v>1221.52</v>
       </c>
       <c r="AU3" t="n">
-        <v>999.28</v>
+        <v>1088.52</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.9663334080264676</v>
+        <v>0.96056575882588</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9654715493550523</v>
+        <v>0.9637867077964822</v>
       </c>
       <c r="AX3" t="n">
-        <v>108.6237728788093</v>
+        <v>107.8284973043513</v>
       </c>
       <c r="AY3" t="n">
-        <v>111.8588658851437</v>
+        <v>111.4300794544802</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-3.235093006334291</v>
+        <v>-3.601582150128959</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.3252144752903074</v>
+        <v>0.3169350360253851</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.6554163167515157</v>
+        <v>0.6621722941264074</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.5042588175578078</v>
+        <v>0.5027230892100826</v>
       </c>
       <c r="BD3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE3" t="n">
         <v>2822.766666666666</v>
@@ -1356,166 +1356,166 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8815775210709956</v>
+        <v>0.868370976803682</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9895742605736871</v>
+        <v>1.000256733485363</v>
       </c>
       <c r="E4" t="n">
-        <v>104.0052670909505</v>
+        <v>102.450107248127</v>
       </c>
       <c r="F4" t="n">
-        <v>110.4704387005334</v>
+        <v>111.7257585039723</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.465171609582924</v>
+        <v>-9.275651255845302</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3717084796757875</v>
+        <v>0.3693100330293841</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7145007106452325</v>
+        <v>0.7098444162299055</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5258505022518318</v>
+        <v>0.5213051583610924</v>
       </c>
       <c r="K4" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="L4" t="n">
-        <v>1157</v>
+        <v>1214</v>
       </c>
       <c r="M4" t="n">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="N4" t="n">
-        <v>636</v>
+        <v>679</v>
       </c>
       <c r="O4" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P4" t="n">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="Q4" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="R4" t="n">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="S4" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="T4" t="n">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="U4" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="V4" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="W4" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="X4" t="n">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="Y4" t="n">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="Z4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA4" t="n">
-        <v>1221</v>
+        <v>1315</v>
       </c>
       <c r="AB4" t="n">
-        <v>1317.76</v>
+        <v>1402.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>1112.76</v>
+        <v>1184.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="AF4" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AG4" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="AH4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AI4" t="n">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="AL4" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="AM4" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AO4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AP4" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AQ4" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="AR4" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>513.64</v>
+        <v>598.6800000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>440.64</v>
+        <v>512.6800000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.8565521787102405</v>
+        <v>0.8299408407222032</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.9895878345533277</v>
+        <v>1.014002976354351</v>
       </c>
       <c r="AX4" t="n">
-        <v>99.70799113972332</v>
+        <v>96.7672366348735</v>
       </c>
       <c r="AY4" t="n">
-        <v>111.9570818325775</v>
+        <v>114.6140066501458</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-12.24909069285422</v>
+        <v>-17.84677001527233</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.3420731009636137</v>
+        <v>0.3408245627307165</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.6993276174719608</v>
+        <v>0.6908522435473949</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.5085029121926712</v>
+        <v>0.5005917818794324</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
         <v>1800</v>
@@ -1860,88 +1860,88 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9111616026552879</v>
+        <v>0.9138223697903589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9441572715315162</v>
+        <v>0.9448939880933515</v>
       </c>
       <c r="E6" t="n">
-        <v>101.2175003278942</v>
+        <v>101.4156788975164</v>
       </c>
       <c r="F6" t="n">
-        <v>109.0308384929754</v>
+        <v>109.0020624119802</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.813338165081285</v>
+        <v>-7.586383514463833</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2688101357363925</v>
+        <v>0.2689500334860668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6132922937209954</v>
+        <v>0.6173630234907</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4377730705100569</v>
+        <v>0.4416188374723601</v>
       </c>
       <c r="K6" t="n">
-        <v>5450</v>
+        <v>5650</v>
       </c>
       <c r="L6" t="n">
-        <v>2066</v>
+        <v>2143</v>
       </c>
       <c r="M6" t="n">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="N6" t="n">
-        <v>959</v>
+        <v>993</v>
       </c>
       <c r="O6" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P6" t="n">
-        <v>714</v>
+        <v>731</v>
       </c>
       <c r="Q6" t="n">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="R6" t="n">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="S6" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="T6" t="n">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="U6" t="n">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="V6" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="W6" t="n">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="X6" t="n">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="Y6" t="n">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="Z6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA6" t="n">
-        <v>2231</v>
+        <v>2311</v>
       </c>
       <c r="AB6" t="n">
-        <v>2271.84</v>
+        <v>2349.96</v>
       </c>
       <c r="AC6" t="n">
-        <v>2043.84</v>
+        <v>2115.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>2800</v>
@@ -2022,82 +2022,82 @@
         <v>14</v>
       </c>
       <c r="BE6" t="n">
-        <v>2650</v>
+        <v>2850</v>
       </c>
       <c r="BF6" t="n">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="BG6" t="n">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="BH6" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="BI6" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="BJ6" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BK6" t="n">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="BL6" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="BM6" t="n">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="BN6" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="BO6" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="BP6" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="BQ6" t="n">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="BR6" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="BS6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="BT6" t="n">
-        <v>1106.76</v>
+        <v>1184.88</v>
       </c>
       <c r="BU6" t="n">
-        <v>984.76</v>
+        <v>1056.88</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9408800244498543</v>
+        <v>0.9440788143060986</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.9545801454105993</v>
+        <v>0.9553090875429069</v>
       </c>
       <c r="BX6" t="n">
-        <v>105.5925021114766</v>
+        <v>105.6763591233223</v>
       </c>
       <c r="BY6" t="n">
-        <v>110.1405205352798</v>
+        <v>110.0037053702676</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-4.548018423803206</v>
+        <v>-4.32734624694531</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.2794604384782243</v>
+        <v>0.278979498067442</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.6070054570739155</v>
+        <v>0.6155959763738306</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.4387577688261045</v>
+        <v>0.4463789671567074</v>
       </c>
       <c r="CD6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -2112,88 +2112,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9519589359236779</v>
+        <v>0.9491909583804049</v>
       </c>
       <c r="D7" t="n">
-        <v>0.949815132141226</v>
+        <v>0.9456440257430797</v>
       </c>
       <c r="E7" t="n">
-        <v>104.7052809981214</v>
+        <v>104.4958678185348</v>
       </c>
       <c r="F7" t="n">
-        <v>106.7354270650476</v>
+        <v>106.4001024097297</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.030146066926122</v>
+        <v>-1.904234591194808</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2456498428867715</v>
+        <v>0.246253568812636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7251584529354757</v>
+        <v>0.7231414947882754</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4961123059389704</v>
+        <v>0.4951267942697807</v>
       </c>
       <c r="K7" t="n">
-        <v>5625</v>
+        <v>5825</v>
       </c>
       <c r="L7" t="n">
-        <v>2221</v>
+        <v>2296</v>
       </c>
       <c r="M7" t="n">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="N7" t="n">
-        <v>992</v>
+        <v>1030</v>
       </c>
       <c r="O7" t="n">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="P7" t="n">
-        <v>701</v>
+        <v>730</v>
       </c>
       <c r="Q7" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="R7" t="n">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="S7" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="T7" t="n">
-        <v>696</v>
+        <v>722</v>
       </c>
       <c r="U7" t="n">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="V7" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="W7" t="n">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="X7" t="n">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="Y7" t="n">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="Z7" t="n">
         <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>2276</v>
+        <v>2350</v>
       </c>
       <c r="AB7" t="n">
-        <v>2337.56</v>
+        <v>2423.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>2125.56</v>
+        <v>2201.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE7" t="n">
         <v>3025</v>
@@ -2274,82 +2274,82 @@
         <v>15</v>
       </c>
       <c r="BE7" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="BF7" t="n">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="BG7" t="n">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="BH7" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="BI7" t="n">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="BJ7" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="BK7" t="n">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="BL7" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="BM7" t="n">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="BN7" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="BO7" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="BP7" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="BQ7" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="BR7" t="n">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="BS7" t="n">
         <v>25</v>
       </c>
       <c r="BT7" t="n">
-        <v>1066.08</v>
+        <v>1152.12</v>
       </c>
       <c r="BU7" t="n">
-        <v>973.08</v>
+        <v>1049.12</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.9837612667706981</v>
+        <v>0.9757560039419882</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.909111672936974</v>
+        <v>0.903378913912546</v>
       </c>
       <c r="BX7" t="n">
-        <v>107.8938210427157</v>
+        <v>107.2322837389581</v>
       </c>
       <c r="BY7" t="n">
-        <v>101.1762221780107</v>
+        <v>100.8787071696405</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.717598864704957</v>
+        <v>6.353576569317601</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.2371471459199654</v>
+        <v>0.2390050565497423</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7517795054775083</v>
+        <v>0.7457000169910195</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5101476850106981</v>
+        <v>0.5071037409051101</v>
       </c>
       <c r="CD7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -2364,88 +2364,88 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9455085669412943</v>
+        <v>0.9444976812638279</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9922283956810483</v>
+        <v>0.9910680182537021</v>
       </c>
       <c r="E8" t="n">
-        <v>103.3708051837332</v>
+        <v>103.315282874219</v>
       </c>
       <c r="F8" t="n">
-        <v>111.6076737219649</v>
+        <v>111.5036729523916</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.23686853823169</v>
+        <v>-8.188390078172585</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2397841231850364</v>
+        <v>0.2389424122218643</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7103322260665734</v>
+        <v>0.7104734220743999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.482202444503248</v>
+        <v>0.4813499762471797</v>
       </c>
       <c r="K8" t="n">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="L8" t="n">
-        <v>2103</v>
+        <v>2177</v>
       </c>
       <c r="M8" t="n">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="N8" t="n">
-        <v>882</v>
+        <v>905</v>
       </c>
       <c r="O8" t="n">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="P8" t="n">
-        <v>700</v>
+        <v>739</v>
       </c>
       <c r="Q8" t="n">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="R8" t="n">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="S8" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="T8" t="n">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="U8" t="n">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="V8" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="W8" t="n">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="X8" t="n">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="Y8" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="Z8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
-        <v>2256</v>
+        <v>2338</v>
       </c>
       <c r="AB8" t="n">
-        <v>2230.48</v>
+        <v>2311.16</v>
       </c>
       <c r="AC8" t="n">
-        <v>2038.48</v>
+        <v>2111.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
         <v>2800</v>
@@ -2526,82 +2526,82 @@
         <v>14</v>
       </c>
       <c r="BE8" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="BF8" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="BG8" t="n">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="BH8" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="BI8" t="n">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="BJ8" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="BK8" t="n">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="BL8" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="BM8" t="n">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="BN8" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="BO8" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="BP8" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="BQ8" t="n">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="BR8" t="n">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="BS8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BT8" t="n">
-        <v>1056.04</v>
+        <v>1136.72</v>
       </c>
       <c r="BU8" t="n">
-        <v>961.04</v>
+        <v>1033.72</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9673826968503583</v>
+        <v>0.9637984876447782</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9821163684746815</v>
+        <v>0.9805179012775869</v>
       </c>
       <c r="BX8" t="n">
-        <v>106.1090983804054</v>
+        <v>105.8024613901862</v>
       </c>
       <c r="BY8" t="n">
-        <v>110.8059199295949</v>
+        <v>110.6551865184748</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-4.69682154918951</v>
+        <v>-4.852725128288601</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2360691571080565</v>
+        <v>0.2346510899014965</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.6982654467103913</v>
+        <v>0.6994097515372</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.4713997101160227</v>
+        <v>0.4704663974886877</v>
       </c>
       <c r="CD8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2616,166 +2616,166 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8832711557463706</v>
+        <v>0.8861823764433897</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9910471164260928</v>
+        <v>0.9908548294979208</v>
       </c>
       <c r="E9" t="n">
-        <v>97.40883213953286</v>
+        <v>97.7951277140177</v>
       </c>
       <c r="F9" t="n">
-        <v>112.1467761069504</v>
+        <v>111.9546233987492</v>
       </c>
       <c r="G9" t="n">
-        <v>-14.73794396741756</v>
+        <v>-14.15949568473148</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2403520886613681</v>
+        <v>0.2415083452351504</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6921257894634965</v>
+        <v>0.6933810372423975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4617989649162559</v>
+        <v>0.4615399109744415</v>
       </c>
       <c r="K9" t="n">
-        <v>5450</v>
+        <v>5650</v>
       </c>
       <c r="L9" t="n">
-        <v>1989</v>
+        <v>2069</v>
       </c>
       <c r="M9" t="n">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="N9" t="n">
-        <v>936</v>
+        <v>962</v>
       </c>
       <c r="O9" t="n">
+        <v>234</v>
+      </c>
+      <c r="P9" t="n">
+        <v>760</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>375</v>
+      </c>
+      <c r="R9" t="n">
+        <v>536</v>
+      </c>
+      <c r="S9" t="n">
         <v>218</v>
       </c>
-      <c r="P9" t="n">
-        <v>727</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>365</v>
-      </c>
-      <c r="R9" t="n">
-        <v>518</v>
-      </c>
-      <c r="S9" t="n">
-        <v>209</v>
-      </c>
       <c r="T9" t="n">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="U9" t="n">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="V9" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="W9" t="n">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="X9" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="Y9" t="n">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="Z9" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2291</v>
+        <v>2368</v>
       </c>
       <c r="AB9" t="n">
-        <v>2252.92</v>
+        <v>2335.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>2043.92</v>
+        <v>2117.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AF9" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="AG9" t="n">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="AH9" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AI9" t="n">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="AJ9" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AK9" t="n">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="AL9" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AM9" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="AN9" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="AO9" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="AQ9" t="n">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="AR9" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>1063.84</v>
+        <v>1146.76</v>
       </c>
       <c r="AU9" t="n">
-        <v>976.84</v>
+        <v>1050.76</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.880725266834</v>
+        <v>0.8867295574360645</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.041466393905793</v>
+        <v>1.037480443086613</v>
       </c>
       <c r="AX9" t="n">
-        <v>95.8159679034119</v>
+        <v>96.70233506924737</v>
       </c>
       <c r="AY9" t="n">
-        <v>118.006782922973</v>
+        <v>117.2039055911403</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-22.19081501956105</v>
+        <v>-20.50157052189293</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2073124914301385</v>
+        <v>0.2119849758085052</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6945777878035942</v>
+        <v>0.696913140622818</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4440137605611068</v>
+        <v>0.4447660244171316</v>
       </c>
       <c r="BD9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE9" t="n">
         <v>2850</v>
@@ -3120,88 +3120,88 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9921104963999936</v>
+        <v>0.9836610317031899</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9548441840700294</v>
+        <v>0.9532101385350609</v>
       </c>
       <c r="E11" t="n">
-        <v>112.2441574333956</v>
+        <v>111.3158406440831</v>
       </c>
       <c r="F11" t="n">
-        <v>107.2425285741542</v>
+        <v>106.9253188299953</v>
       </c>
       <c r="G11" t="n">
-        <v>5.001628859241404</v>
+        <v>4.390521814087848</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3124848398706469</v>
+        <v>0.3136014527324095</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7042415744766607</v>
+        <v>0.7071513141637187</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5062589208340909</v>
+        <v>0.5078211022328734</v>
       </c>
       <c r="K11" t="n">
-        <v>5425</v>
+        <v>5625</v>
       </c>
       <c r="L11" t="n">
-        <v>2194</v>
+        <v>2261</v>
       </c>
       <c r="M11" t="n">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="N11" t="n">
-        <v>871</v>
+        <v>899</v>
       </c>
       <c r="O11" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="P11" t="n">
-        <v>816</v>
+        <v>852</v>
       </c>
       <c r="Q11" t="n">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="R11" t="n">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="S11" t="n">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="T11" t="n">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="U11" t="n">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="V11" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="W11" t="n">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="X11" t="n">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="Y11" t="n">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="Z11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA11" t="n">
-        <v>2077</v>
+        <v>2149</v>
       </c>
       <c r="AB11" t="n">
-        <v>2223.72</v>
+        <v>2312.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1957.72</v>
+        <v>2035.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE11" t="n">
         <v>2825</v>
@@ -3282,82 +3282,82 @@
         <v>14</v>
       </c>
       <c r="BE11" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="BF11" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="BG11" t="n">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="BH11" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="BI11" t="n">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="BJ11" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="BK11" t="n">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="BL11" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="BM11" t="n">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="BN11" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="BO11" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="BP11" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="BQ11" t="n">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="BR11" t="n">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="BS11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BT11" t="n">
-        <v>1074.44</v>
+        <v>1163.12</v>
       </c>
       <c r="BU11" t="n">
-        <v>934.4399999999999</v>
+        <v>1012.12</v>
       </c>
       <c r="BV11" t="n">
-        <v>1.013677946261001</v>
+        <v>0.9952384847344647</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9381394040940479</v>
+        <v>0.9360645115938236</v>
       </c>
       <c r="BX11" t="n">
-        <v>116.025365427898</v>
+        <v>113.8986455639514</v>
       </c>
       <c r="BY11" t="n">
-        <v>105.7503198825735</v>
+        <v>105.2224867293686</v>
       </c>
       <c r="BZ11" t="n">
-        <v>10.27504554532443</v>
+        <v>8.676158834582814</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3543023823524119</v>
+        <v>0.353548640755811</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.695468222155567</v>
+        <v>0.7019143695526184</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.5290337529448877</v>
+        <v>0.530531342020253</v>
       </c>
       <c r="CD11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -3372,166 +3372,166 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9925706404691326</v>
+        <v>0.9914384745121059</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9757770985766129</v>
+        <v>0.9737573285557724</v>
       </c>
       <c r="E12" t="n">
-        <v>110.5505626257644</v>
+        <v>110.4866001963903</v>
       </c>
       <c r="F12" t="n">
-        <v>109.6230935061225</v>
+        <v>109.3538896099574</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9274691196419705</v>
+        <v>1.132710586432826</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2605912314551478</v>
+        <v>0.2614575436709801</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7108755066280439</v>
+        <v>0.7133895851506555</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4854003324687796</v>
+        <v>0.4873405508893964</v>
       </c>
       <c r="K12" t="n">
-        <v>5650</v>
+        <v>5850</v>
       </c>
       <c r="L12" t="n">
-        <v>2314</v>
+        <v>2396</v>
       </c>
       <c r="M12" t="n">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="N12" t="n">
-        <v>990</v>
+        <v>1026</v>
       </c>
       <c r="O12" t="n">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="P12" t="n">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="Q12" t="n">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="R12" t="n">
-        <v>630</v>
+        <v>656</v>
       </c>
       <c r="S12" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="T12" t="n">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="U12" t="n">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="V12" t="n">
+        <v>166</v>
+      </c>
+      <c r="W12" t="n">
+        <v>323</v>
+      </c>
+      <c r="X12" t="n">
+        <v>616</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>610</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2371</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2417.64</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2165.64</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>246</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>518</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>131</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>359</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>307</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>133</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>342</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>173</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP12" t="n">
         <v>161</v>
       </c>
-      <c r="W12" t="n">
-        <v>310</v>
-      </c>
-      <c r="X12" t="n">
-        <v>595</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>587</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2297</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2332.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2090.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2650</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>228</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>482</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>122</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>334</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>221</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>281</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>123</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>313</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>157</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>61</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>148</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="AR12" t="n">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="AS12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT12" t="n">
-        <v>1087.64</v>
+        <v>1173.08</v>
       </c>
       <c r="AU12" t="n">
-        <v>964.64</v>
+        <v>1040.08</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.9597685851356376</v>
+        <v>0.9597663881770461</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.9603150188733838</v>
+        <v>0.957235643809016</v>
       </c>
       <c r="AX12" t="n">
-        <v>108.1294250472061</v>
+        <v>108.1698698419709</v>
       </c>
       <c r="AY12" t="n">
-        <v>108.6966867862862</v>
+        <v>108.2052220527898</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.5672617390801378</v>
+        <v>-0.03535221081892916</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2726914443517993</v>
+        <v>0.2736216473062626</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.7089396640962401</v>
+        <v>0.7142856726453504</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4892854585924872</v>
+        <v>0.4930269734549286</v>
       </c>
       <c r="BD12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE12" t="n">
         <v>3000</v>
@@ -3624,88 +3624,88 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9422541345137335</v>
+        <v>0.9385344520435112</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8981760470580207</v>
+        <v>0.8936164507150456</v>
       </c>
       <c r="E13" t="n">
-        <v>108.4090269385123</v>
+        <v>108.2518516088064</v>
       </c>
       <c r="F13" t="n">
-        <v>101.296168408491</v>
+        <v>100.5672342846793</v>
       </c>
       <c r="G13" t="n">
-        <v>7.112858530021297</v>
+        <v>7.68461732412717</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3490933227272767</v>
+        <v>0.3549654723982138</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7185780419109262</v>
+        <v>0.7248694276321526</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5397349258878932</v>
+        <v>0.5456967737728494</v>
       </c>
       <c r="K13" t="n">
-        <v>5425</v>
+        <v>5625</v>
       </c>
       <c r="L13" t="n">
-        <v>2132</v>
+        <v>2214</v>
       </c>
       <c r="M13" t="n">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="N13" t="n">
-        <v>979</v>
+        <v>1013</v>
       </c>
       <c r="O13" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="P13" t="n">
-        <v>725</v>
+        <v>755</v>
       </c>
       <c r="Q13" t="n">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="R13" t="n">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="S13" t="n">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="T13" t="n">
-        <v>649</v>
+        <v>683</v>
       </c>
       <c r="U13" t="n">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="V13" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="W13" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="X13" t="n">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="Y13" t="n">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="Z13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AA13" t="n">
-        <v>2015</v>
+        <v>2080</v>
       </c>
       <c r="AB13" t="n">
-        <v>2266.36</v>
+        <v>2364.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1966.36</v>
+        <v>2045.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>2600</v>
@@ -3786,82 +3786,82 @@
         <v>13</v>
       </c>
       <c r="BE13" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="BF13" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="BG13" t="n">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="BH13" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="BI13" t="n">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="BJ13" t="n">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="BK13" t="n">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="BL13" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="BM13" t="n">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="BN13" t="n">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="BO13" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="BP13" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="BQ13" t="n">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="BR13" t="n">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="BS13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BT13" t="n">
-        <v>1174.24</v>
+        <v>1272.08</v>
       </c>
       <c r="BU13" t="n">
-        <v>1007.24</v>
+        <v>1086.08</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.9359851073303577</v>
+        <v>0.9294596351981675</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.9142549427108421</v>
+        <v>0.9046717698271004</v>
       </c>
       <c r="BX13" t="n">
-        <v>108.8581418326151</v>
+        <v>108.5348068908906</v>
       </c>
       <c r="BY13" t="n">
-        <v>101.3012512564056</v>
+        <v>99.94023536876274</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7.556890576209494</v>
+        <v>8.594571522127913</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.3485246990723411</v>
+        <v>0.3595239533684192</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.7393733163335593</v>
+        <v>0.7497308847183396</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5339804660701418</v>
+        <v>0.5454928794432434</v>
       </c>
       <c r="CD13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -3876,166 +3876,166 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.026720368572058</v>
+        <v>1.0198973574694</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9281116179551975</v>
+        <v>0.9261659617211823</v>
       </c>
       <c r="E14" t="n">
-        <v>117.7050245941314</v>
+        <v>116.9914379550519</v>
       </c>
       <c r="F14" t="n">
-        <v>103.6190747989198</v>
+        <v>103.4471170055126</v>
       </c>
       <c r="G14" t="n">
-        <v>14.08594979521154</v>
+        <v>13.54432094953935</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3507017541979268</v>
+        <v>0.3501028431336305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7332833055184487</v>
+        <v>0.7334060227510248</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5442800091287897</v>
+        <v>0.543872682347367</v>
       </c>
       <c r="K14" t="n">
-        <v>5600</v>
+        <v>5800</v>
       </c>
       <c r="L14" t="n">
-        <v>2555</v>
+        <v>2629</v>
       </c>
       <c r="M14" t="n">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="N14" t="n">
-        <v>1105</v>
+        <v>1137</v>
       </c>
       <c r="O14" t="n">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="P14" t="n">
-        <v>791</v>
+        <v>830</v>
       </c>
       <c r="Q14" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="R14" t="n">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="S14" t="n">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="T14" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="U14" t="n">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="V14" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="W14" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="X14" t="n">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="Y14" t="n">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="Z14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AA14" t="n">
-        <v>2198</v>
+        <v>2273</v>
       </c>
       <c r="AB14" t="n">
-        <v>2493.56</v>
+        <v>2582.84</v>
       </c>
       <c r="AC14" t="n">
-        <v>2171.56</v>
+        <v>2247.84</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AF14" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="AG14" t="n">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="AH14" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="AI14" t="n">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="AK14" t="n">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="AL14" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="n">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="AN14" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="AO14" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="AP14" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="AQ14" t="n">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="AR14" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="AS14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>1239.68</v>
+        <v>1328.96</v>
       </c>
       <c r="AU14" t="n">
-        <v>1077.68</v>
+        <v>1153.96</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.019654844243572</v>
+        <v>1.006934724400332</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.9171200222139769</v>
+        <v>0.9140911932109624</v>
       </c>
       <c r="AX14" t="n">
-        <v>117.1011809659024</v>
+        <v>115.7618363722308</v>
       </c>
       <c r="AY14" t="n">
-        <v>104.2973947709277</v>
+        <v>103.9197217055399</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.80378619497469</v>
+        <v>11.84211466669091</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3591528604244217</v>
+        <v>0.3574315586183491</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6792622809044958</v>
+        <v>0.6831009358617399</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5206492031213887</v>
+        <v>0.521437091744465</v>
       </c>
       <c r="BD14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE14" t="n">
         <v>2800</v>
@@ -4128,88 +4128,88 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8739823776265447</v>
+        <v>0.876407427266135</v>
       </c>
       <c r="D15" t="n">
-        <v>0.979909289995743</v>
+        <v>0.9765406124679751</v>
       </c>
       <c r="E15" t="n">
-        <v>98.9585051075961</v>
+        <v>99.20483906289108</v>
       </c>
       <c r="F15" t="n">
-        <v>110.9175154931327</v>
+        <v>110.4379583268206</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.95901038553655</v>
+        <v>-11.23311926392955</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2872044134435567</v>
+        <v>0.2858756843920011</v>
       </c>
       <c r="I15" t="n">
-        <v>0.698426830510033</v>
+        <v>0.701722217792482</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4895164299825243</v>
+        <v>0.4905066067442321</v>
       </c>
       <c r="K15" t="n">
-        <v>5400</v>
+        <v>5625</v>
       </c>
       <c r="L15" t="n">
-        <v>2041</v>
+        <v>2135</v>
       </c>
       <c r="M15" t="n">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="N15" t="n">
-        <v>944</v>
+        <v>974</v>
       </c>
       <c r="O15" t="n">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="P15" t="n">
-        <v>790</v>
+        <v>839</v>
       </c>
       <c r="Q15" t="n">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="R15" t="n">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="S15" t="n">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="T15" t="n">
-        <v>641</v>
+        <v>675</v>
       </c>
       <c r="U15" t="n">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="V15" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="W15" t="n">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="X15" t="n">
-        <v>561</v>
+        <v>583</v>
       </c>
       <c r="Y15" t="n">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="Z15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2305</v>
+        <v>2392</v>
       </c>
       <c r="AB15" t="n">
-        <v>2342.12</v>
+        <v>2441.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>2065.12</v>
+        <v>2153.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE15" t="n">
         <v>2800</v>
@@ -4290,82 +4290,82 @@
         <v>14</v>
       </c>
       <c r="BE15" t="n">
-        <v>2600</v>
+        <v>2825</v>
       </c>
       <c r="BF15" t="n">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="BG15" t="n">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="BH15" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="BI15" t="n">
-        <v>370</v>
+        <v>419</v>
       </c>
       <c r="BJ15" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BK15" t="n">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="BL15" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="BM15" t="n">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="BN15" t="n">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="BO15" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="BP15" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="BQ15" t="n">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="BR15" t="n">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="BS15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BT15" t="n">
-        <v>1105.84</v>
+        <v>1205.64</v>
       </c>
       <c r="BU15" t="n">
-        <v>977.84</v>
+        <v>1066.64</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.9086883491675444</v>
+        <v>0.9110594504795105</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9562925546387006</v>
+        <v>0.9512421092515249</v>
       </c>
       <c r="BX15" t="n">
-        <v>102.5964092234174</v>
+        <v>102.8292268400201</v>
       </c>
       <c r="BY15" t="n">
-        <v>107.6391945078743</v>
+        <v>106.9142459599116</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-5.042785284456899</v>
+        <v>-4.085019119891433</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2780920433526182</v>
+        <v>0.2760854688274312</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.7095984735802972</v>
+        <v>0.7153912736401763</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.496096348668224</v>
+        <v>0.4976067079998041</v>
       </c>
       <c r="CD15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -4380,88 +4380,88 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.066320734491772</v>
+        <v>1.06968405922994</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8865698457689081</v>
+        <v>0.8788449517340892</v>
       </c>
       <c r="E16" t="n">
-        <v>119.9038869922654</v>
+        <v>120.2843037266686</v>
       </c>
       <c r="F16" t="n">
-        <v>99.83719295936778</v>
+        <v>99.09738998245373</v>
       </c>
       <c r="G16" t="n">
-        <v>20.06669403289761</v>
+        <v>21.18691374421487</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3233837115954228</v>
+        <v>0.3246914361813006</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7012942234775651</v>
+        <v>0.700057525020033</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5202345665074829</v>
+        <v>0.5211860105607871</v>
       </c>
       <c r="K16" t="n">
-        <v>5450</v>
+        <v>5650</v>
       </c>
       <c r="L16" t="n">
-        <v>2486</v>
+        <v>2580</v>
       </c>
       <c r="M16" t="n">
-        <v>595</v>
+        <v>622</v>
       </c>
       <c r="N16" t="n">
-        <v>1021</v>
+        <v>1062</v>
       </c>
       <c r="O16" t="n">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="P16" t="n">
-        <v>721</v>
+        <v>740</v>
       </c>
       <c r="Q16" t="n">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="R16" t="n">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="S16" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="T16" t="n">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="U16" t="n">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="V16" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="W16" t="n">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="X16" t="n">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="Y16" t="n">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="Z16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA16" t="n">
-        <v>2052</v>
+        <v>2109</v>
       </c>
       <c r="AB16" t="n">
-        <v>2331.28</v>
+        <v>2412.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>2075.28</v>
+        <v>2147.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
         <v>2825</v>
@@ -4542,82 +4542,82 @@
         <v>14</v>
       </c>
       <c r="BE16" t="n">
-        <v>2625</v>
+        <v>2825</v>
       </c>
       <c r="BF16" t="n">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="BG16" t="n">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="BH16" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="BI16" t="n">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="BJ16" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="BK16" t="n">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="BL16" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="BM16" t="n">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="BN16" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="BO16" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="BP16" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="BQ16" t="n">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="BR16" t="n">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="BS16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BT16" t="n">
-        <v>1141.6</v>
+        <v>1222.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>1008.6</v>
+        <v>1080.6</v>
       </c>
       <c r="BV16" t="n">
-        <v>1.053400244981743</v>
+        <v>1.061049786565939</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8545449139691456</v>
+        <v>0.8413826210280622</v>
       </c>
       <c r="BX16" t="n">
-        <v>119.3819681499499</v>
+        <v>120.1800815360646</v>
       </c>
       <c r="BY16" t="n">
-        <v>94.64051716434697</v>
+        <v>93.53210233873467</v>
       </c>
       <c r="BZ16" t="n">
-        <v>24.7414509856029</v>
+        <v>26.64797919732991</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.3330564240004531</v>
+        <v>0.3349809651432779</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.7424556830045079</v>
+        <v>0.7370421818375192</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.5438960019074555</v>
+        <v>0.5441087874854944</v>
       </c>
       <c r="CD16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -4632,88 +4632,88 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.027327099601123</v>
+        <v>1.02182654595744</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9680843155609898</v>
+        <v>0.9619789805518471</v>
       </c>
       <c r="E17" t="n">
-        <v>115.1436809734568</v>
+        <v>114.56141644287</v>
       </c>
       <c r="F17" t="n">
-        <v>108.747229770015</v>
+        <v>108.0821641299977</v>
       </c>
       <c r="G17" t="n">
-        <v>6.396451203441813</v>
+        <v>6.47925231287236</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3013040587341609</v>
+        <v>0.3042794632299189</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7112297333762169</v>
+        <v>0.7113388755515561</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5129668115249663</v>
+        <v>0.515138371534906</v>
       </c>
       <c r="K17" t="n">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="L17" t="n">
-        <v>2299</v>
+        <v>2374</v>
       </c>
       <c r="M17" t="n">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="N17" t="n">
-        <v>872</v>
+        <v>909</v>
       </c>
       <c r="O17" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P17" t="n">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="Q17" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="R17" t="n">
-        <v>609</v>
+        <v>636</v>
       </c>
       <c r="S17" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T17" t="n">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="U17" t="n">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="V17" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="W17" t="n">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="X17" t="n">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="Y17" t="n">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="Z17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AA17" t="n">
-        <v>2183</v>
+        <v>2252</v>
       </c>
       <c r="AB17" t="n">
-        <v>2236.96</v>
+        <v>2322.84</v>
       </c>
       <c r="AC17" t="n">
-        <v>1997.96</v>
+        <v>2073.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>2800</v>
@@ -4794,82 +4794,82 @@
         <v>14</v>
       </c>
       <c r="BE17" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="BF17" t="n">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="BG17" t="n">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="BH17" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="BI17" t="n">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="BJ17" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="BK17" t="n">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="BL17" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="BM17" t="n">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="BN17" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="BO17" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="BP17" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="BQ17" t="n">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="BR17" t="n">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="BS17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="BT17" t="n">
-        <v>1086.96</v>
+        <v>1172.84</v>
       </c>
       <c r="BU17" t="n">
-        <v>962.96</v>
+        <v>1038.84</v>
       </c>
       <c r="BV17" t="n">
-        <v>1.053763594529146</v>
+        <v>1.040874166175494</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.9664037890557728</v>
+        <v>0.9543131566450027</v>
       </c>
       <c r="BX17" t="n">
-        <v>119.1675778662853</v>
+        <v>117.7156275984811</v>
       </c>
       <c r="BY17" t="n">
-        <v>108.7003273660462</v>
+        <v>107.3735462577236</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.46725050023908</v>
+        <v>10.34208134075751</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.3207328772030869</v>
+        <v>0.3252959134468224</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.7025742374355443</v>
+        <v>0.7034107714962706</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.515474118657443</v>
+        <v>0.5196381453107169</v>
       </c>
       <c r="CD17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -4884,166 +4884,166 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8696256375531357</v>
+        <v>0.866085698692478</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9649995485404105</v>
+        <v>0.9604675298549497</v>
       </c>
       <c r="E18" t="n">
-        <v>98.1283370895403</v>
+        <v>97.51253979854822</v>
       </c>
       <c r="F18" t="n">
-        <v>110.5218918796121</v>
+        <v>110.2892570877241</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.39355479007186</v>
+        <v>-12.77671728917592</v>
       </c>
       <c r="H18" t="n">
-        <v>0.278156610787707</v>
+        <v>0.2719818446129581</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6497891332036879</v>
+        <v>0.6439568958209307</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4539133785523674</v>
+        <v>0.4481783769374018</v>
       </c>
       <c r="K18" t="n">
-        <v>5425</v>
+        <v>5625</v>
       </c>
       <c r="L18" t="n">
-        <v>1971</v>
+        <v>2036</v>
       </c>
       <c r="M18" t="n">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="N18" t="n">
-        <v>933</v>
+        <v>978</v>
       </c>
       <c r="O18" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P18" t="n">
-        <v>738</v>
+        <v>755</v>
       </c>
       <c r="Q18" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="R18" t="n">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="S18" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="T18" t="n">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="U18" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="V18" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="W18" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="X18" t="n">
-        <v>540</v>
+        <v>567</v>
       </c>
       <c r="Y18" t="n">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="Z18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2338</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2358.24</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2094.24</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2800</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>224</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>475</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>119</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>381</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>216</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>302</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>117</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>279</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>169</v>
+      </c>
+      <c r="AO18" t="n">
         <v>88</v>
       </c>
-      <c r="AA18" t="n">
-        <v>2256</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2273.88</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2013.88</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>202</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>430</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>116</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>364</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>204</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>283</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>113</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>261</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>163</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>79</v>
-      </c>
       <c r="AP18" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="AQ18" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AR18" t="n">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="AS18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AT18" t="n">
-        <v>1070.52</v>
+        <v>1154.88</v>
       </c>
       <c r="AU18" t="n">
-        <v>957.52</v>
+        <v>1037.88</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.8972871912063265</v>
+        <v>0.8882314882240687</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.014775345764666</v>
+        <v>1.002155894306297</v>
       </c>
       <c r="AX18" t="n">
-        <v>100.3118107378594</v>
+        <v>98.92425375242389</v>
       </c>
       <c r="AY18" t="n">
-        <v>116.0086531193324</v>
+        <v>115.1514720184335</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-15.69684238147296</v>
+        <v>-16.22721826600959</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.2559289690705702</v>
+        <v>0.2451671254151535</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.6495080216317992</v>
+        <v>0.6378636262642768</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.4386711068771499</v>
+        <v>0.4282898373383058</v>
       </c>
       <c r="BD18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE18" t="n">
         <v>2825</v>
@@ -5136,166 +5136,166 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9779892491425078</v>
+        <v>0.9755285941406651</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8737500264904272</v>
+        <v>0.8695277214332509</v>
       </c>
       <c r="E19" t="n">
-        <v>111.3855983541495</v>
+        <v>110.9204218321336</v>
       </c>
       <c r="F19" t="n">
-        <v>98.44802722025337</v>
+        <v>98.01242936712457</v>
       </c>
       <c r="G19" t="n">
-        <v>12.93757113389612</v>
+        <v>12.90799246500904</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3230671505308827</v>
+        <v>0.3191820992364124</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7130498573383734</v>
+        <v>0.7110212910048601</v>
       </c>
       <c r="J19" t="n">
-        <v>0.523726374101411</v>
+        <v>0.5210932893120749</v>
       </c>
       <c r="K19" t="n">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="L19" t="n">
-        <v>2236</v>
+        <v>2308</v>
       </c>
       <c r="M19" t="n">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="N19" t="n">
-        <v>1030</v>
+        <v>1054</v>
       </c>
       <c r="O19" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="P19" t="n">
-        <v>743</v>
+        <v>771</v>
       </c>
       <c r="Q19" t="n">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="R19" t="n">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="S19" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="T19" t="n">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="U19" t="n">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="V19" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="W19" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="X19" t="n">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="Y19" t="n">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>1955</v>
+        <v>2022</v>
       </c>
       <c r="AB19" t="n">
-        <v>2292.08</v>
+        <v>2371.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>2007.08</v>
+        <v>2080.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AF19" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="AG19" t="n">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="AH19" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="AI19" t="n">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="AJ19" t="n">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="AK19" t="n">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="AL19" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AM19" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="AN19" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="AO19" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AP19" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="AQ19" t="n">
+        <v>308</v>
+      </c>
+      <c r="AR19" t="n">
         <v>284</v>
       </c>
-      <c r="AR19" t="n">
-        <v>258</v>
-      </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT19" t="n">
-        <v>1105.32</v>
+        <v>1184.52</v>
       </c>
       <c r="AU19" t="n">
-        <v>966.3200000000001</v>
+        <v>1039.52</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.9643351548656856</v>
+        <v>0.9603891373103444</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.8750276196853359</v>
+        <v>0.8664917529142041</v>
       </c>
       <c r="AX19" t="n">
-        <v>110.190287457777</v>
+        <v>109.3453137634861</v>
       </c>
       <c r="AY19" t="n">
-        <v>97.58597137152154</v>
+        <v>96.77635108303049</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12.60431608625542</v>
+        <v>12.56896268045562</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.3122595573104623</v>
+        <v>0.3052614256658375</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.7377943586381863</v>
+        <v>0.7319697615926016</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.5250217409161783</v>
+        <v>0.5196630451364512</v>
       </c>
       <c r="BD19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE19" t="n">
         <v>2800</v>

--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,88 +852,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9382211469007501</v>
+        <v>0.9417834950806202</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9180905809674205</v>
+        <v>0.9183054859729876</v>
       </c>
       <c r="E2" t="n">
-        <v>106.5214655653528</v>
+        <v>107.1991803011638</v>
       </c>
       <c r="F2" t="n">
-        <v>101.3711110324959</v>
+        <v>101.3236065030316</v>
       </c>
       <c r="G2" t="n">
-        <v>5.150354532856938</v>
+        <v>5.875573798132121</v>
       </c>
       <c r="H2" t="n">
-        <v>0.308023000264709</v>
+        <v>0.3116444558114409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7481165963126565</v>
+        <v>0.7498460431022346</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5232923282123512</v>
+        <v>0.5255462203022425</v>
       </c>
       <c r="K2" t="n">
-        <v>5825</v>
+        <v>6025</v>
       </c>
       <c r="L2" t="n">
-        <v>2373</v>
+        <v>2462</v>
       </c>
       <c r="M2" t="n">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="N2" t="n">
-        <v>929</v>
+        <v>963</v>
       </c>
       <c r="O2" t="n">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="P2" t="n">
-        <v>944</v>
+        <v>980</v>
       </c>
       <c r="Q2" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="R2" t="n">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="S2" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="T2" t="n">
-        <v>690</v>
+        <v>714</v>
       </c>
       <c r="U2" t="n">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="V2" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="W2" t="n">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="Y2" t="n">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="Z2" t="n">
         <v>47</v>
       </c>
       <c r="AA2" t="n">
-        <v>2270</v>
+        <v>2344</v>
       </c>
       <c r="AB2" t="n">
-        <v>2535.92</v>
+        <v>2621.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2229.92</v>
+        <v>2300.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
         <v>3025</v>
@@ -1014,82 +1014,82 @@
         <v>15</v>
       </c>
       <c r="BE2" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="BF2" t="n">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="BG2" t="n">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="BH2" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="BI2" t="n">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="BJ2" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="BK2" t="n">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="BL2" t="n">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="BM2" t="n">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="BN2" t="n">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="BO2" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="BP2" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="BQ2" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="BR2" t="n">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="BS2" t="n">
         <v>25</v>
       </c>
       <c r="BT2" t="n">
-        <v>1198.16</v>
+        <v>1283.32</v>
       </c>
       <c r="BU2" t="n">
-        <v>1067.16</v>
+        <v>1137.32</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9557386360988619</v>
+        <v>0.9616954998453946</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9100569460666302</v>
+        <v>0.911022331737817</v>
       </c>
       <c r="BX2" t="n">
-        <v>107.1858620076165</v>
+        <v>108.4969983830874</v>
       </c>
       <c r="BY2" t="n">
-        <v>100.153641547364</v>
+        <v>100.1397971207776</v>
       </c>
       <c r="BZ2" t="n">
-        <v>7.032220460252481</v>
+        <v>8.357201262309808</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2853815130082458</v>
+        <v>0.2941338565854739</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7539287884212696</v>
+        <v>0.7570002025265183</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.5221924858415766</v>
+        <v>0.5267735928460776</v>
       </c>
       <c r="CD2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1104,244 +1104,244 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9417478490836568</v>
+        <v>0.9417795275667563</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9630565204183384</v>
+        <v>0.9613309241461596</v>
       </c>
       <c r="E3" t="n">
-        <v>106.2528620227581</v>
+        <v>106.4028455590689</v>
       </c>
       <c r="F3" t="n">
-        <v>110.6352929969687</v>
+        <v>110.0781112848323</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.382430974210579</v>
+        <v>-3.675265725763472</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3117903207002066</v>
+        <v>0.3123149288351568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6665233051145197</v>
+        <v>0.6729616994149491</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4949735292691835</v>
+        <v>0.4966832760609744</v>
       </c>
       <c r="K3" t="n">
-        <v>5647.766666666666</v>
+        <v>6047.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2347</v>
+        <v>2511</v>
       </c>
       <c r="M3" t="n">
-        <v>578</v>
+        <v>618</v>
       </c>
       <c r="N3" t="n">
-        <v>1161</v>
+        <v>1246</v>
       </c>
       <c r="O3" t="n">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="P3" t="n">
-        <v>629</v>
+        <v>679</v>
       </c>
       <c r="Q3" t="n">
-        <v>519</v>
+        <v>552</v>
       </c>
       <c r="R3" t="n">
-        <v>701</v>
+        <v>746</v>
       </c>
       <c r="S3" t="n">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="T3" t="n">
-        <v>657</v>
+        <v>704</v>
       </c>
       <c r="U3" t="n">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="V3" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="W3" t="n">
+        <v>414</v>
+      </c>
+      <c r="X3" t="n">
+        <v>644</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>661</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2582</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2667.24</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2359.24</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3025</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>307</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>616</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>124</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>324</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>265</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>352</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>145</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>366</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>181</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>332</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>317</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1312.88</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1167.88</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.953445729837021</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.9474743355164171</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>107.1923501722332</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>109.4022513727048</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-2.209901200471526</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.3168586652026402</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.6676001240906297</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.5047060520939126</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3022.766666666666</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>311</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>630</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>117</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>355</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>287</v>
+      </c>
+      <c r="BK3" t="n">
         <v>394</v>
       </c>
-      <c r="X3" t="n">
-        <v>604</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>615</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2429</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2492.44</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2207.44</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2825</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>288</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>571</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>302</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>249</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>333</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>133</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>337</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>166</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>83</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>202</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>311</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>297</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1221.52</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1088.52</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.96056575882588</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.9637867077964822</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>107.8284973043513</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>111.4300794544802</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.601582150128959</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.3169350360253851</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.6621722941264074</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.5027230892100826</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2822.766666666666</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>290</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>590</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>108</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>327</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>270</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>368</v>
-      </c>
       <c r="BL3" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="BM3" t="n">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="BN3" t="n">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="BO3" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="BP3" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BQ3" t="n">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="BR3" t="n">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="BS3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BT3" t="n">
-        <v>1270.92</v>
+        <v>1354.36</v>
       </c>
       <c r="BU3" t="n">
-        <v>1118.92</v>
+        <v>1191.36</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9229299393414335</v>
+        <v>0.9301133252964917</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.9623263330401947</v>
+        <v>0.975187512775902</v>
       </c>
       <c r="BX3" t="n">
-        <v>104.6772267411649</v>
+        <v>105.6133409459045</v>
       </c>
       <c r="BY3" t="n">
-        <v>109.8405065394571</v>
+        <v>110.7539711969599</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-5.1632797982922</v>
+        <v>-5.140630251055417</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.306645605375028</v>
+        <v>0.3077711924676732</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6708743161026323</v>
+        <v>0.6783232747392683</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.4872239693282844</v>
+        <v>0.4886605000280362</v>
       </c>
       <c r="CD3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1356,244 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.868370976803682</v>
+        <v>0.8788310360799748</v>
       </c>
       <c r="D4" t="n">
-        <v>1.000256733485363</v>
+        <v>1.002530348164475</v>
       </c>
       <c r="E4" t="n">
-        <v>102.450107248127</v>
+        <v>103.4948224967798</v>
       </c>
       <c r="F4" t="n">
-        <v>111.7257585039723</v>
+        <v>111.8109838625481</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.275651255845302</v>
+        <v>-8.3161613657683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3693100330293841</v>
+        <v>0.3674460918274505</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7098444162299055</v>
+        <v>0.7152022051075861</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5213051583610924</v>
+        <v>0.5243142626292148</v>
       </c>
       <c r="K4" t="n">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="L4" t="n">
-        <v>1214</v>
+        <v>1374</v>
       </c>
       <c r="M4" t="n">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="N4" t="n">
-        <v>679</v>
+        <v>749</v>
       </c>
       <c r="O4" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="P4" t="n">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c r="Q4" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="R4" t="n">
-        <v>345</v>
+        <v>401</v>
       </c>
       <c r="S4" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="T4" t="n">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="U4" t="n">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="V4" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="W4" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="X4" t="n">
-        <v>376</v>
+        <v>427</v>
       </c>
       <c r="Y4" t="n">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="Z4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AA4" t="n">
-        <v>1315</v>
+        <v>1481</v>
       </c>
       <c r="AB4" t="n">
-        <v>1402.8</v>
+        <v>1568.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>1184.8</v>
+        <v>1327.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="AF4" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="AG4" t="n">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="AH4" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AI4" t="n">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="AJ4" t="n">
+        <v>122</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>177</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>96</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>173</v>
+      </c>
+      <c r="AN4" t="n">
         <v>103</v>
       </c>
-      <c r="AK4" t="n">
-        <v>147</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>86</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>92</v>
-      </c>
       <c r="AO4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AP4" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AQ4" t="n">
+        <v>194</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>172</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>677.88</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>581.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8366780336117258</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.006689777084927</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>97.31584072603454</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>113.6278990937314</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-16.31205836769686</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.3339357781036627</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.6972376485878415</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.5005178091445034</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>201</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>420</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>83</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>248</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>158</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>224</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>145</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>208</v>
+      </c>
+      <c r="BN4" t="n">
         <v>167</v>
       </c>
-      <c r="AR4" t="n">
-        <v>144</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>598.6800000000001</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>512.6800000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8299408407222032</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.014002976354351</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>96.7672366348735</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>114.6140066501458</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-17.84677001527233</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.3408245627307165</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.6908522435473949</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.5005917818794324</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1800</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>179</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>384</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>73</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>223</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>142</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>198</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>132</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>184</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>147</v>
-      </c>
       <c r="BO4" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="BP4" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="BQ4" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="BR4" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="BS4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BT4" t="n">
-        <v>804.12</v>
+        <v>890.5599999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>672.12</v>
+        <v>745.5599999999999</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.8982610826448324</v>
+        <v>0.9125534380545739</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.9895652112539265</v>
+        <v>0.9992028050281135</v>
       </c>
       <c r="BX4" t="n">
-        <v>106.870117725102</v>
+        <v>108.4380079133761</v>
       </c>
       <c r="BY4" t="n">
-        <v>109.4793432791707</v>
+        <v>110.3574516776016</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-2.609225554068724</v>
+        <v>-1.919443764225453</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3914653988172367</v>
+        <v>0.3942543428064808</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7246161060940803</v>
+        <v>0.729573850323382</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5374155622912722</v>
+        <v>0.5433514254169837</v>
       </c>
       <c r="CD4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1860,244 +1860,244 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9138223697903589</v>
+        <v>0.9071298784240028</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9448939880933515</v>
+        <v>0.9516785996200355</v>
       </c>
       <c r="E6" t="n">
-        <v>101.4156788975164</v>
+        <v>100.8777662927575</v>
       </c>
       <c r="F6" t="n">
-        <v>109.0020624119802</v>
+        <v>109.6748375194346</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.586383514463833</v>
+        <v>-8.797071226677051</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2689500334860668</v>
+        <v>0.2689721296935657</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6173630234907</v>
+        <v>0.6228104268629249</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4416188374723601</v>
+        <v>0.4428661638919517</v>
       </c>
       <c r="K6" t="n">
-        <v>5650</v>
+        <v>6050</v>
       </c>
       <c r="L6" t="n">
-        <v>2143</v>
+        <v>2276</v>
       </c>
       <c r="M6" t="n">
-        <v>538</v>
+        <v>566</v>
       </c>
       <c r="N6" t="n">
-        <v>993</v>
+        <v>1069</v>
       </c>
       <c r="O6" t="n">
+        <v>248</v>
+      </c>
+      <c r="P6" t="n">
+        <v>784</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>400</v>
+      </c>
+      <c r="R6" t="n">
+        <v>594</v>
+      </c>
+      <c r="S6" t="n">
+        <v>255</v>
+      </c>
+      <c r="T6" t="n">
+        <v>577</v>
+      </c>
+      <c r="U6" t="n">
+        <v>461</v>
+      </c>
+      <c r="V6" t="n">
+        <v>251</v>
+      </c>
+      <c r="W6" t="n">
+        <v>399</v>
+      </c>
+      <c r="X6" t="n">
+        <v>651</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>609</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2476</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2513.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2258.36</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>268</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>492</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>405</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>303</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>117</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>296</v>
+      </c>
+      <c r="AN6" t="n">
         <v>229</v>
       </c>
-      <c r="P6" t="n">
-        <v>731</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>380</v>
-      </c>
-      <c r="R6" t="n">
-        <v>559</v>
-      </c>
-      <c r="S6" t="n">
-        <v>234</v>
-      </c>
-      <c r="T6" t="n">
-        <v>533</v>
-      </c>
-      <c r="U6" t="n">
-        <v>431</v>
-      </c>
-      <c r="V6" t="n">
-        <v>245</v>
-      </c>
-      <c r="W6" t="n">
-        <v>380</v>
-      </c>
-      <c r="X6" t="n">
-        <v>617</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>572</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2311</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2349.96</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2115.96</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2800</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>255</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>458</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>109</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>375</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>189</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>282</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>106</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>271</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>214</v>
-      </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP6" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="AQ6" t="n">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="AR6" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>1165.08</v>
+        <v>1248.32</v>
       </c>
       <c r="AU6" t="n">
-        <v>1059.08</v>
+        <v>1131.32</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.883565925274619</v>
+        <v>0.8807243205814752</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9344788886437961</v>
+        <v>0.946111507896537</v>
       </c>
       <c r="AX6" t="n">
-        <v>97.15499867171044</v>
+        <v>97.13794708067651</v>
       </c>
       <c r="AY6" t="n">
-        <v>108.0004194536928</v>
+        <v>109.3236451495537</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-10.84542078198236</v>
+        <v>-12.18569806887719</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2589205689046916</v>
+        <v>0.2595453765061675</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6191300706075695</v>
+        <v>0.6241510288633612</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4368587077880129</v>
+        <v>0.4389036251043099</v>
       </c>
       <c r="BD6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE6" t="n">
-        <v>2850</v>
+        <v>3050</v>
       </c>
       <c r="BF6" t="n">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="BG6" t="n">
-        <v>535</v>
+        <v>577</v>
       </c>
       <c r="BH6" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="BI6" t="n">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="BJ6" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="BK6" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="BL6" t="n">
+        <v>138</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>281</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>232</v>
+      </c>
+      <c r="BO6" t="n">
         <v>128</v>
       </c>
-      <c r="BM6" t="n">
-        <v>262</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>217</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>125</v>
-      </c>
       <c r="BP6" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="BQ6" t="n">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="BR6" t="n">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="BS6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BT6" t="n">
-        <v>1184.88</v>
+        <v>1265.04</v>
       </c>
       <c r="BU6" t="n">
-        <v>1056.88</v>
+        <v>1127.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9440788143060986</v>
+        <v>0.9335354362665306</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.9553090875429069</v>
+        <v>0.9572456913435343</v>
       </c>
       <c r="BX6" t="n">
-        <v>105.6763591233223</v>
+        <v>104.6175855048385</v>
       </c>
       <c r="BY6" t="n">
-        <v>110.0037053702676</v>
+        <v>110.0260298893155</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-4.32734624694531</v>
+        <v>-5.408444384476913</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.278979498067442</v>
+        <v>0.2783988828809639</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.6155959763738306</v>
+        <v>0.6214698248624888</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.4463789671567074</v>
+        <v>0.4468287026795936</v>
       </c>
       <c r="CD6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2112,244 +2112,244 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9491909583804049</v>
+        <v>0.95608432288256</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9456440257430797</v>
+        <v>0.9478528247441815</v>
       </c>
       <c r="E7" t="n">
-        <v>104.4958678185348</v>
+        <v>105.0765529384902</v>
       </c>
       <c r="F7" t="n">
-        <v>106.4001024097297</v>
+        <v>106.2644074972537</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.904234591194808</v>
+        <v>-1.187854558763518</v>
       </c>
       <c r="H7" t="n">
-        <v>0.246253568812636</v>
+        <v>0.2442252621030992</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7231414947882754</v>
+        <v>0.7315559380293846</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4951267942697807</v>
+        <v>0.4993951465574644</v>
       </c>
       <c r="K7" t="n">
-        <v>5825</v>
+        <v>6225</v>
       </c>
       <c r="L7" t="n">
-        <v>2296</v>
+        <v>2476</v>
       </c>
       <c r="M7" t="n">
-        <v>534</v>
+        <v>582</v>
       </c>
       <c r="N7" t="n">
-        <v>1030</v>
+        <v>1111</v>
       </c>
       <c r="O7" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="P7" t="n">
-        <v>730</v>
+        <v>776</v>
       </c>
       <c r="Q7" t="n">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="R7" t="n">
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="S7" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="T7" t="n">
-        <v>722</v>
+        <v>781</v>
       </c>
       <c r="U7" t="n">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="V7" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="W7" t="n">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="X7" t="n">
-        <v>567</v>
+        <v>600</v>
       </c>
       <c r="Y7" t="n">
-        <v>616</v>
+        <v>656</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA7" t="n">
-        <v>2350</v>
+        <v>2512</v>
       </c>
       <c r="AB7" t="n">
-        <v>2423.6</v>
+        <v>2594.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2201.6</v>
+        <v>2360.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AE7" t="n">
-        <v>3025</v>
+        <v>3225</v>
       </c>
       <c r="AF7" t="n">
+        <v>307</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>592</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>139</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>395</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>232</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>123</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>386</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>262</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>317</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>334</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1353.72</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1230.72</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9342595113389796</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.9843801116401869</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>102.6800469143322</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>111.0613583164649</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-8.381311402132738</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.2455385023252114</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.7106257992753169</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.484439246240039</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>275</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>519</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>143</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>381</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>234</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>342</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>111</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>395</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>260</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>108</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>190</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>283</v>
       </c>
-      <c r="AG7" t="n">
-        <v>548</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>132</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>375</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>212</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>317</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>119</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>360</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>242</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>209</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>299</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>313</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1271.48</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1152.48</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.9243969158562604</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.9850914634515775</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>101.9418796261397</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>111.5534046338128</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-9.611525007673057</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.25301884692467</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.7020868740657144</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.4839483107434733</v>
-      </c>
-      <c r="BD7" t="n">
+      <c r="BR7" t="n">
+        <v>322</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1240.48</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1129.48</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.9793641218623789</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.908890385388442</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>107.6328260309254</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>101.1476599567617</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>6.48516607416365</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.2428244725328459</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.7538814193670568</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.5153481068960516</v>
+      </c>
+      <c r="CD7" t="n">
         <v>15</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2800</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>251</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>482</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>133</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>355</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>221</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>323</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>103</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>362</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>241</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>102</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>173</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>268</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>303</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1152.12</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1049.12</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0.9757560039419882</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0.903378913912546</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>107.2322837389581</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>100.8787071696405</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>6.353576569317601</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.2390050565497423</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.7457000169910195</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>0.5071037409051101</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9444976812638279</v>
+        <v>0.9524962979644105</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9910680182537021</v>
+        <v>0.9954261227783577</v>
       </c>
       <c r="E8" t="n">
-        <v>103.315282874219</v>
+        <v>104.0017020145459</v>
       </c>
       <c r="F8" t="n">
-        <v>111.5036729523916</v>
+        <v>111.8191446238814</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.188390078172585</v>
+        <v>-7.817442609335465</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2389424122218643</v>
+        <v>0.2356356389713557</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7104734220743999</v>
+        <v>0.7145464357661719</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4813499762471797</v>
+        <v>0.4825741375469315</v>
       </c>
       <c r="K8" t="n">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="L8" t="n">
-        <v>2177</v>
+        <v>2346</v>
       </c>
       <c r="M8" t="n">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="N8" t="n">
-        <v>905</v>
+        <v>962</v>
       </c>
       <c r="O8" t="n">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="P8" t="n">
-        <v>739</v>
+        <v>800</v>
       </c>
       <c r="Q8" t="n">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="R8" t="n">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="S8" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="T8" t="n">
-        <v>638</v>
+        <v>687</v>
       </c>
       <c r="U8" t="n">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="V8" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="W8" t="n">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="X8" t="n">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="Y8" t="n">
-        <v>622</v>
+        <v>657</v>
       </c>
       <c r="Z8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
-        <v>2338</v>
+        <v>2513</v>
       </c>
       <c r="AB8" t="n">
-        <v>2311.16</v>
+        <v>2470.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>2111.16</v>
+        <v>2260.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AF8" t="n">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="AG8" t="n">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="AH8" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AI8" t="n">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="AJ8" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="AK8" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="AL8" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="AM8" t="n">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="AN8" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="AO8" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AP8" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="AQ8" t="n">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="AR8" t="n">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="AS8" t="n">
         <v>20</v>
       </c>
       <c r="AT8" t="n">
-        <v>1174.44</v>
+        <v>1251.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>1077.44</v>
+        <v>1149.48</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9251968748828777</v>
+        <v>0.9405333518290729</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.001618135229817</v>
+        <v>1.003555641458983</v>
       </c>
       <c r="AX8" t="n">
-        <v>100.8281043582518</v>
+        <v>102.3423958278349</v>
       </c>
       <c r="AY8" t="n">
-        <v>112.3521593863083</v>
+        <v>112.776611414705</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-11.52405502805657</v>
+        <v>-10.4342155868701</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.2432337345422321</v>
+        <v>0.241510905862605</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.7215370926115999</v>
+        <v>0.7185326589865129</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.4922335550056718</v>
+        <v>0.4921665226836562</v>
       </c>
       <c r="BD8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE8" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="BF8" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="BG8" t="n">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="BH8" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="BI8" t="n">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="BJ8" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="BK8" t="n">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="BL8" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="BM8" t="n">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="BN8" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="BO8" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="BP8" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="BQ8" t="n">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="BR8" t="n">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="BS8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BT8" t="n">
-        <v>1136.72</v>
+        <v>1218.88</v>
       </c>
       <c r="BU8" t="n">
-        <v>1033.72</v>
+        <v>1110.88</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9637984876447782</v>
+        <v>0.964459244099748</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9805179012775869</v>
+        <v>0.9872966040977322</v>
       </c>
       <c r="BX8" t="n">
-        <v>105.8024613901862</v>
+        <v>105.6610082012569</v>
       </c>
       <c r="BY8" t="n">
-        <v>110.6551865184748</v>
+        <v>110.8616778330577</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-4.852725128288601</v>
+        <v>-5.20066963180083</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2346510899014965</v>
+        <v>0.2297603720801064</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.6994097515372</v>
+        <v>0.7105602125458311</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.4704663974886877</v>
+        <v>0.4729817524102068</v>
       </c>
       <c r="CD8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -2616,244 +2616,244 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8861823764433897</v>
+        <v>0.8839419550020469</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9908548294979208</v>
+        <v>0.9875859440894209</v>
       </c>
       <c r="E9" t="n">
-        <v>97.7951277140177</v>
+        <v>97.47297443989341</v>
       </c>
       <c r="F9" t="n">
-        <v>111.9546233987492</v>
+        <v>111.5418721202008</v>
       </c>
       <c r="G9" t="n">
-        <v>-14.15949568473148</v>
+        <v>-14.06889768030741</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2415083452351504</v>
+        <v>0.2383407623454296</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6933810372423975</v>
+        <v>0.6934194424268875</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4615399109744415</v>
+        <v>0.4586626914682534</v>
       </c>
       <c r="K9" t="n">
-        <v>5650</v>
+        <v>6050</v>
       </c>
       <c r="L9" t="n">
-        <v>2069</v>
+        <v>2215</v>
       </c>
       <c r="M9" t="n">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="N9" t="n">
-        <v>962</v>
+        <v>1028</v>
       </c>
       <c r="O9" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="P9" t="n">
-        <v>760</v>
+        <v>824</v>
       </c>
       <c r="Q9" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="R9" t="n">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="S9" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="T9" t="n">
-        <v>623</v>
+        <v>668</v>
       </c>
       <c r="U9" t="n">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="V9" t="n">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="W9" t="n">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="X9" t="n">
-        <v>628</v>
+        <v>667</v>
       </c>
       <c r="Y9" t="n">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="Z9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="AA9" t="n">
-        <v>2368</v>
+        <v>2537</v>
       </c>
       <c r="AB9" t="n">
-        <v>2335.84</v>
+        <v>2508</v>
       </c>
       <c r="AC9" t="n">
-        <v>2117.84</v>
+        <v>2275</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AF9" t="n">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="AG9" t="n">
-        <v>482</v>
+        <v>522</v>
       </c>
       <c r="AH9" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="AI9" t="n">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="AJ9" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="AK9" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="AL9" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AM9" t="n">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="AN9" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AP9" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AQ9" t="n">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="AR9" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>1146.76</v>
+        <v>1229.92</v>
       </c>
       <c r="AU9" t="n">
-        <v>1050.76</v>
+        <v>1128.92</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8867295574360645</v>
+        <v>0.8933509860103926</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.037480443086613</v>
+        <v>1.036973598397362</v>
       </c>
       <c r="AX9" t="n">
-        <v>96.70233506924737</v>
+        <v>97.24971266306144</v>
       </c>
       <c r="AY9" t="n">
-        <v>117.2039055911403</v>
+        <v>116.9396730929621</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-20.50157052189293</v>
+        <v>-19.68996042990062</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2119849758085052</v>
+        <v>0.2066245739124996</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.696913140622818</v>
+        <v>0.6973658448282104</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4447660244171316</v>
+        <v>0.4397303407380408</v>
       </c>
       <c r="BD9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE9" t="n">
-        <v>2850</v>
+        <v>3050</v>
       </c>
       <c r="BF9" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="BG9" t="n">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="BH9" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="BI9" t="n">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="BJ9" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="BK9" t="n">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="BL9" t="n">
+        <v>132</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>345</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>229</v>
+      </c>
+      <c r="BO9" t="n">
         <v>122</v>
       </c>
-      <c r="BM9" t="n">
-        <v>319</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>212</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>110</v>
-      </c>
       <c r="BP9" t="n">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="BQ9" t="n">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="BR9" t="n">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="BS9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="BT9" t="n">
-        <v>1189.08</v>
+        <v>1278.08</v>
       </c>
       <c r="BU9" t="n">
-        <v>1067.08</v>
+        <v>1146.08</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8856351954507149</v>
+        <v>0.874532923993701</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.944229215909229</v>
+        <v>0.9381982897814801</v>
       </c>
       <c r="BX9" t="n">
-        <v>98.88792035878804</v>
+        <v>97.69623621672537</v>
       </c>
       <c r="BY9" t="n">
-        <v>106.7053412063581</v>
+        <v>106.1440711474396</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-7.817420847570044</v>
+        <v>-8.44783493071421</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.2710317146617958</v>
+        <v>0.2700569507783598</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.689848933861977</v>
+        <v>0.6894730400255645</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.4783137975317512</v>
+        <v>0.4775950421984657</v>
       </c>
       <c r="CD9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2868,244 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9254185449619178</v>
+        <v>0.9368464089056816</v>
       </c>
       <c r="D10" t="n">
-        <v>1.024995516433016</v>
+        <v>1.017611668525854</v>
       </c>
       <c r="E10" t="n">
-        <v>105.71319139563</v>
+        <v>106.3778655148082</v>
       </c>
       <c r="F10" t="n">
-        <v>115.0254449666538</v>
+        <v>114.3136620341632</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.312253571023758</v>
+        <v>-7.93579651935504</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3270545493061554</v>
+        <v>0.3157833200931524</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6958009919767537</v>
+        <v>0.6942012265968499</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5010515921357155</v>
+        <v>0.4969784243783326</v>
       </c>
       <c r="K10" t="n">
-        <v>5650</v>
+        <v>6075</v>
       </c>
       <c r="L10" t="n">
-        <v>2283</v>
+        <v>2478</v>
       </c>
       <c r="M10" t="n">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="N10" t="n">
-        <v>989</v>
+        <v>1058</v>
       </c>
       <c r="O10" t="n">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="P10" t="n">
-        <v>828</v>
+        <v>886</v>
       </c>
       <c r="Q10" t="n">
-        <v>446</v>
+        <v>481</v>
       </c>
       <c r="R10" t="n">
-        <v>607</v>
+        <v>659</v>
       </c>
       <c r="S10" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="T10" t="n">
-        <v>596</v>
+        <v>645</v>
       </c>
       <c r="U10" t="n">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="V10" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="W10" t="n">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="X10" t="n">
-        <v>689</v>
+        <v>737</v>
       </c>
       <c r="Y10" t="n">
-        <v>605</v>
+        <v>653</v>
       </c>
       <c r="Z10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AA10" t="n">
-        <v>2498</v>
+        <v>2675</v>
       </c>
       <c r="AB10" t="n">
-        <v>2469.08</v>
+        <v>2646.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>2161.08</v>
+        <v>2329.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>2850</v>
+        <v>3050</v>
       </c>
       <c r="AF10" t="n">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="AG10" t="n">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="AH10" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="AI10" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AJ10" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="AK10" t="n">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="AL10" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AM10" t="n">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="AN10" t="n">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="AO10" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AP10" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="AQ10" t="n">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="AR10" t="n">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="AS10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>1249.4</v>
+        <v>1335.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>1090.4</v>
+        <v>1170.48</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.8845918104232021</v>
+        <v>0.8999684654408375</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.040167651451432</v>
+        <v>1.028075049751616</v>
       </c>
       <c r="AX10" t="n">
-        <v>101.4759506481696</v>
+        <v>102.7028952636329</v>
       </c>
       <c r="AY10" t="n">
-        <v>116.3114239866485</v>
+        <v>115.1977619120508</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-14.83547333847888</v>
+        <v>-12.49486664841784</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.3275610465914474</v>
+        <v>0.3205384583001658</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.6916808977023716</v>
+        <v>0.6894284869783538</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.4923594417570263</v>
+        <v>0.4913303507680963</v>
       </c>
       <c r="BD10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>2800</v>
+        <v>3025</v>
       </c>
       <c r="BF10" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="BG10" t="n">
-        <v>479</v>
+        <v>515</v>
       </c>
       <c r="BH10" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="BI10" t="n">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="BJ10" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="BK10" t="n">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="BL10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="BM10" t="n">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="BN10" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="BO10" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="BP10" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="BQ10" t="n">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="BR10" t="n">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="BS10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BT10" t="n">
-        <v>1219.68</v>
+        <v>1311.48</v>
       </c>
       <c r="BU10" t="n">
-        <v>1070.68</v>
+        <v>1159.48</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9662452795006333</v>
+        <v>0.9737243523705258</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.0098233814146</v>
+        <v>1.007148287300091</v>
       </c>
       <c r="BX10" t="n">
-        <v>109.9504321430904</v>
+        <v>110.0528357659835</v>
       </c>
       <c r="BY10" t="n">
-        <v>113.739465946659</v>
+        <v>113.4295621562757</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-3.78903380356864</v>
+        <v>-3.376726390292238</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3265480520208633</v>
+        <v>0.3110281818861391</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.6999210862511355</v>
+        <v>0.6989739662153454</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.5097437425144044</v>
+        <v>0.5026264979885685</v>
       </c>
       <c r="CD10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3120,244 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9836610317031899</v>
+        <v>0.9805145820849607</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9532101385350609</v>
+        <v>0.9519229092465782</v>
       </c>
       <c r="E11" t="n">
-        <v>111.3158406440831</v>
+        <v>110.8575108138257</v>
       </c>
       <c r="F11" t="n">
-        <v>106.9253188299953</v>
+        <v>106.9545875667412</v>
       </c>
       <c r="G11" t="n">
-        <v>4.390521814087848</v>
+        <v>3.902923247084494</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3136014527324095</v>
+        <v>0.3091399770094519</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7071513141637187</v>
+        <v>0.7053227933730806</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5078211022328734</v>
+        <v>0.5049920031096561</v>
       </c>
       <c r="K11" t="n">
-        <v>5625</v>
+        <v>6025</v>
       </c>
       <c r="L11" t="n">
-        <v>2261</v>
+        <v>2406</v>
       </c>
       <c r="M11" t="n">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="N11" t="n">
-        <v>899</v>
+        <v>961</v>
       </c>
       <c r="O11" t="n">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="P11" t="n">
-        <v>852</v>
+        <v>905</v>
       </c>
       <c r="Q11" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="R11" t="n">
-        <v>560</v>
+        <v>612</v>
       </c>
       <c r="S11" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="T11" t="n">
-        <v>585</v>
+        <v>630</v>
       </c>
       <c r="U11" t="n">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="V11" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="W11" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="X11" t="n">
-        <v>641</v>
+        <v>697</v>
       </c>
       <c r="Y11" t="n">
-        <v>579</v>
+        <v>628</v>
       </c>
       <c r="Z11" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA11" t="n">
-        <v>2149</v>
+        <v>2300</v>
       </c>
       <c r="AB11" t="n">
-        <v>2312.4</v>
+        <v>2467.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>2035.4</v>
+        <v>2174.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="AF11" t="n">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="AG11" t="n">
+        <v>498</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>147</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>453</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>212</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>279</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>134</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>316</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>204</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>154</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>354</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>300</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1227.76</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1093.76</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.9684400862711573</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.9712630487496953</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>108.294609354708</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>108.9577828951275</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.6631735404195401</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.2710969215715447</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.7079064608780034</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.4814880870004095</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>248</v>
+      </c>
+      <c r="BG11" t="n">
         <v>463</v>
       </c>
-      <c r="AH11" t="n">
-        <v>137</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>426</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>262</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>126</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>296</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>191</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>88</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>145</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>327</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>278</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1149.28</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1023.28</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.972083578671915</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.9703557654762979</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>108.7330357242149</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>108.628150930622</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.1048847935928835</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.2736542647090081</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.7123882587748193</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.4851108624454937</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2800</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>236</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>436</v>
-      </c>
       <c r="BH11" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="BI11" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="BJ11" t="n">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="BK11" t="n">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="BL11" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="BM11" t="n">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="BN11" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="BO11" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="BP11" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="BQ11" t="n">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="BR11" t="n">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="BS11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BT11" t="n">
-        <v>1163.12</v>
+        <v>1239.52</v>
       </c>
       <c r="BU11" t="n">
-        <v>1012.12</v>
+        <v>1080.52</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9952384847344647</v>
+        <v>0.9925890778987639</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9360645115938236</v>
+        <v>0.9325827697434611</v>
       </c>
       <c r="BX11" t="n">
-        <v>113.8986455639514</v>
+        <v>113.4204122729434</v>
       </c>
       <c r="BY11" t="n">
-        <v>105.2224867293686</v>
+        <v>104.9513922383548</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.676158834582814</v>
+        <v>8.46902003458853</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.353548640755811</v>
+        <v>0.3471830324473591</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7019143695526184</v>
+        <v>0.7027391258681581</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.530531342020253</v>
+        <v>0.5284959192189027</v>
       </c>
       <c r="CD11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -3372,166 +3372,166 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9914384745121059</v>
+        <v>0.9842067744125754</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9737573285557724</v>
+        <v>0.9719272314463954</v>
       </c>
       <c r="E12" t="n">
-        <v>110.4866001963903</v>
+        <v>109.9172666367304</v>
       </c>
       <c r="F12" t="n">
-        <v>109.3538896099574</v>
+        <v>109.1866280683066</v>
       </c>
       <c r="G12" t="n">
-        <v>1.132710586432826</v>
+        <v>0.7306385684237255</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2614575436709801</v>
+        <v>0.264370199192025</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7133895851506555</v>
+        <v>0.7143962570986252</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4873405508893964</v>
+        <v>0.4889820447215385</v>
       </c>
       <c r="K12" t="n">
-        <v>5850</v>
+        <v>6050</v>
       </c>
       <c r="L12" t="n">
-        <v>2396</v>
+        <v>2464</v>
       </c>
       <c r="M12" t="n">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="N12" t="n">
-        <v>1026</v>
+        <v>1061</v>
       </c>
       <c r="O12" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="P12" t="n">
-        <v>780</v>
+        <v>813</v>
       </c>
       <c r="Q12" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="R12" t="n">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="S12" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="T12" t="n">
-        <v>674</v>
+        <v>703</v>
       </c>
       <c r="U12" t="n">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="V12" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="W12" t="n">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="X12" t="n">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="Y12" t="n">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AA12" t="n">
-        <v>2371</v>
+        <v>2448</v>
       </c>
       <c r="AB12" t="n">
-        <v>2417.64</v>
+        <v>2505.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>2165.64</v>
+        <v>2238.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
-        <v>2850</v>
+        <v>3050</v>
       </c>
       <c r="AF12" t="n">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AG12" t="n">
-        <v>518</v>
+        <v>553</v>
       </c>
       <c r="AH12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="AI12" t="n">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="AJ12" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="AK12" t="n">
+        <v>327</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>148</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>371</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>189</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>68</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>172</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>326</v>
+      </c>
+      <c r="AR12" t="n">
         <v>307</v>
       </c>
-      <c r="AL12" t="n">
-        <v>133</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>342</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>173</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>66</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>161</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>304</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>286</v>
-      </c>
       <c r="AS12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>1173.08</v>
+        <v>1260.88</v>
       </c>
       <c r="AU12" t="n">
-        <v>1040.08</v>
+        <v>1112.88</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.9597663881770461</v>
+        <v>0.9474144604003226</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.957235643809016</v>
+        <v>0.954676895240046</v>
       </c>
       <c r="AX12" t="n">
-        <v>108.1698698419709</v>
+        <v>107.1856514129457</v>
       </c>
       <c r="AY12" t="n">
-        <v>108.2052220527898</v>
+        <v>107.9472768066327</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.03535221081892916</v>
+        <v>-0.7616253936870133</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2736216473062626</v>
+        <v>0.2786360181060001</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.7142856726453504</v>
+        <v>0.7162392773749765</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4930269734549286</v>
+        <v>0.4959308662815106</v>
       </c>
       <c r="BD12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE12" t="n">
         <v>3000</v>
@@ -3624,166 +3624,166 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9385344520435112</v>
+        <v>0.9431810964504584</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8936164507150456</v>
+        <v>0.8922507597653803</v>
       </c>
       <c r="E13" t="n">
-        <v>108.2518516088064</v>
+        <v>108.3381482043175</v>
       </c>
       <c r="F13" t="n">
-        <v>100.5672342846793</v>
+        <v>100.6512900318567</v>
       </c>
       <c r="G13" t="n">
-        <v>7.68461732412717</v>
+        <v>7.686858172460884</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3549654723982138</v>
+        <v>0.345775351930968</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7248694276321526</v>
+        <v>0.7213819439604873</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5456967737728494</v>
+        <v>0.5412716457174046</v>
       </c>
       <c r="K13" t="n">
-        <v>5625</v>
+        <v>6025</v>
       </c>
       <c r="L13" t="n">
-        <v>2214</v>
+        <v>2368</v>
       </c>
       <c r="M13" t="n">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="N13" t="n">
-        <v>1013</v>
+        <v>1090</v>
       </c>
       <c r="O13" t="n">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="P13" t="n">
-        <v>755</v>
+        <v>798</v>
       </c>
       <c r="Q13" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="R13" t="n">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="S13" t="n">
+        <v>331</v>
+      </c>
+      <c r="T13" t="n">
+        <v>734</v>
+      </c>
+      <c r="U13" t="n">
+        <v>496</v>
+      </c>
+      <c r="V13" t="n">
+        <v>195</v>
+      </c>
+      <c r="W13" t="n">
+        <v>371</v>
+      </c>
+      <c r="X13" t="n">
+        <v>638</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>606</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>109</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2235</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2516.84</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2185.84</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>321</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>557</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>122</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>364</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>181</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>254</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>145</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>386</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>266</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>99</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>212</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>319</v>
       </c>
-      <c r="T13" t="n">
-        <v>683</v>
-      </c>
-      <c r="U13" t="n">
-        <v>444</v>
-      </c>
-      <c r="V13" t="n">
-        <v>187</v>
-      </c>
-      <c r="W13" t="n">
-        <v>352</v>
-      </c>
-      <c r="X13" t="n">
-        <v>603</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>568</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2080</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2364.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2045.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>275</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>480</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>108</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>321</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>161</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>223</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>133</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>335</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>214</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>91</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>193</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>284</v>
-      </c>
       <c r="AR13" t="n">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="AS13" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AT13" t="n">
-        <v>1092.12</v>
+        <v>1244.76</v>
       </c>
       <c r="AU13" t="n">
-        <v>959.12</v>
+        <v>1099.76</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9490053945573691</v>
+        <v>0.9569025577027492</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.880860313278059</v>
+        <v>0.8798297497036599</v>
       </c>
       <c r="AX13" t="n">
-        <v>107.9253647448632</v>
+        <v>108.1414895177445</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.2906945722753</v>
+        <v>101.3623446949506</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.634670172587852</v>
+        <v>6.779144822793855</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.3497056866633611</v>
+        <v>0.3320267504935167</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.6961831309942441</v>
+        <v>0.6930330032026345</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5459320364608566</v>
+        <v>0.5370504119915659</v>
       </c>
       <c r="BD13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
         <v>3025</v>
@@ -3876,88 +3876,88 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.0198973574694</v>
+        <v>1.016816851948949</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9261659617211823</v>
+        <v>0.9293017475586437</v>
       </c>
       <c r="E14" t="n">
-        <v>116.9914379550519</v>
+        <v>116.7801844268815</v>
       </c>
       <c r="F14" t="n">
-        <v>103.4471170055126</v>
+        <v>103.576679395756</v>
       </c>
       <c r="G14" t="n">
-        <v>13.54432094953935</v>
+        <v>13.20350503112543</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3501028431336305</v>
+        <v>0.3513689208118738</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7334060227510248</v>
+        <v>0.7385661131499969</v>
       </c>
       <c r="J14" t="n">
-        <v>0.543872682347367</v>
+        <v>0.5461217371426472</v>
       </c>
       <c r="K14" t="n">
-        <v>5800</v>
+        <v>6200</v>
       </c>
       <c r="L14" t="n">
-        <v>2629</v>
+        <v>2802</v>
       </c>
       <c r="M14" t="n">
-        <v>614</v>
+        <v>650</v>
       </c>
       <c r="N14" t="n">
-        <v>1137</v>
+        <v>1219</v>
       </c>
       <c r="O14" t="n">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="P14" t="n">
-        <v>830</v>
+        <v>888</v>
       </c>
       <c r="Q14" t="n">
-        <v>507</v>
+        <v>542</v>
       </c>
       <c r="R14" t="n">
-        <v>661</v>
+        <v>709</v>
       </c>
       <c r="S14" t="n">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="T14" t="n">
-        <v>711</v>
+        <v>762</v>
       </c>
       <c r="U14" t="n">
-        <v>555</v>
+        <v>598</v>
       </c>
       <c r="V14" t="n">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="W14" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="X14" t="n">
-        <v>629</v>
+        <v>671</v>
       </c>
       <c r="Y14" t="n">
-        <v>638</v>
+        <v>682</v>
       </c>
       <c r="Z14" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AA14" t="n">
-        <v>2273</v>
+        <v>2426</v>
       </c>
       <c r="AB14" t="n">
-        <v>2582.84</v>
+        <v>2760.96</v>
       </c>
       <c r="AC14" t="n">
-        <v>2247.84</v>
+        <v>2399.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AE14" t="n">
         <v>3000</v>
@@ -4038,82 +4038,82 @@
         <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="BF14" t="n">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="BG14" t="n">
-        <v>536</v>
+        <v>618</v>
       </c>
       <c r="BH14" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="BI14" t="n">
-        <v>426</v>
+        <v>484</v>
       </c>
       <c r="BJ14" t="n">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="BK14" t="n">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="BL14" t="n">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="BM14" t="n">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="BN14" t="n">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="BO14" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="BP14" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="BQ14" t="n">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="BR14" t="n">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="BS14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BT14" t="n">
-        <v>1253.88</v>
+        <v>1432</v>
       </c>
       <c r="BU14" t="n">
-        <v>1093.88</v>
+        <v>1246</v>
       </c>
       <c r="BV14" t="n">
-        <v>1.033785892900543</v>
+        <v>1.026081346525777</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.9391032136964179</v>
+        <v>0.943561642259595</v>
       </c>
       <c r="BX14" t="n">
-        <v>118.3088682223603</v>
+        <v>117.7348857281165</v>
       </c>
       <c r="BY14" t="n">
-        <v>102.9407548269119</v>
+        <v>103.2550772303337</v>
       </c>
       <c r="BZ14" t="n">
-        <v>15.3681133954484</v>
+        <v>14.47980849778279</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3422506479714318</v>
+        <v>0.3456851978683031</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7873043301324011</v>
+        <v>0.7905647168577374</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5679108151361908</v>
+        <v>0.5692635922034429</v>
       </c>
       <c r="CD14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4128,244 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.876407427266135</v>
+        <v>0.8756436102594356</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9765406124679751</v>
+        <v>0.9843744358736066</v>
       </c>
       <c r="E15" t="n">
-        <v>99.20483906289108</v>
+        <v>99.25389039677863</v>
       </c>
       <c r="F15" t="n">
-        <v>110.4379583268206</v>
+        <v>110.9897842371766</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.23311926392955</v>
+        <v>-11.73589384039792</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2858756843920011</v>
+        <v>0.2884059993896494</v>
       </c>
       <c r="I15" t="n">
-        <v>0.701722217792482</v>
+        <v>0.7071292887948688</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4905066067442321</v>
+        <v>0.4931164598657798</v>
       </c>
       <c r="K15" t="n">
-        <v>5625</v>
+        <v>6025</v>
       </c>
       <c r="L15" t="n">
-        <v>2135</v>
+        <v>2289</v>
       </c>
       <c r="M15" t="n">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="N15" t="n">
-        <v>974</v>
+        <v>1030</v>
       </c>
       <c r="O15" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="P15" t="n">
-        <v>839</v>
+        <v>910</v>
       </c>
       <c r="Q15" t="n">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="R15" t="n">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="S15" t="n">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="T15" t="n">
-        <v>675</v>
+        <v>722</v>
       </c>
       <c r="U15" t="n">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="V15" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="W15" t="n">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="X15" t="n">
-        <v>583</v>
+        <v>629</v>
       </c>
       <c r="Y15" t="n">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="Z15" t="n">
         <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2392</v>
+        <v>2574</v>
       </c>
       <c r="AB15" t="n">
-        <v>2441.92</v>
+        <v>2620.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>2153.92</v>
+        <v>2308.04</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AF15" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="AG15" t="n">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="AH15" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="AI15" t="n">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="AJ15" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="AK15" t="n">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="AL15" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="AM15" t="n">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="AN15" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AO15" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AP15" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="AQ15" t="n">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="AR15" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>1236.28</v>
+        <v>1320.08</v>
       </c>
       <c r="AU15" t="n">
-        <v>1087.28</v>
+        <v>1160.08</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.8417554040527594</v>
+        <v>0.843713158341048</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.001839115684425</v>
+        <v>1.006573460733275</v>
       </c>
       <c r="AX15" t="n">
-        <v>95.58045128576205</v>
+        <v>95.89340288502628</v>
       </c>
       <c r="AY15" t="n">
-        <v>113.9616706937297</v>
+        <v>114.200930919761</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-18.38121940796766</v>
+        <v>-18.30752803473473</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.2956658999565711</v>
+        <v>0.2963252103298367</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.6880531619447876</v>
+        <v>0.694708203673721</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.4834065054886604</v>
+        <v>0.4869281973932811</v>
       </c>
       <c r="BD15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE15" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="BF15" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="BG15" t="n">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="BH15" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="BI15" t="n">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="BJ15" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="BK15" t="n">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="BL15" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="BM15" t="n">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="BN15" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="BO15" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="BP15" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="BQ15" t="n">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="BR15" t="n">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="BS15" t="n">
         <v>23</v>
       </c>
       <c r="BT15" t="n">
-        <v>1205.64</v>
+        <v>1299.96</v>
       </c>
       <c r="BU15" t="n">
-        <v>1066.64</v>
+        <v>1147.96</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.9110594504795105</v>
+        <v>0.907574062177823</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9512421092515249</v>
+        <v>0.9621754110139388</v>
       </c>
       <c r="BX15" t="n">
-        <v>102.8292268400201</v>
+        <v>102.614377908531</v>
       </c>
       <c r="BY15" t="n">
-        <v>106.9142459599116</v>
+        <v>107.7786375545921</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-4.085019119891433</v>
+        <v>-5.164259646061113</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2760854688274312</v>
+        <v>0.2804867884494621</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.7153912736401763</v>
+        <v>0.7195503739160164</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.4976067079998041</v>
+        <v>0.4993047223382787</v>
       </c>
       <c r="CD15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -4380,244 +4380,244 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.06968405922994</v>
+        <v>1.066524328506282</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8788449517340892</v>
+        <v>0.8896719042791157</v>
       </c>
       <c r="E16" t="n">
-        <v>120.2843037266686</v>
+        <v>120.2137292851303</v>
       </c>
       <c r="F16" t="n">
-        <v>99.09738998245373</v>
+        <v>99.83030193897015</v>
       </c>
       <c r="G16" t="n">
-        <v>21.18691374421487</v>
+        <v>20.38342734616017</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3246914361813006</v>
+        <v>0.3276629450534852</v>
       </c>
       <c r="I16" t="n">
-        <v>0.700057525020033</v>
+        <v>0.7092363823263899</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5211860105607871</v>
+        <v>0.5255498135838617</v>
       </c>
       <c r="K16" t="n">
-        <v>5650</v>
+        <v>6075</v>
       </c>
       <c r="L16" t="n">
-        <v>2580</v>
+        <v>2765</v>
       </c>
       <c r="M16" t="n">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="N16" t="n">
-        <v>1062</v>
+        <v>1127</v>
       </c>
       <c r="O16" t="n">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="P16" t="n">
-        <v>740</v>
+        <v>812</v>
       </c>
       <c r="Q16" t="n">
-        <v>493</v>
+        <v>528</v>
       </c>
       <c r="R16" t="n">
-        <v>662</v>
+        <v>707</v>
       </c>
       <c r="S16" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="T16" t="n">
-        <v>645</v>
+        <v>694</v>
       </c>
       <c r="U16" t="n">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="V16" t="n">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="W16" t="n">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="X16" t="n">
-        <v>588</v>
+        <v>630</v>
       </c>
       <c r="Y16" t="n">
-        <v>639</v>
+        <v>682</v>
       </c>
       <c r="Z16" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA16" t="n">
-        <v>2109</v>
+        <v>2287</v>
       </c>
       <c r="AB16" t="n">
-        <v>2412.28</v>
+        <v>2594.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>2147.28</v>
+        <v>2304.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE16" t="n">
-        <v>2825</v>
+        <v>3050</v>
       </c>
       <c r="AF16" t="n">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="AG16" t="n">
-        <v>524</v>
+        <v>559</v>
       </c>
       <c r="AH16" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="AI16" t="n">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="AJ16" t="n">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="AK16" t="n">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="AL16" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="AM16" t="n">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="AN16" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="AO16" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="AP16" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="AQ16" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="AR16" t="n">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="AS16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT16" t="n">
-        <v>1189.68</v>
+        <v>1288.68</v>
       </c>
       <c r="AU16" t="n">
-        <v>1066.68</v>
+        <v>1154.68</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.078318331893942</v>
+        <v>1.071076907747477</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.9163072824401171</v>
+        <v>0.9271155551140439</v>
       </c>
       <c r="AX16" t="n">
-        <v>120.3885259172726</v>
+        <v>119.6353514621817</v>
       </c>
       <c r="AY16" t="n">
-        <v>104.6626776261728</v>
+        <v>105.1175982168604</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.72584829109983</v>
+        <v>14.51775324532135</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.3144019072193234</v>
+        <v>0.3143941610237494</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.6630728682025467</v>
+        <v>0.6792846769890436</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.4982632336360799</v>
+        <v>0.5048466797518835</v>
       </c>
       <c r="BD16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="BF16" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="BG16" t="n">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="BH16" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="BI16" t="n">
-        <v>388</v>
+        <v>423</v>
       </c>
       <c r="BJ16" t="n">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="BK16" t="n">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="BL16" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="BM16" t="n">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="BN16" t="n">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="BO16" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="BP16" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="BQ16" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="BR16" t="n">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="BS16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BT16" t="n">
-        <v>1222.6</v>
+        <v>1305.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>1080.6</v>
+        <v>1149.4</v>
       </c>
       <c r="BV16" t="n">
-        <v>1.061049786565939</v>
+        <v>1.061971749265086</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8413826210280622</v>
+        <v>0.8522282534441883</v>
       </c>
       <c r="BX16" t="n">
-        <v>120.1800815360646</v>
+        <v>120.7921071080789</v>
       </c>
       <c r="BY16" t="n">
-        <v>93.53210233873467</v>
+        <v>94.54300566107989</v>
       </c>
       <c r="BZ16" t="n">
-        <v>26.64797919732991</v>
+        <v>26.24910144699898</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.3349809651432779</v>
+        <v>0.3409317290832209</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.7370421818375192</v>
+        <v>0.739188087663736</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.5441087874854944</v>
+        <v>0.5462529474158399</v>
       </c>
       <c r="CD16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -4632,244 +4632,244 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.02182654595744</v>
+        <v>1.022935489516515</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9619789805518471</v>
+        <v>0.962713746696065</v>
       </c>
       <c r="E17" t="n">
-        <v>114.56141644287</v>
+        <v>114.4655295552824</v>
       </c>
       <c r="F17" t="n">
-        <v>108.0821641299977</v>
+        <v>108.531192867698</v>
       </c>
       <c r="G17" t="n">
-        <v>6.47925231287236</v>
+        <v>5.93433668758446</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3042794632299189</v>
+        <v>0.2987571804442724</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7113388755515561</v>
+        <v>0.7062563511881862</v>
       </c>
       <c r="J17" t="n">
-        <v>0.515138371534906</v>
+        <v>0.5103790444159573</v>
       </c>
       <c r="K17" t="n">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="L17" t="n">
-        <v>2374</v>
+        <v>2539</v>
       </c>
       <c r="M17" t="n">
-        <v>516</v>
+        <v>549</v>
       </c>
       <c r="N17" t="n">
-        <v>909</v>
+        <v>965</v>
       </c>
       <c r="O17" t="n">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="P17" t="n">
-        <v>796</v>
+        <v>859</v>
       </c>
       <c r="Q17" t="n">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="R17" t="n">
-        <v>636</v>
+        <v>672</v>
       </c>
       <c r="S17" t="n">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="T17" t="n">
-        <v>637</v>
+        <v>681</v>
       </c>
       <c r="U17" t="n">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="V17" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="W17" t="n">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="X17" t="n">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="Y17" t="n">
-        <v>650</v>
+        <v>689</v>
       </c>
       <c r="Z17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AA17" t="n">
-        <v>2252</v>
+        <v>2414</v>
       </c>
       <c r="AB17" t="n">
-        <v>2322.84</v>
+        <v>2481.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>2073.84</v>
+        <v>2219.68</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AF17" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="AG17" t="n">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="AH17" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="AI17" t="n">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="AJ17" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="AK17" t="n">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="AL17" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="AM17" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="AN17" t="n">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="AO17" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="AQ17" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="AR17" t="n">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="AS17" t="n">
         <v>31</v>
       </c>
       <c r="AT17" t="n">
-        <v>1150</v>
+        <v>1228.68</v>
       </c>
       <c r="AU17" t="n">
-        <v>1035</v>
+        <v>1107.68</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.002778925739386</v>
+        <v>1.002864804508091</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.9696448044586913</v>
+        <v>0.9766604326316545</v>
       </c>
       <c r="AX17" t="n">
-        <v>111.407205287259</v>
+        <v>111.2264350797026</v>
       </c>
       <c r="AY17" t="n">
-        <v>108.7907820022718</v>
+        <v>110.1620942098723</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.616423284987204</v>
+        <v>1.064340869830321</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.2832630130130154</v>
+        <v>0.2797634275300964</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.7192669796068415</v>
+        <v>0.7096996860168905</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.510638597759095</v>
+        <v>0.5048446121457768</v>
       </c>
       <c r="BD17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE17" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="BF17" t="n">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="BG17" t="n">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="BH17" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="BI17" t="n">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="BJ17" t="n">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="BK17" t="n">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="BL17" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="BM17" t="n">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="BN17" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="BO17" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="BP17" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="BQ17" t="n">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="BR17" t="n">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="BS17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BT17" t="n">
-        <v>1172.84</v>
+        <v>1253</v>
       </c>
       <c r="BU17" t="n">
-        <v>1038.84</v>
+        <v>1112</v>
       </c>
       <c r="BV17" t="n">
-        <v>1.040874166175494</v>
+        <v>1.043006174524939</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.9543131566450027</v>
+        <v>0.9487670607604751</v>
       </c>
       <c r="BX17" t="n">
-        <v>117.7156275984811</v>
+        <v>117.7046240308623</v>
       </c>
       <c r="BY17" t="n">
-        <v>107.3735462577236</v>
+        <v>106.9002915255237</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.34208134075751</v>
+        <v>10.8043325053386</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.3252959134468224</v>
+        <v>0.3177509333584484</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.7034107714962706</v>
+        <v>0.7028130163594822</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.5196381453107169</v>
+        <v>0.5159134766861377</v>
       </c>
       <c r="CD17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -4884,244 +4884,244 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.866085698692478</v>
+        <v>0.8697930569932759</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9604675298549497</v>
+        <v>0.9570889966587213</v>
       </c>
       <c r="E18" t="n">
-        <v>97.51253979854822</v>
+        <v>97.82110442894506</v>
       </c>
       <c r="F18" t="n">
-        <v>110.2892570877241</v>
+        <v>110.2786233167517</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.77671728917592</v>
+        <v>-12.4575188878066</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2719818446129581</v>
+        <v>0.2690633968524361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6439568958209307</v>
+        <v>0.6421763069005689</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4481783769374018</v>
+        <v>0.4473833365828167</v>
       </c>
       <c r="K18" t="n">
-        <v>5625</v>
+        <v>6025</v>
       </c>
       <c r="L18" t="n">
-        <v>2036</v>
+        <v>2187</v>
       </c>
       <c r="M18" t="n">
-        <v>449</v>
+        <v>489</v>
       </c>
       <c r="N18" t="n">
-        <v>978</v>
+        <v>1055</v>
       </c>
       <c r="O18" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="P18" t="n">
-        <v>755</v>
+        <v>805</v>
       </c>
       <c r="Q18" t="n">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="R18" t="n">
-        <v>621</v>
+        <v>657</v>
       </c>
       <c r="S18" t="n">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="T18" t="n">
-        <v>579</v>
+        <v>628</v>
       </c>
       <c r="U18" t="n">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="V18" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="W18" t="n">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="X18" t="n">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="Y18" t="n">
-        <v>592</v>
+        <v>630</v>
       </c>
       <c r="Z18" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AA18" t="n">
-        <v>2338</v>
+        <v>2495</v>
       </c>
       <c r="AB18" t="n">
-        <v>2358.24</v>
+        <v>2522.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>2094.24</v>
+        <v>2242.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE18" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AF18" t="n">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="AG18" t="n">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="AH18" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="AI18" t="n">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="AJ18" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="AK18" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="AL18" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="AM18" t="n">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="AN18" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="AO18" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AP18" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="AQ18" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="AR18" t="n">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="AS18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AT18" t="n">
-        <v>1154.88</v>
+        <v>1234.92</v>
       </c>
       <c r="AU18" t="n">
-        <v>1037.88</v>
+        <v>1111.92</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.8882314882240687</v>
+        <v>0.8906519044180929</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.002155894306297</v>
+        <v>1.005018274172334</v>
       </c>
       <c r="AX18" t="n">
-        <v>98.92425375242389</v>
+        <v>98.99236851216686</v>
       </c>
       <c r="AY18" t="n">
-        <v>115.1514720184335</v>
+        <v>115.9315677265166</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-16.22721826600959</v>
+        <v>-16.93919921434978</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.2451671254151535</v>
+        <v>0.2421559837208099</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.6378636262642768</v>
+        <v>0.6342282734022139</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.4282898373383058</v>
+        <v>0.4270099087884794</v>
       </c>
       <c r="BD18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE18" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="BF18" t="n">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="BG18" t="n">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="BH18" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="BI18" t="n">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="BJ18" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="BK18" t="n">
+        <v>339</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>157</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>328</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>208</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>104</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>195</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>303</v>
+      </c>
+      <c r="BR18" t="n">
         <v>319</v>
       </c>
-      <c r="BL18" t="n">
-        <v>147</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>300</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>196</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>99</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>186</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>282</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>299</v>
-      </c>
       <c r="BS18" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="BT18" t="n">
-        <v>1203.36</v>
+        <v>1287.16</v>
       </c>
       <c r="BU18" t="n">
-        <v>1056.36</v>
+        <v>1130.16</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8439399091608871</v>
+        <v>0.8489342095684588</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9187791654036023</v>
+        <v>0.9091597191451085</v>
       </c>
       <c r="BX18" t="n">
-        <v>96.10082584467253</v>
+        <v>96.64984034572326</v>
       </c>
       <c r="BY18" t="n">
-        <v>105.4270421570148</v>
+        <v>104.6256789069867</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-9.326216312342265</v>
+        <v>-7.975838561263433</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.2987965638107627</v>
+        <v>0.2959708099840623</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.650050165377585</v>
+        <v>0.6501243403989243</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.4680669165364976</v>
+        <v>0.4677567643771539</v>
       </c>
       <c r="CD18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -5136,244 +5136,244 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9755285941406651</v>
+        <v>0.9836569987456442</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8695277214332509</v>
+        <v>0.8742967563916912</v>
       </c>
       <c r="E19" t="n">
-        <v>110.9204218321336</v>
+        <v>111.7293681151609</v>
       </c>
       <c r="F19" t="n">
-        <v>98.01242936712457</v>
+        <v>98.79320888978441</v>
       </c>
       <c r="G19" t="n">
-        <v>12.90799246500904</v>
+        <v>12.93615922537647</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3191820992364124</v>
+        <v>0.3156153595262668</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7110212910048601</v>
+        <v>0.7073649542166526</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5210932893120749</v>
+        <v>0.5175435146552414</v>
       </c>
       <c r="K19" t="n">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="L19" t="n">
-        <v>2308</v>
+        <v>2493</v>
       </c>
       <c r="M19" t="n">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="N19" t="n">
-        <v>1054</v>
+        <v>1132</v>
       </c>
       <c r="O19" t="n">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="P19" t="n">
-        <v>771</v>
+        <v>825</v>
       </c>
       <c r="Q19" t="n">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="R19" t="n">
-        <v>562</v>
+        <v>602</v>
       </c>
       <c r="S19" t="n">
+        <v>309</v>
+      </c>
+      <c r="T19" t="n">
+        <v>697</v>
+      </c>
+      <c r="U19" t="n">
+        <v>448</v>
+      </c>
+      <c r="V19" t="n">
+        <v>237</v>
+      </c>
+      <c r="W19" t="n">
+        <v>318</v>
+      </c>
+      <c r="X19" t="n">
+        <v>643</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>599</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2182</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2539.88</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2230.88</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>278</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>552</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>418</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>223</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>314</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>152</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>343</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>115</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>162</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>333</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>308</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1270.16</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1118.16</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.9687592714227079</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.8781379451694071</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>109.9396546634856</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>98.49452898468466</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>11.44512567880098</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.2999644273956418</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.7218814549057829</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.5119005625574621</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>319</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>580</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>143</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>407</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>197</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>288</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>157</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>354</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>228</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>122</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>156</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>310</v>
+      </c>
+      <c r="BR19" t="n">
         <v>291</v>
       </c>
-      <c r="T19" t="n">
-        <v>649</v>
-      </c>
-      <c r="U19" t="n">
-        <v>403</v>
-      </c>
-      <c r="V19" t="n">
-        <v>221</v>
-      </c>
-      <c r="W19" t="n">
-        <v>299</v>
-      </c>
-      <c r="X19" t="n">
-        <v>598</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>559</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2371.28</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2080.28</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2800</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>265</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>517</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>137</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>393</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>195</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>283</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>145</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>325</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>199</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>106</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>308</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>284</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1184.52</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1039.52</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.9603891373103444</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.8664917529142041</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>109.3453137634861</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>96.77635108303049</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>12.56896268045562</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0.3052614256658375</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0.7319697615926016</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0.5196630451364512</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2800</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>293</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>537</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>131</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>378</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>193</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>279</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>146</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>324</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>204</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>115</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>149</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>290</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>275</v>
-      </c>
       <c r="BS19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BT19" t="n">
-        <v>1186.76</v>
+        <v>1269.72</v>
       </c>
       <c r="BU19" t="n">
-        <v>1040.76</v>
+        <v>1112.72</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.9906680509709858</v>
+        <v>0.9985547260685805</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.8725636899522975</v>
+        <v>0.8704555676139751</v>
       </c>
       <c r="BX19" t="n">
-        <v>112.4955299007811</v>
+        <v>113.5190815668361</v>
       </c>
       <c r="BY19" t="n">
-        <v>99.24850765121865</v>
+        <v>99.09188879488417</v>
       </c>
       <c r="BZ19" t="n">
-        <v>13.24702224956247</v>
+        <v>14.42719277195196</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.3331027728069874</v>
+        <v>0.3312662916568919</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.6900728204171187</v>
+        <v>0.6928484535275222</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.5225235334876986</v>
+        <v>0.5231864667530209</v>
       </c>
       <c r="CD19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,244 +852,244 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9417834950806202</v>
+        <v>0.9513670599526608</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9183054859729876</v>
+        <v>0.9213215134648567</v>
       </c>
       <c r="E2" t="n">
-        <v>107.1991803011638</v>
+        <v>107.8296407911593</v>
       </c>
       <c r="F2" t="n">
-        <v>101.3236065030316</v>
+        <v>101.7138406744517</v>
       </c>
       <c r="G2" t="n">
-        <v>5.875573798132121</v>
+        <v>6.115800116707605</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3116444558114409</v>
+        <v>0.306750052550015</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7498460431022346</v>
+        <v>0.7508789930976755</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5255462203022425</v>
+        <v>0.525500538861946</v>
       </c>
       <c r="K2" t="n">
-        <v>6025</v>
+        <v>5225</v>
       </c>
       <c r="L2" t="n">
-        <v>2462</v>
+        <v>2163</v>
       </c>
       <c r="M2" t="n">
-        <v>512</v>
+        <v>450</v>
       </c>
       <c r="N2" t="n">
-        <v>963</v>
+        <v>840</v>
       </c>
       <c r="O2" t="n">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="P2" t="n">
-        <v>980</v>
+        <v>852</v>
       </c>
       <c r="Q2" t="n">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="R2" t="n">
-        <v>632</v>
+        <v>562</v>
       </c>
       <c r="S2" t="n">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="T2" t="n">
-        <v>714</v>
+        <v>625</v>
       </c>
       <c r="U2" t="n">
-        <v>463</v>
+        <v>404</v>
       </c>
       <c r="V2" t="n">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="W2" t="n">
-        <v>400</v>
+        <v>342</v>
       </c>
       <c r="X2" t="n">
-        <v>619</v>
+        <v>540</v>
       </c>
       <c r="Y2" t="n">
-        <v>629</v>
+        <v>553</v>
       </c>
       <c r="Z2" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AA2" t="n">
-        <v>2344</v>
+        <v>2048</v>
       </c>
       <c r="AB2" t="n">
-        <v>2621.08</v>
+        <v>2281.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>2300.08</v>
+        <v>2009.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>3025</v>
+        <v>2825</v>
       </c>
       <c r="AF2" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="AG2" t="n">
-        <v>504</v>
+        <v>476</v>
       </c>
       <c r="AH2" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="AI2" t="n">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="AJ2" t="n">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="AK2" t="n">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="AL2" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="AM2" t="n">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="AN2" t="n">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="AO2" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AP2" t="n">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="AQ2" t="n">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="AR2" t="n">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1337.76</v>
+        <v>1251.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1162.76</v>
+        <v>1086.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.9218714903158456</v>
+        <v>0.9307812442451924</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9255886402081579</v>
+        <v>0.9293227146817394</v>
       </c>
       <c r="AX2" t="n">
-        <v>105.9013622192401</v>
+        <v>107.028217245648</v>
       </c>
       <c r="AY2" t="n">
-        <v>102.5074158852856</v>
+        <v>102.7693545830184</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.393946333954433</v>
+        <v>4.258862662629544</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.329155055037408</v>
+        <v>0.3322579671319167</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.742691883677951</v>
+        <v>0.7517852599846179</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.5243188477584073</v>
+        <v>0.5313252291556706</v>
       </c>
       <c r="BD2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="BF2" t="n">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="BG2" t="n">
-        <v>459</v>
+        <v>364</v>
       </c>
       <c r="BH2" t="n">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="BI2" t="n">
-        <v>467</v>
+        <v>371</v>
       </c>
       <c r="BJ2" t="n">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="BK2" t="n">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="BL2" t="n">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="BM2" t="n">
-        <v>358</v>
+        <v>285</v>
       </c>
       <c r="BN2" t="n">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="BO2" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="BP2" t="n">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="BQ2" t="n">
-        <v>306</v>
+        <v>247</v>
       </c>
       <c r="BR2" t="n">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="BS2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BT2" t="n">
-        <v>1283.32</v>
+        <v>1030.08</v>
       </c>
       <c r="BU2" t="n">
-        <v>1137.32</v>
+        <v>923.08</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9616954998453946</v>
+        <v>0.9753838449447071</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.911022331737817</v>
+        <v>0.9119867787118268</v>
       </c>
       <c r="BX2" t="n">
-        <v>108.4969983830874</v>
+        <v>108.7646349275893</v>
       </c>
       <c r="BY2" t="n">
-        <v>100.1397971207776</v>
+        <v>100.4824077811239</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.357201262309808</v>
+        <v>8.282227146465344</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2941338565854739</v>
+        <v>0.2769908188711299</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7570002025265183</v>
+        <v>0.7498216817295763</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.5267735928460776</v>
+        <v>0.5187050668526008</v>
       </c>
       <c r="CD2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1104,244 +1104,244 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9417795275667563</v>
+        <v>0.9451462608068156</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9613309241461596</v>
+        <v>0.9652789106172202</v>
       </c>
       <c r="E3" t="n">
-        <v>106.4028455590689</v>
+        <v>106.6574808032636</v>
       </c>
       <c r="F3" t="n">
-        <v>110.0781112848323</v>
+        <v>111.3589823186588</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.675265725763472</v>
+        <v>-4.70150151539512</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3123149288351568</v>
+        <v>0.3153302198611653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6729616994149491</v>
+        <v>0.659169145206523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4966832760609744</v>
+        <v>0.4943916704434566</v>
       </c>
       <c r="K3" t="n">
-        <v>6047.766666666666</v>
+        <v>5022.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2511</v>
+        <v>2099</v>
       </c>
       <c r="M3" t="n">
-        <v>618</v>
+        <v>520</v>
       </c>
       <c r="N3" t="n">
-        <v>1246</v>
+        <v>1044</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="P3" t="n">
-        <v>679</v>
+        <v>543</v>
       </c>
       <c r="Q3" t="n">
-        <v>552</v>
+        <v>459</v>
       </c>
       <c r="R3" t="n">
-        <v>746</v>
+        <v>624</v>
       </c>
       <c r="S3" t="n">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="T3" t="n">
-        <v>704</v>
+        <v>584</v>
       </c>
       <c r="U3" t="n">
-        <v>389</v>
+        <v>310</v>
       </c>
       <c r="V3" t="n">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="W3" t="n">
-        <v>414</v>
+        <v>359</v>
       </c>
       <c r="X3" t="n">
-        <v>644</v>
+        <v>540</v>
       </c>
       <c r="Y3" t="n">
-        <v>661</v>
+        <v>550</v>
       </c>
       <c r="Z3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AA3" t="n">
-        <v>2582</v>
+        <v>2177</v>
       </c>
       <c r="AB3" t="n">
-        <v>2667.24</v>
+        <v>2220.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>2359.24</v>
+        <v>1965.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
-        <v>3025</v>
+        <v>2600</v>
       </c>
       <c r="AF3" t="n">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="AG3" t="n">
-        <v>616</v>
+        <v>529</v>
       </c>
       <c r="AH3" t="n">
+        <v>106</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>265</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>234</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>312</v>
+      </c>
+      <c r="AL3" t="n">
         <v>124</v>
       </c>
-      <c r="AI3" t="n">
-        <v>324</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>265</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>352</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>145</v>
-      </c>
       <c r="AM3" t="n">
-        <v>366</v>
+        <v>304</v>
       </c>
       <c r="AN3" t="n">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="AO3" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="AP3" t="n">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="AQ3" t="n">
-        <v>332</v>
+        <v>287</v>
       </c>
       <c r="AR3" t="n">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="AS3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>1312.88</v>
+        <v>1123.28</v>
       </c>
       <c r="AU3" t="n">
-        <v>1167.88</v>
+        <v>999.28</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.953445729837021</v>
+        <v>0.9663334080264676</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9474743355164171</v>
+        <v>0.9654715493550523</v>
       </c>
       <c r="AX3" t="n">
-        <v>107.1923501722332</v>
+        <v>108.6237728788093</v>
       </c>
       <c r="AY3" t="n">
-        <v>109.4022513727048</v>
+        <v>111.8588658851437</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-2.209901200471526</v>
+        <v>-3.235093006334291</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.3168586652026402</v>
+        <v>0.3252144752903074</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.6676001240906297</v>
+        <v>0.6554163167515157</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.5047060520939126</v>
+        <v>0.5042588175578078</v>
       </c>
       <c r="BD3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>3022.766666666666</v>
+        <v>2422.766666666666</v>
       </c>
       <c r="BF3" t="n">
-        <v>311</v>
+        <v>253</v>
       </c>
       <c r="BG3" t="n">
-        <v>630</v>
+        <v>515</v>
       </c>
       <c r="BH3" t="n">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="BI3" t="n">
-        <v>355</v>
+        <v>278</v>
       </c>
       <c r="BJ3" t="n">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="BK3" t="n">
-        <v>394</v>
+        <v>312</v>
       </c>
       <c r="BL3" t="n">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="BM3" t="n">
-        <v>338</v>
+        <v>280</v>
       </c>
       <c r="BN3" t="n">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="BO3" t="n">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="BP3" t="n">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="BQ3" t="n">
-        <v>312</v>
+        <v>253</v>
       </c>
       <c r="BR3" t="n">
-        <v>344</v>
+        <v>274</v>
       </c>
       <c r="BS3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="BT3" t="n">
-        <v>1354.36</v>
+        <v>1097.28</v>
       </c>
       <c r="BU3" t="n">
-        <v>1191.36</v>
+        <v>966.28</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9301133252964917</v>
+        <v>0.9221935179855261</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.975187512775902</v>
+        <v>0.9650702186512353</v>
       </c>
       <c r="BX3" t="n">
-        <v>105.6133409459045</v>
+        <v>104.5273310547558</v>
       </c>
       <c r="BY3" t="n">
-        <v>110.7539711969599</v>
+        <v>110.8174417883001</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-5.140630251055417</v>
+        <v>-6.29011073354435</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.3077711924676732</v>
+        <v>0.3046222764795947</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6783232747392683</v>
+        <v>0.6632347093661144</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.4886605000280362</v>
+        <v>0.483702261069576</v>
       </c>
       <c r="CD3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1356,244 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8788310360799748</v>
+        <v>0.9102302420787259</v>
       </c>
       <c r="D4" t="n">
-        <v>1.002530348164475</v>
+        <v>1.001898562194691</v>
       </c>
       <c r="E4" t="n">
-        <v>103.4948224967798</v>
+        <v>106.7337395527079</v>
       </c>
       <c r="F4" t="n">
-        <v>111.8109838625481</v>
+        <v>111.8994828137643</v>
       </c>
       <c r="G4" t="n">
-        <v>-8.3161613657683</v>
+        <v>-5.1657432610564</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3674460918274505</v>
+        <v>0.3721297357183876</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7152022051075861</v>
+        <v>0.7098974497146971</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5243142626292148</v>
+        <v>0.5266028018987361</v>
       </c>
       <c r="K4" t="n">
-        <v>3600</v>
+        <v>2600</v>
       </c>
       <c r="L4" t="n">
-        <v>1374</v>
+        <v>1034</v>
       </c>
       <c r="M4" t="n">
-        <v>337</v>
+        <v>252</v>
       </c>
       <c r="N4" t="n">
-        <v>749</v>
+        <v>548</v>
       </c>
       <c r="O4" t="n">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="P4" t="n">
-        <v>431</v>
+        <v>317</v>
       </c>
       <c r="Q4" t="n">
-        <v>280</v>
+        <v>203</v>
       </c>
       <c r="R4" t="n">
-        <v>401</v>
+        <v>282</v>
       </c>
       <c r="S4" t="n">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="T4" t="n">
-        <v>381</v>
+        <v>271</v>
       </c>
       <c r="U4" t="n">
-        <v>270</v>
+        <v>202</v>
       </c>
       <c r="V4" t="n">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="W4" t="n">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="X4" t="n">
-        <v>427</v>
+        <v>300</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>288</v>
       </c>
       <c r="Z4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>1481</v>
+        <v>1077</v>
       </c>
       <c r="AB4" t="n">
-        <v>1568.44</v>
+        <v>1141.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>1327.44</v>
+        <v>970.08</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>205</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>121</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>104</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>58</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>104</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>426.76</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8989491706217176</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.011121276035282</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>104.0680646041733</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>114.7939083022978</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-10.72584369812456</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.349263231360418</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.6862519644957648</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.5114083139083139</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1600</v>
       </c>
-      <c r="AF4" t="n">
-        <v>136</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>329</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>57</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>183</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>122</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>177</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>96</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>173</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>103</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>43</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>88</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>194</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>172</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>677.88</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>581.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8366780336117258</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.006689777084927</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>97.31584072603454</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>113.6278990937314</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-16.31205836769686</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.3339357781036627</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.6972376485878415</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.5005178091445034</v>
-      </c>
-      <c r="BD4" t="n">
+      <c r="BF4" t="n">
+        <v>162</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>343</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>66</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>196</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>130</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>113</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>163</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>134</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>54</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>97</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>182</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>184</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>714.3199999999999</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>601.3199999999999</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.9172809117393561</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.9961343660443216</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>108.399786395542</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>110.0904668834308</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-1.690680487888798</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.3864213009421186</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.72467587797653</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.5360993568927498</v>
+      </c>
+      <c r="CD4" t="n">
         <v>8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>201</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>420</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>83</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>248</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>158</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>224</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>145</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>208</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>167</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>68</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>124</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>233</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>228</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>890.5599999999999</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>745.5599999999999</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.9125534380545739</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.9992028050281135</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>108.4380079133761</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>110.3574516776016</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>-1.919443764225453</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.3942543428064808</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0.729573850323382</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>0.5433514254169837</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1860,244 +1860,244 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9071298784240028</v>
+        <v>0.9087129240726243</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9516785996200355</v>
+        <v>0.94514919170816</v>
       </c>
       <c r="E6" t="n">
-        <v>100.8777662927575</v>
+        <v>100.9504844798601</v>
       </c>
       <c r="F6" t="n">
-        <v>109.6748375194346</v>
+        <v>109.0257007240447</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.797071226677051</v>
+        <v>-8.07521624418459</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2689721296935657</v>
+        <v>0.2657710606894645</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6228104268629249</v>
+        <v>0.6142560244749703</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4428661638919517</v>
+        <v>0.4357171089844654</v>
       </c>
       <c r="K6" t="n">
-        <v>6050</v>
+        <v>5250</v>
       </c>
       <c r="L6" t="n">
-        <v>2276</v>
+        <v>1987</v>
       </c>
       <c r="M6" t="n">
-        <v>566</v>
+        <v>500</v>
       </c>
       <c r="N6" t="n">
-        <v>1069</v>
+        <v>933</v>
       </c>
       <c r="O6" t="n">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="P6" t="n">
-        <v>784</v>
+        <v>682</v>
       </c>
       <c r="Q6" t="n">
-        <v>400</v>
+        <v>354</v>
       </c>
       <c r="R6" t="n">
-        <v>594</v>
+        <v>520</v>
       </c>
       <c r="S6" t="n">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="T6" t="n">
+        <v>489</v>
+      </c>
+      <c r="U6" t="n">
+        <v>398</v>
+      </c>
+      <c r="V6" t="n">
+        <v>229</v>
+      </c>
+      <c r="W6" t="n">
+        <v>347</v>
+      </c>
+      <c r="X6" t="n">
         <v>577</v>
       </c>
-      <c r="U6" t="n">
-        <v>461</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
+        <v>535</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2150</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2190.8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1970.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>239</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>432</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>97</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>343</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>178</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>266</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>98</v>
+      </c>
+      <c r="AM6" t="n">
         <v>251</v>
       </c>
-      <c r="W6" t="n">
-        <v>399</v>
-      </c>
-      <c r="X6" t="n">
-        <v>651</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>609</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2476</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2513.36</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2258.36</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>268</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>492</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>405</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>303</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>117</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>296</v>
-      </c>
       <c r="AN6" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="AO6" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="AP6" t="n">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="AQ6" t="n">
-        <v>323</v>
+        <v>285</v>
       </c>
       <c r="AR6" t="n">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="AS6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT6" t="n">
-        <v>1248.32</v>
+        <v>1084.04</v>
       </c>
       <c r="AU6" t="n">
-        <v>1131.32</v>
+        <v>986.04</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8807243205814752</v>
+        <v>0.8765458236953942</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.946111507896537</v>
+        <v>0.9357182380057207</v>
       </c>
       <c r="AX6" t="n">
-        <v>97.13794708067651</v>
+        <v>96.30846684824357</v>
       </c>
       <c r="AY6" t="n">
-        <v>109.3236451495537</v>
+        <v>107.9108809128095</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-12.18569806887719</v>
+        <v>-11.60241406456598</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2595453765061675</v>
+        <v>0.2520816829007047</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6241510288633612</v>
+        <v>0.6215065918760251</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4389036251043099</v>
+        <v>0.4326764491428264</v>
       </c>
       <c r="BD6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BE6" t="n">
-        <v>3050</v>
+        <v>2650</v>
       </c>
       <c r="BF6" t="n">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="BG6" t="n">
-        <v>577</v>
+        <v>501</v>
       </c>
       <c r="BH6" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BI6" t="n">
-        <v>379</v>
+        <v>339</v>
       </c>
       <c r="BJ6" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="BK6" t="n">
-        <v>291</v>
+        <v>254</v>
       </c>
       <c r="BL6" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="BM6" t="n">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="BN6" t="n">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="BO6" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="BP6" t="n">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="BQ6" t="n">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="BR6" t="n">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="BS6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="BT6" t="n">
-        <v>1265.04</v>
+        <v>1106.76</v>
       </c>
       <c r="BU6" t="n">
-        <v>1127.04</v>
+        <v>984.76</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9335354362665306</v>
+        <v>0.9408800244498543</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.9572456913435343</v>
+        <v>0.9545801454105993</v>
       </c>
       <c r="BX6" t="n">
-        <v>104.6175855048385</v>
+        <v>105.5925021114766</v>
       </c>
       <c r="BY6" t="n">
-        <v>110.0260298893155</v>
+        <v>110.1405205352798</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-5.408444384476913</v>
+        <v>-4.548018423803206</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.2783988828809639</v>
+        <v>0.2794604384782243</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.6214698248624888</v>
+        <v>0.6070054570739155</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.4468287026795936</v>
+        <v>0.4387577688261045</v>
       </c>
       <c r="CD6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2112,244 +2112,244 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.95608432288256</v>
+        <v>0.9541817439874302</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9478528247441815</v>
+        <v>0.9553313539133701</v>
       </c>
       <c r="E7" t="n">
-        <v>105.0765529384902</v>
+        <v>105.0516767509059</v>
       </c>
       <c r="F7" t="n">
-        <v>106.2644074972537</v>
+        <v>107.4146540648682</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.187854558763518</v>
+        <v>-2.362977313962327</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2442252621030992</v>
+        <v>0.2478907648670726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7315559380293846</v>
+        <v>0.7243566706475588</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4993951465574644</v>
+        <v>0.4970642783908503</v>
       </c>
       <c r="K7" t="n">
-        <v>6225</v>
+        <v>5225</v>
       </c>
       <c r="L7" t="n">
-        <v>2476</v>
+        <v>2069</v>
       </c>
       <c r="M7" t="n">
-        <v>582</v>
+        <v>472</v>
       </c>
       <c r="N7" t="n">
-        <v>1111</v>
+        <v>919</v>
       </c>
       <c r="O7" t="n">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="P7" t="n">
-        <v>776</v>
+        <v>653</v>
       </c>
       <c r="Q7" t="n">
-        <v>466</v>
+        <v>396</v>
       </c>
       <c r="R7" t="n">
-        <v>680</v>
+        <v>586</v>
       </c>
       <c r="S7" t="n">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="T7" t="n">
-        <v>781</v>
+        <v>649</v>
       </c>
       <c r="U7" t="n">
-        <v>522</v>
+        <v>435</v>
       </c>
       <c r="V7" t="n">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="W7" t="n">
-        <v>408</v>
+        <v>343</v>
       </c>
       <c r="X7" t="n">
-        <v>600</v>
+        <v>511</v>
       </c>
       <c r="Y7" t="n">
-        <v>656</v>
+        <v>553</v>
       </c>
       <c r="Z7" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="AA7" t="n">
-        <v>2512</v>
+        <v>2131</v>
       </c>
       <c r="AB7" t="n">
-        <v>2594.2</v>
+        <v>2172.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>2360.2</v>
+        <v>1973.84</v>
       </c>
       <c r="AD7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>3225</v>
+        <v>2625</v>
       </c>
       <c r="AF7" t="n">
+        <v>241</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>475</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>327</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>279</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>106</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>313</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>209</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>258</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>270</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1106.76</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1000.76</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9246022212041622</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.001551034889766</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>102.2095324590962</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>113.6530859517258</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-11.44355349262961</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.2586343838141796</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.6969338358176095</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.4839808717710026</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>231</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>444</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>123</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>326</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>216</v>
+      </c>
+      <c r="BK7" t="n">
         <v>307</v>
       </c>
-      <c r="AG7" t="n">
-        <v>592</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>139</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>395</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>232</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>338</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>123</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>386</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>262</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>105</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>218</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>317</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>334</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>31</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1353.72</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1230.72</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.9342595113389796</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.9843801116401869</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>102.6800469143322</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>111.0613583164649</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-8.381311402132738</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.2455385023252114</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.7106257992753169</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.484439246240039</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>275</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>519</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>143</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>381</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>234</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>342</v>
-      </c>
       <c r="BL7" t="n">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="BM7" t="n">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="BN7" t="n">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="BO7" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="BP7" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="BQ7" t="n">
+        <v>253</v>
+      </c>
+      <c r="BR7" t="n">
         <v>283</v>
       </c>
-      <c r="BR7" t="n">
-        <v>322</v>
-      </c>
       <c r="BS7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BT7" t="n">
-        <v>1240.48</v>
+        <v>1066.08</v>
       </c>
       <c r="BU7" t="n">
-        <v>1129.48</v>
+        <v>973.08</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.9793641218623789</v>
+        <v>0.9837612667706981</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.908890385388442</v>
+        <v>0.909111672936974</v>
       </c>
       <c r="BX7" t="n">
-        <v>107.6328260309254</v>
+        <v>107.8938210427157</v>
       </c>
       <c r="BY7" t="n">
-        <v>101.1476599567617</v>
+        <v>101.1762221780107</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.48516607416365</v>
+        <v>6.717598864704957</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.2428244725328459</v>
+        <v>0.2371471459199654</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7538814193670568</v>
+        <v>0.7517795054775083</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5153481068960516</v>
+        <v>0.5101476850106981</v>
       </c>
       <c r="CD7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9524962979644105</v>
+        <v>0.9459419347929299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9954261227783577</v>
+        <v>1.001979567531668</v>
       </c>
       <c r="E8" t="n">
-        <v>104.0017020145459</v>
+        <v>103.3401279584083</v>
       </c>
       <c r="F8" t="n">
-        <v>111.8191446238814</v>
+        <v>112.0248759185563</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.817442609335465</v>
+        <v>-8.684747960147986</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2356356389713557</v>
+        <v>0.2394475217963702</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7145464357661719</v>
+        <v>0.7199870869801822</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4825741375469315</v>
+        <v>0.4858848540797874</v>
       </c>
       <c r="K8" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="L8" t="n">
-        <v>2346</v>
+        <v>1952</v>
       </c>
       <c r="M8" t="n">
-        <v>498</v>
+        <v>427</v>
       </c>
       <c r="N8" t="n">
-        <v>962</v>
+        <v>820</v>
       </c>
       <c r="O8" t="n">
-        <v>275</v>
+        <v>223</v>
       </c>
       <c r="P8" t="n">
-        <v>800</v>
+        <v>653</v>
       </c>
       <c r="Q8" t="n">
-        <v>525</v>
+        <v>429</v>
       </c>
       <c r="R8" t="n">
-        <v>669</v>
+        <v>552</v>
       </c>
       <c r="S8" t="n">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="T8" t="n">
-        <v>687</v>
+        <v>566</v>
       </c>
       <c r="U8" t="n">
-        <v>453</v>
+        <v>375</v>
       </c>
       <c r="V8" t="n">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="W8" t="n">
-        <v>414</v>
+        <v>354</v>
       </c>
       <c r="X8" t="n">
-        <v>658</v>
+        <v>548</v>
       </c>
       <c r="Y8" t="n">
-        <v>657</v>
+        <v>551</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>2513</v>
+        <v>2101</v>
       </c>
       <c r="AB8" t="n">
-        <v>2470.36</v>
+        <v>2069.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>2260.36</v>
+        <v>1892.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="AF8" t="n">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="AG8" t="n">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="AH8" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="AI8" t="n">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="AJ8" t="n">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="AK8" t="n">
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="AL8" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="AM8" t="n">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="AN8" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="AO8" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="AP8" t="n">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="AQ8" t="n">
-        <v>342</v>
+        <v>296</v>
       </c>
       <c r="AR8" t="n">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="AS8" t="n">
         <v>20</v>
       </c>
       <c r="AT8" t="n">
-        <v>1251.48</v>
+        <v>1097.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1149.48</v>
+        <v>1008.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9405333518290729</v>
+        <v>0.9242880211868864</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.003555641458983</v>
+        <v>1.021273187948369</v>
       </c>
       <c r="AX8" t="n">
-        <v>102.3423958278349</v>
+        <v>100.5387005054181</v>
       </c>
       <c r="AY8" t="n">
-        <v>112.776611414705</v>
+        <v>113.7151894651335</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-10.4342155868701</v>
+        <v>-13.1764889597154</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.241510905862605</v>
+        <v>0.2407238626635178</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.7185326589865129</v>
+        <v>0.7333336521831216</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.4921665226836562</v>
+        <v>0.4953242288891429</v>
       </c>
       <c r="BD8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="BF8" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="BG8" t="n">
-        <v>488</v>
+        <v>397</v>
       </c>
       <c r="BH8" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="BI8" t="n">
-        <v>409</v>
+        <v>315</v>
       </c>
       <c r="BJ8" t="n">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="BK8" t="n">
-        <v>327</v>
+        <v>262</v>
       </c>
       <c r="BL8" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="BM8" t="n">
-        <v>336</v>
+        <v>263</v>
       </c>
       <c r="BN8" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="BO8" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="BP8" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="BQ8" t="n">
-        <v>316</v>
+        <v>252</v>
       </c>
       <c r="BR8" t="n">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="BS8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BT8" t="n">
-        <v>1218.88</v>
+        <v>972.28</v>
       </c>
       <c r="BU8" t="n">
-        <v>1110.88</v>
+        <v>884.28</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.964459244099748</v>
+        <v>0.9694003411994768</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9872966040977322</v>
+        <v>0.9810781454135754</v>
       </c>
       <c r="BX8" t="n">
-        <v>105.6610082012569</v>
+        <v>106.3750076991478</v>
       </c>
       <c r="BY8" t="n">
-        <v>110.8616778330577</v>
+        <v>110.1937029097644</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-5.20066963180083</v>
+        <v>-3.818695210616629</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2297603720801064</v>
+        <v>0.2380648191902935</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.7105602125458311</v>
+        <v>0.7055283080103313</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.4729817524102068</v>
+        <v>0.4756588647029859</v>
       </c>
       <c r="CD8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2616,244 +2616,244 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8839419550020469</v>
+        <v>0.8723044961578448</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9875859440894209</v>
+        <v>0.9853653904493135</v>
       </c>
       <c r="E9" t="n">
-        <v>97.47297443989341</v>
+        <v>96.00194118830481</v>
       </c>
       <c r="F9" t="n">
-        <v>111.5418721202008</v>
+        <v>111.5058390920437</v>
       </c>
       <c r="G9" t="n">
-        <v>-14.06889768030741</v>
+        <v>-15.50389790373888</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2383407623454296</v>
+        <v>0.2355802557542776</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6934194424268875</v>
+        <v>0.6965921489168726</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4586626914682534</v>
+        <v>0.4623154498926504</v>
       </c>
       <c r="K9" t="n">
-        <v>6050</v>
+        <v>5050</v>
       </c>
       <c r="L9" t="n">
-        <v>2215</v>
+        <v>1826</v>
       </c>
       <c r="M9" t="n">
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="N9" t="n">
-        <v>1028</v>
+        <v>867</v>
       </c>
       <c r="O9" t="n">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="P9" t="n">
-        <v>824</v>
+        <v>676</v>
       </c>
       <c r="Q9" t="n">
-        <v>400</v>
+        <v>339</v>
       </c>
       <c r="R9" t="n">
-        <v>575</v>
+        <v>480</v>
       </c>
       <c r="S9" t="n">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="T9" t="n">
-        <v>668</v>
+        <v>574</v>
       </c>
       <c r="U9" t="n">
-        <v>429</v>
+        <v>337</v>
       </c>
       <c r="V9" t="n">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="W9" t="n">
-        <v>403</v>
+        <v>339</v>
       </c>
       <c r="X9" t="n">
-        <v>667</v>
+        <v>567</v>
       </c>
       <c r="Y9" t="n">
-        <v>605</v>
+        <v>512</v>
       </c>
       <c r="Z9" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>2537</v>
+        <v>2118</v>
       </c>
       <c r="AB9" t="n">
-        <v>2508</v>
+        <v>2093.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2275</v>
+        <v>1902.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="AF9" t="n">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="AG9" t="n">
-        <v>522</v>
+        <v>421</v>
       </c>
       <c r="AH9" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="n">
-        <v>395</v>
+        <v>307</v>
       </c>
       <c r="AJ9" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="AK9" t="n">
+        <v>219</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>79</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>271</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>143</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>159</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>281</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>244</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>983.36</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>904.36</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.867140907857443</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.035799638762833</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>94.1427952507713</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>117.5835699025132</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-23.4407746517419</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.2023663101604278</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.6957926034538938</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.4431361193957445</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2650</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>232</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>446</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>107</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>369</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>188</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>261</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>112</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>303</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>194</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>102</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>180</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>286</v>
+      </c>
+      <c r="BR9" t="n">
         <v>268</v>
       </c>
-      <c r="AL9" t="n">
-        <v>101</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>323</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>91</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>195</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>342</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>295</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1229.92</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1128.92</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.8933509860103926</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.036973598397362</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>97.24971266306144</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>116.9396730929621</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-19.68996042990062</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.2066245739124996</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.6973658448282104</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.4397303407380408</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3050</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>266</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>506</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>123</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>429</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>215</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>307</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>132</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>345</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>229</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>122</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>208</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>325</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>310</v>
-      </c>
       <c r="BS9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="BT9" t="n">
-        <v>1278.08</v>
+        <v>1109.84</v>
       </c>
       <c r="BU9" t="n">
-        <v>1146.08</v>
+        <v>997.84</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.874532923993701</v>
+        <v>0.8770708853582156</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.9381982897814801</v>
+        <v>0.9388106996983723</v>
       </c>
       <c r="BX9" t="n">
-        <v>97.69623621672537</v>
+        <v>97.71807589987421</v>
       </c>
       <c r="BY9" t="n">
-        <v>106.1440711474396</v>
+        <v>105.8956260362257</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-8.44783493071421</v>
+        <v>-8.177550136351487</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.2700569507783598</v>
+        <v>0.2662392824562929</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.6894730400255645</v>
+        <v>0.697330190882699</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.4775950421984657</v>
+        <v>0.4800194472744096</v>
       </c>
       <c r="CD9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -2868,244 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9368464089056816</v>
+        <v>0.9309111154602038</v>
       </c>
       <c r="D10" t="n">
-        <v>1.017611668525854</v>
+        <v>1.01327207159717</v>
       </c>
       <c r="E10" t="n">
-        <v>106.3778655148082</v>
+        <v>106.0387469668643</v>
       </c>
       <c r="F10" t="n">
-        <v>114.3136620341632</v>
+        <v>113.9117954482826</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.93579651935504</v>
+        <v>-7.873048481418281</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3157833200931524</v>
+        <v>0.3233664377143212</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6942012265968499</v>
+        <v>0.6985995075245754</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4969784243783326</v>
+        <v>0.5028829305041638</v>
       </c>
       <c r="K10" t="n">
-        <v>6075</v>
+        <v>5250</v>
       </c>
       <c r="L10" t="n">
-        <v>2478</v>
+        <v>2137</v>
       </c>
       <c r="M10" t="n">
-        <v>544</v>
+        <v>471</v>
       </c>
       <c r="N10" t="n">
-        <v>1058</v>
+        <v>925</v>
       </c>
       <c r="O10" t="n">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="P10" t="n">
-        <v>886</v>
+        <v>765</v>
       </c>
       <c r="Q10" t="n">
-        <v>481</v>
+        <v>412</v>
       </c>
       <c r="R10" t="n">
-        <v>659</v>
+        <v>564</v>
       </c>
       <c r="S10" t="n">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="T10" t="n">
-        <v>645</v>
+        <v>569</v>
       </c>
       <c r="U10" t="n">
-        <v>459</v>
+        <v>396</v>
       </c>
       <c r="V10" t="n">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="W10" t="n">
-        <v>413</v>
+        <v>360</v>
       </c>
       <c r="X10" t="n">
-        <v>737</v>
+        <v>644</v>
       </c>
       <c r="Y10" t="n">
-        <v>653</v>
+        <v>561</v>
       </c>
       <c r="Z10" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA10" t="n">
-        <v>2675</v>
+        <v>2314</v>
       </c>
       <c r="AB10" t="n">
-        <v>2646.96</v>
+        <v>2298.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2329.96</v>
+        <v>2017.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>3050</v>
+        <v>2650</v>
       </c>
       <c r="AF10" t="n">
+        <v>236</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>476</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>119</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>206</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>293</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>145</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>271</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>205</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>323</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>283</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1166.92</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1021.92</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.887353442635865</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.0290983253107</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>101.4187448389346</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>115.051534451985</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-13.63278961305036</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.322843520260875</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.6947198965222865</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.4924235969899657</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>235</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>449</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>142</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>385</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>206</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>271</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>136</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>298</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>191</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>92</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>178</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>321</v>
+      </c>
+      <c r="BR10" t="n">
         <v>278</v>
       </c>
-      <c r="AG10" t="n">
-        <v>543</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>136</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>431</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>237</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>342</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>165</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>311</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>241</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>105</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>211</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>373</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>333</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1335.48</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1170.48</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.8999684654408375</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.028075049751616</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>102.7028952636329</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>115.1977619120508</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-12.49486664841784</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.3205384583001658</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0.6894284869783538</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.4913303507680963</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3025</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>266</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>515</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>167</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>455</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>244</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>317</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>152</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>334</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>218</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>110</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>202</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>364</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>320</v>
-      </c>
       <c r="BS10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BT10" t="n">
-        <v>1311.48</v>
+        <v>1131.24</v>
       </c>
       <c r="BU10" t="n">
-        <v>1159.48</v>
+        <v>995.24</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9737243523705258</v>
+        <v>0.9744687882845425</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.007148287300091</v>
+        <v>0.9974458178836401</v>
       </c>
       <c r="BX10" t="n">
-        <v>110.0528357659835</v>
+        <v>110.658749094794</v>
       </c>
       <c r="BY10" t="n">
-        <v>113.4295621562757</v>
+        <v>112.7720564445802</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-3.376726390292238</v>
+        <v>-2.113307349786196</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3110281818861391</v>
+        <v>0.3238893551677674</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.6989739662153454</v>
+        <v>0.7024791185268638</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.5026264979885685</v>
+        <v>0.5133422640183615</v>
       </c>
       <c r="CD10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -3120,244 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9805145820849607</v>
+        <v>0.9835297833947405</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9519229092465782</v>
+        <v>0.9574052460631601</v>
       </c>
       <c r="E11" t="n">
-        <v>110.8575108138257</v>
+        <v>111.2268249738531</v>
       </c>
       <c r="F11" t="n">
-        <v>106.9545875667412</v>
+        <v>107.1693098803709</v>
       </c>
       <c r="G11" t="n">
-        <v>3.902923247084494</v>
+        <v>4.057515093482283</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3091399770094519</v>
+        <v>0.3072742872857415</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7053227933730806</v>
+        <v>0.7094697893236824</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5049920031096561</v>
+        <v>0.5046662654850583</v>
       </c>
       <c r="K11" t="n">
-        <v>6025</v>
+        <v>5025</v>
       </c>
       <c r="L11" t="n">
-        <v>2406</v>
+        <v>2023</v>
       </c>
       <c r="M11" t="n">
-        <v>514</v>
+        <v>435</v>
       </c>
       <c r="N11" t="n">
-        <v>961</v>
+        <v>810</v>
       </c>
       <c r="O11" t="n">
+        <v>263</v>
+      </c>
+      <c r="P11" t="n">
+        <v>763</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>364</v>
+      </c>
+      <c r="R11" t="n">
+        <v>490</v>
+      </c>
+      <c r="S11" t="n">
+        <v>247</v>
+      </c>
+      <c r="T11" t="n">
+        <v>521</v>
+      </c>
+      <c r="U11" t="n">
+        <v>380</v>
+      </c>
+      <c r="V11" t="n">
+        <v>161</v>
+      </c>
+      <c r="W11" t="n">
+        <v>279</v>
+      </c>
+      <c r="X11" t="n">
+        <v>573</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>513</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1928</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2067.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1820.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2625</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>232</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>431</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>395</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>242</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>115</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>276</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>172</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>81</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>135</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>306</v>
       </c>
-      <c r="P11" t="n">
-        <v>905</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>460</v>
-      </c>
-      <c r="R11" t="n">
-        <v>612</v>
-      </c>
-      <c r="S11" t="n">
-        <v>293</v>
-      </c>
-      <c r="T11" t="n">
-        <v>630</v>
-      </c>
-      <c r="U11" t="n">
-        <v>464</v>
-      </c>
-      <c r="V11" t="n">
-        <v>190</v>
-      </c>
-      <c r="W11" t="n">
-        <v>332</v>
-      </c>
-      <c r="X11" t="n">
-        <v>697</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>628</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2300</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2467.28</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2174.28</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3025</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>266</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>498</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>147</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>453</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>212</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>279</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>134</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>316</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>204</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>91</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>154</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>354</v>
-      </c>
       <c r="AR11" t="n">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="AS11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
-        <v>1227.76</v>
+        <v>1067.48</v>
       </c>
       <c r="AU11" t="n">
-        <v>1093.76</v>
+        <v>952.48</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.9684400862711573</v>
+        <v>0.9688077057504956</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9712630487496953</v>
+        <v>0.9683084223088435</v>
       </c>
       <c r="AX11" t="n">
-        <v>108.294609354708</v>
+        <v>108.0792970554561</v>
       </c>
       <c r="AY11" t="n">
-        <v>108.9577828951275</v>
+        <v>108.2075549772338</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.6631735404195401</v>
+        <v>-0.1282579217777639</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.2710969215715447</v>
+        <v>0.2633655614245158</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.7079064608780034</v>
+        <v>0.7159053043216003</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.4814880870004095</v>
+        <v>0.4805917250087773</v>
       </c>
       <c r="BD11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BE11" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="BF11" t="n">
+        <v>203</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>379</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>135</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>368</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>182</v>
+      </c>
+      <c r="BK11" t="n">
         <v>248</v>
       </c>
-      <c r="BG11" t="n">
-        <v>463</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>159</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>452</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>248</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>333</v>
-      </c>
       <c r="BL11" t="n">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="BM11" t="n">
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="BN11" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="BO11" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="BP11" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="BQ11" t="n">
-        <v>343</v>
+        <v>267</v>
       </c>
       <c r="BR11" t="n">
-        <v>328</v>
+        <v>254</v>
       </c>
       <c r="BS11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BT11" t="n">
-        <v>1239.52</v>
+        <v>1000.12</v>
       </c>
       <c r="BU11" t="n">
-        <v>1080.52</v>
+        <v>868.12</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9925890778987639</v>
+        <v>0.9994787008426725</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9325827697434611</v>
+        <v>0.9455934717970034</v>
       </c>
       <c r="BX11" t="n">
-        <v>113.4204122729434</v>
+        <v>114.63664688545</v>
       </c>
       <c r="BY11" t="n">
-        <v>104.9513922383548</v>
+        <v>106.0445443587693</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.46902003458853</v>
+        <v>8.592102526680669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3471830324473591</v>
+        <v>0.3548420736354028</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7027391258681581</v>
+        <v>0.7024979814092718</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.5284959192189027</v>
+        <v>0.5307470176676962</v>
       </c>
       <c r="CD11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -3372,244 +3372,244 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9842067744125754</v>
+        <v>1.004732132916311</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9719272314463954</v>
+        <v>0.9783666965370409</v>
       </c>
       <c r="E12" t="n">
-        <v>109.9172666367304</v>
+        <v>111.8733182421374</v>
       </c>
       <c r="F12" t="n">
-        <v>109.1866280683066</v>
+        <v>109.7216528852768</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7306385684237255</v>
+        <v>2.151665356860573</v>
       </c>
       <c r="H12" t="n">
-        <v>0.264370199192025</v>
+        <v>0.2632112790867055</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7143962570986252</v>
+        <v>0.7161188109373329</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4889820447215385</v>
+        <v>0.4915199927464975</v>
       </c>
       <c r="K12" t="n">
-        <v>6050</v>
+        <v>5250</v>
       </c>
       <c r="L12" t="n">
-        <v>2464</v>
+        <v>2166</v>
       </c>
       <c r="M12" t="n">
-        <v>511</v>
+        <v>450</v>
       </c>
       <c r="N12" t="n">
-        <v>1061</v>
+        <v>904</v>
       </c>
       <c r="O12" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="P12" t="n">
-        <v>813</v>
+        <v>697</v>
       </c>
       <c r="Q12" t="n">
-        <v>542</v>
+        <v>486</v>
       </c>
       <c r="R12" t="n">
-        <v>676</v>
+        <v>599</v>
       </c>
       <c r="S12" t="n">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="T12" t="n">
-        <v>703</v>
+        <v>604</v>
       </c>
       <c r="U12" t="n">
-        <v>473</v>
+        <v>418</v>
       </c>
       <c r="V12" t="n">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="W12" t="n">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="X12" t="n">
-        <v>638</v>
+        <v>557</v>
       </c>
       <c r="Y12" t="n">
-        <v>631</v>
+        <v>547</v>
       </c>
       <c r="Z12" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AA12" t="n">
-        <v>2448</v>
+        <v>2134</v>
       </c>
       <c r="AB12" t="n">
-        <v>2505.44</v>
+        <v>2154.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>2238.44</v>
+        <v>1931.56</v>
       </c>
       <c r="AD12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>3050</v>
+        <v>2450</v>
       </c>
       <c r="AF12" t="n">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="AG12" t="n">
-        <v>553</v>
+        <v>438</v>
       </c>
       <c r="AH12" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="AI12" t="n">
-        <v>392</v>
+        <v>311</v>
       </c>
       <c r="AJ12" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="AK12" t="n">
-        <v>327</v>
+        <v>269</v>
       </c>
       <c r="AL12" t="n">
+        <v>115</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>289</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>147</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>135</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>263</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>244</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1002.36</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>887.36</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.9674384813015685</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.9690199491248445</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>109.1605693359916</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>109.2877208455712</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.1271515095796675</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.2763681123334968</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.715386390490225</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.4935295664432309</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2800</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>239</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>466</v>
+      </c>
+      <c r="BH12" t="n">
         <v>148</v>
       </c>
-      <c r="AM12" t="n">
-        <v>371</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>189</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>68</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>172</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>326</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>307</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1260.88</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1112.88</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.9474144604003226</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.954676895240046</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>107.1856514129457</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>107.9472768066327</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.7616253936870133</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.2786360181060001</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.7162392773749765</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.4959308662815106</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>254</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>508</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>158</v>
-      </c>
       <c r="BI12" t="n">
-        <v>421</v>
+        <v>386</v>
       </c>
       <c r="BJ12" t="n">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="BK12" t="n">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="BL12" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="BM12" t="n">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="BN12" t="n">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="BO12" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="BP12" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="BQ12" t="n">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="BR12" t="n">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="BS12" t="n">
         <v>30</v>
       </c>
       <c r="BT12" t="n">
-        <v>1244.56</v>
+        <v>1152.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>1125.56</v>
+        <v>1044.2</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.020999088424828</v>
+        <v>1.036698120014661</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.9891775676527448</v>
+        <v>0.9863781943189237</v>
       </c>
       <c r="BX12" t="n">
-        <v>112.648881860515</v>
+        <v>114.1985315902624</v>
       </c>
       <c r="BY12" t="n">
-        <v>110.4259793299805</v>
+        <v>110.0935946335959</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.222902530534465</v>
+        <v>4.104936956666495</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2501043802780497</v>
+        <v>0.2519339934465984</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.7125532368222738</v>
+        <v>0.7167465998919967</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.4820332231615664</v>
+        <v>0.4897975010064402</v>
       </c>
       <c r="CD12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -3624,244 +3624,244 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9431810964504584</v>
+        <v>0.9515919644242917</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8922507597653803</v>
+        <v>0.9016632170157765</v>
       </c>
       <c r="E13" t="n">
-        <v>108.3381482043175</v>
+        <v>109.5877821991982</v>
       </c>
       <c r="F13" t="n">
-        <v>100.6512900318567</v>
+        <v>101.5542176600192</v>
       </c>
       <c r="G13" t="n">
-        <v>7.686858172460884</v>
+        <v>8.033564539178935</v>
       </c>
       <c r="H13" t="n">
-        <v>0.345775351930968</v>
+        <v>0.3505430557519366</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7213819439604873</v>
+        <v>0.7160438771005349</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5412716457174046</v>
+        <v>0.5368214122666169</v>
       </c>
       <c r="K13" t="n">
-        <v>6025</v>
+        <v>5025</v>
       </c>
       <c r="L13" t="n">
-        <v>2368</v>
+        <v>1991</v>
       </c>
       <c r="M13" t="n">
-        <v>611</v>
+        <v>500</v>
       </c>
       <c r="N13" t="n">
-        <v>1090</v>
+        <v>906</v>
       </c>
       <c r="O13" t="n">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="P13" t="n">
-        <v>798</v>
+        <v>669</v>
       </c>
       <c r="Q13" t="n">
-        <v>420</v>
+        <v>358</v>
       </c>
       <c r="R13" t="n">
-        <v>586</v>
+        <v>491</v>
       </c>
       <c r="S13" t="n">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="T13" t="n">
-        <v>734</v>
+        <v>582</v>
       </c>
       <c r="U13" t="n">
-        <v>496</v>
+        <v>394</v>
       </c>
       <c r="V13" t="n">
+        <v>166</v>
+      </c>
+      <c r="W13" t="n">
+        <v>304</v>
+      </c>
+      <c r="X13" t="n">
+        <v>544</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>506</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1868</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2095.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1816.04</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>228</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>407</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>99</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>265</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>141</v>
+      </c>
+      <c r="AK13" t="n">
         <v>195</v>
       </c>
-      <c r="W13" t="n">
-        <v>371</v>
-      </c>
-      <c r="X13" t="n">
-        <v>638</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>606</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>109</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2235</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2516.84</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2185.84</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>321</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>557</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>122</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>364</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AL13" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>268</v>
+      </c>
+      <c r="AN13" t="n">
         <v>181</v>
       </c>
-      <c r="AK13" t="n">
-        <v>254</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>145</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>386</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>266</v>
-      </c>
       <c r="AO13" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="AQ13" t="n">
-        <v>319</v>
+        <v>246</v>
       </c>
       <c r="AR13" t="n">
-        <v>285</v>
+        <v>211</v>
       </c>
       <c r="AS13" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="AT13" t="n">
-        <v>1244.76</v>
+        <v>920.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>1099.76</v>
+        <v>808.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9569025577027492</v>
+        <v>0.9714552370892989</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8798297497036599</v>
+        <v>0.8856373843129653</v>
       </c>
       <c r="AX13" t="n">
-        <v>108.1414895177445</v>
+        <v>110.5164153930311</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.3623446949506</v>
+        <v>101.876174900982</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.779144822793855</v>
+        <v>8.640240492049131</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.3320267504935167</v>
+        <v>0.353111873344149</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.6930330032026345</v>
+        <v>0.686351863531231</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5370504119915659</v>
+        <v>0.5404371619712222</v>
       </c>
       <c r="BD13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BE13" t="n">
-        <v>3025</v>
+        <v>2825</v>
       </c>
       <c r="BF13" t="n">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="BG13" t="n">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="BH13" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="BI13" t="n">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="BJ13" t="n">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="BK13" t="n">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="BL13" t="n">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="BM13" t="n">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="BN13" t="n">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="BO13" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="BP13" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="BQ13" t="n">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="BR13" t="n">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="BS13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BT13" t="n">
-        <v>1272.08</v>
+        <v>1174.24</v>
       </c>
       <c r="BU13" t="n">
-        <v>1086.08</v>
+        <v>1007.24</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.9294596351981675</v>
+        <v>0.9359851073303577</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.9046717698271004</v>
+        <v>0.9142549427108421</v>
       </c>
       <c r="BX13" t="n">
-        <v>108.5348068908906</v>
+        <v>108.8581418326151</v>
       </c>
       <c r="BY13" t="n">
-        <v>99.94023536876274</v>
+        <v>101.3012512564056</v>
       </c>
       <c r="BZ13" t="n">
-        <v>8.594571522127913</v>
+        <v>7.556890576209494</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.3595239533684192</v>
+        <v>0.3485246990723411</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.7497308847183396</v>
+        <v>0.7393733163335593</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5454928794432434</v>
+        <v>0.5339804660701418</v>
       </c>
       <c r="CD13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -3876,244 +3876,244 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.016816851948949</v>
+        <v>1.028670537269259</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9293017475586437</v>
+        <v>0.9190865287410088</v>
       </c>
       <c r="E14" t="n">
-        <v>116.7801844268815</v>
+        <v>117.7476046919323</v>
       </c>
       <c r="F14" t="n">
-        <v>103.576679395756</v>
+        <v>102.7277481173657</v>
       </c>
       <c r="G14" t="n">
-        <v>13.20350503112543</v>
+        <v>15.01985657456663</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3513689208118738</v>
+        <v>0.3481326878394413</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7385661131499969</v>
+        <v>0.7337456576911964</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5461217371426472</v>
+        <v>0.5442575441697856</v>
       </c>
       <c r="K14" t="n">
-        <v>6200</v>
+        <v>5200</v>
       </c>
       <c r="L14" t="n">
-        <v>2802</v>
+        <v>2383</v>
       </c>
       <c r="M14" t="n">
-        <v>650</v>
+        <v>560</v>
       </c>
       <c r="N14" t="n">
-        <v>1219</v>
+        <v>1032</v>
       </c>
       <c r="O14" t="n">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="P14" t="n">
-        <v>888</v>
+        <v>732</v>
       </c>
       <c r="Q14" t="n">
-        <v>542</v>
+        <v>462</v>
       </c>
       <c r="R14" t="n">
-        <v>709</v>
+        <v>604</v>
       </c>
       <c r="S14" t="n">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="T14" t="n">
-        <v>762</v>
+        <v>641</v>
       </c>
       <c r="U14" t="n">
-        <v>598</v>
+        <v>515</v>
       </c>
       <c r="V14" t="n">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="W14" t="n">
-        <v>342</v>
+        <v>292</v>
       </c>
       <c r="X14" t="n">
-        <v>671</v>
+        <v>557</v>
       </c>
       <c r="Y14" t="n">
-        <v>682</v>
+        <v>579</v>
       </c>
       <c r="Z14" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>2426</v>
+        <v>2027</v>
       </c>
       <c r="AB14" t="n">
-        <v>2760.96</v>
+        <v>2321.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>2399.96</v>
+        <v>2024.76</v>
       </c>
       <c r="AD14" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="AF14" t="n">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="AG14" t="n">
-        <v>601</v>
+        <v>521</v>
       </c>
       <c r="AH14" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="AI14" t="n">
-        <v>404</v>
+        <v>339</v>
       </c>
       <c r="AJ14" t="n">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="AK14" t="n">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="AL14" t="n">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="AM14" t="n">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="AN14" t="n">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="AO14" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="AP14" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="AQ14" t="n">
-        <v>337</v>
+        <v>294</v>
       </c>
       <c r="AR14" t="n">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AT14" t="n">
-        <v>1328.96</v>
+        <v>1151.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1153.96</v>
+        <v>1003.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.006934724400332</v>
+        <v>1.021584059554004</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.9140911932109624</v>
+        <v>0.9151161035642108</v>
       </c>
       <c r="AX14" t="n">
-        <v>115.7618363722308</v>
+        <v>117.0203084119286</v>
       </c>
       <c r="AY14" t="n">
-        <v>103.9197217055399</v>
+        <v>104.4034877105762</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11.84211466669091</v>
+        <v>12.61682070135243</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3574315586183491</v>
+        <v>0.3568654736194627</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6831009358617399</v>
+        <v>0.6709071649833965</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.521437091744465</v>
+        <v>0.5161060537516851</v>
       </c>
       <c r="BD14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BE14" t="n">
-        <v>3200</v>
+        <v>2600</v>
       </c>
       <c r="BF14" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="BG14" t="n">
-        <v>618</v>
+        <v>511</v>
       </c>
       <c r="BH14" t="n">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="BI14" t="n">
-        <v>484</v>
+        <v>393</v>
       </c>
       <c r="BJ14" t="n">
-        <v>278</v>
+        <v>220</v>
       </c>
       <c r="BK14" t="n">
-        <v>375</v>
+        <v>299</v>
       </c>
       <c r="BL14" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="BM14" t="n">
-        <v>421</v>
+        <v>354</v>
       </c>
       <c r="BN14" t="n">
-        <v>337</v>
+        <v>282</v>
       </c>
       <c r="BO14" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="BP14" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="BQ14" t="n">
-        <v>334</v>
+        <v>263</v>
       </c>
       <c r="BR14" t="n">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="BS14" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BT14" t="n">
-        <v>1432</v>
+        <v>1170.56</v>
       </c>
       <c r="BU14" t="n">
-        <v>1246</v>
+        <v>1021.56</v>
       </c>
       <c r="BV14" t="n">
-        <v>1.026081346525777</v>
+        <v>1.035757014984514</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.943561642259595</v>
+        <v>0.9230569539178066</v>
       </c>
       <c r="BX14" t="n">
-        <v>117.7348857281165</v>
+        <v>118.474900971936</v>
       </c>
       <c r="BY14" t="n">
-        <v>103.2550772303337</v>
+        <v>101.0520085241552</v>
       </c>
       <c r="BZ14" t="n">
-        <v>14.47980849778279</v>
+        <v>17.42289244778084</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3456851978683031</v>
+        <v>0.3393999020594199</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7905647168577374</v>
+        <v>0.7965841503989961</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5692635922034429</v>
+        <v>0.5724090345878862</v>
       </c>
       <c r="CD14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4128,244 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8756436102594356</v>
+        <v>0.8696020133271409</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9843744358736066</v>
+        <v>0.9988797880295546</v>
       </c>
       <c r="E15" t="n">
-        <v>99.25389039677863</v>
+        <v>98.42777545090779</v>
       </c>
       <c r="F15" t="n">
-        <v>110.9897842371766</v>
+        <v>113.0500217719582</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.73589384039792</v>
+        <v>-14.62224632105038</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2884059993896494</v>
+        <v>0.2897070823085149</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7071292887948688</v>
+        <v>0.6961633251289732</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4931164598657798</v>
+        <v>0.489443645147027</v>
       </c>
       <c r="K15" t="n">
-        <v>6025</v>
+        <v>5000</v>
       </c>
       <c r="L15" t="n">
-        <v>2289</v>
+        <v>1886</v>
       </c>
       <c r="M15" t="n">
-        <v>495</v>
+        <v>426</v>
       </c>
       <c r="N15" t="n">
-        <v>1030</v>
+        <v>889</v>
       </c>
       <c r="O15" t="n">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="P15" t="n">
-        <v>910</v>
+        <v>715</v>
       </c>
       <c r="Q15" t="n">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="R15" t="n">
-        <v>541</v>
+        <v>444</v>
       </c>
       <c r="S15" t="n">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="T15" t="n">
-        <v>722</v>
+        <v>585</v>
       </c>
       <c r="U15" t="n">
-        <v>478</v>
+        <v>397</v>
       </c>
       <c r="V15" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="W15" t="n">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="X15" t="n">
-        <v>629</v>
+        <v>525</v>
       </c>
       <c r="Y15" t="n">
-        <v>619</v>
+        <v>512</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AA15" t="n">
-        <v>2574</v>
+        <v>2176</v>
       </c>
       <c r="AB15" t="n">
-        <v>2620.04</v>
+        <v>2175.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>2308.04</v>
+        <v>1918.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="AF15" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="AG15" t="n">
-        <v>525</v>
+        <v>472</v>
       </c>
       <c r="AH15" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="AI15" t="n">
-        <v>454</v>
+        <v>383</v>
       </c>
       <c r="AJ15" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="AK15" t="n">
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="AL15" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AM15" t="n">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="AN15" t="n">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AP15" t="n">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="AQ15" t="n">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="AR15" t="n">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>1320.08</v>
+        <v>1149.92</v>
       </c>
       <c r="AU15" t="n">
-        <v>1160.08</v>
+        <v>1009.92</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.843713158341048</v>
+        <v>0.8334663071542632</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.006573460733275</v>
+        <v>1.012529632105617</v>
       </c>
       <c r="AX15" t="n">
-        <v>95.89340288502628</v>
+        <v>94.77910663484582</v>
       </c>
       <c r="AY15" t="n">
-        <v>114.200930919761</v>
+        <v>115.3239094597772</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-18.30752803473473</v>
+        <v>-20.54480282493135</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.2963252103298367</v>
+        <v>0.3001908072406798</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.694708203673721</v>
+        <v>0.6818087306150967</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.4869281973932811</v>
+        <v>0.4816305823344414</v>
       </c>
       <c r="BD15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>3025</v>
+        <v>2400</v>
       </c>
       <c r="BF15" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="BG15" t="n">
-        <v>505</v>
+        <v>417</v>
       </c>
       <c r="BH15" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="BI15" t="n">
-        <v>456</v>
+        <v>332</v>
       </c>
       <c r="BJ15" t="n">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="BK15" t="n">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="BL15" t="n">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="BM15" t="n">
-        <v>376</v>
+        <v>295</v>
       </c>
       <c r="BN15" t="n">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="BO15" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="BP15" t="n">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="BQ15" t="n">
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="BR15" t="n">
-        <v>313</v>
+        <v>246</v>
       </c>
       <c r="BS15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BT15" t="n">
-        <v>1299.96</v>
+        <v>1025.44</v>
       </c>
       <c r="BU15" t="n">
-        <v>1147.96</v>
+        <v>908.4400000000001</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.907574062177823</v>
+        <v>0.9087490283477585</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9621754110139388</v>
+        <v>0.9840924569471531</v>
       </c>
       <c r="BX15" t="n">
-        <v>102.614377908531</v>
+        <v>102.3805000016416</v>
       </c>
       <c r="BY15" t="n">
-        <v>107.7786375545921</v>
+        <v>110.5866434434876</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-5.164259646061113</v>
+        <v>-8.206143441846001</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2804867884494621</v>
+        <v>0.2783497136320031</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.7195503739160164</v>
+        <v>0.7117141358523394</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.4993047223382787</v>
+        <v>0.4979077965273281</v>
       </c>
       <c r="CD15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -4380,244 +4380,244 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.066524328506282</v>
+        <v>1.066378724431395</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8896719042791157</v>
+        <v>0.8926546426226705</v>
       </c>
       <c r="E16" t="n">
-        <v>120.2137292851303</v>
+        <v>119.72513940432</v>
       </c>
       <c r="F16" t="n">
-        <v>99.83030193897015</v>
+        <v>100.4061841698055</v>
       </c>
       <c r="G16" t="n">
-        <v>20.38342734616017</v>
+        <v>19.31895523451453</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3276629450534852</v>
+        <v>0.3201634994321476</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7092363823263899</v>
+        <v>0.7036812862599849</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5255498135838617</v>
+        <v>0.5196219946664736</v>
       </c>
       <c r="K16" t="n">
-        <v>6075</v>
+        <v>5050</v>
       </c>
       <c r="L16" t="n">
-        <v>2765</v>
+        <v>2313</v>
       </c>
       <c r="M16" t="n">
-        <v>658</v>
+        <v>557</v>
       </c>
       <c r="N16" t="n">
-        <v>1127</v>
+        <v>965</v>
       </c>
       <c r="O16" t="n">
-        <v>307</v>
+        <v>253</v>
       </c>
       <c r="P16" t="n">
-        <v>812</v>
+        <v>661</v>
       </c>
       <c r="Q16" t="n">
-        <v>528</v>
+        <v>440</v>
       </c>
       <c r="R16" t="n">
-        <v>707</v>
+        <v>579</v>
       </c>
       <c r="S16" t="n">
+        <v>235</v>
+      </c>
+      <c r="T16" t="n">
+        <v>575</v>
+      </c>
+      <c r="U16" t="n">
+        <v>507</v>
+      </c>
+      <c r="V16" t="n">
+        <v>229</v>
+      </c>
+      <c r="W16" t="n">
+        <v>288</v>
+      </c>
+      <c r="X16" t="n">
+        <v>525</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>566</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1915</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2168.76</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1933.76</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2625</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>289</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>498</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>326</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>229</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>308</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>115</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>276</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>247</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>115</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>275</v>
+      </c>
+      <c r="AR16" t="n">
         <v>290</v>
       </c>
-      <c r="T16" t="n">
-        <v>694</v>
-      </c>
-      <c r="U16" t="n">
-        <v>588</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="AS16" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1109.52</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>994.52</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.072980927361294</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.9092415883348237</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>119.841915852236</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>103.779003406811</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16.06291244542495</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.3129456436720919</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.6663331153587108</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.4988553256284053</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2425</v>
+      </c>
+      <c r="BF16" t="n">
         <v>268</v>
       </c>
-      <c r="W16" t="n">
-        <v>344</v>
-      </c>
-      <c r="X16" t="n">
-        <v>630</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>682</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>68</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2287</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2594.08</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2304.08</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>3050</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>326</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>559</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>151</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>389</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>274</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>372</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>134</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>323</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>275</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>128</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>177</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>318</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>340</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1288.68</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1154.68</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.071076907747477</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.9271155551140439</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>119.6353514621817</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>105.1175982168604</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>14.51775324532135</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0.3143941610237494</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0.6792846769890436</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.5048466797518835</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>3025</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>332</v>
-      </c>
       <c r="BG16" t="n">
-        <v>568</v>
+        <v>467</v>
       </c>
       <c r="BH16" t="n">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="BI16" t="n">
-        <v>423</v>
+        <v>335</v>
       </c>
       <c r="BJ16" t="n">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="BK16" t="n">
-        <v>335</v>
+        <v>271</v>
       </c>
       <c r="BL16" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="BM16" t="n">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="BN16" t="n">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="BO16" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="BP16" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="BQ16" t="n">
-        <v>312</v>
+        <v>250</v>
       </c>
       <c r="BR16" t="n">
-        <v>342</v>
+        <v>276</v>
       </c>
       <c r="BS16" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BT16" t="n">
-        <v>1305.4</v>
+        <v>1059.24</v>
       </c>
       <c r="BU16" t="n">
-        <v>1149.4</v>
+        <v>939.24</v>
       </c>
       <c r="BV16" t="n">
-        <v>1.061971749265086</v>
+        <v>1.059226337924005</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8522282534441883</v>
+        <v>0.8746854514345053</v>
       </c>
       <c r="BX16" t="n">
-        <v>120.7921071080789</v>
+        <v>119.5986315857444</v>
       </c>
       <c r="BY16" t="n">
-        <v>94.54300566107989</v>
+        <v>96.75229666304953</v>
       </c>
       <c r="BZ16" t="n">
-        <v>26.24910144699898</v>
+        <v>22.8463349226949</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.3409317290832209</v>
+        <v>0.327982843172208</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.739188087663736</v>
+        <v>0.7441418047363652</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.5462529474158399</v>
+        <v>0.5421192194577145</v>
       </c>
       <c r="CD16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -4632,244 +4632,244 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.022935489516515</v>
+        <v>1.018305301051677</v>
       </c>
       <c r="D17" t="n">
-        <v>0.962713746696065</v>
+        <v>0.9694079712113691</v>
       </c>
       <c r="E17" t="n">
-        <v>114.4655295552824</v>
+        <v>114.3791303056464</v>
       </c>
       <c r="F17" t="n">
-        <v>108.531192867698</v>
+        <v>108.7815540913745</v>
       </c>
       <c r="G17" t="n">
-        <v>5.93433668758446</v>
+        <v>5.597576214271908</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2987571804442724</v>
+        <v>0.2992750500995604</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7062563511881862</v>
+        <v>0.7132392231574252</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5103790444159573</v>
+        <v>0.5107044931473004</v>
       </c>
       <c r="K17" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="L17" t="n">
-        <v>2539</v>
+        <v>2113</v>
       </c>
       <c r="M17" t="n">
-        <v>549</v>
+        <v>457</v>
       </c>
       <c r="N17" t="n">
-        <v>965</v>
+        <v>821</v>
       </c>
       <c r="O17" t="n">
+        <v>258</v>
+      </c>
+      <c r="P17" t="n">
+        <v>716</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>425</v>
+      </c>
+      <c r="R17" t="n">
+        <v>561</v>
+      </c>
+      <c r="S17" t="n">
+        <v>225</v>
+      </c>
+      <c r="T17" t="n">
+        <v>567</v>
+      </c>
+      <c r="U17" t="n">
+        <v>387</v>
+      </c>
+      <c r="V17" t="n">
+        <v>155</v>
+      </c>
+      <c r="W17" t="n">
+        <v>290</v>
+      </c>
+      <c r="X17" t="n">
+        <v>546</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>584</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2073.84</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1848.84</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>246</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>446</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>126</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>353</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>250</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>109</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>299</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>211</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>87</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>159</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>283</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>275</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1068</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>959</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.9898594810026412</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.978129815162451</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>110.2603911190724</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>109.4098950969893</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.850496022083112</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.2794114499114524</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.7254499096620687</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.5086079485838687</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>211</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>375</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>132</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>363</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>235</v>
+      </c>
+      <c r="BK17" t="n">
         <v>311</v>
       </c>
-      <c r="P17" t="n">
-        <v>859</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>508</v>
-      </c>
-      <c r="R17" t="n">
-        <v>672</v>
-      </c>
-      <c r="S17" t="n">
-        <v>262</v>
-      </c>
-      <c r="T17" t="n">
-        <v>681</v>
-      </c>
-      <c r="U17" t="n">
-        <v>476</v>
-      </c>
-      <c r="V17" t="n">
-        <v>194</v>
-      </c>
-      <c r="W17" t="n">
-        <v>362</v>
-      </c>
-      <c r="X17" t="n">
-        <v>651</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>689</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>74</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2414</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2481.68</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2219.68</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>278</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>493</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>151</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>411</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>226</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>297</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>121</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>341</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>247</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>194</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>328</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>319</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>31</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1228.68</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1107.68</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.002864804508091</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.9766604326316545</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>111.2264350797026</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>110.1620942098723</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.064340869830321</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0.2797634275300964</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0.7096996860168905</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0.5048446121457768</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>3000</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>271</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>472</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>160</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>448</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>282</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>375</v>
-      </c>
       <c r="BL17" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="BM17" t="n">
-        <v>340</v>
+        <v>268</v>
       </c>
       <c r="BN17" t="n">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="BO17" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="BP17" t="n">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="BQ17" t="n">
-        <v>323</v>
+        <v>263</v>
       </c>
       <c r="BR17" t="n">
-        <v>370</v>
+        <v>309</v>
       </c>
       <c r="BS17" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="BT17" t="n">
-        <v>1253</v>
+        <v>1005.84</v>
       </c>
       <c r="BU17" t="n">
-        <v>1112</v>
+        <v>889.84</v>
       </c>
       <c r="BV17" t="n">
-        <v>1.043006174524939</v>
+        <v>1.0491216061048</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.9487670607604751</v>
+        <v>0.9599593069310303</v>
       </c>
       <c r="BX17" t="n">
-        <v>117.7046240308623</v>
+        <v>118.8410977577682</v>
       </c>
       <c r="BY17" t="n">
-        <v>106.9002915255237</v>
+        <v>108.1008513352918</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.8043325053386</v>
+        <v>10.74024642247644</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.3177509333584484</v>
+        <v>0.3207939503033441</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.7028130163594822</v>
+        <v>0.700010979444062</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.5159134766861377</v>
+        <v>0.5129757497576845</v>
       </c>
       <c r="CD17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -4884,244 +4884,244 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8697930569932759</v>
+        <v>0.8694043673832872</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9570889966587213</v>
+        <v>0.9784362771082007</v>
       </c>
       <c r="E18" t="n">
-        <v>97.82110442894506</v>
+        <v>98.21758340793994</v>
       </c>
       <c r="F18" t="n">
-        <v>110.2786233167517</v>
+        <v>112.0074210073753</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.4575188878066</v>
+        <v>-13.78983759943529</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2690633968524361</v>
+        <v>0.281766605714072</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6421763069005689</v>
+        <v>0.643490846029693</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4473833365828167</v>
+        <v>0.4502452252408753</v>
       </c>
       <c r="K18" t="n">
-        <v>6025</v>
+        <v>5025</v>
       </c>
       <c r="L18" t="n">
-        <v>2187</v>
+        <v>1824</v>
       </c>
       <c r="M18" t="n">
-        <v>489</v>
+        <v>391</v>
       </c>
       <c r="N18" t="n">
-        <v>1055</v>
+        <v>853</v>
       </c>
       <c r="O18" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="P18" t="n">
-        <v>805</v>
+        <v>691</v>
       </c>
       <c r="Q18" t="n">
-        <v>474</v>
+        <v>397</v>
       </c>
       <c r="R18" t="n">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="S18" t="n">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="T18" t="n">
-        <v>628</v>
+        <v>498</v>
       </c>
       <c r="U18" t="n">
-        <v>393</v>
+        <v>330</v>
       </c>
       <c r="V18" t="n">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="W18" t="n">
-        <v>373</v>
+        <v>318</v>
       </c>
       <c r="X18" t="n">
-        <v>607</v>
+        <v>496</v>
       </c>
       <c r="Y18" t="n">
-        <v>630</v>
+        <v>529</v>
       </c>
       <c r="Z18" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2118</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2105.32</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1862.32</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>202</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>430</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>116</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>364</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>204</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>283</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>113</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>261</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>163</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>152</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>258</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>272</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1070.52</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>957.52</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.8972871912063265</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.014775345764666</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>100.3118107378594</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>116.0086531193324</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-15.69684238147296</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.2559289690705702</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.6495080216317992</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.4386711068771499</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2425</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>189</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>423</v>
+      </c>
+      <c r="BH18" t="n">
         <v>99</v>
       </c>
-      <c r="AA18" t="n">
-        <v>2495</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2522.08</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2242.08</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>248</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>518</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>124</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>399</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>227</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>318</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>123</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>185</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>93</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>178</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>304</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>311</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>37</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1234.92</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1111.92</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.8906519044180929</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.005018274172334</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>98.99236851216686</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>115.9315677265166</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-16.93919921434978</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0.2421559837208099</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0.6342282734022139</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0.4270099087884794</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>3025</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>241</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>537</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>121</v>
-      </c>
       <c r="BI18" t="n">
-        <v>406</v>
+        <v>327</v>
       </c>
       <c r="BJ18" t="n">
-        <v>247</v>
+        <v>193</v>
       </c>
       <c r="BK18" t="n">
-        <v>339</v>
+        <v>270</v>
       </c>
       <c r="BL18" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="BM18" t="n">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="BN18" t="n">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="BO18" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="BP18" t="n">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="BQ18" t="n">
-        <v>303</v>
+        <v>238</v>
       </c>
       <c r="BR18" t="n">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="BS18" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="BT18" t="n">
-        <v>1287.16</v>
+        <v>1034.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>1130.16</v>
+        <v>904.8</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8489342095684588</v>
+        <v>0.8391979749083278</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9091597191451085</v>
+        <v>0.9390689527303638</v>
       </c>
       <c r="BX18" t="n">
-        <v>96.64984034572326</v>
+        <v>95.94883713386052</v>
       </c>
       <c r="BY18" t="n">
-        <v>104.6256789069867</v>
+        <v>107.6727528860883</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-7.975838561263433</v>
+        <v>-11.72391575222783</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.2959708099840623</v>
+        <v>0.3097573787445323</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.6501243403989243</v>
+        <v>0.6369722391274116</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.4677567643771539</v>
+        <v>0.4627838534682442</v>
       </c>
       <c r="CD18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -5136,244 +5136,244 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9836569987456442</v>
+        <v>0.992032740863957</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8742967563916912</v>
+        <v>0.8695293686756513</v>
       </c>
       <c r="E19" t="n">
-        <v>111.7293681151609</v>
+        <v>113.0043073993123</v>
       </c>
       <c r="F19" t="n">
-        <v>98.79320888978441</v>
+        <v>97.74287415486252</v>
       </c>
       <c r="G19" t="n">
-        <v>12.93615922537647</v>
+        <v>15.26143324444977</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3156153595262668</v>
+        <v>0.3248090494829252</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7073649542166526</v>
+        <v>0.7171648285413645</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5175435146552414</v>
+        <v>0.5271472881554786</v>
       </c>
       <c r="K19" t="n">
-        <v>6000</v>
+        <v>5200</v>
       </c>
       <c r="L19" t="n">
-        <v>2493</v>
+        <v>2183</v>
       </c>
       <c r="M19" t="n">
-        <v>597</v>
+        <v>528</v>
       </c>
       <c r="N19" t="n">
-        <v>1132</v>
+        <v>989</v>
       </c>
       <c r="O19" t="n">
+        <v>257</v>
+      </c>
+      <c r="P19" t="n">
+        <v>720</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>356</v>
+      </c>
+      <c r="R19" t="n">
+        <v>515</v>
+      </c>
+      <c r="S19" t="n">
+        <v>275</v>
+      </c>
+      <c r="T19" t="n">
+        <v>608</v>
+      </c>
+      <c r="U19" t="n">
+        <v>384</v>
+      </c>
+      <c r="V19" t="n">
+        <v>206</v>
+      </c>
+      <c r="W19" t="n">
+        <v>270</v>
+      </c>
+      <c r="X19" t="n">
+        <v>553</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>510</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1874</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2205.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1930.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>235</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>452</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>126</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>342</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>163</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>236</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>129</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>284</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>121</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>263</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>235</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1018.84</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>889.84</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.9936248790724237</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.8659893271862308</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>113.5978811475987</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>95.98630174244708</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>17.61157940515162</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.315133038938186</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.7487721713529848</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.5325416686012221</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2800</v>
+      </c>
+      <c r="BF19" t="n">
         <v>293</v>
       </c>
-      <c r="P19" t="n">
-        <v>825</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>420</v>
-      </c>
-      <c r="R19" t="n">
-        <v>602</v>
-      </c>
-      <c r="S19" t="n">
-        <v>309</v>
-      </c>
-      <c r="T19" t="n">
-        <v>697</v>
-      </c>
-      <c r="U19" t="n">
-        <v>448</v>
-      </c>
-      <c r="V19" t="n">
-        <v>237</v>
-      </c>
-      <c r="W19" t="n">
-        <v>318</v>
-      </c>
-      <c r="X19" t="n">
-        <v>643</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>599</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2182</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2539.88</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2230.88</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>278</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>552</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>418</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>223</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>314</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>152</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>343</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>220</v>
-      </c>
-      <c r="AO19" t="n">
+      <c r="BG19" t="n">
+        <v>537</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>131</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>378</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>193</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>279</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>146</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>324</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>204</v>
+      </c>
+      <c r="BO19" t="n">
         <v>115</v>
       </c>
-      <c r="AP19" t="n">
-        <v>162</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>333</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>308</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1270.16</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1118.16</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.9687592714227079</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.8781379451694071</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>109.9396546634856</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>98.49452898468466</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>11.44512567880098</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0.2999644273956418</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0.7218814549057829</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0.5119005625574621</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>319</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>580</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>143</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>407</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>197</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>288</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>157</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>354</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>228</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>122</v>
-      </c>
       <c r="BP19" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="BQ19" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="BR19" t="n">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="BS19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BT19" t="n">
-        <v>1269.72</v>
+        <v>1186.76</v>
       </c>
       <c r="BU19" t="n">
-        <v>1112.72</v>
+        <v>1040.76</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.9985547260685805</v>
+        <v>0.9906680509709858</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.8704555676139751</v>
+        <v>0.8725636899522975</v>
       </c>
       <c r="BX19" t="n">
-        <v>113.5190815668361</v>
+        <v>112.4955299007811</v>
       </c>
       <c r="BY19" t="n">
-        <v>99.09188879488417</v>
+        <v>99.24850765121865</v>
       </c>
       <c r="BZ19" t="n">
-        <v>14.42719277195196</v>
+        <v>13.24702224956247</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.3312662916568919</v>
+        <v>0.3331027728069874</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.6928484535275222</v>
+        <v>0.6900728204171187</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.5231864667530209</v>
+        <v>0.5225235334876986</v>
       </c>
       <c r="CD19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,244 +852,244 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9513670599526608</v>
+        <v>0.9417834950806202</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9213215134648567</v>
+        <v>0.9183054859729876</v>
       </c>
       <c r="E2" t="n">
-        <v>107.8296407911593</v>
+        <v>107.1991803011638</v>
       </c>
       <c r="F2" t="n">
-        <v>101.7138406744517</v>
+        <v>101.3236065030316</v>
       </c>
       <c r="G2" t="n">
-        <v>6.115800116707605</v>
+        <v>5.875573798132121</v>
       </c>
       <c r="H2" t="n">
-        <v>0.306750052550015</v>
+        <v>0.3116444558114409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7508789930976755</v>
+        <v>0.7498460431022346</v>
       </c>
       <c r="J2" t="n">
-        <v>0.525500538861946</v>
+        <v>0.5255462203022425</v>
       </c>
       <c r="K2" t="n">
-        <v>5225</v>
+        <v>6025</v>
       </c>
       <c r="L2" t="n">
-        <v>2163</v>
+        <v>2462</v>
       </c>
       <c r="M2" t="n">
-        <v>450</v>
+        <v>512</v>
       </c>
       <c r="N2" t="n">
-        <v>840</v>
+        <v>963</v>
       </c>
       <c r="O2" t="n">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="P2" t="n">
-        <v>852</v>
+        <v>980</v>
       </c>
       <c r="Q2" t="n">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="R2" t="n">
-        <v>562</v>
+        <v>632</v>
       </c>
       <c r="S2" t="n">
-        <v>272</v>
+        <v>321</v>
       </c>
       <c r="T2" t="n">
-        <v>625</v>
+        <v>714</v>
       </c>
       <c r="U2" t="n">
-        <v>404</v>
+        <v>463</v>
       </c>
       <c r="V2" t="n">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="W2" t="n">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>540</v>
+        <v>619</v>
       </c>
       <c r="Y2" t="n">
-        <v>553</v>
+        <v>629</v>
       </c>
       <c r="Z2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA2" t="n">
-        <v>2048</v>
+        <v>2344</v>
       </c>
       <c r="AB2" t="n">
-        <v>2281.28</v>
+        <v>2621.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2009.28</v>
+        <v>2300.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="AF2" t="n">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="AG2" t="n">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="AH2" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="AI2" t="n">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="AJ2" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="AK2" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="AL2" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AM2" t="n">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="AN2" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AO2" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="AQ2" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="AR2" t="n">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1251.2</v>
+        <v>1337.76</v>
       </c>
       <c r="AU2" t="n">
-        <v>1086.2</v>
+        <v>1162.76</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.9307812442451924</v>
+        <v>0.9218714903158456</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9293227146817394</v>
+        <v>0.9255886402081579</v>
       </c>
       <c r="AX2" t="n">
-        <v>107.028217245648</v>
+        <v>105.9013622192401</v>
       </c>
       <c r="AY2" t="n">
-        <v>102.7693545830184</v>
+        <v>102.5074158852856</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.258862662629544</v>
+        <v>3.393946333954433</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.3322579671319167</v>
+        <v>0.329155055037408</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.7517852599846179</v>
+        <v>0.742691883677951</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.5313252291556706</v>
+        <v>0.5243188477584073</v>
       </c>
       <c r="BD2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE2" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="BF2" t="n">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="BG2" t="n">
-        <v>364</v>
+        <v>459</v>
       </c>
       <c r="BH2" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="BI2" t="n">
-        <v>371</v>
+        <v>467</v>
       </c>
       <c r="BJ2" t="n">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="BK2" t="n">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="BL2" t="n">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="BM2" t="n">
-        <v>285</v>
+        <v>358</v>
       </c>
       <c r="BN2" t="n">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="BO2" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="BP2" t="n">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="BQ2" t="n">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="BR2" t="n">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BT2" t="n">
-        <v>1030.08</v>
+        <v>1283.32</v>
       </c>
       <c r="BU2" t="n">
-        <v>923.08</v>
+        <v>1137.32</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9753838449447071</v>
+        <v>0.9616954998453946</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9119867787118268</v>
+        <v>0.911022331737817</v>
       </c>
       <c r="BX2" t="n">
-        <v>108.7646349275893</v>
+        <v>108.4969983830874</v>
       </c>
       <c r="BY2" t="n">
-        <v>100.4824077811239</v>
+        <v>100.1397971207776</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.282227146465344</v>
+        <v>8.357201262309808</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2769908188711299</v>
+        <v>0.2941338565854739</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7498216817295763</v>
+        <v>0.7570002025265183</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.5187050668526008</v>
+        <v>0.5267735928460776</v>
       </c>
       <c r="CD2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1104,244 +1104,244 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9451462608068156</v>
+        <v>0.9417795275667563</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9652789106172202</v>
+        <v>0.9613309241461596</v>
       </c>
       <c r="E3" t="n">
-        <v>106.6574808032636</v>
+        <v>106.4028455590689</v>
       </c>
       <c r="F3" t="n">
-        <v>111.3589823186588</v>
+        <v>110.0781112848323</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.70150151539512</v>
+        <v>-3.675265725763472</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3153302198611653</v>
+        <v>0.3123149288351568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659169145206523</v>
+        <v>0.6729616994149491</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4943916704434566</v>
+        <v>0.4966832760609744</v>
       </c>
       <c r="K3" t="n">
-        <v>5022.766666666666</v>
+        <v>6047.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2099</v>
+        <v>2511</v>
       </c>
       <c r="M3" t="n">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="N3" t="n">
-        <v>1044</v>
+        <v>1246</v>
       </c>
       <c r="O3" t="n">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="P3" t="n">
-        <v>543</v>
+        <v>679</v>
       </c>
       <c r="Q3" t="n">
-        <v>459</v>
+        <v>552</v>
       </c>
       <c r="R3" t="n">
-        <v>624</v>
+        <v>746</v>
       </c>
       <c r="S3" t="n">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="T3" t="n">
-        <v>584</v>
+        <v>704</v>
       </c>
       <c r="U3" t="n">
-        <v>310</v>
+        <v>389</v>
       </c>
       <c r="V3" t="n">
+        <v>203</v>
+      </c>
+      <c r="W3" t="n">
+        <v>414</v>
+      </c>
+      <c r="X3" t="n">
+        <v>644</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>661</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2582</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2667.24</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2359.24</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3025</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>307</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>616</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>124</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>324</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>265</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>352</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>145</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>366</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>181</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>332</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>317</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1312.88</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1167.88</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.953445729837021</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.9474743355164171</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>107.1923501722332</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>109.4022513727048</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-2.209901200471526</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.3168586652026402</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.6676001240906297</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.5047060520939126</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3022.766666666666</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>311</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>630</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>117</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>355</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>287</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>394</v>
+      </c>
+      <c r="BL3" t="n">
         <v>163</v>
       </c>
-      <c r="W3" t="n">
-        <v>359</v>
-      </c>
-      <c r="X3" t="n">
-        <v>540</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>550</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>63</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2177</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2220.56</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1965.56</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>267</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>529</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>106</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>265</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>234</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="BM3" t="n">
+        <v>338</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>208</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>112</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>196</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>312</v>
       </c>
-      <c r="AL3" t="n">
-        <v>124</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>304</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>156</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>76</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>192</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>287</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>276</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1123.28</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>999.28</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.9663334080264676</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.9654715493550523</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>108.6237728788093</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>111.8588658851437</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.235093006334291</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.3252144752903074</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.6554163167515157</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.5042588175578078</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2422.766666666666</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>253</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>515</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>94</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>278</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>225</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>312</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>131</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>280</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>154</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>87</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>167</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>253</v>
-      </c>
       <c r="BR3" t="n">
-        <v>274</v>
+        <v>344</v>
       </c>
       <c r="BS3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="BT3" t="n">
-        <v>1097.28</v>
+        <v>1354.36</v>
       </c>
       <c r="BU3" t="n">
-        <v>966.28</v>
+        <v>1191.36</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9221935179855261</v>
+        <v>0.9301133252964917</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.9650702186512353</v>
+        <v>0.975187512775902</v>
       </c>
       <c r="BX3" t="n">
-        <v>104.5273310547558</v>
+        <v>105.6133409459045</v>
       </c>
       <c r="BY3" t="n">
-        <v>110.8174417883001</v>
+        <v>110.7539711969599</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-6.29011073354435</v>
+        <v>-5.140630251055417</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.3046222764795947</v>
+        <v>0.3077711924676732</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6632347093661144</v>
+        <v>0.6783232747392683</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.483702261069576</v>
+        <v>0.4886605000280362</v>
       </c>
       <c r="CD3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1356,244 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9102302420787259</v>
+        <v>0.8788310360799748</v>
       </c>
       <c r="D4" t="n">
-        <v>1.001898562194691</v>
+        <v>1.002530348164475</v>
       </c>
       <c r="E4" t="n">
-        <v>106.7337395527079</v>
+        <v>103.4948224967798</v>
       </c>
       <c r="F4" t="n">
-        <v>111.8994828137643</v>
+        <v>111.8109838625481</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.1657432610564</v>
+        <v>-8.3161613657683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3721297357183876</v>
+        <v>0.3674460918274505</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7098974497146971</v>
+        <v>0.7152022051075861</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5266028018987361</v>
+        <v>0.5243142626292148</v>
       </c>
       <c r="K4" t="n">
-        <v>2600</v>
+        <v>3600</v>
       </c>
       <c r="L4" t="n">
-        <v>1034</v>
+        <v>1374</v>
       </c>
       <c r="M4" t="n">
-        <v>252</v>
+        <v>337</v>
       </c>
       <c r="N4" t="n">
-        <v>548</v>
+        <v>749</v>
       </c>
       <c r="O4" t="n">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="P4" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="Q4" t="n">
-        <v>203</v>
+        <v>280</v>
       </c>
       <c r="R4" t="n">
-        <v>282</v>
+        <v>401</v>
       </c>
       <c r="S4" t="n">
-        <v>171</v>
+        <v>241</v>
       </c>
       <c r="T4" t="n">
-        <v>271</v>
+        <v>381</v>
       </c>
       <c r="U4" t="n">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="V4" t="n">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="W4" t="n">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="X4" t="n">
-        <v>300</v>
+        <v>427</v>
       </c>
       <c r="Y4" t="n">
-        <v>288</v>
+        <v>400</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AA4" t="n">
-        <v>1077</v>
+        <v>1481</v>
       </c>
       <c r="AB4" t="n">
-        <v>1141.08</v>
+        <v>1568.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>970.08</v>
+        <v>1327.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="AF4" t="n">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="AG4" t="n">
-        <v>205</v>
+        <v>329</v>
       </c>
       <c r="AH4" t="n">
+        <v>57</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>183</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>122</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>177</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>96</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>173</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>103</v>
+      </c>
+      <c r="AO4" t="n">
         <v>43</v>
       </c>
-      <c r="AI4" t="n">
-        <v>121</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>73</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>104</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>58</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
+        <v>88</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>194</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>172</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>677.88</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>581.88</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8366780336117258</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.006689777084927</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>97.31584072603454</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>113.6278990937314</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-16.31205836769686</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.3339357781036627</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.6972376485878415</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.5005178091445034</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>201</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>420</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>83</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>248</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>158</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>224</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>145</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>208</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>167</v>
+      </c>
+      <c r="BO4" t="n">
         <v>68</v>
       </c>
-      <c r="AO4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>118</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>104</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BP4" t="n">
+        <v>124</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>233</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>228</v>
+      </c>
+      <c r="BS4" t="n">
         <v>15</v>
       </c>
-      <c r="AT4" t="n">
-        <v>426.76</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>368.76</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8989491706217176</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.011121276035282</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>104.0680646041733</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>114.7939083022978</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-10.72584369812456</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.349263231360418</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.6862519644957648</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.5114083139083139</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>162</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>343</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>66</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>196</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>130</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>178</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>113</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>163</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>134</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>54</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>97</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>182</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>184</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>12</v>
-      </c>
       <c r="BT4" t="n">
-        <v>714.3199999999999</v>
+        <v>890.5599999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>601.3199999999999</v>
+        <v>745.5599999999999</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.9172809117393561</v>
+        <v>0.9125534380545739</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.9961343660443216</v>
+        <v>0.9992028050281135</v>
       </c>
       <c r="BX4" t="n">
-        <v>108.399786395542</v>
+        <v>108.4380079133761</v>
       </c>
       <c r="BY4" t="n">
-        <v>110.0904668834308</v>
+        <v>110.3574516776016</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-1.690680487888798</v>
+        <v>-1.919443764225453</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3864213009421186</v>
+        <v>0.3942543428064808</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.72467587797653</v>
+        <v>0.729573850323382</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5360993568927498</v>
+        <v>0.5433514254169837</v>
       </c>
       <c r="CD4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1860,244 +1860,244 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9087129240726243</v>
+        <v>0.9071298784240028</v>
       </c>
       <c r="D6" t="n">
-        <v>0.94514919170816</v>
+        <v>0.9516785996200355</v>
       </c>
       <c r="E6" t="n">
-        <v>100.9504844798601</v>
+        <v>100.8777662927575</v>
       </c>
       <c r="F6" t="n">
-        <v>109.0257007240447</v>
+        <v>109.6748375194346</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.07521624418459</v>
+        <v>-8.797071226677051</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2657710606894645</v>
+        <v>0.2689721296935657</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6142560244749703</v>
+        <v>0.6228104268629249</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4357171089844654</v>
+        <v>0.4428661638919517</v>
       </c>
       <c r="K6" t="n">
-        <v>5250</v>
+        <v>6050</v>
       </c>
       <c r="L6" t="n">
-        <v>1987</v>
+        <v>2276</v>
       </c>
       <c r="M6" t="n">
-        <v>500</v>
+        <v>566</v>
       </c>
       <c r="N6" t="n">
-        <v>933</v>
+        <v>1069</v>
       </c>
       <c r="O6" t="n">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="P6" t="n">
-        <v>682</v>
+        <v>784</v>
       </c>
       <c r="Q6" t="n">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="R6" t="n">
-        <v>520</v>
+        <v>594</v>
       </c>
       <c r="S6" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="T6" t="n">
-        <v>489</v>
+        <v>577</v>
       </c>
       <c r="U6" t="n">
-        <v>398</v>
+        <v>461</v>
       </c>
       <c r="V6" t="n">
+        <v>251</v>
+      </c>
+      <c r="W6" t="n">
+        <v>399</v>
+      </c>
+      <c r="X6" t="n">
+        <v>651</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>609</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2476</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2513.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2258.36</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>268</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>492</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>405</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>303</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>117</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>296</v>
+      </c>
+      <c r="AN6" t="n">
         <v>229</v>
       </c>
-      <c r="W6" t="n">
-        <v>347</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="AO6" t="n">
+        <v>123</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>323</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>309</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1248.32</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1131.32</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.8807243205814752</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.946111507896537</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>97.13794708067651</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>109.3236451495537</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-12.18569806887719</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.2595453765061675</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.6241510288633612</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.4389036251043099</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3050</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>298</v>
+      </c>
+      <c r="BG6" t="n">
         <v>577</v>
       </c>
-      <c r="Y6" t="n">
-        <v>535</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2150</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2190.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1970.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>239</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>432</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>97</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>343</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>178</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>266</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>98</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>251</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>192</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>113</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>192</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>285</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1084.04</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>986.04</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.8765458236953942</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.9357182380057207</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>96.30846684824357</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>107.9108809128095</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-11.60241406456598</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.2520816829007047</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0.6215065918760251</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.4326764491428264</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2650</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>261</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>501</v>
-      </c>
       <c r="BH6" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="BI6" t="n">
-        <v>339</v>
+        <v>379</v>
       </c>
       <c r="BJ6" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="BK6" t="n">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="BL6" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="BM6" t="n">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="BN6" t="n">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="BO6" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="BP6" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="BQ6" t="n">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="BR6" t="n">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="BS6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="BT6" t="n">
-        <v>1106.76</v>
+        <v>1265.04</v>
       </c>
       <c r="BU6" t="n">
-        <v>984.76</v>
+        <v>1127.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9408800244498543</v>
+        <v>0.9335354362665306</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.9545801454105993</v>
+        <v>0.9572456913435343</v>
       </c>
       <c r="BX6" t="n">
-        <v>105.5925021114766</v>
+        <v>104.6175855048385</v>
       </c>
       <c r="BY6" t="n">
-        <v>110.1405205352798</v>
+        <v>110.0260298893155</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-4.548018423803206</v>
+        <v>-5.408444384476913</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.2794604384782243</v>
+        <v>0.2783988828809639</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.6070054570739155</v>
+        <v>0.6214698248624888</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.4387577688261045</v>
+        <v>0.4468287026795936</v>
       </c>
       <c r="CD6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2112,244 +2112,244 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9541817439874302</v>
+        <v>0.95608432288256</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9553313539133701</v>
+        <v>0.9478528247441815</v>
       </c>
       <c r="E7" t="n">
-        <v>105.0516767509059</v>
+        <v>105.0765529384902</v>
       </c>
       <c r="F7" t="n">
-        <v>107.4146540648682</v>
+        <v>106.2644074972537</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.362977313962327</v>
+        <v>-1.187854558763518</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2478907648670726</v>
+        <v>0.2442252621030992</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7243566706475588</v>
+        <v>0.7315559380293846</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4970642783908503</v>
+        <v>0.4993951465574644</v>
       </c>
       <c r="K7" t="n">
-        <v>5225</v>
+        <v>6225</v>
       </c>
       <c r="L7" t="n">
-        <v>2069</v>
+        <v>2476</v>
       </c>
       <c r="M7" t="n">
-        <v>472</v>
+        <v>582</v>
       </c>
       <c r="N7" t="n">
-        <v>919</v>
+        <v>1111</v>
       </c>
       <c r="O7" t="n">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="P7" t="n">
-        <v>653</v>
+        <v>776</v>
       </c>
       <c r="Q7" t="n">
-        <v>396</v>
+        <v>466</v>
       </c>
       <c r="R7" t="n">
-        <v>586</v>
+        <v>680</v>
       </c>
       <c r="S7" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="T7" t="n">
-        <v>649</v>
+        <v>781</v>
       </c>
       <c r="U7" t="n">
-        <v>435</v>
+        <v>522</v>
       </c>
       <c r="V7" t="n">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="W7" t="n">
-        <v>343</v>
+        <v>408</v>
       </c>
       <c r="X7" t="n">
-        <v>511</v>
+        <v>600</v>
       </c>
       <c r="Y7" t="n">
-        <v>553</v>
+        <v>656</v>
       </c>
       <c r="Z7" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="AA7" t="n">
-        <v>2131</v>
+        <v>2512</v>
       </c>
       <c r="AB7" t="n">
-        <v>2172.84</v>
+        <v>2594.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1973.84</v>
+        <v>2360.2</v>
       </c>
       <c r="AD7" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3225</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>307</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>592</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>139</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>395</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>232</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>123</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>386</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>262</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>317</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>334</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1353.72</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1230.72</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9342595113389796</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.9843801116401869</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>102.6800469143322</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>111.0613583164649</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-8.381311402132738</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.2455385023252114</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.7106257992753169</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.484439246240039</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>275</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>519</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>143</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>381</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>234</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>342</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>111</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>395</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>260</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>108</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>190</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>283</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>322</v>
+      </c>
+      <c r="BS7" t="n">
         <v>26</v>
       </c>
-      <c r="AE7" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>241</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>475</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>327</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>279</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>106</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>313</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>209</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>182</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>258</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>270</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1106.76</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1000.76</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.9246022212041622</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.001551034889766</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>102.2095324590962</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>113.6530859517258</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-11.44355349262961</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.2586343838141796</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.6969338358176095</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.4839808717710026</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2600</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>231</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>444</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>123</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>326</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>216</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>307</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>93</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>336</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>226</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>94</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>161</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>253</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>283</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>25</v>
-      </c>
       <c r="BT7" t="n">
-        <v>1066.08</v>
+        <v>1240.48</v>
       </c>
       <c r="BU7" t="n">
-        <v>973.08</v>
+        <v>1129.48</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.9837612667706981</v>
+        <v>0.9793641218623789</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.909111672936974</v>
+        <v>0.908890385388442</v>
       </c>
       <c r="BX7" t="n">
-        <v>107.8938210427157</v>
+        <v>107.6328260309254</v>
       </c>
       <c r="BY7" t="n">
-        <v>101.1762221780107</v>
+        <v>101.1476599567617</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.717598864704957</v>
+        <v>6.48516607416365</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.2371471459199654</v>
+        <v>0.2428244725328459</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7517795054775083</v>
+        <v>0.7538814193670568</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5101476850106981</v>
+        <v>0.5153481068960516</v>
       </c>
       <c r="CD7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9459419347929299</v>
+        <v>0.9524962979644105</v>
       </c>
       <c r="D8" t="n">
-        <v>1.001979567531668</v>
+        <v>0.9954261227783577</v>
       </c>
       <c r="E8" t="n">
-        <v>103.3401279584083</v>
+        <v>104.0017020145459</v>
       </c>
       <c r="F8" t="n">
-        <v>112.0248759185563</v>
+        <v>111.8191446238814</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.684747960147986</v>
+        <v>-7.817442609335465</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2394475217963702</v>
+        <v>0.2356356389713557</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7199870869801822</v>
+        <v>0.7145464357661719</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4858848540797874</v>
+        <v>0.4825741375469315</v>
       </c>
       <c r="K8" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="L8" t="n">
-        <v>1952</v>
+        <v>2346</v>
       </c>
       <c r="M8" t="n">
-        <v>427</v>
+        <v>498</v>
       </c>
       <c r="N8" t="n">
-        <v>820</v>
+        <v>962</v>
       </c>
       <c r="O8" t="n">
+        <v>275</v>
+      </c>
+      <c r="P8" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>525</v>
+      </c>
+      <c r="R8" t="n">
+        <v>669</v>
+      </c>
+      <c r="S8" t="n">
+        <v>210</v>
+      </c>
+      <c r="T8" t="n">
+        <v>687</v>
+      </c>
+      <c r="U8" t="n">
+        <v>453</v>
+      </c>
+      <c r="V8" t="n">
+        <v>179</v>
+      </c>
+      <c r="W8" t="n">
+        <v>414</v>
+      </c>
+      <c r="X8" t="n">
+        <v>658</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>657</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2513</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2470.36</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2260.36</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>243</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>474</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>137</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>391</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>278</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>342</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>102</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>351</v>
+      </c>
+      <c r="AN8" t="n">
         <v>223</v>
       </c>
-      <c r="P8" t="n">
-        <v>653</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>429</v>
-      </c>
-      <c r="R8" t="n">
-        <v>552</v>
-      </c>
-      <c r="S8" t="n">
-        <v>177</v>
-      </c>
-      <c r="T8" t="n">
-        <v>566</v>
-      </c>
-      <c r="U8" t="n">
-        <v>375</v>
-      </c>
-      <c r="V8" t="n">
-        <v>152</v>
-      </c>
-      <c r="W8" t="n">
-        <v>354</v>
-      </c>
-      <c r="X8" t="n">
-        <v>548</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>551</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2101</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2069.88</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1892.88</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>215</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>423</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>117</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>338</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>233</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>290</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>89</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>303</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>195</v>
-      </c>
       <c r="AO8" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AP8" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="AQ8" t="n">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="AR8" t="n">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="AS8" t="n">
         <v>20</v>
       </c>
       <c r="AT8" t="n">
-        <v>1097.6</v>
+        <v>1251.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>1008.6</v>
+        <v>1149.48</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9242880211868864</v>
+        <v>0.9405333518290729</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.021273187948369</v>
+        <v>1.003555641458983</v>
       </c>
       <c r="AX8" t="n">
-        <v>100.5387005054181</v>
+        <v>102.3423958278349</v>
       </c>
       <c r="AY8" t="n">
-        <v>113.7151894651335</v>
+        <v>112.776611414705</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-13.1764889597154</v>
+        <v>-10.4342155868701</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.2407238626635178</v>
+        <v>0.241510905862605</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.7333336521831216</v>
+        <v>0.7185326589865129</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.4953242288891429</v>
+        <v>0.4921665226836562</v>
       </c>
       <c r="BD8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE8" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="BF8" t="n">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="BG8" t="n">
-        <v>397</v>
+        <v>488</v>
       </c>
       <c r="BH8" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="BI8" t="n">
-        <v>315</v>
+        <v>409</v>
       </c>
       <c r="BJ8" t="n">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="BK8" t="n">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="BL8" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="BM8" t="n">
-        <v>263</v>
+        <v>336</v>
       </c>
       <c r="BN8" t="n">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="BO8" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="BP8" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="BQ8" t="n">
-        <v>252</v>
+        <v>316</v>
       </c>
       <c r="BR8" t="n">
-        <v>267</v>
+        <v>327</v>
       </c>
       <c r="BS8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BT8" t="n">
-        <v>972.28</v>
+        <v>1218.88</v>
       </c>
       <c r="BU8" t="n">
-        <v>884.28</v>
+        <v>1110.88</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9694003411994768</v>
+        <v>0.964459244099748</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9810781454135754</v>
+        <v>0.9872966040977322</v>
       </c>
       <c r="BX8" t="n">
-        <v>106.3750076991478</v>
+        <v>105.6610082012569</v>
       </c>
       <c r="BY8" t="n">
-        <v>110.1937029097644</v>
+        <v>110.8616778330577</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-3.818695210616629</v>
+        <v>-5.20066963180083</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2380648191902935</v>
+        <v>0.2297603720801064</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.7055283080103313</v>
+        <v>0.7105602125458311</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.4756588647029859</v>
+        <v>0.4729817524102068</v>
       </c>
       <c r="CD8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -2616,244 +2616,244 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8723044961578448</v>
+        <v>0.8839419550020469</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9853653904493135</v>
+        <v>0.9875859440894209</v>
       </c>
       <c r="E9" t="n">
-        <v>96.00194118830481</v>
+        <v>97.47297443989341</v>
       </c>
       <c r="F9" t="n">
-        <v>111.5058390920437</v>
+        <v>111.5418721202008</v>
       </c>
       <c r="G9" t="n">
-        <v>-15.50389790373888</v>
+        <v>-14.06889768030741</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2355802557542776</v>
+        <v>0.2383407623454296</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6965921489168726</v>
+        <v>0.6934194424268875</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4623154498926504</v>
+        <v>0.4586626914682534</v>
       </c>
       <c r="K9" t="n">
-        <v>5050</v>
+        <v>6050</v>
       </c>
       <c r="L9" t="n">
-        <v>1826</v>
+        <v>2215</v>
       </c>
       <c r="M9" t="n">
-        <v>448</v>
+        <v>528</v>
       </c>
       <c r="N9" t="n">
-        <v>867</v>
+        <v>1028</v>
       </c>
       <c r="O9" t="n">
-        <v>197</v>
+        <v>253</v>
       </c>
       <c r="P9" t="n">
-        <v>676</v>
+        <v>824</v>
       </c>
       <c r="Q9" t="n">
-        <v>339</v>
+        <v>400</v>
       </c>
       <c r="R9" t="n">
-        <v>480</v>
+        <v>575</v>
       </c>
       <c r="S9" t="n">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="T9" t="n">
-        <v>574</v>
+        <v>668</v>
       </c>
       <c r="U9" t="n">
-        <v>337</v>
+        <v>429</v>
       </c>
       <c r="V9" t="n">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="W9" t="n">
-        <v>339</v>
+        <v>403</v>
       </c>
       <c r="X9" t="n">
-        <v>567</v>
+        <v>667</v>
       </c>
       <c r="Y9" t="n">
-        <v>512</v>
+        <v>605</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="AA9" t="n">
-        <v>2118</v>
+        <v>2537</v>
       </c>
       <c r="AB9" t="n">
-        <v>2093.2</v>
+        <v>2508</v>
       </c>
       <c r="AC9" t="n">
-        <v>1902.2</v>
+        <v>2275</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="AF9" t="n">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="AG9" t="n">
-        <v>421</v>
+        <v>522</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AI9" t="n">
+        <v>395</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>185</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>268</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>101</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>323</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>195</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>342</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>295</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1229.92</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1128.92</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.8933509860103926</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.036973598397362</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>97.24971266306144</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>116.9396730929621</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-19.68996042990062</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.2066245739124996</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.6973658448282104</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.4397303407380408</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3050</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>266</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>506</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>123</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>429</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>215</v>
+      </c>
+      <c r="BK9" t="n">
         <v>307</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>151</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>219</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>79</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>271</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>143</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>159</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>281</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>244</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>983.36</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>904.36</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.867140907857443</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.035799638762833</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>94.1427952507713</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>117.5835699025132</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-23.4407746517419</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.2023663101604278</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.6957926034538938</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.4431361193957445</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2650</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>232</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>446</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>107</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>369</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>188</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>261</v>
-      </c>
       <c r="BL9" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="BM9" t="n">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="BN9" t="n">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="BO9" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="BP9" t="n">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="BQ9" t="n">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="BR9" t="n">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="BS9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="BT9" t="n">
-        <v>1109.84</v>
+        <v>1278.08</v>
       </c>
       <c r="BU9" t="n">
-        <v>997.84</v>
+        <v>1146.08</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8770708853582156</v>
+        <v>0.874532923993701</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.9388106996983723</v>
+        <v>0.9381982897814801</v>
       </c>
       <c r="BX9" t="n">
-        <v>97.71807589987421</v>
+        <v>97.69623621672537</v>
       </c>
       <c r="BY9" t="n">
-        <v>105.8956260362257</v>
+        <v>106.1440711474396</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-8.177550136351487</v>
+        <v>-8.44783493071421</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.2662392824562929</v>
+        <v>0.2700569507783598</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.697330190882699</v>
+        <v>0.6894730400255645</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.4800194472744096</v>
+        <v>0.4775950421984657</v>
       </c>
       <c r="CD9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2868,244 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9309111154602038</v>
+        <v>0.9368464089056816</v>
       </c>
       <c r="D10" t="n">
-        <v>1.01327207159717</v>
+        <v>1.017611668525854</v>
       </c>
       <c r="E10" t="n">
-        <v>106.0387469668643</v>
+        <v>106.3778655148082</v>
       </c>
       <c r="F10" t="n">
-        <v>113.9117954482826</v>
+        <v>114.3136620341632</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.873048481418281</v>
+        <v>-7.93579651935504</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3233664377143212</v>
+        <v>0.3157833200931524</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6985995075245754</v>
+        <v>0.6942012265968499</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5028829305041638</v>
+        <v>0.4969784243783326</v>
       </c>
       <c r="K10" t="n">
-        <v>5250</v>
+        <v>6075</v>
       </c>
       <c r="L10" t="n">
-        <v>2137</v>
+        <v>2478</v>
       </c>
       <c r="M10" t="n">
-        <v>471</v>
+        <v>544</v>
       </c>
       <c r="N10" t="n">
-        <v>925</v>
+        <v>1058</v>
       </c>
       <c r="O10" t="n">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="P10" t="n">
-        <v>765</v>
+        <v>886</v>
       </c>
       <c r="Q10" t="n">
-        <v>412</v>
+        <v>481</v>
       </c>
       <c r="R10" t="n">
-        <v>564</v>
+        <v>659</v>
       </c>
       <c r="S10" t="n">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="T10" t="n">
-        <v>569</v>
+        <v>645</v>
       </c>
       <c r="U10" t="n">
-        <v>396</v>
+        <v>459</v>
       </c>
       <c r="V10" t="n">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="W10" t="n">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="X10" t="n">
-        <v>644</v>
+        <v>737</v>
       </c>
       <c r="Y10" t="n">
-        <v>561</v>
+        <v>653</v>
       </c>
       <c r="Z10" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AA10" t="n">
-        <v>2314</v>
+        <v>2675</v>
       </c>
       <c r="AB10" t="n">
-        <v>2298.16</v>
+        <v>2646.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>2017.16</v>
+        <v>2329.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>2650</v>
+        <v>3050</v>
       </c>
       <c r="AF10" t="n">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="AG10" t="n">
-        <v>476</v>
+        <v>543</v>
       </c>
       <c r="AH10" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="AI10" t="n">
-        <v>380</v>
+        <v>431</v>
       </c>
       <c r="AJ10" t="n">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="AK10" t="n">
-        <v>293</v>
+        <v>342</v>
       </c>
       <c r="AL10" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="AM10" t="n">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="AN10" t="n">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AP10" t="n">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="AQ10" t="n">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="AR10" t="n">
-        <v>283</v>
+        <v>333</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>1166.92</v>
+        <v>1335.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>1021.92</v>
+        <v>1170.48</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.887353442635865</v>
+        <v>0.8999684654408375</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.0290983253107</v>
+        <v>1.028075049751616</v>
       </c>
       <c r="AX10" t="n">
-        <v>101.4187448389346</v>
+        <v>102.7028952636329</v>
       </c>
       <c r="AY10" t="n">
-        <v>115.051534451985</v>
+        <v>115.1977619120508</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-13.63278961305036</v>
+        <v>-12.49486664841784</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.322843520260875</v>
+        <v>0.3205384583001658</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.6947198965222865</v>
+        <v>0.6894284869783538</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.4924235969899657</v>
+        <v>0.4913303507680963</v>
       </c>
       <c r="BD10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>2600</v>
+        <v>3025</v>
       </c>
       <c r="BF10" t="n">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="BG10" t="n">
-        <v>449</v>
+        <v>515</v>
       </c>
       <c r="BH10" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="BI10" t="n">
-        <v>385</v>
+        <v>455</v>
       </c>
       <c r="BJ10" t="n">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="BK10" t="n">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="BL10" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="BM10" t="n">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="BN10" t="n">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="BO10" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="BP10" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="BQ10" t="n">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="BR10" t="n">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="BS10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BT10" t="n">
-        <v>1131.24</v>
+        <v>1311.48</v>
       </c>
       <c r="BU10" t="n">
-        <v>995.24</v>
+        <v>1159.48</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9744687882845425</v>
+        <v>0.9737243523705258</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.9974458178836401</v>
+        <v>1.007148287300091</v>
       </c>
       <c r="BX10" t="n">
-        <v>110.658749094794</v>
+        <v>110.0528357659835</v>
       </c>
       <c r="BY10" t="n">
-        <v>112.7720564445802</v>
+        <v>113.4295621562757</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-2.113307349786196</v>
+        <v>-3.376726390292238</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3238893551677674</v>
+        <v>0.3110281818861391</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7024791185268638</v>
+        <v>0.6989739662153454</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.5133422640183615</v>
+        <v>0.5026264979885685</v>
       </c>
       <c r="CD10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3120,244 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9835297833947405</v>
+        <v>0.9805145820849607</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9574052460631601</v>
+        <v>0.9519229092465782</v>
       </c>
       <c r="E11" t="n">
-        <v>111.2268249738531</v>
+        <v>110.8575108138257</v>
       </c>
       <c r="F11" t="n">
-        <v>107.1693098803709</v>
+        <v>106.9545875667412</v>
       </c>
       <c r="G11" t="n">
-        <v>4.057515093482283</v>
+        <v>3.902923247084494</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3072742872857415</v>
+        <v>0.3091399770094519</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7094697893236824</v>
+        <v>0.7053227933730806</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5046662654850583</v>
+        <v>0.5049920031096561</v>
       </c>
       <c r="K11" t="n">
-        <v>5025</v>
+        <v>6025</v>
       </c>
       <c r="L11" t="n">
-        <v>2023</v>
+        <v>2406</v>
       </c>
       <c r="M11" t="n">
-        <v>435</v>
+        <v>514</v>
       </c>
       <c r="N11" t="n">
-        <v>810</v>
+        <v>961</v>
       </c>
       <c r="O11" t="n">
-        <v>263</v>
+        <v>306</v>
       </c>
       <c r="P11" t="n">
-        <v>763</v>
+        <v>905</v>
       </c>
       <c r="Q11" t="n">
-        <v>364</v>
+        <v>460</v>
       </c>
       <c r="R11" t="n">
-        <v>490</v>
+        <v>612</v>
       </c>
       <c r="S11" t="n">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="T11" t="n">
-        <v>521</v>
+        <v>630</v>
       </c>
       <c r="U11" t="n">
-        <v>380</v>
+        <v>464</v>
       </c>
       <c r="V11" t="n">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="W11" t="n">
+        <v>332</v>
+      </c>
+      <c r="X11" t="n">
+        <v>697</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>628</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2467.28</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2174.28</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3025</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>266</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>498</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>147</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>453</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>212</v>
+      </c>
+      <c r="AK11" t="n">
         <v>279</v>
       </c>
-      <c r="X11" t="n">
-        <v>573</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>513</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1928</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2067.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1820.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>232</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>431</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>128</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>395</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>242</v>
-      </c>
       <c r="AL11" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="AM11" t="n">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="AN11" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="AO11" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AP11" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="AQ11" t="n">
-        <v>306</v>
+        <v>354</v>
       </c>
       <c r="AR11" t="n">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="AS11" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AT11" t="n">
-        <v>1067.48</v>
+        <v>1227.76</v>
       </c>
       <c r="AU11" t="n">
-        <v>952.48</v>
+        <v>1093.76</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.9688077057504956</v>
+        <v>0.9684400862711573</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9683084223088435</v>
+        <v>0.9712630487496953</v>
       </c>
       <c r="AX11" t="n">
-        <v>108.0792970554561</v>
+        <v>108.294609354708</v>
       </c>
       <c r="AY11" t="n">
-        <v>108.2075549772338</v>
+        <v>108.9577828951275</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.1282579217777639</v>
+        <v>-0.6631735404195401</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.2633655614245158</v>
+        <v>0.2710969215715447</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.7159053043216003</v>
+        <v>0.7079064608780034</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.4805917250087773</v>
+        <v>0.4814880870004095</v>
       </c>
       <c r="BD11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE11" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="BF11" t="n">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="BG11" t="n">
-        <v>379</v>
+        <v>463</v>
       </c>
       <c r="BH11" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="BI11" t="n">
-        <v>368</v>
+        <v>452</v>
       </c>
       <c r="BJ11" t="n">
-        <v>182</v>
+        <v>248</v>
       </c>
       <c r="BK11" t="n">
-        <v>248</v>
+        <v>333</v>
       </c>
       <c r="BL11" t="n">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="BM11" t="n">
-        <v>245</v>
+        <v>314</v>
       </c>
       <c r="BN11" t="n">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="BO11" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="BP11" t="n">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="BQ11" t="n">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="BR11" t="n">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="BS11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000.12</v>
+        <v>1239.52</v>
       </c>
       <c r="BU11" t="n">
-        <v>868.12</v>
+        <v>1080.52</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9994787008426725</v>
+        <v>0.9925890778987639</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9455934717970034</v>
+        <v>0.9325827697434611</v>
       </c>
       <c r="BX11" t="n">
-        <v>114.63664688545</v>
+        <v>113.4204122729434</v>
       </c>
       <c r="BY11" t="n">
-        <v>106.0445443587693</v>
+        <v>104.9513922383548</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.592102526680669</v>
+        <v>8.46902003458853</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3548420736354028</v>
+        <v>0.3471830324473591</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7024979814092718</v>
+        <v>0.7027391258681581</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.5307470176676962</v>
+        <v>0.5284959192189027</v>
       </c>
       <c r="CD11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -3372,244 +3372,244 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.004732132916311</v>
+        <v>0.9842067744125754</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9783666965370409</v>
+        <v>0.9719272314463954</v>
       </c>
       <c r="E12" t="n">
-        <v>111.8733182421374</v>
+        <v>109.9172666367304</v>
       </c>
       <c r="F12" t="n">
-        <v>109.7216528852768</v>
+        <v>109.1866280683066</v>
       </c>
       <c r="G12" t="n">
-        <v>2.151665356860573</v>
+        <v>0.7306385684237255</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2632112790867055</v>
+        <v>0.264370199192025</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7161188109373329</v>
+        <v>0.7143962570986252</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4915199927464975</v>
+        <v>0.4889820447215385</v>
       </c>
       <c r="K12" t="n">
-        <v>5250</v>
+        <v>6050</v>
       </c>
       <c r="L12" t="n">
-        <v>2166</v>
+        <v>2464</v>
       </c>
       <c r="M12" t="n">
-        <v>450</v>
+        <v>511</v>
       </c>
       <c r="N12" t="n">
-        <v>904</v>
+        <v>1061</v>
       </c>
       <c r="O12" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="P12" t="n">
-        <v>697</v>
+        <v>813</v>
       </c>
       <c r="Q12" t="n">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="R12" t="n">
-        <v>599</v>
+        <v>676</v>
       </c>
       <c r="S12" t="n">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="T12" t="n">
-        <v>604</v>
+        <v>703</v>
       </c>
       <c r="U12" t="n">
-        <v>418</v>
+        <v>473</v>
       </c>
       <c r="V12" t="n">
+        <v>168</v>
+      </c>
+      <c r="W12" t="n">
+        <v>334</v>
+      </c>
+      <c r="X12" t="n">
+        <v>638</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>631</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2448</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2505.44</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2238.44</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3050</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>257</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>553</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>142</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>392</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>253</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>327</v>
+      </c>
+      <c r="AL12" t="n">
         <v>148</v>
       </c>
-      <c r="W12" t="n">
-        <v>290</v>
-      </c>
-      <c r="X12" t="n">
-        <v>557</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>547</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2134</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2154.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1931.56</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2450</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>438</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>112</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>311</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>269</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>115</v>
-      </c>
       <c r="AM12" t="n">
+        <v>371</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>189</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>68</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>172</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>326</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>307</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1260.88</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1112.88</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.9474144604003226</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.954676895240046</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>107.1856514129457</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>107.9472768066327</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.7616253936870133</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.2786360181060001</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.7162392773749765</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.4959308662815106</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>254</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>508</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>158</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>421</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>289</v>
       </c>
-      <c r="AN12" t="n">
-        <v>147</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>56</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>135</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>263</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>244</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1002.36</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>887.36</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.9674384813015685</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.9690199491248445</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>109.1605693359916</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>109.2877208455712</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.1271515095796675</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.2763681123334968</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.715386390490225</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.4935295664432309</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>239</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>466</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>148</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>386</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>275</v>
-      </c>
       <c r="BK12" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="BL12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="BM12" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="BN12" t="n">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="BO12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="BP12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="BQ12" t="n">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="BR12" t="n">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="BS12" t="n">
         <v>30</v>
       </c>
       <c r="BT12" t="n">
-        <v>1152.2</v>
+        <v>1244.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>1044.2</v>
+        <v>1125.56</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.036698120014661</v>
+        <v>1.020999088424828</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.9863781943189237</v>
+        <v>0.9891775676527448</v>
       </c>
       <c r="BX12" t="n">
-        <v>114.1985315902624</v>
+        <v>112.648881860515</v>
       </c>
       <c r="BY12" t="n">
-        <v>110.0935946335959</v>
+        <v>110.4259793299805</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.104936956666495</v>
+        <v>2.222902530534465</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2519339934465984</v>
+        <v>0.2501043802780497</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.7167465998919967</v>
+        <v>0.7125532368222738</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.4897975010064402</v>
+        <v>0.4820332231615664</v>
       </c>
       <c r="CD12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -3624,244 +3624,244 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9515919644242917</v>
+        <v>0.9431810964504584</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9016632170157765</v>
+        <v>0.8922507597653803</v>
       </c>
       <c r="E13" t="n">
-        <v>109.5877821991982</v>
+        <v>108.3381482043175</v>
       </c>
       <c r="F13" t="n">
-        <v>101.5542176600192</v>
+        <v>100.6512900318567</v>
       </c>
       <c r="G13" t="n">
-        <v>8.033564539178935</v>
+        <v>7.686858172460884</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3505430557519366</v>
+        <v>0.345775351930968</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7160438771005349</v>
+        <v>0.7213819439604873</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5368214122666169</v>
+        <v>0.5412716457174046</v>
       </c>
       <c r="K13" t="n">
-        <v>5025</v>
+        <v>6025</v>
       </c>
       <c r="L13" t="n">
-        <v>1991</v>
+        <v>2368</v>
       </c>
       <c r="M13" t="n">
-        <v>500</v>
+        <v>611</v>
       </c>
       <c r="N13" t="n">
-        <v>906</v>
+        <v>1090</v>
       </c>
       <c r="O13" t="n">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="P13" t="n">
-        <v>669</v>
+        <v>798</v>
       </c>
       <c r="Q13" t="n">
-        <v>358</v>
+        <v>420</v>
       </c>
       <c r="R13" t="n">
-        <v>491</v>
+        <v>586</v>
       </c>
       <c r="S13" t="n">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="T13" t="n">
-        <v>582</v>
+        <v>734</v>
       </c>
       <c r="U13" t="n">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="V13" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="W13" t="n">
-        <v>304</v>
+        <v>371</v>
       </c>
       <c r="X13" t="n">
-        <v>544</v>
+        <v>638</v>
       </c>
       <c r="Y13" t="n">
-        <v>506</v>
+        <v>606</v>
       </c>
       <c r="Z13" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AA13" t="n">
-        <v>1868</v>
+        <v>2235</v>
       </c>
       <c r="AB13" t="n">
-        <v>2095.04</v>
+        <v>2516.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>1816.04</v>
+        <v>2185.84</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="AF13" t="n">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="AG13" t="n">
-        <v>407</v>
+        <v>557</v>
       </c>
       <c r="AH13" t="n">
+        <v>122</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>364</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>181</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>254</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>145</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>386</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>266</v>
+      </c>
+      <c r="AO13" t="n">
         <v>99</v>
       </c>
-      <c r="AI13" t="n">
-        <v>265</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>141</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>195</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>112</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>268</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>181</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>80</v>
-      </c>
       <c r="AP13" t="n">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="AQ13" t="n">
-        <v>246</v>
+        <v>319</v>
       </c>
       <c r="AR13" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="AS13" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="AT13" t="n">
-        <v>920.8</v>
+        <v>1244.76</v>
       </c>
       <c r="AU13" t="n">
-        <v>808.8</v>
+        <v>1099.76</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9714552370892989</v>
+        <v>0.9569025577027492</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8856373843129653</v>
+        <v>0.8798297497036599</v>
       </c>
       <c r="AX13" t="n">
-        <v>110.5164153930311</v>
+        <v>108.1414895177445</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.876174900982</v>
+        <v>101.3623446949506</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.640240492049131</v>
+        <v>6.779144822793855</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.353111873344149</v>
+        <v>0.3320267504935167</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.686351863531231</v>
+        <v>0.6930330032026345</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5404371619712222</v>
+        <v>0.5370504119915659</v>
       </c>
       <c r="BD13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="BF13" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="BG13" t="n">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="BH13" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="BI13" t="n">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="BJ13" t="n">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="BK13" t="n">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="BL13" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="BM13" t="n">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="BN13" t="n">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="BO13" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="BP13" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="BQ13" t="n">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="BR13" t="n">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="BS13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BT13" t="n">
-        <v>1174.24</v>
+        <v>1272.08</v>
       </c>
       <c r="BU13" t="n">
-        <v>1007.24</v>
+        <v>1086.08</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.9359851073303577</v>
+        <v>0.9294596351981675</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.9142549427108421</v>
+        <v>0.9046717698271004</v>
       </c>
       <c r="BX13" t="n">
-        <v>108.8581418326151</v>
+        <v>108.5348068908906</v>
       </c>
       <c r="BY13" t="n">
-        <v>101.3012512564056</v>
+        <v>99.94023536876274</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7.556890576209494</v>
+        <v>8.594571522127913</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.3485246990723411</v>
+        <v>0.3595239533684192</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.7393733163335593</v>
+        <v>0.7497308847183396</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5339804660701418</v>
+        <v>0.5454928794432434</v>
       </c>
       <c r="CD13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -3876,244 +3876,244 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.028670537269259</v>
+        <v>1.016816851948949</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9190865287410088</v>
+        <v>0.9293017475586437</v>
       </c>
       <c r="E14" t="n">
-        <v>117.7476046919323</v>
+        <v>116.7801844268815</v>
       </c>
       <c r="F14" t="n">
-        <v>102.7277481173657</v>
+        <v>103.576679395756</v>
       </c>
       <c r="G14" t="n">
-        <v>15.01985657456663</v>
+        <v>13.20350503112543</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3481326878394413</v>
+        <v>0.3513689208118738</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7337456576911964</v>
+        <v>0.7385661131499969</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5442575441697856</v>
+        <v>0.5461217371426472</v>
       </c>
       <c r="K14" t="n">
-        <v>5200</v>
+        <v>6200</v>
       </c>
       <c r="L14" t="n">
-        <v>2383</v>
+        <v>2802</v>
       </c>
       <c r="M14" t="n">
-        <v>560</v>
+        <v>650</v>
       </c>
       <c r="N14" t="n">
-        <v>1032</v>
+        <v>1219</v>
       </c>
       <c r="O14" t="n">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="P14" t="n">
-        <v>732</v>
+        <v>888</v>
       </c>
       <c r="Q14" t="n">
-        <v>462</v>
+        <v>542</v>
       </c>
       <c r="R14" t="n">
-        <v>604</v>
+        <v>709</v>
       </c>
       <c r="S14" t="n">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="T14" t="n">
-        <v>641</v>
+        <v>762</v>
       </c>
       <c r="U14" t="n">
-        <v>515</v>
+        <v>598</v>
       </c>
       <c r="V14" t="n">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="W14" t="n">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="X14" t="n">
-        <v>557</v>
+        <v>671</v>
       </c>
       <c r="Y14" t="n">
-        <v>579</v>
+        <v>682</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AA14" t="n">
-        <v>2027</v>
+        <v>2426</v>
       </c>
       <c r="AB14" t="n">
-        <v>2321.76</v>
+        <v>2760.96</v>
       </c>
       <c r="AC14" t="n">
-        <v>2024.76</v>
+        <v>2399.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AE14" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="AF14" t="n">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="AG14" t="n">
-        <v>521</v>
+        <v>601</v>
       </c>
       <c r="AH14" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="AI14" t="n">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="AJ14" t="n">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="AK14" t="n">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="AL14" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="n">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="AN14" t="n">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="AO14" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AP14" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="AQ14" t="n">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="AR14" t="n">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="AS14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>1151.2</v>
+        <v>1328.96</v>
       </c>
       <c r="AU14" t="n">
-        <v>1003.2</v>
+        <v>1153.96</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.021584059554004</v>
+        <v>1.006934724400332</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.9151161035642108</v>
+        <v>0.9140911932109624</v>
       </c>
       <c r="AX14" t="n">
-        <v>117.0203084119286</v>
+        <v>115.7618363722308</v>
       </c>
       <c r="AY14" t="n">
-        <v>104.4034877105762</v>
+        <v>103.9197217055399</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.61682070135243</v>
+        <v>11.84211466669091</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3568654736194627</v>
+        <v>0.3574315586183491</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6709071649833965</v>
+        <v>0.6831009358617399</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5161060537516851</v>
+        <v>0.521437091744465</v>
       </c>
       <c r="BD14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="BF14" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="BG14" t="n">
-        <v>511</v>
+        <v>618</v>
       </c>
       <c r="BH14" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="BI14" t="n">
-        <v>393</v>
+        <v>484</v>
       </c>
       <c r="BJ14" t="n">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="BK14" t="n">
-        <v>299</v>
+        <v>375</v>
       </c>
       <c r="BL14" t="n">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="BM14" t="n">
-        <v>354</v>
+        <v>421</v>
       </c>
       <c r="BN14" t="n">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="BO14" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="BP14" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="BQ14" t="n">
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="BR14" t="n">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="BS14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BT14" t="n">
-        <v>1170.56</v>
+        <v>1432</v>
       </c>
       <c r="BU14" t="n">
-        <v>1021.56</v>
+        <v>1246</v>
       </c>
       <c r="BV14" t="n">
-        <v>1.035757014984514</v>
+        <v>1.026081346525777</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.9230569539178066</v>
+        <v>0.943561642259595</v>
       </c>
       <c r="BX14" t="n">
-        <v>118.474900971936</v>
+        <v>117.7348857281165</v>
       </c>
       <c r="BY14" t="n">
-        <v>101.0520085241552</v>
+        <v>103.2550772303337</v>
       </c>
       <c r="BZ14" t="n">
-        <v>17.42289244778084</v>
+        <v>14.47980849778279</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3393999020594199</v>
+        <v>0.3456851978683031</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7965841503989961</v>
+        <v>0.7905647168577374</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5724090345878862</v>
+        <v>0.5692635922034429</v>
       </c>
       <c r="CD14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4128,244 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8696020133271409</v>
+        <v>0.8756436102594356</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9988797880295546</v>
+        <v>0.9843744358736066</v>
       </c>
       <c r="E15" t="n">
-        <v>98.42777545090779</v>
+        <v>99.25389039677863</v>
       </c>
       <c r="F15" t="n">
-        <v>113.0500217719582</v>
+        <v>110.9897842371766</v>
       </c>
       <c r="G15" t="n">
-        <v>-14.62224632105038</v>
+        <v>-11.73589384039792</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2897070823085149</v>
+        <v>0.2884059993896494</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6961633251289732</v>
+        <v>0.7071292887948688</v>
       </c>
       <c r="J15" t="n">
-        <v>0.489443645147027</v>
+        <v>0.4931164598657798</v>
       </c>
       <c r="K15" t="n">
-        <v>5000</v>
+        <v>6025</v>
       </c>
       <c r="L15" t="n">
-        <v>1886</v>
+        <v>2289</v>
       </c>
       <c r="M15" t="n">
-        <v>426</v>
+        <v>495</v>
       </c>
       <c r="N15" t="n">
-        <v>889</v>
+        <v>1030</v>
       </c>
       <c r="O15" t="n">
-        <v>234</v>
+        <v>297</v>
       </c>
       <c r="P15" t="n">
-        <v>715</v>
+        <v>910</v>
       </c>
       <c r="Q15" t="n">
-        <v>332</v>
+        <v>408</v>
       </c>
       <c r="R15" t="n">
-        <v>444</v>
+        <v>541</v>
       </c>
       <c r="S15" t="n">
+        <v>312</v>
+      </c>
+      <c r="T15" t="n">
+        <v>722</v>
+      </c>
+      <c r="U15" t="n">
+        <v>478</v>
+      </c>
+      <c r="V15" t="n">
+        <v>190</v>
+      </c>
+      <c r="W15" t="n">
+        <v>442</v>
+      </c>
+      <c r="X15" t="n">
+        <v>629</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>619</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2574</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2620.04</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2308.04</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>525</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>146</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>454</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>195</v>
+      </c>
+      <c r="AK15" t="n">
         <v>257</v>
       </c>
-      <c r="T15" t="n">
-        <v>585</v>
-      </c>
-      <c r="U15" t="n">
-        <v>397</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AL15" t="n">
         <v>160</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AM15" t="n">
+        <v>346</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>227</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>86</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>228</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>315</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>306</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1320.08</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1160.08</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.843713158341048</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.006573460733275</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>95.89340288502628</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>114.200930919761</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-18.30752803473473</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.2963252103298367</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.694708203673721</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.4869281973932811</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>3025</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>255</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>505</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>151</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>456</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>213</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>284</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>152</v>
+      </c>
+      <c r="BM15" t="n">
         <v>376</v>
       </c>
-      <c r="X15" t="n">
-        <v>525</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>512</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2176</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2175.36</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1918.36</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="BN15" t="n">
+        <v>251</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>104</v>
+      </c>
+      <c r="BP15" t="n">
         <v>214</v>
       </c>
-      <c r="AG15" t="n">
-        <v>472</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>122</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>383</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>164</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>218</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>196</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>79</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>199</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>280</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>266</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1149.92</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1009.92</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.8334663071542632</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.012529632105617</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>94.77910663484582</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>115.3239094597772</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-20.54480282493135</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0.3001908072406798</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0.6818087306150967</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.4816305823344414</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>212</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>417</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>112</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>332</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>168</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>226</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>117</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>295</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>201</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>81</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>177</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>245</v>
+        <v>314</v>
       </c>
       <c r="BR15" t="n">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="BS15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BT15" t="n">
-        <v>1025.44</v>
+        <v>1299.96</v>
       </c>
       <c r="BU15" t="n">
-        <v>908.4400000000001</v>
+        <v>1147.96</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.9087490283477585</v>
+        <v>0.907574062177823</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9840924569471531</v>
+        <v>0.9621754110139388</v>
       </c>
       <c r="BX15" t="n">
-        <v>102.3805000016416</v>
+        <v>102.614377908531</v>
       </c>
       <c r="BY15" t="n">
-        <v>110.5866434434876</v>
+        <v>107.7786375545921</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-8.206143441846001</v>
+        <v>-5.164259646061113</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2783497136320031</v>
+        <v>0.2804867884494621</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.7117141358523394</v>
+        <v>0.7195503739160164</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.4979077965273281</v>
+        <v>0.4993047223382787</v>
       </c>
       <c r="CD15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -4380,244 +4380,244 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.066378724431395</v>
+        <v>1.066524328506282</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8926546426226705</v>
+        <v>0.8896719042791157</v>
       </c>
       <c r="E16" t="n">
-        <v>119.72513940432</v>
+        <v>120.2137292851303</v>
       </c>
       <c r="F16" t="n">
-        <v>100.4061841698055</v>
+        <v>99.83030193897015</v>
       </c>
       <c r="G16" t="n">
-        <v>19.31895523451453</v>
+        <v>20.38342734616017</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3201634994321476</v>
+        <v>0.3276629450534852</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7036812862599849</v>
+        <v>0.7092363823263899</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5196219946664736</v>
+        <v>0.5255498135838617</v>
       </c>
       <c r="K16" t="n">
-        <v>5050</v>
+        <v>6075</v>
       </c>
       <c r="L16" t="n">
-        <v>2313</v>
+        <v>2765</v>
       </c>
       <c r="M16" t="n">
-        <v>557</v>
+        <v>658</v>
       </c>
       <c r="N16" t="n">
-        <v>965</v>
+        <v>1127</v>
       </c>
       <c r="O16" t="n">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="P16" t="n">
-        <v>661</v>
+        <v>812</v>
       </c>
       <c r="Q16" t="n">
-        <v>440</v>
+        <v>528</v>
       </c>
       <c r="R16" t="n">
-        <v>579</v>
+        <v>707</v>
       </c>
       <c r="S16" t="n">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="T16" t="n">
-        <v>575</v>
+        <v>694</v>
       </c>
       <c r="U16" t="n">
-        <v>507</v>
+        <v>588</v>
       </c>
       <c r="V16" t="n">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="W16" t="n">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="X16" t="n">
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="Y16" t="n">
-        <v>566</v>
+        <v>682</v>
       </c>
       <c r="Z16" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="AA16" t="n">
-        <v>1915</v>
+        <v>2287</v>
       </c>
       <c r="AB16" t="n">
-        <v>2168.76</v>
+        <v>2594.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>1933.76</v>
+        <v>2304.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE16" t="n">
-        <v>2625</v>
+        <v>3050</v>
       </c>
       <c r="AF16" t="n">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="AG16" t="n">
-        <v>498</v>
+        <v>559</v>
       </c>
       <c r="AH16" t="n">
+        <v>151</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>389</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>274</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>372</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>134</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>323</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>275</v>
+      </c>
+      <c r="AO16" t="n">
         <v>128</v>
       </c>
-      <c r="AI16" t="n">
-        <v>326</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>229</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>308</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>276</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>247</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>115</v>
-      </c>
       <c r="AP16" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="AQ16" t="n">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="AR16" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AS16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AT16" t="n">
-        <v>1109.52</v>
+        <v>1288.68</v>
       </c>
       <c r="AU16" t="n">
-        <v>994.52</v>
+        <v>1154.68</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.072980927361294</v>
+        <v>1.071076907747477</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.9092415883348237</v>
+        <v>0.9271155551140439</v>
       </c>
       <c r="AX16" t="n">
-        <v>119.841915852236</v>
+        <v>119.6353514621817</v>
       </c>
       <c r="AY16" t="n">
-        <v>103.779003406811</v>
+        <v>105.1175982168604</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.06291244542495</v>
+        <v>14.51775324532135</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.3129456436720919</v>
+        <v>0.3143941610237494</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.6663331153587108</v>
+        <v>0.6792846769890436</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.4988553256284053</v>
+        <v>0.5048466797518835</v>
       </c>
       <c r="BD16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>2425</v>
+        <v>3025</v>
       </c>
       <c r="BF16" t="n">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="BG16" t="n">
-        <v>467</v>
+        <v>568</v>
       </c>
       <c r="BH16" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="BI16" t="n">
+        <v>423</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>254</v>
+      </c>
+      <c r="BK16" t="n">
         <v>335</v>
       </c>
-      <c r="BJ16" t="n">
-        <v>211</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>271</v>
-      </c>
       <c r="BL16" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="BM16" t="n">
-        <v>299</v>
+        <v>371</v>
       </c>
       <c r="BN16" t="n">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="BO16" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="BP16" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="BQ16" t="n">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="BR16" t="n">
-        <v>276</v>
+        <v>342</v>
       </c>
       <c r="BS16" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BT16" t="n">
-        <v>1059.24</v>
+        <v>1305.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>939.24</v>
+        <v>1149.4</v>
       </c>
       <c r="BV16" t="n">
-        <v>1.059226337924005</v>
+        <v>1.061971749265086</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8746854514345053</v>
+        <v>0.8522282534441883</v>
       </c>
       <c r="BX16" t="n">
-        <v>119.5986315857444</v>
+        <v>120.7921071080789</v>
       </c>
       <c r="BY16" t="n">
-        <v>96.75229666304953</v>
+        <v>94.54300566107989</v>
       </c>
       <c r="BZ16" t="n">
-        <v>22.8463349226949</v>
+        <v>26.24910144699898</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.327982843172208</v>
+        <v>0.3409317290832209</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.7441418047363652</v>
+        <v>0.739188087663736</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.5421192194577145</v>
+        <v>0.5462529474158399</v>
       </c>
       <c r="CD16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -4632,244 +4632,244 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.018305301051677</v>
+        <v>1.022935489516515</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9694079712113691</v>
+        <v>0.962713746696065</v>
       </c>
       <c r="E17" t="n">
-        <v>114.3791303056464</v>
+        <v>114.4655295552824</v>
       </c>
       <c r="F17" t="n">
-        <v>108.7815540913745</v>
+        <v>108.531192867698</v>
       </c>
       <c r="G17" t="n">
-        <v>5.597576214271908</v>
+        <v>5.93433668758446</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2992750500995604</v>
+        <v>0.2987571804442724</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7132392231574252</v>
+        <v>0.7062563511881862</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5107044931473004</v>
+        <v>0.5103790444159573</v>
       </c>
       <c r="K17" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="L17" t="n">
-        <v>2113</v>
+        <v>2539</v>
       </c>
       <c r="M17" t="n">
-        <v>457</v>
+        <v>549</v>
       </c>
       <c r="N17" t="n">
-        <v>821</v>
+        <v>965</v>
       </c>
       <c r="O17" t="n">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="P17" t="n">
-        <v>716</v>
+        <v>859</v>
       </c>
       <c r="Q17" t="n">
-        <v>425</v>
+        <v>508</v>
       </c>
       <c r="R17" t="n">
-        <v>561</v>
+        <v>672</v>
       </c>
       <c r="S17" t="n">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="T17" t="n">
-        <v>567</v>
+        <v>681</v>
       </c>
       <c r="U17" t="n">
-        <v>387</v>
+        <v>476</v>
       </c>
       <c r="V17" t="n">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="W17" t="n">
-        <v>290</v>
+        <v>362</v>
       </c>
       <c r="X17" t="n">
-        <v>546</v>
+        <v>651</v>
       </c>
       <c r="Y17" t="n">
-        <v>584</v>
+        <v>689</v>
       </c>
       <c r="Z17" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="AA17" t="n">
-        <v>2023</v>
+        <v>2414</v>
       </c>
       <c r="AB17" t="n">
-        <v>2073.84</v>
+        <v>2481.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>1848.84</v>
+        <v>2219.68</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="AF17" t="n">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="AG17" t="n">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="AH17" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="AI17" t="n">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="AJ17" t="n">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="AK17" t="n">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="AL17" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AM17" t="n">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="AN17" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="AO17" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="AQ17" t="n">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="AR17" t="n">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AT17" t="n">
-        <v>1068</v>
+        <v>1228.68</v>
       </c>
       <c r="AU17" t="n">
-        <v>959</v>
+        <v>1107.68</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.9898594810026412</v>
+        <v>1.002864804508091</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.978129815162451</v>
+        <v>0.9766604326316545</v>
       </c>
       <c r="AX17" t="n">
-        <v>110.2603911190724</v>
+        <v>111.2264350797026</v>
       </c>
       <c r="AY17" t="n">
-        <v>109.4098950969893</v>
+        <v>110.1620942098723</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.850496022083112</v>
+        <v>1.064340869830321</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.2794114499114524</v>
+        <v>0.2797634275300964</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.7254499096620687</v>
+        <v>0.7096996860168905</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.5086079485838687</v>
+        <v>0.5048446121457768</v>
       </c>
       <c r="BD17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE17" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="BF17" t="n">
-        <v>211</v>
+        <v>271</v>
       </c>
       <c r="BG17" t="n">
+        <v>472</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>160</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>448</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>282</v>
+      </c>
+      <c r="BK17" t="n">
         <v>375</v>
       </c>
-      <c r="BH17" t="n">
-        <v>132</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>363</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>235</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>311</v>
-      </c>
       <c r="BL17" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="BM17" t="n">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="BN17" t="n">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="BO17" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="BP17" t="n">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="BQ17" t="n">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="BR17" t="n">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="BS17" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BT17" t="n">
-        <v>1005.84</v>
+        <v>1253</v>
       </c>
       <c r="BU17" t="n">
-        <v>889.84</v>
+        <v>1112</v>
       </c>
       <c r="BV17" t="n">
-        <v>1.0491216061048</v>
+        <v>1.043006174524939</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.9599593069310303</v>
+        <v>0.9487670607604751</v>
       </c>
       <c r="BX17" t="n">
-        <v>118.8410977577682</v>
+        <v>117.7046240308623</v>
       </c>
       <c r="BY17" t="n">
-        <v>108.1008513352918</v>
+        <v>106.9002915255237</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.74024642247644</v>
+        <v>10.8043325053386</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.3207939503033441</v>
+        <v>0.3177509333584484</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.700010979444062</v>
+        <v>0.7028130163594822</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.5129757497576845</v>
+        <v>0.5159134766861377</v>
       </c>
       <c r="CD17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -4884,244 +4884,244 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8694043673832872</v>
+        <v>0.8697930569932759</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9784362771082007</v>
+        <v>0.9570889966587213</v>
       </c>
       <c r="E18" t="n">
-        <v>98.21758340793994</v>
+        <v>97.82110442894506</v>
       </c>
       <c r="F18" t="n">
-        <v>112.0074210073753</v>
+        <v>110.2786233167517</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.78983759943529</v>
+        <v>-12.4575188878066</v>
       </c>
       <c r="H18" t="n">
-        <v>0.281766605714072</v>
+        <v>0.2690633968524361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.643490846029693</v>
+        <v>0.6421763069005689</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4502452252408753</v>
+        <v>0.4473833365828167</v>
       </c>
       <c r="K18" t="n">
-        <v>5025</v>
+        <v>6025</v>
       </c>
       <c r="L18" t="n">
-        <v>1824</v>
+        <v>2187</v>
       </c>
       <c r="M18" t="n">
-        <v>391</v>
+        <v>489</v>
       </c>
       <c r="N18" t="n">
-        <v>853</v>
+        <v>1055</v>
       </c>
       <c r="O18" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="P18" t="n">
-        <v>691</v>
+        <v>805</v>
       </c>
       <c r="Q18" t="n">
-        <v>397</v>
+        <v>474</v>
       </c>
       <c r="R18" t="n">
-        <v>553</v>
+        <v>657</v>
       </c>
       <c r="S18" t="n">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="T18" t="n">
-        <v>498</v>
+        <v>628</v>
       </c>
       <c r="U18" t="n">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="V18" t="n">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="W18" t="n">
+        <v>373</v>
+      </c>
+      <c r="X18" t="n">
+        <v>607</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>630</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>99</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2495</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2522.08</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2242.08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>248</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>518</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>124</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>399</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>227</v>
+      </c>
+      <c r="AK18" t="n">
         <v>318</v>
       </c>
-      <c r="X18" t="n">
-        <v>496</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>529</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>78</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2118</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2105.32</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1862.32</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>202</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>430</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>116</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>364</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>204</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>283</v>
-      </c>
       <c r="AL18" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="AM18" t="n">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="AN18" t="n">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="AO18" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="AP18" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="AQ18" t="n">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="AR18" t="n">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="AS18" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AT18" t="n">
-        <v>1070.52</v>
+        <v>1234.92</v>
       </c>
       <c r="AU18" t="n">
-        <v>957.52</v>
+        <v>1111.92</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.8972871912063265</v>
+        <v>0.8906519044180929</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.014775345764666</v>
+        <v>1.005018274172334</v>
       </c>
       <c r="AX18" t="n">
-        <v>100.3118107378594</v>
+        <v>98.99236851216686</v>
       </c>
       <c r="AY18" t="n">
-        <v>116.0086531193324</v>
+        <v>115.9315677265166</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-15.69684238147296</v>
+        <v>-16.93919921434978</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.2559289690705702</v>
+        <v>0.2421559837208099</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.6495080216317992</v>
+        <v>0.6342282734022139</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.4386711068771499</v>
+        <v>0.4270099087884794</v>
       </c>
       <c r="BD18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE18" t="n">
-        <v>2425</v>
+        <v>3025</v>
       </c>
       <c r="BF18" t="n">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="BG18" t="n">
-        <v>423</v>
+        <v>537</v>
       </c>
       <c r="BH18" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="BI18" t="n">
-        <v>327</v>
+        <v>406</v>
       </c>
       <c r="BJ18" t="n">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="BK18" t="n">
-        <v>270</v>
+        <v>339</v>
       </c>
       <c r="BL18" t="n">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="BM18" t="n">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="BN18" t="n">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="BO18" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="BP18" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="BQ18" t="n">
-        <v>238</v>
+        <v>303</v>
       </c>
       <c r="BR18" t="n">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="BS18" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="BT18" t="n">
-        <v>1034.8</v>
+        <v>1287.16</v>
       </c>
       <c r="BU18" t="n">
-        <v>904.8</v>
+        <v>1130.16</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8391979749083278</v>
+        <v>0.8489342095684588</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9390689527303638</v>
+        <v>0.9091597191451085</v>
       </c>
       <c r="BX18" t="n">
-        <v>95.94883713386052</v>
+        <v>96.64984034572326</v>
       </c>
       <c r="BY18" t="n">
-        <v>107.6727528860883</v>
+        <v>104.6256789069867</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-11.72391575222783</v>
+        <v>-7.975838561263433</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.3097573787445323</v>
+        <v>0.2959708099840623</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.6369722391274116</v>
+        <v>0.6501243403989243</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.4627838534682442</v>
+        <v>0.4677567643771539</v>
       </c>
       <c r="CD18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -5136,244 +5136,244 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.992032740863957</v>
+        <v>0.9836569987456442</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8695293686756513</v>
+        <v>0.8742967563916912</v>
       </c>
       <c r="E19" t="n">
-        <v>113.0043073993123</v>
+        <v>111.7293681151609</v>
       </c>
       <c r="F19" t="n">
-        <v>97.74287415486252</v>
+        <v>98.79320888978441</v>
       </c>
       <c r="G19" t="n">
-        <v>15.26143324444977</v>
+        <v>12.93615922537647</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3248090494829252</v>
+        <v>0.3156153595262668</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7171648285413645</v>
+        <v>0.7073649542166526</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5271472881554786</v>
+        <v>0.5175435146552414</v>
       </c>
       <c r="K19" t="n">
-        <v>5200</v>
+        <v>6000</v>
       </c>
       <c r="L19" t="n">
-        <v>2183</v>
+        <v>2493</v>
       </c>
       <c r="M19" t="n">
-        <v>528</v>
+        <v>597</v>
       </c>
       <c r="N19" t="n">
-        <v>989</v>
+        <v>1132</v>
       </c>
       <c r="O19" t="n">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="P19" t="n">
-        <v>720</v>
+        <v>825</v>
       </c>
       <c r="Q19" t="n">
-        <v>356</v>
+        <v>420</v>
       </c>
       <c r="R19" t="n">
-        <v>515</v>
+        <v>602</v>
       </c>
       <c r="S19" t="n">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="T19" t="n">
-        <v>608</v>
+        <v>697</v>
       </c>
       <c r="U19" t="n">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="V19" t="n">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="W19" t="n">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="X19" t="n">
-        <v>553</v>
+        <v>643</v>
       </c>
       <c r="Y19" t="n">
-        <v>510</v>
+        <v>599</v>
       </c>
       <c r="Z19" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="AA19" t="n">
-        <v>1874</v>
+        <v>2182</v>
       </c>
       <c r="AB19" t="n">
-        <v>2205.6</v>
+        <v>2539.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>1930.6</v>
+        <v>2230.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="AF19" t="n">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="AG19" t="n">
-        <v>452</v>
+        <v>552</v>
       </c>
       <c r="AH19" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="AI19" t="n">
-        <v>342</v>
+        <v>418</v>
       </c>
       <c r="AJ19" t="n">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="AK19" t="n">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="AL19" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="AM19" t="n">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="AN19" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AO19" t="n">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="AP19" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="AQ19" t="n">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="AR19" t="n">
-        <v>235</v>
+        <v>308</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AT19" t="n">
-        <v>1018.84</v>
+        <v>1270.16</v>
       </c>
       <c r="AU19" t="n">
-        <v>889.84</v>
+        <v>1118.16</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.9936248790724237</v>
+        <v>0.9687592714227079</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.8659893271862308</v>
+        <v>0.8781379451694071</v>
       </c>
       <c r="AX19" t="n">
-        <v>113.5978811475987</v>
+        <v>109.9396546634856</v>
       </c>
       <c r="AY19" t="n">
-        <v>95.98630174244708</v>
+        <v>98.49452898468466</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.61157940515162</v>
+        <v>11.44512567880098</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.315133038938186</v>
+        <v>0.2999644273956418</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.7487721713529848</v>
+        <v>0.7218814549057829</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.5325416686012221</v>
+        <v>0.5119005625574621</v>
       </c>
       <c r="BD19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BE19" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="BF19" t="n">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="BG19" t="n">
-        <v>537</v>
+        <v>580</v>
       </c>
       <c r="BH19" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="BI19" t="n">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="BJ19" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="BK19" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="BL19" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="BM19" t="n">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="BN19" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="BO19" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="BP19" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="BQ19" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="BR19" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="BS19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BT19" t="n">
-        <v>1186.76</v>
+        <v>1269.72</v>
       </c>
       <c r="BU19" t="n">
-        <v>1040.76</v>
+        <v>1112.72</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.9906680509709858</v>
+        <v>0.9985547260685805</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.8725636899522975</v>
+        <v>0.8704555676139751</v>
       </c>
       <c r="BX19" t="n">
-        <v>112.4955299007811</v>
+        <v>113.5190815668361</v>
       </c>
       <c r="BY19" t="n">
-        <v>99.24850765121865</v>
+        <v>99.09188879488417</v>
       </c>
       <c r="BZ19" t="n">
-        <v>13.24702224956247</v>
+        <v>14.42719277195196</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.3331027728069874</v>
+        <v>0.3312662916568919</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.6900728204171187</v>
+        <v>0.6928484535275222</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.5225235334876986</v>
+        <v>0.5231864667530209</v>
       </c>
       <c r="CD19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,244 +852,244 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9513670599526608</v>
+        <v>0.9417337814841368</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9213215134648567</v>
+        <v>0.9165997032775537</v>
       </c>
       <c r="E2" t="n">
-        <v>107.8296407911593</v>
+        <v>107.3829207096868</v>
       </c>
       <c r="F2" t="n">
-        <v>101.7138406744517</v>
+        <v>101.1479184572993</v>
       </c>
       <c r="G2" t="n">
-        <v>6.115800116707605</v>
+        <v>6.235002252387472</v>
       </c>
       <c r="H2" t="n">
-        <v>0.306750052550015</v>
+        <v>0.3130609428999607</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7508789930976755</v>
+        <v>0.7493766261520676</v>
       </c>
       <c r="J2" t="n">
-        <v>0.525500538861946</v>
+        <v>0.5253346435754654</v>
       </c>
       <c r="K2" t="n">
-        <v>5225</v>
+        <v>6225</v>
       </c>
       <c r="L2" t="n">
-        <v>2163</v>
+        <v>2552</v>
       </c>
       <c r="M2" t="n">
-        <v>450</v>
+        <v>536</v>
       </c>
       <c r="N2" t="n">
-        <v>840</v>
+        <v>1002</v>
       </c>
       <c r="O2" t="n">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="P2" t="n">
-        <v>852</v>
+        <v>1021</v>
       </c>
       <c r="Q2" t="n">
-        <v>402</v>
+        <v>463</v>
       </c>
       <c r="R2" t="n">
-        <v>562</v>
+        <v>645</v>
       </c>
       <c r="S2" t="n">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="T2" t="n">
-        <v>625</v>
+        <v>739</v>
       </c>
       <c r="U2" t="n">
-        <v>404</v>
+        <v>481</v>
       </c>
       <c r="V2" t="n">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="W2" t="n">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="X2" t="n">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="Y2" t="n">
-        <v>553</v>
+        <v>650</v>
       </c>
       <c r="Z2" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>2048</v>
+        <v>2424</v>
       </c>
       <c r="AB2" t="n">
-        <v>2281.28</v>
+        <v>2716.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>2009.28</v>
+        <v>2379.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AE2" t="n">
-        <v>2825</v>
+        <v>3025</v>
       </c>
       <c r="AF2" t="n">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="AG2" t="n">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="AH2" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="AI2" t="n">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="AJ2" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="AK2" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="AL2" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AM2" t="n">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="AN2" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AO2" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="AQ2" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="AR2" t="n">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1251.2</v>
+        <v>1337.76</v>
       </c>
       <c r="AU2" t="n">
-        <v>1086.2</v>
+        <v>1162.76</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.9307812442451924</v>
+        <v>0.9218714903158456</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9293227146817394</v>
+        <v>0.9255886402081579</v>
       </c>
       <c r="AX2" t="n">
-        <v>107.028217245648</v>
+        <v>105.9013622192401</v>
       </c>
       <c r="AY2" t="n">
-        <v>102.7693545830184</v>
+        <v>102.5074158852856</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.258862662629544</v>
+        <v>3.393946333954433</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.3322579671319167</v>
+        <v>0.329155055037408</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.7517852599846179</v>
+        <v>0.742691883677951</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.5313252291556706</v>
+        <v>0.5243188477584073</v>
       </c>
       <c r="BD2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE2" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="BF2" t="n">
-        <v>203</v>
+        <v>278</v>
       </c>
       <c r="BG2" t="n">
-        <v>364</v>
+        <v>498</v>
       </c>
       <c r="BH2" t="n">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="BI2" t="n">
-        <v>371</v>
+        <v>508</v>
       </c>
       <c r="BJ2" t="n">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="BK2" t="n">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="BL2" t="n">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="BM2" t="n">
-        <v>285</v>
+        <v>383</v>
       </c>
       <c r="BN2" t="n">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="BO2" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="BP2" t="n">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="BQ2" t="n">
-        <v>247</v>
+        <v>327</v>
       </c>
       <c r="BR2" t="n">
-        <v>267</v>
+        <v>344</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BT2" t="n">
-        <v>1030.08</v>
+        <v>1379.04</v>
       </c>
       <c r="BU2" t="n">
-        <v>923.08</v>
+        <v>1217.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9753838449447071</v>
+        <v>0.9603546794544098</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9119867787118268</v>
+        <v>0.9081725749051122</v>
       </c>
       <c r="BX2" t="n">
-        <v>108.7646349275893</v>
+        <v>108.7718817944806</v>
       </c>
       <c r="BY2" t="n">
-        <v>100.4824077811239</v>
+        <v>99.87338961856219</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.282227146465344</v>
+        <v>8.898492175918449</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2769908188711299</v>
+        <v>0.2979727127711039</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7498216817295763</v>
+        <v>0.7556435722215522</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.5187050668526008</v>
+        <v>0.5262869521539573</v>
       </c>
       <c r="CD2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1104,244 +1104,244 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9451462608068156</v>
+        <v>0.9393165177231364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9652789106172202</v>
+        <v>0.9606506483217557</v>
       </c>
       <c r="E3" t="n">
-        <v>106.6574808032636</v>
+        <v>106.0633110921741</v>
       </c>
       <c r="F3" t="n">
-        <v>111.3589823186588</v>
+        <v>110.1689829519467</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.70150151539512</v>
+        <v>-4.105671859772651</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3153302198611653</v>
+        <v>0.3107791531421821</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659169145206523</v>
+        <v>0.6720417879642876</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4943916704434566</v>
+        <v>0.4961777722599058</v>
       </c>
       <c r="K3" t="n">
-        <v>5022.766666666666</v>
+        <v>6247.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2099</v>
+        <v>2591</v>
       </c>
       <c r="M3" t="n">
-        <v>520</v>
+        <v>643</v>
       </c>
       <c r="N3" t="n">
-        <v>1044</v>
+        <v>1295</v>
       </c>
       <c r="O3" t="n">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="P3" t="n">
-        <v>543</v>
+        <v>699</v>
       </c>
       <c r="Q3" t="n">
-        <v>459</v>
+        <v>573</v>
       </c>
       <c r="R3" t="n">
-        <v>624</v>
+        <v>772</v>
       </c>
       <c r="S3" t="n">
-        <v>255</v>
+        <v>317</v>
       </c>
       <c r="T3" t="n">
-        <v>584</v>
+        <v>733</v>
       </c>
       <c r="U3" t="n">
-        <v>310</v>
+        <v>395</v>
       </c>
       <c r="V3" t="n">
+        <v>211</v>
+      </c>
+      <c r="W3" t="n">
+        <v>426</v>
+      </c>
+      <c r="X3" t="n">
+        <v>666</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>682</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>73</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2672</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2759.68</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2442.68</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3225</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>332</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>665</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>127</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>344</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>286</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>378</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>395</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>187</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>99</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>354</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>338</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1405.32</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1251.32</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.9479445106231158</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.9470223378959933</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>106.4851581043018</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>109.6205564722469</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-3.135398367945059</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.313599116274534</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.6661528941127431</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.5032252149772836</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3022.766666666666</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>311</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>630</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>117</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>355</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>287</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>394</v>
+      </c>
+      <c r="BL3" t="n">
         <v>163</v>
       </c>
-      <c r="W3" t="n">
-        <v>359</v>
-      </c>
-      <c r="X3" t="n">
-        <v>540</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>550</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>63</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2177</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2220.56</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1965.56</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>267</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>529</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>106</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>265</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>234</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="BM3" t="n">
+        <v>338</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>208</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>112</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>196</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>312</v>
       </c>
-      <c r="AL3" t="n">
-        <v>124</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>304</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>156</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>76</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>192</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>287</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>276</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1123.28</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>999.28</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.9663334080264676</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.9654715493550523</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>108.6237728788093</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>111.8588658851437</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.235093006334291</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.3252144752903074</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.6554163167515157</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.5042588175578078</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2422.766666666666</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>253</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>515</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>94</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>278</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>225</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>312</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>131</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>280</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>154</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>87</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>167</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>253</v>
-      </c>
       <c r="BR3" t="n">
-        <v>274</v>
+        <v>344</v>
       </c>
       <c r="BS3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="BT3" t="n">
-        <v>1097.28</v>
+        <v>1354.36</v>
       </c>
       <c r="BU3" t="n">
-        <v>966.28</v>
+        <v>1191.36</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9221935179855261</v>
+        <v>0.9301133252964917</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.9650702186512353</v>
+        <v>0.975187512775902</v>
       </c>
       <c r="BX3" t="n">
-        <v>104.5273310547558</v>
+        <v>105.6133409459045</v>
       </c>
       <c r="BY3" t="n">
-        <v>110.8174417883001</v>
+        <v>110.7539711969599</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-6.29011073354435</v>
+        <v>-5.140630251055417</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.3046222764795947</v>
+        <v>0.3077711924676732</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6632347093661144</v>
+        <v>0.6783232747392683</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.483702261069576</v>
+        <v>0.4886605000280362</v>
       </c>
       <c r="CD3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1356,244 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9102302420787259</v>
+        <v>0.8827689043507106</v>
       </c>
       <c r="D4" t="n">
-        <v>1.001898562194691</v>
+        <v>0.9995074092848157</v>
       </c>
       <c r="E4" t="n">
-        <v>106.7337395527079</v>
+        <v>103.9793029720495</v>
       </c>
       <c r="F4" t="n">
-        <v>111.8994828137643</v>
+        <v>111.3923829627076</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.1657432610564</v>
+        <v>-7.413079990658183</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3721297357183876</v>
+        <v>0.3763023125583365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7098974497146971</v>
+        <v>0.7166092197793431</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5266028018987361</v>
+        <v>0.5306170802071598</v>
       </c>
       <c r="K4" t="n">
-        <v>2600</v>
+        <v>3800</v>
       </c>
       <c r="L4" t="n">
-        <v>1034</v>
+        <v>1467</v>
       </c>
       <c r="M4" t="n">
-        <v>252</v>
+        <v>359</v>
       </c>
       <c r="N4" t="n">
-        <v>548</v>
+        <v>791</v>
       </c>
       <c r="O4" t="n">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="P4" t="n">
-        <v>317</v>
+        <v>454</v>
       </c>
       <c r="Q4" t="n">
-        <v>203</v>
+        <v>302</v>
       </c>
       <c r="R4" t="n">
-        <v>282</v>
+        <v>434</v>
       </c>
       <c r="S4" t="n">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="T4" t="n">
-        <v>271</v>
+        <v>404</v>
       </c>
       <c r="U4" t="n">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="V4" t="n">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="W4" t="n">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="X4" t="n">
-        <v>300</v>
+        <v>449</v>
       </c>
       <c r="Y4" t="n">
-        <v>288</v>
+        <v>427</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AA4" t="n">
-        <v>1077</v>
+        <v>1565</v>
       </c>
       <c r="AB4" t="n">
-        <v>1141.08</v>
+        <v>1665.96</v>
       </c>
       <c r="AC4" t="n">
-        <v>970.08</v>
+        <v>1409.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="AF4" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="AG4" t="n">
-        <v>205</v>
+        <v>371</v>
       </c>
       <c r="AH4" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="AI4" t="n">
-        <v>121</v>
+        <v>206</v>
       </c>
       <c r="AJ4" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="AK4" t="n">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="AL4" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="AM4" t="n">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="AN4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>106</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>216</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>199</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>775.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>664.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8496749780130846</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.9998458584589286</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>99.02518637057544</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>112.5423066128255</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-13.5171202422501</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.3563556122826207</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.7022040747304111</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.5164678077517997</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>201</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>420</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>83</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>248</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>158</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>224</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>145</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>208</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>167</v>
+      </c>
+      <c r="BO4" t="n">
         <v>68</v>
       </c>
-      <c r="AO4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>118</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>104</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BP4" t="n">
+        <v>124</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>233</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>228</v>
+      </c>
+      <c r="BS4" t="n">
         <v>15</v>
       </c>
-      <c r="AT4" t="n">
-        <v>426.76</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>368.76</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8989491706217176</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.011121276035282</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>104.0680646041733</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>114.7939083022978</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-10.72584369812456</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.349263231360418</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.6862519644957648</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.5114083139083139</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>162</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>343</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>66</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>196</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>130</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>178</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>113</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>163</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>134</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>54</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>97</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>182</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>184</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>12</v>
-      </c>
       <c r="BT4" t="n">
-        <v>714.3199999999999</v>
+        <v>890.5599999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>601.3199999999999</v>
+        <v>745.5599999999999</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.9172809117393561</v>
+        <v>0.9125534380545739</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.9961343660443216</v>
+        <v>0.9992028050281135</v>
       </c>
       <c r="BX4" t="n">
-        <v>108.399786395542</v>
+        <v>108.4380079133761</v>
       </c>
       <c r="BY4" t="n">
-        <v>110.0904668834308</v>
+        <v>110.3574516776016</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-1.690680487888798</v>
+        <v>-1.919443764225453</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3864213009421186</v>
+        <v>0.3942543428064808</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.72467587797653</v>
+        <v>0.729573850323382</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5360993568927498</v>
+        <v>0.5433514254169837</v>
       </c>
       <c r="CD4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1860,244 +1860,244 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9087129240726243</v>
+        <v>0.9052293754333669</v>
       </c>
       <c r="D6" t="n">
-        <v>0.94514919170816</v>
+        <v>0.95873150689357</v>
       </c>
       <c r="E6" t="n">
-        <v>100.9504844798601</v>
+        <v>100.9099891737401</v>
       </c>
       <c r="F6" t="n">
-        <v>109.0257007240447</v>
+        <v>110.3297742480397</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.07521624418459</v>
+        <v>-9.419785074299647</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2657710606894645</v>
+        <v>0.271048297552913</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6142560244749703</v>
+        <v>0.6250522741353367</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4357171089844654</v>
+        <v>0.4435733435210618</v>
       </c>
       <c r="K6" t="n">
-        <v>5250</v>
+        <v>6250</v>
       </c>
       <c r="L6" t="n">
-        <v>1987</v>
+        <v>2352</v>
       </c>
       <c r="M6" t="n">
-        <v>500</v>
+        <v>584</v>
       </c>
       <c r="N6" t="n">
-        <v>933</v>
+        <v>1108</v>
       </c>
       <c r="O6" t="n">
-        <v>211</v>
+        <v>259</v>
       </c>
       <c r="P6" t="n">
-        <v>682</v>
+        <v>821</v>
       </c>
       <c r="Q6" t="n">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="R6" t="n">
-        <v>520</v>
+        <v>609</v>
       </c>
       <c r="S6" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="T6" t="n">
-        <v>489</v>
+        <v>595</v>
       </c>
       <c r="U6" t="n">
-        <v>398</v>
+        <v>477</v>
       </c>
       <c r="V6" t="n">
+        <v>255</v>
+      </c>
+      <c r="W6" t="n">
+        <v>406</v>
+      </c>
+      <c r="X6" t="n">
+        <v>674</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>626</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2570</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2602.96</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2332.96</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>268</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>492</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>405</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>303</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>117</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>296</v>
+      </c>
+      <c r="AN6" t="n">
         <v>229</v>
       </c>
-      <c r="W6" t="n">
-        <v>347</v>
-      </c>
-      <c r="X6" t="n">
-        <v>577</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>535</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2150</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2190.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1970.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>239</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>432</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>97</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>343</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>178</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>266</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>98</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>251</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>192</v>
-      </c>
       <c r="AO6" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="AP6" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="AQ6" t="n">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="AR6" t="n">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="AS6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>1084.04</v>
+        <v>1248.32</v>
       </c>
       <c r="AU6" t="n">
-        <v>986.04</v>
+        <v>1131.32</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8765458236953942</v>
+        <v>0.8807243205814752</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9357182380057207</v>
+        <v>0.946111507896537</v>
       </c>
       <c r="AX6" t="n">
-        <v>96.30846684824357</v>
+        <v>97.13794708067651</v>
       </c>
       <c r="AY6" t="n">
-        <v>107.9108809128095</v>
+        <v>109.3236451495537</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-11.60241406456598</v>
+        <v>-12.18569806887719</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2520816829007047</v>
+        <v>0.2595453765061675</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6215065918760251</v>
+        <v>0.6241510288633612</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4326764491428264</v>
+        <v>0.4389036251043099</v>
       </c>
       <c r="BD6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE6" t="n">
-        <v>2650</v>
+        <v>3250</v>
       </c>
       <c r="BF6" t="n">
-        <v>261</v>
+        <v>316</v>
       </c>
       <c r="BG6" t="n">
-        <v>501</v>
+        <v>616</v>
       </c>
       <c r="BH6" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="BI6" t="n">
-        <v>339</v>
+        <v>416</v>
       </c>
       <c r="BJ6" t="n">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="BK6" t="n">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="BL6" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="BM6" t="n">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="BN6" t="n">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="BO6" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="BP6" t="n">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="BQ6" t="n">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="BR6" t="n">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="BS6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="BT6" t="n">
-        <v>1106.76</v>
+        <v>1354.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>984.76</v>
+        <v>1201.64</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9408800244498543</v>
+        <v>0.9282028643570152</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.9545801454105993</v>
+        <v>0.9705627559532886</v>
       </c>
       <c r="BX6" t="n">
-        <v>105.5925021114766</v>
+        <v>104.4462786359872</v>
       </c>
       <c r="BY6" t="n">
-        <v>110.1405205352798</v>
+        <v>111.2730202778704</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-4.548018423803206</v>
+        <v>-6.826741641883203</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.2794604384782243</v>
+        <v>0.281832286034237</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.6070054570739155</v>
+        <v>0.625897191577814</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.4387577688261045</v>
+        <v>0.4479512045367668</v>
       </c>
       <c r="CD6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -2112,244 +2112,244 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9541817439874302</v>
+        <v>0.95608432288256</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9553313539133701</v>
+        <v>0.9478528247441815</v>
       </c>
       <c r="E7" t="n">
-        <v>105.0516767509059</v>
+        <v>105.0765529384902</v>
       </c>
       <c r="F7" t="n">
-        <v>107.4146540648682</v>
+        <v>106.2644074972537</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.362977313962327</v>
+        <v>-1.187854558763518</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2478907648670726</v>
+        <v>0.2442252621030992</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7243566706475588</v>
+        <v>0.7315559380293846</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4970642783908503</v>
+        <v>0.4993951465574644</v>
       </c>
       <c r="K7" t="n">
-        <v>5225</v>
+        <v>6225</v>
       </c>
       <c r="L7" t="n">
-        <v>2069</v>
+        <v>2476</v>
       </c>
       <c r="M7" t="n">
-        <v>472</v>
+        <v>582</v>
       </c>
       <c r="N7" t="n">
-        <v>919</v>
+        <v>1111</v>
       </c>
       <c r="O7" t="n">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="P7" t="n">
-        <v>653</v>
+        <v>776</v>
       </c>
       <c r="Q7" t="n">
-        <v>396</v>
+        <v>466</v>
       </c>
       <c r="R7" t="n">
-        <v>586</v>
+        <v>680</v>
       </c>
       <c r="S7" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="T7" t="n">
-        <v>649</v>
+        <v>781</v>
       </c>
       <c r="U7" t="n">
-        <v>435</v>
+        <v>522</v>
       </c>
       <c r="V7" t="n">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="W7" t="n">
-        <v>343</v>
+        <v>408</v>
       </c>
       <c r="X7" t="n">
-        <v>511</v>
+        <v>600</v>
       </c>
       <c r="Y7" t="n">
-        <v>553</v>
+        <v>656</v>
       </c>
       <c r="Z7" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="AA7" t="n">
-        <v>2131</v>
+        <v>2512</v>
       </c>
       <c r="AB7" t="n">
-        <v>2172.84</v>
+        <v>2594.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1973.84</v>
+        <v>2360.2</v>
       </c>
       <c r="AD7" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3225</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>307</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>592</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>139</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>395</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>232</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>123</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>386</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>262</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>317</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>334</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1353.72</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1230.72</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9342595113389796</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.9843801116401869</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>102.6800469143322</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>111.0613583164649</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-8.381311402132738</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.2455385023252114</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.7106257992753169</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.484439246240039</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>275</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>519</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>143</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>381</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>234</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>342</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>111</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>395</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>260</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>108</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>190</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>283</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>322</v>
+      </c>
+      <c r="BS7" t="n">
         <v>26</v>
       </c>
-      <c r="AE7" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>241</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>475</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>327</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>279</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>106</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>313</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>209</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>182</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>258</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>270</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1106.76</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1000.76</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.9246022212041622</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.001551034889766</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>102.2095324590962</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>113.6530859517258</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-11.44355349262961</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.2586343838141796</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.6969338358176095</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.4839808717710026</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2600</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>231</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>444</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>123</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>326</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>216</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>307</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>93</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>336</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>226</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>94</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>161</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>253</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>283</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>25</v>
-      </c>
       <c r="BT7" t="n">
-        <v>1066.08</v>
+        <v>1240.48</v>
       </c>
       <c r="BU7" t="n">
-        <v>973.08</v>
+        <v>1129.48</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.9837612667706981</v>
+        <v>0.9793641218623789</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.909111672936974</v>
+        <v>0.908890385388442</v>
       </c>
       <c r="BX7" t="n">
-        <v>107.8938210427157</v>
+        <v>107.6328260309254</v>
       </c>
       <c r="BY7" t="n">
-        <v>101.1762221780107</v>
+        <v>101.1476599567617</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.717598864704957</v>
+        <v>6.48516607416365</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.2371471459199654</v>
+        <v>0.2428244725328459</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7517795054775083</v>
+        <v>0.7538814193670568</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5101476850106981</v>
+        <v>0.5153481068960516</v>
       </c>
       <c r="CD7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9459419347929299</v>
+        <v>0.9484879171711749</v>
       </c>
       <c r="D8" t="n">
-        <v>1.001979567531668</v>
+        <v>0.9994197041146552</v>
       </c>
       <c r="E8" t="n">
-        <v>103.3401279584083</v>
+        <v>103.5397087785857</v>
       </c>
       <c r="F8" t="n">
-        <v>112.0248759185563</v>
+        <v>112.1469959984908</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.684747960147986</v>
+        <v>-8.607287219905137</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2394475217963702</v>
+        <v>0.2342779856850789</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7199870869801822</v>
+        <v>0.714346013107048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4858848540797874</v>
+        <v>0.4804969659545085</v>
       </c>
       <c r="K8" t="n">
-        <v>5000</v>
+        <v>6200</v>
       </c>
       <c r="L8" t="n">
-        <v>1952</v>
+        <v>2411</v>
       </c>
       <c r="M8" t="n">
-        <v>427</v>
+        <v>511</v>
       </c>
       <c r="N8" t="n">
-        <v>820</v>
+        <v>987</v>
       </c>
       <c r="O8" t="n">
+        <v>284</v>
+      </c>
+      <c r="P8" t="n">
+        <v>827</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>537</v>
+      </c>
+      <c r="R8" t="n">
+        <v>686</v>
+      </c>
+      <c r="S8" t="n">
+        <v>216</v>
+      </c>
+      <c r="T8" t="n">
+        <v>704</v>
+      </c>
+      <c r="U8" t="n">
+        <v>469</v>
+      </c>
+      <c r="V8" t="n">
+        <v>186</v>
+      </c>
+      <c r="W8" t="n">
+        <v>433</v>
+      </c>
+      <c r="X8" t="n">
+        <v>680</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>677</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2608</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2548.84</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2332.84</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>243</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>474</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>137</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>391</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>278</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>342</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>102</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>351</v>
+      </c>
+      <c r="AN8" t="n">
         <v>223</v>
       </c>
-      <c r="P8" t="n">
-        <v>653</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>429</v>
-      </c>
-      <c r="R8" t="n">
-        <v>552</v>
-      </c>
-      <c r="S8" t="n">
-        <v>177</v>
-      </c>
-      <c r="T8" t="n">
-        <v>566</v>
-      </c>
-      <c r="U8" t="n">
-        <v>375</v>
-      </c>
-      <c r="V8" t="n">
-        <v>152</v>
-      </c>
-      <c r="W8" t="n">
-        <v>354</v>
-      </c>
-      <c r="X8" t="n">
-        <v>548</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>551</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2101</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2069.88</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1892.88</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>215</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>423</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>117</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>338</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>233</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>290</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>89</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>303</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>195</v>
-      </c>
       <c r="AO8" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AP8" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="AQ8" t="n">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="AR8" t="n">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="AS8" t="n">
         <v>20</v>
       </c>
       <c r="AT8" t="n">
-        <v>1097.6</v>
+        <v>1251.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>1008.6</v>
+        <v>1149.48</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9242880211868864</v>
+        <v>0.9405333518290729</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.021273187948369</v>
+        <v>1.003555641458983</v>
       </c>
       <c r="AX8" t="n">
-        <v>100.5387005054181</v>
+        <v>102.3423958278349</v>
       </c>
       <c r="AY8" t="n">
-        <v>113.7151894651335</v>
+        <v>112.776611414705</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-13.1764889597154</v>
+        <v>-10.4342155868701</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.2407238626635178</v>
+        <v>0.241510905862605</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.7333336521831216</v>
+        <v>0.7185326589865129</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.4953242288891429</v>
+        <v>0.4921665226836562</v>
       </c>
       <c r="BD8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE8" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="BF8" t="n">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="BG8" t="n">
-        <v>397</v>
+        <v>513</v>
       </c>
       <c r="BH8" t="n">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="BI8" t="n">
-        <v>315</v>
+        <v>436</v>
       </c>
       <c r="BJ8" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="BK8" t="n">
-        <v>262</v>
+        <v>344</v>
       </c>
       <c r="BL8" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="BM8" t="n">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="BN8" t="n">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="BO8" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BP8" t="n">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="BQ8" t="n">
-        <v>252</v>
+        <v>338</v>
       </c>
       <c r="BR8" t="n">
-        <v>267</v>
+        <v>347</v>
       </c>
       <c r="BS8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BT8" t="n">
-        <v>972.28</v>
+        <v>1297.36</v>
       </c>
       <c r="BU8" t="n">
-        <v>884.28</v>
+        <v>1183.36</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9694003411994768</v>
+        <v>0.9559453221793955</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9810781454135754</v>
+        <v>0.9955422628543478</v>
       </c>
       <c r="BX8" t="n">
-        <v>106.3750076991478</v>
+        <v>104.6621896699146</v>
       </c>
       <c r="BY8" t="n">
-        <v>110.1937029097644</v>
+        <v>111.55673154579</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-3.818695210616629</v>
+        <v>-6.894541875875484</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2380648191902935</v>
+        <v>0.2274971230186481</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.7055283080103313</v>
+        <v>0.7104210325950501</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.4756588647029859</v>
+        <v>0.4695567565209325</v>
       </c>
       <c r="CD8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -2616,244 +2616,244 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8723044961578448</v>
+        <v>0.8847680299348241</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9853653904493135</v>
+        <v>0.98875981763415</v>
       </c>
       <c r="E9" t="n">
-        <v>96.00194118830481</v>
+        <v>97.50334410689696</v>
       </c>
       <c r="F9" t="n">
-        <v>111.5058390920437</v>
+        <v>111.5632892086128</v>
       </c>
       <c r="G9" t="n">
-        <v>-15.50389790373888</v>
+        <v>-14.0599451017159</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2355802557542776</v>
+        <v>0.2367007377536416</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6965921489168726</v>
+        <v>0.6955227084665095</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4623154498926504</v>
+        <v>0.4586741012093621</v>
       </c>
       <c r="K9" t="n">
-        <v>5050</v>
+        <v>6250</v>
       </c>
       <c r="L9" t="n">
-        <v>1826</v>
+        <v>2287</v>
       </c>
       <c r="M9" t="n">
-        <v>448</v>
+        <v>541</v>
       </c>
       <c r="N9" t="n">
-        <v>867</v>
+        <v>1056</v>
       </c>
       <c r="O9" t="n">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="P9" t="n">
-        <v>676</v>
+        <v>859</v>
       </c>
       <c r="Q9" t="n">
-        <v>339</v>
+        <v>410</v>
       </c>
       <c r="R9" t="n">
-        <v>480</v>
+        <v>589</v>
       </c>
       <c r="S9" t="n">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="T9" t="n">
-        <v>574</v>
+        <v>690</v>
       </c>
       <c r="U9" t="n">
-        <v>337</v>
+        <v>445</v>
       </c>
       <c r="V9" t="n">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="W9" t="n">
-        <v>339</v>
+        <v>413</v>
       </c>
       <c r="X9" t="n">
-        <v>567</v>
+        <v>684</v>
       </c>
       <c r="Y9" t="n">
-        <v>512</v>
+        <v>623</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2118</v>
+        <v>2619</v>
       </c>
       <c r="AB9" t="n">
-        <v>2093.2</v>
+        <v>2587.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>1902.2</v>
+        <v>2348.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AE9" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="AF9" t="n">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="AG9" t="n">
-        <v>421</v>
+        <v>522</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AI9" t="n">
-        <v>307</v>
+        <v>395</v>
       </c>
       <c r="AJ9" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="AK9" t="n">
-        <v>219</v>
+        <v>268</v>
       </c>
       <c r="AL9" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AM9" t="n">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="AN9" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="AP9" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="AQ9" t="n">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="AR9" t="n">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>983.36</v>
+        <v>1229.92</v>
       </c>
       <c r="AU9" t="n">
-        <v>904.36</v>
+        <v>1128.92</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.867140907857443</v>
+        <v>0.8933509860103926</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.035799638762833</v>
+        <v>1.036973598397362</v>
       </c>
       <c r="AX9" t="n">
-        <v>94.1427952507713</v>
+        <v>97.24971266306144</v>
       </c>
       <c r="AY9" t="n">
-        <v>117.5835699025132</v>
+        <v>116.9396730929621</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-23.4407746517419</v>
+        <v>-19.68996042990062</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2023663101604278</v>
+        <v>0.2066245739124996</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6957926034538938</v>
+        <v>0.6973658448282104</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4431361193957445</v>
+        <v>0.4397303407380408</v>
       </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BE9" t="n">
-        <v>2650</v>
+        <v>3250</v>
       </c>
       <c r="BF9" t="n">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="BG9" t="n">
-        <v>446</v>
+        <v>534</v>
       </c>
       <c r="BH9" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="BI9" t="n">
-        <v>369</v>
+        <v>464</v>
       </c>
       <c r="BJ9" t="n">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="BK9" t="n">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="BL9" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="BM9" t="n">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="BN9" t="n">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="BO9" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="BP9" t="n">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="BQ9" t="n">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="BR9" t="n">
-        <v>268</v>
+        <v>328</v>
       </c>
       <c r="BS9" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="BT9" t="n">
-        <v>1109.84</v>
+        <v>1357.24</v>
       </c>
       <c r="BU9" t="n">
-        <v>997.84</v>
+        <v>1219.24</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8770708853582156</v>
+        <v>0.8767215086139785</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.9388106996983723</v>
+        <v>0.9435593981686391</v>
       </c>
       <c r="BX9" t="n">
-        <v>97.71807589987421</v>
+        <v>97.74112358549277</v>
       </c>
       <c r="BY9" t="n">
-        <v>105.8956260362257</v>
+        <v>106.5229293170355</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-8.177550136351487</v>
+        <v>-8.781805731542725</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.2662392824562929</v>
+        <v>0.2648971413547124</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.697330190882699</v>
+        <v>0.693794768127415</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.4800194472744096</v>
+        <v>0.4764338766512254</v>
       </c>
       <c r="CD9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2868,244 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9309111154602038</v>
+        <v>0.943162598785794</v>
       </c>
       <c r="D10" t="n">
-        <v>1.01327207159717</v>
+        <v>1.015393385169808</v>
       </c>
       <c r="E10" t="n">
-        <v>106.0387469668643</v>
+        <v>107.0290879822072</v>
       </c>
       <c r="F10" t="n">
-        <v>113.9117954482826</v>
+        <v>114.6387556139332</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.873048481418281</v>
+        <v>-7.60966763172602</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3233664377143212</v>
+        <v>0.3167630144822071</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6985995075245754</v>
+        <v>0.6879366709001774</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5028829305041638</v>
+        <v>0.4952837798643361</v>
       </c>
       <c r="K10" t="n">
-        <v>5250</v>
+        <v>6275</v>
       </c>
       <c r="L10" t="n">
-        <v>2137</v>
+        <v>2575</v>
       </c>
       <c r="M10" t="n">
-        <v>471</v>
+        <v>567</v>
       </c>
       <c r="N10" t="n">
-        <v>925</v>
+        <v>1093</v>
       </c>
       <c r="O10" t="n">
+        <v>312</v>
+      </c>
+      <c r="P10" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>505</v>
+      </c>
+      <c r="R10" t="n">
+        <v>690</v>
+      </c>
+      <c r="S10" t="n">
+        <v>326</v>
+      </c>
+      <c r="T10" t="n">
+        <v>668</v>
+      </c>
+      <c r="U10" t="n">
+        <v>482</v>
+      </c>
+      <c r="V10" t="n">
+        <v>219</v>
+      </c>
+      <c r="W10" t="n">
+        <v>426</v>
+      </c>
+      <c r="X10" t="n">
+        <v>761</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>676</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2767</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2732.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2406.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3250</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>301</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>578</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>145</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>455</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>261</v>
       </c>
-      <c r="P10" t="n">
-        <v>765</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>412</v>
-      </c>
-      <c r="R10" t="n">
-        <v>564</v>
-      </c>
-      <c r="S10" t="n">
-        <v>281</v>
-      </c>
-      <c r="T10" t="n">
-        <v>569</v>
-      </c>
-      <c r="U10" t="n">
-        <v>396</v>
-      </c>
-      <c r="V10" t="n">
-        <v>187</v>
-      </c>
-      <c r="W10" t="n">
-        <v>360</v>
-      </c>
-      <c r="X10" t="n">
-        <v>644</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>561</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2314</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2298.16</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2017.16</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2650</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>236</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>476</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>119</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>206</v>
-      </c>
       <c r="AK10" t="n">
-        <v>293</v>
+        <v>373</v>
       </c>
       <c r="AL10" t="n">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="AM10" t="n">
-        <v>271</v>
+        <v>334</v>
       </c>
       <c r="AN10" t="n">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="AP10" t="n">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="AQ10" t="n">
-        <v>323</v>
+        <v>397</v>
       </c>
       <c r="AR10" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>1166.92</v>
+        <v>1421.12</v>
       </c>
       <c r="AU10" t="n">
-        <v>1021.92</v>
+        <v>1247.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.887353442635865</v>
+        <v>0.9145109548001079</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.0290983253107</v>
+        <v>1.023123164422668</v>
       </c>
       <c r="AX10" t="n">
-        <v>101.4187448389346</v>
+        <v>104.1943244349169</v>
       </c>
       <c r="AY10" t="n">
-        <v>115.051534451985</v>
+        <v>115.772374480487</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-13.63278961305036</v>
+        <v>-11.57805004557019</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.322843520260875</v>
+        <v>0.3221394200410208</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.6947198965222865</v>
+        <v>0.6775892065422067</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.4924235969899657</v>
+        <v>0.4883999816228681</v>
       </c>
       <c r="BD10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BE10" t="n">
-        <v>2600</v>
+        <v>3025</v>
       </c>
       <c r="BF10" t="n">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="BG10" t="n">
-        <v>449</v>
+        <v>515</v>
       </c>
       <c r="BH10" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="BI10" t="n">
-        <v>385</v>
+        <v>455</v>
       </c>
       <c r="BJ10" t="n">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="BK10" t="n">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="BL10" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="BM10" t="n">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="BN10" t="n">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="BO10" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="BP10" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="BQ10" t="n">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="BR10" t="n">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="BS10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BT10" t="n">
-        <v>1131.24</v>
+        <v>1311.48</v>
       </c>
       <c r="BU10" t="n">
-        <v>995.24</v>
+        <v>1159.48</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9744687882845425</v>
+        <v>0.9737243523705258</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.9974458178836401</v>
+        <v>1.007148287300091</v>
       </c>
       <c r="BX10" t="n">
-        <v>110.658749094794</v>
+        <v>110.0528357659835</v>
       </c>
       <c r="BY10" t="n">
-        <v>112.7720564445802</v>
+        <v>113.4295621562757</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-2.113307349786196</v>
+        <v>-3.376726390292238</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3238893551677674</v>
+        <v>0.3110281818861391</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7024791185268638</v>
+        <v>0.6989739662153454</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.5133422640183615</v>
+        <v>0.5026264979885685</v>
       </c>
       <c r="CD10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3120,244 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9835297833947405</v>
+        <v>0.9741225410072877</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9574052460631601</v>
+        <v>0.9545205049993054</v>
       </c>
       <c r="E11" t="n">
-        <v>111.2268249738531</v>
+        <v>110.2649714081432</v>
       </c>
       <c r="F11" t="n">
-        <v>107.1693098803709</v>
+        <v>107.1000837146807</v>
       </c>
       <c r="G11" t="n">
-        <v>4.057515093482283</v>
+        <v>3.164887693462475</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3072742872857415</v>
+        <v>0.3105016342462874</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7094697893236824</v>
+        <v>0.7073843409813931</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5046662654850583</v>
+        <v>0.5055990199064261</v>
       </c>
       <c r="K11" t="n">
-        <v>5025</v>
+        <v>6225</v>
       </c>
       <c r="L11" t="n">
-        <v>2023</v>
+        <v>2472</v>
       </c>
       <c r="M11" t="n">
-        <v>435</v>
+        <v>529</v>
       </c>
       <c r="N11" t="n">
-        <v>810</v>
+        <v>996</v>
       </c>
       <c r="O11" t="n">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="P11" t="n">
-        <v>763</v>
+        <v>933</v>
       </c>
       <c r="Q11" t="n">
-        <v>364</v>
+        <v>472</v>
       </c>
       <c r="R11" t="n">
-        <v>490</v>
+        <v>631</v>
       </c>
       <c r="S11" t="n">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="T11" t="n">
-        <v>521</v>
+        <v>650</v>
       </c>
       <c r="U11" t="n">
-        <v>380</v>
+        <v>474</v>
       </c>
       <c r="V11" t="n">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="W11" t="n">
-        <v>279</v>
+        <v>345</v>
       </c>
       <c r="X11" t="n">
-        <v>573</v>
+        <v>719</v>
       </c>
       <c r="Y11" t="n">
-        <v>513</v>
+        <v>648</v>
       </c>
       <c r="Z11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="n">
-        <v>1928</v>
+        <v>2384</v>
       </c>
       <c r="AB11" t="n">
-        <v>2067.6</v>
+        <v>2551.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>1820.6</v>
+        <v>2245.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AE11" t="n">
-        <v>2625</v>
+        <v>3225</v>
       </c>
       <c r="AF11" t="n">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="AG11" t="n">
-        <v>431</v>
+        <v>533</v>
       </c>
       <c r="AH11" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AI11" t="n">
-        <v>395</v>
+        <v>481</v>
       </c>
       <c r="AJ11" t="n">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="AK11" t="n">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="AL11" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="AM11" t="n">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="AN11" t="n">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="AO11" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AP11" t="n">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="AQ11" t="n">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="AR11" t="n">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="AS11" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AT11" t="n">
-        <v>1067.48</v>
+        <v>1312.12</v>
       </c>
       <c r="AU11" t="n">
-        <v>952.48</v>
+        <v>1165.12</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.9688077057504956</v>
+        <v>0.9568101626715286</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9683084223088435</v>
+        <v>0.9750871318016594</v>
       </c>
       <c r="AX11" t="n">
-        <v>108.0792970554561</v>
+        <v>107.306745597393</v>
       </c>
       <c r="AY11" t="n">
-        <v>108.2075549772338</v>
+        <v>109.1144819737362</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.1282579217777639</v>
+        <v>-1.8077363763432</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.2633655614245158</v>
+        <v>0.2761128234327827</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.7159053043216003</v>
+        <v>0.7117392301500512</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.4805917250087773</v>
+        <v>0.4841331768009792</v>
       </c>
       <c r="BD11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BE11" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="BF11" t="n">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="BG11" t="n">
-        <v>379</v>
+        <v>463</v>
       </c>
       <c r="BH11" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="BI11" t="n">
-        <v>368</v>
+        <v>452</v>
       </c>
       <c r="BJ11" t="n">
-        <v>182</v>
+        <v>248</v>
       </c>
       <c r="BK11" t="n">
-        <v>248</v>
+        <v>333</v>
       </c>
       <c r="BL11" t="n">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="BM11" t="n">
-        <v>245</v>
+        <v>314</v>
       </c>
       <c r="BN11" t="n">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="BO11" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="BP11" t="n">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="BQ11" t="n">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="BR11" t="n">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="BS11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000.12</v>
+        <v>1239.52</v>
       </c>
       <c r="BU11" t="n">
-        <v>868.12</v>
+        <v>1080.52</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9994787008426725</v>
+        <v>0.9925890778987639</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9455934717970034</v>
+        <v>0.9325827697434611</v>
       </c>
       <c r="BX11" t="n">
-        <v>114.63664688545</v>
+        <v>113.4204122729434</v>
       </c>
       <c r="BY11" t="n">
-        <v>106.0445443587693</v>
+        <v>104.9513922383548</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.592102526680669</v>
+        <v>8.46902003458853</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3548420736354028</v>
+        <v>0.3471830324473591</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7024979814092718</v>
+        <v>0.7027391258681581</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.5307470176676962</v>
+        <v>0.5284959192189027</v>
       </c>
       <c r="CD11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -3372,244 +3372,244 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.004732132916311</v>
+        <v>0.9830660682859907</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9783666965370409</v>
+        <v>0.9771117818897105</v>
       </c>
       <c r="E12" t="n">
-        <v>111.8733182421374</v>
+        <v>110.3841794228691</v>
       </c>
       <c r="F12" t="n">
-        <v>109.7216528852768</v>
+        <v>109.7472452920443</v>
       </c>
       <c r="G12" t="n">
-        <v>2.151665356860573</v>
+        <v>0.6369341308247487</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2632112790867055</v>
+        <v>0.2719711605084112</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7161188109373329</v>
+        <v>0.7124430279614486</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4915199927464975</v>
+        <v>0.4911295773290874</v>
       </c>
       <c r="K12" t="n">
-        <v>5250</v>
+        <v>6250</v>
       </c>
       <c r="L12" t="n">
-        <v>2166</v>
+        <v>2556</v>
       </c>
       <c r="M12" t="n">
+        <v>534</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1107</v>
+      </c>
+      <c r="O12" t="n">
+        <v>306</v>
+      </c>
+      <c r="P12" t="n">
+        <v>842</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>570</v>
+      </c>
+      <c r="R12" t="n">
+        <v>710</v>
+      </c>
+      <c r="S12" t="n">
+        <v>290</v>
+      </c>
+      <c r="T12" t="n">
+        <v>720</v>
+      </c>
+      <c r="U12" t="n">
+        <v>491</v>
+      </c>
+      <c r="V12" t="n">
+        <v>175</v>
+      </c>
+      <c r="W12" t="n">
+        <v>341</v>
+      </c>
+      <c r="X12" t="n">
+        <v>662</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>654</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2545</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2602.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2312.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3050</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>257</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>553</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>142</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>392</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>253</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>327</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>148</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>371</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>189</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>68</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>172</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>326</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>307</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1260.88</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1112.88</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.9474144604003226</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.954676895240046</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>107.1856514129457</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>107.9472768066327</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.7616253936870133</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.2786360181060001</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.7162392773749765</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.4959308662815106</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3200</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>277</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>554</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>164</v>
+      </c>
+      <c r="BI12" t="n">
         <v>450</v>
       </c>
-      <c r="N12" t="n">
-        <v>904</v>
-      </c>
-      <c r="O12" t="n">
-        <v>260</v>
-      </c>
-      <c r="P12" t="n">
-        <v>697</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>486</v>
-      </c>
-      <c r="R12" t="n">
-        <v>599</v>
-      </c>
-      <c r="S12" t="n">
-        <v>223</v>
-      </c>
-      <c r="T12" t="n">
-        <v>604</v>
-      </c>
-      <c r="U12" t="n">
-        <v>418</v>
-      </c>
-      <c r="V12" t="n">
-        <v>148</v>
-      </c>
-      <c r="W12" t="n">
-        <v>290</v>
-      </c>
-      <c r="X12" t="n">
-        <v>557</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>547</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2134</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2154.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1931.56</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2450</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>438</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>112</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>311</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>211</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>269</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>289</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>147</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>56</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>135</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>263</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>244</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="BJ12" t="n">
+        <v>317</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>383</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>142</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>349</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>302</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>169</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>336</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>347</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>33</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1341.52</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1199.52</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1.016489450678804</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.998144488123771</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>113.3827994321722</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>111.4347157471177</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1.948083685054526</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.2657228565106716</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.7088840441362663</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.4866283689361907</v>
+      </c>
+      <c r="CD12" t="n">
         <v>16</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1002.36</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>887.36</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.9674384813015685</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.9690199491248445</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>109.1605693359916</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>109.2877208455712</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.1271515095796675</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.2763681123334968</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.715386390490225</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.4935295664432309</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>239</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>466</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>148</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>386</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>275</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>330</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>108</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>315</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>271</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>92</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>155</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>294</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>303</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>30</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1152.2</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>1044.2</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1.036698120014661</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0.9863781943189237</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>114.1985315902624</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>110.0935946335959</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>4.104936956666495</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0.2519339934465984</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>0.7167465998919967</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>0.4897975010064402</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -3624,244 +3624,244 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9515919644242917</v>
+        <v>0.9460606861643507</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9016632170157765</v>
+        <v>0.8887059387625326</v>
       </c>
       <c r="E13" t="n">
-        <v>109.5877821991982</v>
+        <v>108.4390133639481</v>
       </c>
       <c r="F13" t="n">
-        <v>101.5542176600192</v>
+        <v>100.3879835546248</v>
       </c>
       <c r="G13" t="n">
-        <v>8.033564539178935</v>
+        <v>8.051029809323374</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3505430557519366</v>
+        <v>0.3420654770547829</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7160438771005349</v>
+        <v>0.7190357086278473</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5368214122666169</v>
+        <v>0.5391722531520198</v>
       </c>
       <c r="K13" t="n">
-        <v>5025</v>
+        <v>6225</v>
       </c>
       <c r="L13" t="n">
-        <v>1991</v>
+        <v>2452</v>
       </c>
       <c r="M13" t="n">
-        <v>500</v>
+        <v>633</v>
       </c>
       <c r="N13" t="n">
-        <v>906</v>
+        <v>1125</v>
       </c>
       <c r="O13" t="n">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="P13" t="n">
-        <v>669</v>
+        <v>821</v>
       </c>
       <c r="Q13" t="n">
-        <v>358</v>
+        <v>436</v>
       </c>
       <c r="R13" t="n">
-        <v>491</v>
+        <v>605</v>
       </c>
       <c r="S13" t="n">
-        <v>279</v>
+        <v>337</v>
       </c>
       <c r="T13" t="n">
-        <v>582</v>
+        <v>758</v>
       </c>
       <c r="U13" t="n">
-        <v>394</v>
+        <v>518</v>
       </c>
       <c r="V13" t="n">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="W13" t="n">
-        <v>304</v>
+        <v>386</v>
       </c>
       <c r="X13" t="n">
-        <v>544</v>
+        <v>658</v>
       </c>
       <c r="Y13" t="n">
-        <v>506</v>
+        <v>628</v>
       </c>
       <c r="Z13" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AA13" t="n">
-        <v>1868</v>
+        <v>2301</v>
       </c>
       <c r="AB13" t="n">
-        <v>2095.04</v>
+        <v>2598.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1816.04</v>
+        <v>2261.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AE13" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="AF13" t="n">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="AG13" t="n">
-        <v>407</v>
+        <v>557</v>
       </c>
       <c r="AH13" t="n">
+        <v>122</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>364</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>181</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>254</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>145</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>386</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>266</v>
+      </c>
+      <c r="AO13" t="n">
         <v>99</v>
       </c>
-      <c r="AI13" t="n">
-        <v>265</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>141</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>195</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>112</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>268</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>181</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>80</v>
-      </c>
       <c r="AP13" t="n">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="AQ13" t="n">
-        <v>246</v>
+        <v>319</v>
       </c>
       <c r="AR13" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="AS13" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="AT13" t="n">
-        <v>920.8</v>
+        <v>1244.76</v>
       </c>
       <c r="AU13" t="n">
-        <v>808.8</v>
+        <v>1099.76</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9714552370892989</v>
+        <v>0.9569025577027492</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8856373843129653</v>
+        <v>0.8798297497036599</v>
       </c>
       <c r="AX13" t="n">
-        <v>110.5164153930311</v>
+        <v>108.1414895177445</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.876174900982</v>
+        <v>101.3623446949506</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.640240492049131</v>
+        <v>6.779144822793855</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.353111873344149</v>
+        <v>0.3320267504935167</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.686351863531231</v>
+        <v>0.6930330032026345</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5404371619712222</v>
+        <v>0.5370504119915659</v>
       </c>
       <c r="BD13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
-        <v>2825</v>
+        <v>3225</v>
       </c>
       <c r="BF13" t="n">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="BG13" t="n">
-        <v>499</v>
+        <v>568</v>
       </c>
       <c r="BH13" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="BI13" t="n">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="BJ13" t="n">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="BK13" t="n">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="BL13" t="n">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="BM13" t="n">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="BN13" t="n">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="BO13" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="BP13" t="n">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="BQ13" t="n">
-        <v>298</v>
+        <v>339</v>
       </c>
       <c r="BR13" t="n">
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="BS13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BT13" t="n">
-        <v>1174.24</v>
+        <v>1353.44</v>
       </c>
       <c r="BU13" t="n">
-        <v>1007.24</v>
+        <v>1161.44</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.9359851073303577</v>
+        <v>0.9358964315971021</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.9142549427108421</v>
+        <v>0.8970273660052253</v>
       </c>
       <c r="BX13" t="n">
-        <v>108.8581418326151</v>
+        <v>108.7179419697641</v>
       </c>
       <c r="BY13" t="n">
-        <v>101.3012512564056</v>
+        <v>99.47451998556933</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7.556890576209494</v>
+        <v>9.243421984194798</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.3485246990723411</v>
+        <v>0.35147678320597</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.7393733163335593</v>
+        <v>0.743413244963984</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5339804660701418</v>
+        <v>0.5411614792399455</v>
       </c>
       <c r="CD13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -3876,244 +3876,244 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.028670537269259</v>
+        <v>1.021613785484907</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9190865287410088</v>
+        <v>0.9267677643760075</v>
       </c>
       <c r="E14" t="n">
-        <v>117.7476046919323</v>
+        <v>117.19261229186</v>
       </c>
       <c r="F14" t="n">
-        <v>102.7277481173657</v>
+        <v>103.5235542772392</v>
       </c>
       <c r="G14" t="n">
-        <v>15.01985657456663</v>
+        <v>13.66905801462081</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3481326878394413</v>
+        <v>0.3500040266518874</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7337456576911964</v>
+        <v>0.7363192554473929</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5442575441697856</v>
+        <v>0.5457807849696155</v>
       </c>
       <c r="K14" t="n">
-        <v>5200</v>
+        <v>6400</v>
       </c>
       <c r="L14" t="n">
-        <v>2383</v>
+        <v>2896</v>
       </c>
       <c r="M14" t="n">
-        <v>560</v>
+        <v>671</v>
       </c>
       <c r="N14" t="n">
-        <v>1032</v>
+        <v>1253</v>
       </c>
       <c r="O14" t="n">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="P14" t="n">
-        <v>732</v>
+        <v>913</v>
       </c>
       <c r="Q14" t="n">
-        <v>462</v>
+        <v>561</v>
       </c>
       <c r="R14" t="n">
-        <v>604</v>
+        <v>737</v>
       </c>
       <c r="S14" t="n">
-        <v>297</v>
+        <v>369</v>
       </c>
       <c r="T14" t="n">
-        <v>641</v>
+        <v>792</v>
       </c>
       <c r="U14" t="n">
-        <v>515</v>
+        <v>617</v>
       </c>
       <c r="V14" t="n">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="W14" t="n">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="X14" t="n">
-        <v>557</v>
+        <v>689</v>
       </c>
       <c r="Y14" t="n">
-        <v>579</v>
+        <v>705</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>2027</v>
+        <v>2502</v>
       </c>
       <c r="AB14" t="n">
-        <v>2321.76</v>
+        <v>2841.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>2024.76</v>
+        <v>2472.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="AF14" t="n">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="AG14" t="n">
-        <v>521</v>
+        <v>635</v>
       </c>
       <c r="AH14" t="n">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="AI14" t="n">
-        <v>339</v>
+        <v>429</v>
       </c>
       <c r="AJ14" t="n">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="AK14" t="n">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="AL14" t="n">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="AM14" t="n">
-        <v>287</v>
+        <v>371</v>
       </c>
       <c r="AN14" t="n">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="AO14" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="AP14" t="n">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="AQ14" t="n">
-        <v>294</v>
+        <v>355</v>
       </c>
       <c r="AR14" t="n">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="AS14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
-        <v>1151.2</v>
+        <v>1409.28</v>
       </c>
       <c r="AU14" t="n">
-        <v>1003.2</v>
+        <v>1226.28</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.021584059554004</v>
+        <v>1.017146224444037</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.9151161035642108</v>
+        <v>0.9099738864924202</v>
       </c>
       <c r="AX14" t="n">
-        <v>117.0203084119286</v>
+        <v>116.6503388556036</v>
       </c>
       <c r="AY14" t="n">
-        <v>104.4034877105762</v>
+        <v>103.7920313241447</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.61682070135243</v>
+        <v>12.85830753145883</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3568654736194627</v>
+        <v>0.3543228554354715</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6709071649833965</v>
+        <v>0.6820737940370478</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5161060537516851</v>
+        <v>0.522297977735788</v>
       </c>
       <c r="BD14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="BF14" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="BG14" t="n">
-        <v>511</v>
+        <v>618</v>
       </c>
       <c r="BH14" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="BI14" t="n">
-        <v>393</v>
+        <v>484</v>
       </c>
       <c r="BJ14" t="n">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="BK14" t="n">
-        <v>299</v>
+        <v>375</v>
       </c>
       <c r="BL14" t="n">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="BM14" t="n">
-        <v>354</v>
+        <v>421</v>
       </c>
       <c r="BN14" t="n">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="BO14" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="BP14" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="BQ14" t="n">
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="BR14" t="n">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="BS14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BT14" t="n">
-        <v>1170.56</v>
+        <v>1432</v>
       </c>
       <c r="BU14" t="n">
-        <v>1021.56</v>
+        <v>1246</v>
       </c>
       <c r="BV14" t="n">
-        <v>1.035757014984514</v>
+        <v>1.026081346525777</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.9230569539178066</v>
+        <v>0.943561642259595</v>
       </c>
       <c r="BX14" t="n">
-        <v>118.474900971936</v>
+        <v>117.7348857281165</v>
       </c>
       <c r="BY14" t="n">
-        <v>101.0520085241552</v>
+        <v>103.2550772303337</v>
       </c>
       <c r="BZ14" t="n">
-        <v>17.42289244778084</v>
+        <v>14.47980849778279</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3393999020594199</v>
+        <v>0.3456851978683031</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7965841503989961</v>
+        <v>0.7905647168577374</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5724090345878862</v>
+        <v>0.5692635922034429</v>
       </c>
       <c r="CD14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4128,244 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8696020133271409</v>
+        <v>0.8778839618462584</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9988797880295546</v>
+        <v>0.9833833422397469</v>
       </c>
       <c r="E15" t="n">
-        <v>98.42777545090779</v>
+        <v>99.40239608609475</v>
       </c>
       <c r="F15" t="n">
-        <v>113.0500217719582</v>
+        <v>111.0449509239419</v>
       </c>
       <c r="G15" t="n">
-        <v>-14.62224632105038</v>
+        <v>-11.64255483784715</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2897070823085149</v>
+        <v>0.2874272418651134</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6961633251289732</v>
+        <v>0.6992956251010252</v>
       </c>
       <c r="J15" t="n">
-        <v>0.489443645147027</v>
+        <v>0.4886911612697814</v>
       </c>
       <c r="K15" t="n">
-        <v>5000</v>
+        <v>6225</v>
       </c>
       <c r="L15" t="n">
-        <v>1886</v>
+        <v>2373</v>
       </c>
       <c r="M15" t="n">
-        <v>426</v>
+        <v>516</v>
       </c>
       <c r="N15" t="n">
-        <v>889</v>
+        <v>1062</v>
       </c>
       <c r="O15" t="n">
+        <v>304</v>
+      </c>
+      <c r="P15" t="n">
+        <v>936</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>429</v>
+      </c>
+      <c r="R15" t="n">
+        <v>568</v>
+      </c>
+      <c r="S15" t="n">
+        <v>320</v>
+      </c>
+      <c r="T15" t="n">
+        <v>735</v>
+      </c>
+      <c r="U15" t="n">
+        <v>496</v>
+      </c>
+      <c r="V15" t="n">
+        <v>197</v>
+      </c>
+      <c r="W15" t="n">
+        <v>461</v>
+      </c>
+      <c r="X15" t="n">
+        <v>656</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>641</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2667</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2708.92</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2388.92</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>525</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>146</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>454</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>195</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>257</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>346</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>227</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>86</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>228</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>315</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>306</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1320.08</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1160.08</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.843713158341048</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.006573460733275</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>95.89340288502628</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>114.200930919761</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-18.30752803473473</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.2963252103298367</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.694708203673721</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.4869281973932811</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>3225</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>276</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>537</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>158</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>482</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>234</v>
       </c>
-      <c r="P15" t="n">
-        <v>715</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>332</v>
-      </c>
-      <c r="R15" t="n">
-        <v>444</v>
-      </c>
-      <c r="S15" t="n">
-        <v>257</v>
-      </c>
-      <c r="T15" t="n">
-        <v>585</v>
-      </c>
-      <c r="U15" t="n">
-        <v>397</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="BK15" t="n">
+        <v>311</v>
+      </c>
+      <c r="BL15" t="n">
         <v>160</v>
       </c>
-      <c r="W15" t="n">
-        <v>376</v>
-      </c>
-      <c r="X15" t="n">
-        <v>525</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>512</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2176</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2175.36</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1918.36</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>214</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>472</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>122</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>383</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>164</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>218</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>196</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>79</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>199</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>280</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>266</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1149.92</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1009.92</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.8334663071542632</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.012529632105617</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>94.77910663484582</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>115.3239094597772</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-20.54480282493135</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0.3001908072406798</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0.6818087306150967</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.4816305823344414</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>212</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>417</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>112</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>332</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>168</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>226</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>117</v>
-      </c>
       <c r="BM15" t="n">
-        <v>295</v>
+        <v>389</v>
       </c>
       <c r="BN15" t="n">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="BO15" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="BP15" t="n">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="BQ15" t="n">
-        <v>245</v>
+        <v>341</v>
       </c>
       <c r="BR15" t="n">
-        <v>246</v>
+        <v>335</v>
       </c>
       <c r="BS15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BT15" t="n">
-        <v>1025.44</v>
+        <v>1388.84</v>
       </c>
       <c r="BU15" t="n">
-        <v>908.4400000000001</v>
+        <v>1228.84</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.9087490283477585</v>
+        <v>0.9099190901323932</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9840924569471531</v>
+        <v>0.9616426061520646</v>
       </c>
       <c r="BX15" t="n">
-        <v>102.3805000016416</v>
+        <v>102.6920772120965</v>
       </c>
       <c r="BY15" t="n">
-        <v>110.5866434434876</v>
+        <v>108.0862196778615</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-8.206143441846001</v>
+        <v>-5.39414246576504</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2783497136320031</v>
+        <v>0.2790853964294353</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.7117141358523394</v>
+        <v>0.7035963326891225</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.4979077965273281</v>
+        <v>0.4903439399040007</v>
       </c>
       <c r="CD15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -4380,244 +4380,244 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.066378724431395</v>
+        <v>1.068224419335226</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8926546426226705</v>
+        <v>0.887690116830567</v>
       </c>
       <c r="E16" t="n">
-        <v>119.72513940432</v>
+        <v>120.2707876061511</v>
       </c>
       <c r="F16" t="n">
-        <v>100.4061841698055</v>
+        <v>99.50286999577044</v>
       </c>
       <c r="G16" t="n">
-        <v>19.31895523451453</v>
+        <v>20.76791761038066</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3201634994321476</v>
+        <v>0.3265017747829426</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7036812862599849</v>
+        <v>0.7123723575062877</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5196219946664736</v>
+        <v>0.5273649222365817</v>
       </c>
       <c r="K16" t="n">
-        <v>5050</v>
+        <v>6275</v>
       </c>
       <c r="L16" t="n">
-        <v>2313</v>
+        <v>2860</v>
       </c>
       <c r="M16" t="n">
-        <v>557</v>
+        <v>681</v>
       </c>
       <c r="N16" t="n">
-        <v>965</v>
+        <v>1163</v>
       </c>
       <c r="O16" t="n">
-        <v>253</v>
+        <v>316</v>
       </c>
       <c r="P16" t="n">
-        <v>661</v>
+        <v>835</v>
       </c>
       <c r="Q16" t="n">
-        <v>440</v>
+        <v>550</v>
       </c>
       <c r="R16" t="n">
-        <v>579</v>
+        <v>734</v>
       </c>
       <c r="S16" t="n">
-        <v>235</v>
+        <v>297</v>
       </c>
       <c r="T16" t="n">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="U16" t="n">
-        <v>507</v>
+        <v>604</v>
       </c>
       <c r="V16" t="n">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="W16" t="n">
-        <v>288</v>
+        <v>358</v>
       </c>
       <c r="X16" t="n">
-        <v>525</v>
+        <v>650</v>
       </c>
       <c r="Y16" t="n">
-        <v>566</v>
+        <v>704</v>
       </c>
       <c r="Z16" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AA16" t="n">
-        <v>1915</v>
+        <v>2352</v>
       </c>
       <c r="AB16" t="n">
-        <v>2168.76</v>
+        <v>2678.96</v>
       </c>
       <c r="AC16" t="n">
-        <v>1933.76</v>
+        <v>2381.96</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AE16" t="n">
-        <v>2625</v>
+        <v>3250</v>
       </c>
       <c r="AF16" t="n">
-        <v>289</v>
+        <v>349</v>
       </c>
       <c r="AG16" t="n">
-        <v>498</v>
+        <v>595</v>
       </c>
       <c r="AH16" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="AI16" t="n">
-        <v>326</v>
+        <v>412</v>
       </c>
       <c r="AJ16" t="n">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="AK16" t="n">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="AL16" t="n">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AM16" t="n">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="AN16" t="n">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="AO16" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="AP16" t="n">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="AQ16" t="n">
-        <v>275</v>
+        <v>338</v>
       </c>
       <c r="AR16" t="n">
-        <v>290</v>
+        <v>362</v>
       </c>
       <c r="AS16" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AT16" t="n">
-        <v>1109.52</v>
+        <v>1373.56</v>
       </c>
       <c r="AU16" t="n">
-        <v>994.52</v>
+        <v>1232.56</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.072980927361294</v>
+        <v>1.074086297525984</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.9092415883348237</v>
+        <v>0.9209356137552979</v>
       </c>
       <c r="AX16" t="n">
-        <v>119.841915852236</v>
+        <v>119.7820505730938</v>
       </c>
       <c r="AY16" t="n">
-        <v>103.779003406811</v>
+        <v>104.1527428095428</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.06291244542495</v>
+        <v>15.62930776355097</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.3129456436720919</v>
+        <v>0.3129736926264318</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.6663331153587108</v>
+        <v>0.68723261048368</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.4988553256284053</v>
+        <v>0.5096573986310271</v>
       </c>
       <c r="BD16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>2425</v>
+        <v>3025</v>
       </c>
       <c r="BF16" t="n">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="BG16" t="n">
-        <v>467</v>
+        <v>568</v>
       </c>
       <c r="BH16" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="BI16" t="n">
+        <v>423</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>254</v>
+      </c>
+      <c r="BK16" t="n">
         <v>335</v>
       </c>
-      <c r="BJ16" t="n">
-        <v>211</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>271</v>
-      </c>
       <c r="BL16" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="BM16" t="n">
-        <v>299</v>
+        <v>371</v>
       </c>
       <c r="BN16" t="n">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="BO16" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="BP16" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="BQ16" t="n">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="BR16" t="n">
-        <v>276</v>
+        <v>342</v>
       </c>
       <c r="BS16" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BT16" t="n">
-        <v>1059.24</v>
+        <v>1305.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>939.24</v>
+        <v>1149.4</v>
       </c>
       <c r="BV16" t="n">
-        <v>1.059226337924005</v>
+        <v>1.061971749265086</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8746854514345053</v>
+        <v>0.8522282534441883</v>
       </c>
       <c r="BX16" t="n">
-        <v>119.5986315857444</v>
+        <v>120.7921071080789</v>
       </c>
       <c r="BY16" t="n">
-        <v>96.75229666304953</v>
+        <v>94.54300566107989</v>
       </c>
       <c r="BZ16" t="n">
-        <v>22.8463349226949</v>
+        <v>26.24910144699898</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.327982843172208</v>
+        <v>0.3409317290832209</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.7441418047363652</v>
+        <v>0.739188087663736</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.5421192194577145</v>
+        <v>0.5462529474158399</v>
       </c>
       <c r="CD16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -4632,244 +4632,244 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.018305301051677</v>
+        <v>1.01903839489033</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9694079712113691</v>
+        <v>0.9603141056122063</v>
       </c>
       <c r="E17" t="n">
-        <v>114.3791303056464</v>
+        <v>114.0024385783518</v>
       </c>
       <c r="F17" t="n">
-        <v>108.7815540913745</v>
+        <v>108.2652360962009</v>
       </c>
       <c r="G17" t="n">
-        <v>5.597576214271908</v>
+        <v>5.737202482150895</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2992750500995604</v>
+        <v>0.2969399888952391</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7132392231574252</v>
+        <v>0.7063667082258202</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5107044931473004</v>
+        <v>0.5090361720154426</v>
       </c>
       <c r="K17" t="n">
-        <v>5000</v>
+        <v>6200</v>
       </c>
       <c r="L17" t="n">
-        <v>2113</v>
+        <v>2612</v>
       </c>
       <c r="M17" t="n">
-        <v>457</v>
+        <v>566</v>
       </c>
       <c r="N17" t="n">
-        <v>821</v>
+        <v>997</v>
       </c>
       <c r="O17" t="n">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="P17" t="n">
-        <v>716</v>
+        <v>891</v>
       </c>
       <c r="Q17" t="n">
-        <v>425</v>
+        <v>517</v>
       </c>
       <c r="R17" t="n">
-        <v>561</v>
+        <v>690</v>
       </c>
       <c r="S17" t="n">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="T17" t="n">
-        <v>567</v>
+        <v>703</v>
       </c>
       <c r="U17" t="n">
-        <v>387</v>
+        <v>492</v>
       </c>
       <c r="V17" t="n">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="W17" t="n">
-        <v>290</v>
+        <v>371</v>
       </c>
       <c r="X17" t="n">
-        <v>546</v>
+        <v>669</v>
       </c>
       <c r="Y17" t="n">
-        <v>584</v>
+        <v>710</v>
       </c>
       <c r="Z17" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2023</v>
+        <v>2484</v>
       </c>
       <c r="AB17" t="n">
-        <v>2073.84</v>
+        <v>2562.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1848.84</v>
+        <v>2292.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AE17" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="AF17" t="n">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="AG17" t="n">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="AH17" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="AI17" t="n">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="AJ17" t="n">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="AK17" t="n">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="AL17" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AM17" t="n">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="AN17" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="AO17" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="AQ17" t="n">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="AR17" t="n">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AT17" t="n">
-        <v>1068</v>
+        <v>1228.68</v>
       </c>
       <c r="AU17" t="n">
-        <v>959</v>
+        <v>1107.68</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.9898594810026412</v>
+        <v>1.002864804508091</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.978129815162451</v>
+        <v>0.9766604326316545</v>
       </c>
       <c r="AX17" t="n">
-        <v>110.2603911190724</v>
+        <v>111.2264350797026</v>
       </c>
       <c r="AY17" t="n">
-        <v>109.4098950969893</v>
+        <v>110.1620942098723</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.850496022083112</v>
+        <v>1.064340869830321</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.2794114499114524</v>
+        <v>0.2797634275300964</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.7254499096620687</v>
+        <v>0.7096996860168905</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.5086079485838687</v>
+        <v>0.5048446121457768</v>
       </c>
       <c r="BD17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE17" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="BF17" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="BG17" t="n">
-        <v>375</v>
+        <v>504</v>
       </c>
       <c r="BH17" t="n">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="BI17" t="n">
-        <v>363</v>
+        <v>480</v>
       </c>
       <c r="BJ17" t="n">
-        <v>235</v>
+        <v>291</v>
       </c>
       <c r="BK17" t="n">
-        <v>311</v>
+        <v>393</v>
       </c>
       <c r="BL17" t="n">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="BM17" t="n">
-        <v>268</v>
+        <v>362</v>
       </c>
       <c r="BN17" t="n">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="BO17" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="BP17" t="n">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="BQ17" t="n">
-        <v>263</v>
+        <v>341</v>
       </c>
       <c r="BR17" t="n">
-        <v>309</v>
+        <v>391</v>
       </c>
       <c r="BS17" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BT17" t="n">
-        <v>1005.84</v>
+        <v>1333.92</v>
       </c>
       <c r="BU17" t="n">
-        <v>889.84</v>
+        <v>1184.92</v>
       </c>
       <c r="BV17" t="n">
-        <v>1.0491216061048</v>
+        <v>1.03420113587368</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.9599593069310303</v>
+        <v>0.9449894240314733</v>
       </c>
       <c r="BX17" t="n">
-        <v>118.8410977577682</v>
+        <v>116.6049418583355</v>
       </c>
       <c r="BY17" t="n">
-        <v>108.1008513352918</v>
+        <v>106.4869316146341</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.74024642247644</v>
+        <v>10.11801024370143</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.3207939503033441</v>
+        <v>0.3130430151750605</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.700010979444062</v>
+        <v>0.703242041546692</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.5129757497576845</v>
+        <v>0.5129657593932542</v>
       </c>
       <c r="CD17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -4884,244 +4884,244 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8694043673832872</v>
+        <v>0.870390857512733</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9784362771082007</v>
+        <v>0.9553159824473043</v>
       </c>
       <c r="E18" t="n">
-        <v>98.21758340793994</v>
+        <v>97.90063438127875</v>
       </c>
       <c r="F18" t="n">
-        <v>112.0074210073753</v>
+        <v>109.9505938313866</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.78983759943529</v>
+        <v>-12.04995945010781</v>
       </c>
       <c r="H18" t="n">
-        <v>0.281766605714072</v>
+        <v>0.2697491769747821</v>
       </c>
       <c r="I18" t="n">
-        <v>0.643490846029693</v>
+        <v>0.6458988698255751</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4502452252408753</v>
+        <v>0.4500887128220807</v>
       </c>
       <c r="K18" t="n">
-        <v>5025</v>
+        <v>6225</v>
       </c>
       <c r="L18" t="n">
-        <v>1824</v>
+        <v>2257</v>
       </c>
       <c r="M18" t="n">
-        <v>391</v>
+        <v>509</v>
       </c>
       <c r="N18" t="n">
-        <v>853</v>
+        <v>1091</v>
       </c>
       <c r="O18" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="P18" t="n">
-        <v>691</v>
+        <v>829</v>
       </c>
       <c r="Q18" t="n">
-        <v>397</v>
+        <v>489</v>
       </c>
       <c r="R18" t="n">
-        <v>553</v>
+        <v>677</v>
       </c>
       <c r="S18" t="n">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="T18" t="n">
-        <v>498</v>
+        <v>653</v>
       </c>
       <c r="U18" t="n">
-        <v>330</v>
+        <v>402</v>
       </c>
       <c r="V18" t="n">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="W18" t="n">
-        <v>318</v>
+        <v>383</v>
       </c>
       <c r="X18" t="n">
-        <v>496</v>
+        <v>629</v>
       </c>
       <c r="Y18" t="n">
-        <v>529</v>
+        <v>648</v>
       </c>
       <c r="Z18" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AA18" t="n">
-        <v>2118</v>
+        <v>2568</v>
       </c>
       <c r="AB18" t="n">
-        <v>2105.32</v>
+        <v>2600.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>1862.32</v>
+        <v>2311.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AE18" t="n">
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="AF18" t="n">
-        <v>202</v>
+        <v>268</v>
       </c>
       <c r="AG18" t="n">
-        <v>430</v>
+        <v>554</v>
       </c>
       <c r="AH18" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="AI18" t="n">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="AJ18" t="n">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="AK18" t="n">
-        <v>283</v>
+        <v>338</v>
       </c>
       <c r="AL18" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="AM18" t="n">
-        <v>261</v>
+        <v>325</v>
       </c>
       <c r="AN18" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="AO18" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AP18" t="n">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="AQ18" t="n">
-        <v>258</v>
+        <v>326</v>
       </c>
       <c r="AR18" t="n">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="AS18" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AT18" t="n">
-        <v>1070.52</v>
+        <v>1313.72</v>
       </c>
       <c r="AU18" t="n">
-        <v>957.52</v>
+        <v>1181.72</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.8972871912063265</v>
+        <v>0.8905064649604901</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.014775345764666</v>
+        <v>0.998587479293113</v>
       </c>
       <c r="AX18" t="n">
-        <v>100.3118107378594</v>
+        <v>99.07325378961201</v>
       </c>
       <c r="AY18" t="n">
-        <v>116.0086531193324</v>
+        <v>114.9427015730114</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-15.69684238147296</v>
+        <v>-15.86944778339941</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.2559289690705702</v>
+        <v>0.2451663960285819</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.6495080216317992</v>
+        <v>0.6419374911630604</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.4386711068771499</v>
+        <v>0.4335249144891994</v>
       </c>
       <c r="BD18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>2425</v>
+        <v>3025</v>
       </c>
       <c r="BF18" t="n">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="BG18" t="n">
-        <v>423</v>
+        <v>537</v>
       </c>
       <c r="BH18" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="BI18" t="n">
-        <v>327</v>
+        <v>406</v>
       </c>
       <c r="BJ18" t="n">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="BK18" t="n">
-        <v>270</v>
+        <v>339</v>
       </c>
       <c r="BL18" t="n">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="BM18" t="n">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="BN18" t="n">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="BO18" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="BP18" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="BQ18" t="n">
-        <v>238</v>
+        <v>303</v>
       </c>
       <c r="BR18" t="n">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="BS18" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="BT18" t="n">
-        <v>1034.8</v>
+        <v>1287.16</v>
       </c>
       <c r="BU18" t="n">
-        <v>904.8</v>
+        <v>1130.16</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8391979749083278</v>
+        <v>0.8489342095684588</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9390689527303638</v>
+        <v>0.9091597191451085</v>
       </c>
       <c r="BX18" t="n">
-        <v>95.94883713386052</v>
+        <v>96.64984034572326</v>
       </c>
       <c r="BY18" t="n">
-        <v>107.6727528860883</v>
+        <v>104.6256789069867</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-11.72391575222783</v>
+        <v>-7.975838561263433</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.3097573787445323</v>
+        <v>0.2959708099840623</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.6369722391274116</v>
+        <v>0.6501243403989243</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.4627838534682442</v>
+        <v>0.4677567643771539</v>
       </c>
       <c r="CD18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -5136,244 +5136,244 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.992032740863957</v>
+        <v>0.9849576124627533</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8695293686756513</v>
+        <v>0.8754339667635122</v>
       </c>
       <c r="E19" t="n">
-        <v>113.0043073993123</v>
+        <v>111.744736945671</v>
       </c>
       <c r="F19" t="n">
-        <v>97.74287415486252</v>
+        <v>98.78099034872697</v>
       </c>
       <c r="G19" t="n">
-        <v>15.26143324444977</v>
+        <v>12.96374659694402</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3248090494829252</v>
+        <v>0.3132206482623495</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7171648285413645</v>
+        <v>0.710756407306438</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5271472881554786</v>
+        <v>0.5182996466520845</v>
       </c>
       <c r="K19" t="n">
-        <v>5200</v>
+        <v>6200</v>
       </c>
       <c r="L19" t="n">
-        <v>2183</v>
+        <v>2575</v>
       </c>
       <c r="M19" t="n">
-        <v>528</v>
+        <v>611</v>
       </c>
       <c r="N19" t="n">
-        <v>989</v>
+        <v>1166</v>
       </c>
       <c r="O19" t="n">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="P19" t="n">
-        <v>720</v>
+        <v>856</v>
       </c>
       <c r="Q19" t="n">
-        <v>356</v>
+        <v>426</v>
       </c>
       <c r="R19" t="n">
-        <v>515</v>
+        <v>609</v>
       </c>
       <c r="S19" t="n">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="T19" t="n">
-        <v>608</v>
+        <v>723</v>
       </c>
       <c r="U19" t="n">
-        <v>384</v>
+        <v>468</v>
       </c>
       <c r="V19" t="n">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="W19" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="X19" t="n">
-        <v>553</v>
+        <v>662</v>
       </c>
       <c r="Y19" t="n">
-        <v>510</v>
+        <v>616</v>
       </c>
       <c r="Z19" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="n">
-        <v>1874</v>
+        <v>2254</v>
       </c>
       <c r="AB19" t="n">
-        <v>2205.6</v>
+        <v>2619.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>1930.6</v>
+        <v>2303.96</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AE19" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="AF19" t="n">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AG19" t="n">
-        <v>452</v>
+        <v>586</v>
       </c>
       <c r="AH19" t="n">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="AI19" t="n">
-        <v>342</v>
+        <v>449</v>
       </c>
       <c r="AJ19" t="n">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="AK19" t="n">
-        <v>236</v>
+        <v>321</v>
       </c>
       <c r="AL19" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="AM19" t="n">
-        <v>284</v>
+        <v>369</v>
       </c>
       <c r="AN19" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AO19" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="AP19" t="n">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="AQ19" t="n">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="AR19" t="n">
-        <v>235</v>
+        <v>325</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AT19" t="n">
-        <v>1018.84</v>
+        <v>1350.24</v>
       </c>
       <c r="AU19" t="n">
-        <v>889.84</v>
+        <v>1191.24</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.9936248790724237</v>
+        <v>0.9722103184572901</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.8659893271862308</v>
+        <v>0.8801012159662031</v>
       </c>
       <c r="AX19" t="n">
-        <v>113.5978811475987</v>
+        <v>110.0812888633287</v>
       </c>
       <c r="AY19" t="n">
-        <v>95.98630174244708</v>
+        <v>98.48952305545461</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.61157940515162</v>
+        <v>11.59176580787407</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.315133038938186</v>
+        <v>0.2963028575799659</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.7487721713529848</v>
+        <v>0.7275451139741715</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.5325416686012221</v>
+        <v>0.5137182528074568</v>
       </c>
       <c r="BD19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BE19" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="BF19" t="n">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="BG19" t="n">
-        <v>537</v>
+        <v>580</v>
       </c>
       <c r="BH19" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="BI19" t="n">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="BJ19" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="BK19" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="BL19" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="BM19" t="n">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="BN19" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="BO19" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="BP19" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="BQ19" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="BR19" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="BS19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BT19" t="n">
-        <v>1186.76</v>
+        <v>1269.72</v>
       </c>
       <c r="BU19" t="n">
-        <v>1040.76</v>
+        <v>1112.72</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.9906680509709858</v>
+        <v>0.9985547260685805</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.8725636899522975</v>
+        <v>0.8704555676139751</v>
       </c>
       <c r="BX19" t="n">
-        <v>112.4955299007811</v>
+        <v>113.5190815668361</v>
       </c>
       <c r="BY19" t="n">
-        <v>99.24850765121865</v>
+        <v>99.09188879488417</v>
       </c>
       <c r="BZ19" t="n">
-        <v>13.24702224956247</v>
+        <v>14.42719277195196</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.3331027728069874</v>
+        <v>0.3312662916568919</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.6900728204171187</v>
+        <v>0.6928484535275222</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.5225235334876986</v>
+        <v>0.5231864667530209</v>
       </c>
       <c r="CD19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/teams_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/teams_25_26_1FEB.xlsx
@@ -852,166 +852,166 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9417337814841368</v>
+        <v>0.9418158310322573</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9165997032775537</v>
+        <v>0.9157443263712683</v>
       </c>
       <c r="E2" t="n">
-        <v>107.3829207096868</v>
+        <v>107.3138729991919</v>
       </c>
       <c r="F2" t="n">
-        <v>101.1479184572993</v>
+        <v>101.1702532232037</v>
       </c>
       <c r="G2" t="n">
-        <v>6.235002252387472</v>
+        <v>6.143619775988144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3130609428999607</v>
+        <v>0.3104206455771941</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7493766261520676</v>
+        <v>0.7487626606388695</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5253346435754654</v>
+        <v>0.5241089081859543</v>
       </c>
       <c r="K2" t="n">
-        <v>6225</v>
+        <v>6425</v>
       </c>
       <c r="L2" t="n">
-        <v>2552</v>
+        <v>2626</v>
       </c>
       <c r="M2" t="n">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="N2" t="n">
-        <v>1002</v>
+        <v>1030</v>
       </c>
       <c r="O2" t="n">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="P2" t="n">
-        <v>1021</v>
+        <v>1058</v>
       </c>
       <c r="Q2" t="n">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="R2" t="n">
-        <v>645</v>
+        <v>664</v>
       </c>
       <c r="S2" t="n">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="T2" t="n">
-        <v>739</v>
+        <v>766</v>
       </c>
       <c r="U2" t="n">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="V2" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W2" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="X2" t="n">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="Y2" t="n">
-        <v>650</v>
+        <v>672</v>
       </c>
       <c r="Z2" t="n">
         <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>2424</v>
+        <v>2494</v>
       </c>
       <c r="AB2" t="n">
-        <v>2716.8</v>
+        <v>2795.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2379.8</v>
+        <v>2450.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="n">
-        <v>3025</v>
+        <v>3225</v>
       </c>
       <c r="AF2" t="n">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="AG2" t="n">
-        <v>504</v>
+        <v>532</v>
       </c>
       <c r="AH2" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="AI2" t="n">
-        <v>513</v>
+        <v>550</v>
       </c>
       <c r="AJ2" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="AL2" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AM2" t="n">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="AN2" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="AO2" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="AP2" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AQ2" t="n">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="AR2" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1337.76</v>
+        <v>1416.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1162.76</v>
+        <v>1233.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.9218714903158456</v>
+        <v>0.9232769826101047</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9255886402081579</v>
+        <v>0.9233160778374244</v>
       </c>
       <c r="AX2" t="n">
-        <v>105.9013622192401</v>
+        <v>105.8558642039031</v>
       </c>
       <c r="AY2" t="n">
-        <v>102.5074158852856</v>
+        <v>102.4671168278453</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.393946333954433</v>
+        <v>3.38874737605784</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.329155055037408</v>
+        <v>0.3228685783832843</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.742691883677951</v>
+        <v>0.7418817490561872</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.5243188477584073</v>
+        <v>0.5219308642179513</v>
       </c>
       <c r="BD2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE2" t="n">
         <v>3200</v>
@@ -1104,88 +1104,88 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9393165177231364</v>
+        <v>0.940621859995825</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9606506483217557</v>
+        <v>0.96111029502782</v>
       </c>
       <c r="E3" t="n">
-        <v>106.0633110921741</v>
+        <v>106.4226994760677</v>
       </c>
       <c r="F3" t="n">
-        <v>110.1689829519467</v>
+        <v>110.0750460023239</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.105671859772651</v>
+        <v>-3.65234652625617</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3107791531421821</v>
+        <v>0.3120048046064889</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6720417879642876</v>
+        <v>0.6747473786421277</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4961777722599058</v>
+        <v>0.4969765647028708</v>
       </c>
       <c r="K3" t="n">
-        <v>6247.766666666666</v>
+        <v>6447.766666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>2591</v>
+        <v>2674</v>
       </c>
       <c r="M3" t="n">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="N3" t="n">
-        <v>1295</v>
+        <v>1335</v>
       </c>
       <c r="O3" t="n">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="P3" t="n">
-        <v>699</v>
+        <v>731</v>
       </c>
       <c r="Q3" t="n">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="R3" t="n">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="S3" t="n">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="T3" t="n">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="U3" t="n">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="V3" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="W3" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="X3" t="n">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="Y3" t="n">
-        <v>682</v>
+        <v>700</v>
       </c>
       <c r="Z3" t="n">
         <v>73</v>
       </c>
       <c r="AA3" t="n">
-        <v>2672</v>
+        <v>2748</v>
       </c>
       <c r="AB3" t="n">
-        <v>2759.68</v>
+        <v>2844.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>2442.68</v>
+        <v>2513.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
         <v>3225</v>
@@ -1266,82 +1266,82 @@
         <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>3022.766666666666</v>
+        <v>3222.766666666666</v>
       </c>
       <c r="BF3" t="n">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="BG3" t="n">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="BH3" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="BI3" t="n">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="BJ3" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="BK3" t="n">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="BL3" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="BM3" t="n">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="BN3" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="BO3" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="BP3" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="BQ3" t="n">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="BR3" t="n">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="BS3" t="n">
         <v>33</v>
       </c>
       <c r="BT3" t="n">
-        <v>1354.36</v>
+        <v>1438.96</v>
       </c>
       <c r="BU3" t="n">
-        <v>1191.36</v>
+        <v>1261.96</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9301133252964917</v>
+        <v>0.9332992093685343</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.975187512775902</v>
+        <v>0.9751982521596463</v>
       </c>
       <c r="BX3" t="n">
-        <v>105.6133409459045</v>
+        <v>106.3602408478336</v>
       </c>
       <c r="BY3" t="n">
-        <v>110.7539711969599</v>
+        <v>110.5295355324009</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-5.140630251055417</v>
+        <v>-4.169294684567282</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.3077711924676732</v>
+        <v>0.3104104929384436</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6783232747392683</v>
+        <v>0.6833418631715124</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.4886605000280362</v>
+        <v>0.4907279144284579</v>
       </c>
       <c r="CD3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1356,88 +1356,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8827689043507106</v>
+        <v>0.8830918412469961</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9995074092848157</v>
+        <v>0.9967500071717745</v>
       </c>
       <c r="E4" t="n">
-        <v>103.9793029720495</v>
+        <v>103.873469371759</v>
       </c>
       <c r="F4" t="n">
-        <v>111.3923829627076</v>
+        <v>111.0814335132647</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.413079990658183</v>
+        <v>-7.207964141505721</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3763023125583365</v>
+        <v>0.3710007104439332</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7166092197793431</v>
+        <v>0.7193501873618046</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5306170802071598</v>
+        <v>0.5297806706412462</v>
       </c>
       <c r="K4" t="n">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="L4" t="n">
-        <v>1467</v>
+        <v>1537</v>
       </c>
       <c r="M4" t="n">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="N4" t="n">
-        <v>791</v>
+        <v>832</v>
       </c>
       <c r="O4" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P4" t="n">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="Q4" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R4" t="n">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="S4" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="T4" t="n">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="U4" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="V4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W4" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="X4" t="n">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="Y4" t="n">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="Z4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA4" t="n">
-        <v>1565</v>
+        <v>1639</v>
       </c>
       <c r="AB4" t="n">
-        <v>1665.96</v>
+        <v>1744.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>1409.96</v>
+        <v>1478.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
         <v>1800</v>
@@ -1518,82 +1518,82 @@
         <v>9</v>
       </c>
       <c r="BE4" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="BF4" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="BG4" t="n">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="BH4" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="BI4" t="n">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="BJ4" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="BK4" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="BL4" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="BM4" t="n">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="BN4" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="BO4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BP4" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="BQ4" t="n">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="BR4" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="BS4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BT4" t="n">
-        <v>890.5599999999999</v>
+        <v>969.28</v>
       </c>
       <c r="BU4" t="n">
-        <v>745.5599999999999</v>
+        <v>814.28</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.9125534380545739</v>
+        <v>0.9104329111656512</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.9992028050281135</v>
+        <v>0.9942170379368297</v>
       </c>
       <c r="BX4" t="n">
-        <v>108.4380079133761</v>
+        <v>107.8402463727273</v>
       </c>
       <c r="BY4" t="n">
-        <v>110.3574516776016</v>
+        <v>109.8861737045331</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-1.919443764225453</v>
+        <v>-2.045927331805771</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3942543428064808</v>
+        <v>0.3829830634850071</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.729573850323382</v>
+        <v>0.7333788249693083</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5433514254169837</v>
+        <v>0.5406730130053387</v>
       </c>
       <c r="CD4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -1860,166 +1860,166 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9052293754333669</v>
+        <v>0.9092869145869727</v>
       </c>
       <c r="D6" t="n">
-        <v>0.95873150689357</v>
+        <v>0.9494039807856884</v>
       </c>
       <c r="E6" t="n">
-        <v>100.9099891737401</v>
+        <v>101.3892790361307</v>
       </c>
       <c r="F6" t="n">
-        <v>110.3297742480397</v>
+        <v>109.4656991839544</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.419785074299647</v>
+        <v>-8.076420147823681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.271048297552913</v>
+        <v>0.2729947049210512</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6250522741353367</v>
+        <v>0.6242693905686075</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4435733435210618</v>
+        <v>0.4453366765360287</v>
       </c>
       <c r="K6" t="n">
-        <v>6250</v>
+        <v>6450</v>
       </c>
       <c r="L6" t="n">
-        <v>2352</v>
+        <v>2437</v>
       </c>
       <c r="M6" t="n">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="N6" t="n">
-        <v>1108</v>
+        <v>1134</v>
       </c>
       <c r="O6" t="n">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="P6" t="n">
-        <v>821</v>
+        <v>854</v>
       </c>
       <c r="Q6" t="n">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="R6" t="n">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="S6" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="T6" t="n">
-        <v>595</v>
+        <v>622</v>
       </c>
       <c r="U6" t="n">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="V6" t="n">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="W6" t="n">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="X6" t="n">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="Y6" t="n">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="Z6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA6" t="n">
-        <v>2570</v>
+        <v>2629</v>
       </c>
       <c r="AB6" t="n">
-        <v>2602.96</v>
+        <v>2685.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>2332.96</v>
+        <v>2406.08</v>
       </c>
       <c r="AD6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="AF6" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="AG6" t="n">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="AH6" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="AI6" t="n">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="AJ6" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="AK6" t="n">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="AL6" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="AM6" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="AN6" t="n">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="AO6" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="AP6" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="AQ6" t="n">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="AR6" t="n">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="AS6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT6" t="n">
-        <v>1248.32</v>
+        <v>1330.44</v>
       </c>
       <c r="AU6" t="n">
-        <v>1131.32</v>
+        <v>1204.44</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8807243205814752</v>
+        <v>0.8903709648169305</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.946111507896537</v>
+        <v>0.9282452056180884</v>
       </c>
       <c r="AX6" t="n">
-        <v>97.13794708067651</v>
+        <v>98.33227943627428</v>
       </c>
       <c r="AY6" t="n">
-        <v>109.3236451495537</v>
+        <v>107.6583780900384</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-12.18569806887719</v>
+        <v>-9.326098653764163</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2595453765061675</v>
+        <v>0.2641571238078653</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6241510288633612</v>
+        <v>0.6226415895594011</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4389036251043099</v>
+        <v>0.4427221485352905</v>
       </c>
       <c r="BD6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE6" t="n">
         <v>3250</v>
@@ -2112,88 +2112,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.95608432288256</v>
+        <v>0.957718605026634</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9478528247441815</v>
+        <v>0.9463060892686671</v>
       </c>
       <c r="E7" t="n">
-        <v>105.0765529384902</v>
+        <v>105.3128784765995</v>
       </c>
       <c r="F7" t="n">
-        <v>106.2644074972537</v>
+        <v>106.2620610251005</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.187854558763518</v>
+        <v>-0.9491825485009828</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2442252621030992</v>
+        <v>0.2446577387914096</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7315559380293846</v>
+        <v>0.7274448149659664</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4993951465574644</v>
+        <v>0.4971087203586911</v>
       </c>
       <c r="K7" t="n">
-        <v>6225</v>
+        <v>6425</v>
       </c>
       <c r="L7" t="n">
-        <v>2476</v>
+        <v>2553</v>
       </c>
       <c r="M7" t="n">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="N7" t="n">
-        <v>1111</v>
+        <v>1152</v>
       </c>
       <c r="O7" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="P7" t="n">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="Q7" t="n">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="R7" t="n">
-        <v>680</v>
+        <v>699</v>
       </c>
       <c r="S7" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="T7" t="n">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="U7" t="n">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="V7" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="W7" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="X7" t="n">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="Y7" t="n">
-        <v>656</v>
+        <v>675</v>
       </c>
       <c r="Z7" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>2512</v>
+        <v>2582</v>
       </c>
       <c r="AB7" t="n">
-        <v>2594.2</v>
+        <v>2670.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>2360.2</v>
+        <v>2428.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE7" t="n">
         <v>3225</v>
@@ -2274,82 +2274,82 @@
         <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="BF7" t="n">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="BG7" t="n">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="BH7" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="BI7" t="n">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="BJ7" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="BK7" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="BL7" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="BM7" t="n">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="BN7" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="BO7" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="BP7" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="BQ7" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="BR7" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="BS7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BT7" t="n">
-        <v>1240.48</v>
+        <v>1316.84</v>
       </c>
       <c r="BU7" t="n">
-        <v>1129.48</v>
+        <v>1197.84</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.9793641218623789</v>
+        <v>0.9811776987142883</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.908890385388442</v>
+        <v>0.9082320668971469</v>
       </c>
       <c r="BX7" t="n">
-        <v>107.6328260309254</v>
+        <v>107.9457100388667</v>
       </c>
       <c r="BY7" t="n">
-        <v>101.1476599567617</v>
+        <v>101.462763733736</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.48516607416365</v>
+        <v>6.482946305130773</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.2428244725328459</v>
+        <v>0.2437769752576076</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7538814193670568</v>
+        <v>0.7442638306566157</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5153481068960516</v>
+        <v>0.5097781944773434</v>
       </c>
       <c r="CD7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -2364,166 +2364,166 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9484879171711749</v>
+        <v>0.9451903961564928</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9994197041146552</v>
+        <v>1.002910060583295</v>
       </c>
       <c r="E8" t="n">
-        <v>103.5397087785857</v>
+        <v>103.2990271618398</v>
       </c>
       <c r="F8" t="n">
-        <v>112.1469959984908</v>
+        <v>112.7542444788012</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.607287219905137</v>
+        <v>-9.455217316961374</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2342779856850789</v>
+        <v>0.2345787498519324</v>
       </c>
       <c r="I8" t="n">
-        <v>0.714346013107048</v>
+        <v>0.7081864933009011</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4804969659545085</v>
+        <v>0.4766421500541444</v>
       </c>
       <c r="K8" t="n">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="L8" t="n">
-        <v>2411</v>
+        <v>2481</v>
       </c>
       <c r="M8" t="n">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="N8" t="n">
-        <v>987</v>
+        <v>1017</v>
       </c>
       <c r="O8" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="P8" t="n">
-        <v>827</v>
+        <v>861</v>
       </c>
       <c r="Q8" t="n">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="R8" t="n">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="S8" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="T8" t="n">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="U8" t="n">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="V8" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="W8" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="X8" t="n">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="Y8" t="n">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="Z8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>2608</v>
+        <v>2708</v>
       </c>
       <c r="AB8" t="n">
-        <v>2548.84</v>
+        <v>2631.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>2332.84</v>
+        <v>2405.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE8" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="AF8" t="n">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="AG8" t="n">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="AH8" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AI8" t="n">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="AJ8" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AK8" t="n">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="AL8" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>366</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>233</v>
+      </c>
+      <c r="AO8" t="n">
         <v>102</v>
       </c>
-      <c r="AM8" t="n">
-        <v>351</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>223</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>96</v>
-      </c>
       <c r="AP8" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AQ8" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="AR8" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>1251.48</v>
+        <v>1334.52</v>
       </c>
       <c r="AU8" t="n">
-        <v>1149.48</v>
+        <v>1222.52</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9405333518290729</v>
+        <v>0.9344354701335902</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.003555641458983</v>
+        <v>1.010277858312241</v>
       </c>
       <c r="AX8" t="n">
-        <v>102.3423958278349</v>
+        <v>101.935864653765</v>
       </c>
       <c r="AY8" t="n">
-        <v>112.776611414705</v>
+        <v>113.9517574118123</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-10.4342155868701</v>
+        <v>-12.01589275804726</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.241510905862605</v>
+        <v>0.2416603766852166</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.7185326589865129</v>
+        <v>0.7059519540067524</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.4921665226836562</v>
+        <v>0.4837275435873563</v>
       </c>
       <c r="BD8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
         <v>3200</v>
@@ -2616,166 +2616,166 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8847680299348241</v>
+        <v>0.8876813761876248</v>
       </c>
       <c r="D9" t="n">
-        <v>0.98875981763415</v>
+        <v>0.9918602544280758</v>
       </c>
       <c r="E9" t="n">
-        <v>97.50334410689696</v>
+        <v>97.71157293688977</v>
       </c>
       <c r="F9" t="n">
-        <v>111.5632892086128</v>
+        <v>111.8769494961575</v>
       </c>
       <c r="G9" t="n">
-        <v>-14.0599451017159</v>
+        <v>-14.16537655926775</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2367007377536416</v>
+        <v>0.2341866521988403</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6955227084665095</v>
+        <v>0.6946209571602645</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4586741012093621</v>
+        <v>0.4565227389364</v>
       </c>
       <c r="K9" t="n">
-        <v>6250</v>
+        <v>6450</v>
       </c>
       <c r="L9" t="n">
-        <v>2287</v>
+        <v>2367</v>
       </c>
       <c r="M9" t="n">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="N9" t="n">
-        <v>1056</v>
+        <v>1096</v>
       </c>
       <c r="O9" t="n">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="P9" t="n">
-        <v>859</v>
+        <v>882</v>
       </c>
       <c r="Q9" t="n">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="R9" t="n">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="S9" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="T9" t="n">
-        <v>690</v>
+        <v>708</v>
       </c>
       <c r="U9" t="n">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="V9" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="W9" t="n">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="X9" t="n">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="Y9" t="n">
-        <v>623</v>
+        <v>645</v>
       </c>
       <c r="Z9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA9" t="n">
-        <v>2619</v>
+        <v>2712</v>
       </c>
       <c r="AB9" t="n">
-        <v>2587.16</v>
+        <v>2668.96</v>
       </c>
       <c r="AC9" t="n">
-        <v>2348.16</v>
+        <v>2424.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE9" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="AF9" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="AG9" t="n">
-        <v>522</v>
+        <v>562</v>
       </c>
       <c r="AH9" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AI9" t="n">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="AJ9" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="AK9" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="AL9" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AM9" t="n">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="AN9" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="AO9" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="AP9" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AQ9" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="AR9" t="n">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="AS9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>1229.92</v>
+        <v>1311.72</v>
       </c>
       <c r="AU9" t="n">
-        <v>1128.92</v>
+        <v>1205.72</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8933509860103926</v>
+        <v>0.8986412437612712</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.036973598397362</v>
+        <v>1.040161110687513</v>
       </c>
       <c r="AX9" t="n">
-        <v>97.24971266306144</v>
+        <v>97.68202228828676</v>
       </c>
       <c r="AY9" t="n">
-        <v>116.9396730929621</v>
+        <v>117.2309696752796</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-19.68996042990062</v>
+        <v>-19.54894738699278</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2066245739124996</v>
+        <v>0.2034761630429684</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6973658448282104</v>
+        <v>0.6954471461931139</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4397303407380408</v>
+        <v>0.4366116012215743</v>
       </c>
       <c r="BD9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE9" t="n">
         <v>3250</v>
@@ -2868,88 +2868,88 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.943162598785794</v>
+        <v>0.9476879486687309</v>
       </c>
       <c r="D10" t="n">
-        <v>1.015393385169808</v>
+        <v>1.014224689071516</v>
       </c>
       <c r="E10" t="n">
-        <v>107.0290879822072</v>
+        <v>107.484442058077</v>
       </c>
       <c r="F10" t="n">
-        <v>114.6387556139332</v>
+        <v>114.3115028343311</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.60966763172602</v>
+        <v>-6.827060776254108</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3167630144822071</v>
+        <v>0.3172808369463048</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6879366709001774</v>
+        <v>0.6928058374345468</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4952837798643361</v>
+        <v>0.4988739583537452</v>
       </c>
       <c r="K10" t="n">
-        <v>6275</v>
+        <v>6475</v>
       </c>
       <c r="L10" t="n">
-        <v>2575</v>
+        <v>2668</v>
       </c>
       <c r="M10" t="n">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="N10" t="n">
-        <v>1093</v>
+        <v>1133</v>
       </c>
       <c r="O10" t="n">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="P10" t="n">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="Q10" t="n">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="R10" t="n">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="S10" t="n">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="T10" t="n">
-        <v>668</v>
+        <v>695</v>
       </c>
       <c r="U10" t="n">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="V10" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="W10" t="n">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="X10" t="n">
-        <v>761</v>
+        <v>783</v>
       </c>
       <c r="Y10" t="n">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="Z10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AA10" t="n">
-        <v>2767</v>
+        <v>2847</v>
       </c>
       <c r="AB10" t="n">
-        <v>2732.6</v>
+        <v>2818.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>2406.6</v>
+        <v>2483.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE10" t="n">
         <v>3250</v>
@@ -3030,82 +3030,82 @@
         <v>16</v>
       </c>
       <c r="BE10" t="n">
-        <v>3025</v>
+        <v>3225</v>
       </c>
       <c r="BF10" t="n">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="BG10" t="n">
-        <v>515</v>
+        <v>555</v>
       </c>
       <c r="BH10" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="BI10" t="n">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="BJ10" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="BK10" t="n">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="BL10" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="BM10" t="n">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="BN10" t="n">
+        <v>239</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>115</v>
+      </c>
+      <c r="BP10" t="n">
         <v>218</v>
       </c>
-      <c r="BO10" t="n">
-        <v>110</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>202</v>
-      </c>
       <c r="BQ10" t="n">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="BR10" t="n">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="BS10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BT10" t="n">
-        <v>1311.48</v>
+        <v>1396.96</v>
       </c>
       <c r="BU10" t="n">
-        <v>1159.48</v>
+        <v>1235.96</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9737243523705258</v>
+        <v>0.9808649425373539</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.007148287300091</v>
+        <v>1.005326213720363</v>
       </c>
       <c r="BX10" t="n">
-        <v>110.0528357659835</v>
+        <v>110.7745596812371</v>
       </c>
       <c r="BY10" t="n">
-        <v>113.4295621562757</v>
+        <v>112.8506311881751</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-3.376726390292238</v>
+        <v>-2.076071506938025</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3110281818861391</v>
+        <v>0.3124222538515887</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.6989739662153454</v>
+        <v>0.7080224683268863</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.5026264979885685</v>
+        <v>0.5093479350846219</v>
       </c>
       <c r="CD10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -3120,88 +3120,88 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9741225410072877</v>
+        <v>0.9783430210831936</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9545205049993054</v>
+        <v>0.9502366983461425</v>
       </c>
       <c r="E11" t="n">
-        <v>110.2649714081432</v>
+        <v>110.9078262491759</v>
       </c>
       <c r="F11" t="n">
-        <v>107.1000837146807</v>
+        <v>106.5984261289459</v>
       </c>
       <c r="G11" t="n">
-        <v>3.164887693462475</v>
+        <v>4.309400120229958</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3105016342462874</v>
+        <v>0.3126227825004152</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7073843409813931</v>
+        <v>0.7082565215021952</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5055990199064261</v>
+        <v>0.5069645434920967</v>
       </c>
       <c r="K11" t="n">
-        <v>6225</v>
+        <v>6425</v>
       </c>
       <c r="L11" t="n">
-        <v>2472</v>
+        <v>2574</v>
       </c>
       <c r="M11" t="n">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="N11" t="n">
-        <v>996</v>
+        <v>1032</v>
       </c>
       <c r="O11" t="n">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="P11" t="n">
-        <v>933</v>
+        <v>974</v>
       </c>
       <c r="Q11" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="R11" t="n">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="S11" t="n">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="T11" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="U11" t="n">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="V11" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="W11" t="n">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="X11" t="n">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="Y11" t="n">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="Z11" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2384</v>
+        <v>2456</v>
       </c>
       <c r="AB11" t="n">
-        <v>2551.64</v>
+        <v>2643.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>2245.64</v>
+        <v>2323.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE11" t="n">
         <v>3225</v>
@@ -3282,82 +3282,82 @@
         <v>16</v>
       </c>
       <c r="BE11" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="BF11" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="BG11" t="n">
-        <v>463</v>
+        <v>499</v>
       </c>
       <c r="BH11" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="BI11" t="n">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="BJ11" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="BK11" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="BL11" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="BM11" t="n">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="BN11" t="n">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="BO11" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="BP11" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="BQ11" t="n">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="BR11" t="n">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="BS11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BT11" t="n">
-        <v>1239.52</v>
+        <v>1331.48</v>
       </c>
       <c r="BU11" t="n">
-        <v>1080.52</v>
+        <v>1158.48</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9925890778987639</v>
+        <v>0.9998758794948586</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9325827697434611</v>
+        <v>0.9253862648906255</v>
       </c>
       <c r="BX11" t="n">
-        <v>113.4204122729434</v>
+        <v>114.5089069009588</v>
       </c>
       <c r="BY11" t="n">
-        <v>104.9513922383548</v>
+        <v>104.0823702841557</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.46902003458853</v>
+        <v>10.42653661680312</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3471830324473591</v>
+        <v>0.3491327415680478</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7027391258681581</v>
+        <v>0.7047738128543395</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.5284959192189027</v>
+        <v>0.5297959101832143</v>
       </c>
       <c r="CD11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -3372,166 +3372,166 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9830660682859907</v>
+        <v>0.9828252331181726</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9771117818897105</v>
+        <v>0.9772360221571936</v>
       </c>
       <c r="E12" t="n">
-        <v>110.3841794228691</v>
+        <v>110.2835175835299</v>
       </c>
       <c r="F12" t="n">
-        <v>109.7472452920443</v>
+        <v>109.991510732192</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6369341308247487</v>
+        <v>0.2920068513378893</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2719711605084112</v>
+        <v>0.2710151651907993</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7124430279614486</v>
+        <v>0.7104916833376533</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4911295773290874</v>
+        <v>0.4907274302114665</v>
       </c>
       <c r="K12" t="n">
-        <v>6250</v>
+        <v>6450</v>
       </c>
       <c r="L12" t="n">
-        <v>2556</v>
+        <v>2632</v>
       </c>
       <c r="M12" t="n">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="N12" t="n">
-        <v>1107</v>
+        <v>1121</v>
       </c>
       <c r="O12" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="P12" t="n">
-        <v>842</v>
+        <v>886</v>
       </c>
       <c r="Q12" t="n">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="R12" t="n">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="S12" t="n">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="T12" t="n">
-        <v>720</v>
+        <v>746</v>
       </c>
       <c r="U12" t="n">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="V12" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W12" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="X12" t="n">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="Y12" t="n">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA12" t="n">
-        <v>2545</v>
+        <v>2628</v>
       </c>
       <c r="AB12" t="n">
-        <v>2602.4</v>
+        <v>2680.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>2312.4</v>
+        <v>2383.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="n">
-        <v>3050</v>
+        <v>3250</v>
       </c>
       <c r="AF12" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG12" t="n">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="AH12" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="AI12" t="n">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="AJ12" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="AK12" t="n">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="AL12" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="n">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="AN12" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AO12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP12" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="AQ12" t="n">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="AR12" t="n">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>1260.88</v>
+        <v>1338.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1112.88</v>
+        <v>1183.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.9474144604003226</v>
+        <v>0.9491610155575407</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.954676895240046</v>
+        <v>0.9563275561906164</v>
       </c>
       <c r="AX12" t="n">
-        <v>107.1856514129457</v>
+        <v>107.1842357348876</v>
       </c>
       <c r="AY12" t="n">
-        <v>107.9472768066327</v>
+        <v>108.5483057172663</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.7616253936870133</v>
+        <v>-1.364069982378747</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2786360181060001</v>
+        <v>0.2763074738709268</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.7162392773749765</v>
+        <v>0.7120993225390405</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4959308662815106</v>
+        <v>0.4948264914867422</v>
       </c>
       <c r="BD12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE12" t="n">
         <v>3200</v>
@@ -3624,166 +3624,166 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9460606861643507</v>
+        <v>0.9444127374358503</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8887059387625326</v>
+        <v>0.8921691792110106</v>
       </c>
       <c r="E13" t="n">
-        <v>108.4390133639481</v>
+        <v>107.9967722883935</v>
       </c>
       <c r="F13" t="n">
-        <v>100.3879835546248</v>
+        <v>100.7440863173592</v>
       </c>
       <c r="G13" t="n">
-        <v>8.051029809323374</v>
+        <v>7.25268597103438</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3420654770547829</v>
+        <v>0.3361836232045132</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7190357086278473</v>
+        <v>0.7192931154604998</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5391722531520198</v>
+        <v>0.5371536287155954</v>
       </c>
       <c r="K13" t="n">
-        <v>6225</v>
+        <v>6425</v>
       </c>
       <c r="L13" t="n">
-        <v>2452</v>
+        <v>2520</v>
       </c>
       <c r="M13" t="n">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="N13" t="n">
-        <v>1125</v>
+        <v>1149</v>
       </c>
       <c r="O13" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="P13" t="n">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="Q13" t="n">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="R13" t="n">
-        <v>605</v>
+        <v>628</v>
       </c>
       <c r="S13" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="T13" t="n">
-        <v>758</v>
+        <v>782</v>
       </c>
       <c r="U13" t="n">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="V13" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="W13" t="n">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="X13" t="n">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="Y13" t="n">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="Z13" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA13" t="n">
-        <v>2301</v>
+        <v>2386</v>
       </c>
       <c r="AB13" t="n">
-        <v>2598.2</v>
+        <v>2674.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>2261.2</v>
+        <v>2333.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="AF13" t="n">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="AG13" t="n">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="AH13" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="AI13" t="n">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="AJ13" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="AK13" t="n">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="AL13" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AM13" t="n">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="AN13" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="AO13" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="AP13" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="AQ13" t="n">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="AR13" t="n">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="AS13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AT13" t="n">
-        <v>1244.76</v>
+        <v>1320.88</v>
       </c>
       <c r="AU13" t="n">
-        <v>1099.76</v>
+        <v>1171.88</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9569025577027492</v>
+        <v>0.9529290432745985</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8798297497036599</v>
+        <v>0.8873109924167955</v>
       </c>
       <c r="AX13" t="n">
-        <v>108.1414895177445</v>
+        <v>107.275602607023</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.3623446949506</v>
+        <v>102.013652649149</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.779144822793855</v>
+        <v>5.261949957873961</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.3320267504935167</v>
+        <v>0.3208904632030565</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.6930330032026345</v>
+        <v>0.6951729859570153</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5370504119915659</v>
+        <v>0.5331457781912456</v>
       </c>
       <c r="BD13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE13" t="n">
         <v>3225</v>
@@ -4128,166 +4128,166 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8778839618462584</v>
+        <v>0.8759950471666282</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9833833422397469</v>
+        <v>0.9873144222771384</v>
       </c>
       <c r="E15" t="n">
-        <v>99.40239608609475</v>
+        <v>99.14129123875331</v>
       </c>
       <c r="F15" t="n">
-        <v>111.0449509239419</v>
+        <v>111.6634314051059</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.64255483784715</v>
+        <v>-12.52214016635261</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2874272418651134</v>
+        <v>0.286717199380358</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6992956251010252</v>
+        <v>0.6968683124922938</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4886911612697814</v>
+        <v>0.4875040695223543</v>
       </c>
       <c r="K15" t="n">
-        <v>6225</v>
+        <v>6425</v>
       </c>
       <c r="L15" t="n">
-        <v>2373</v>
+        <v>2445</v>
       </c>
       <c r="M15" t="n">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="N15" t="n">
-        <v>1062</v>
+        <v>1094</v>
       </c>
       <c r="O15" t="n">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="P15" t="n">
-        <v>936</v>
+        <v>958</v>
       </c>
       <c r="Q15" t="n">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="R15" t="n">
-        <v>568</v>
+        <v>600</v>
       </c>
       <c r="S15" t="n">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="T15" t="n">
-        <v>735</v>
+        <v>758</v>
       </c>
       <c r="U15" t="n">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="V15" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="W15" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="X15" t="n">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="Y15" t="n">
-        <v>641</v>
+        <v>667</v>
       </c>
       <c r="Z15" t="n">
         <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2667</v>
+        <v>2769</v>
       </c>
       <c r="AB15" t="n">
-        <v>2708.92</v>
+        <v>2797</v>
       </c>
       <c r="AC15" t="n">
-        <v>2388.92</v>
+        <v>2468</v>
       </c>
       <c r="AD15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE15" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="AF15" t="n">
+        <v>251</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>557</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>154</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>476</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>221</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>289</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>169</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>369</v>
+      </c>
+      <c r="AN15" t="n">
         <v>240</v>
       </c>
-      <c r="AG15" t="n">
-        <v>525</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>146</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>454</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>195</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>257</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>346</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>227</v>
-      </c>
       <c r="AO15" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="AP15" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="AQ15" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="AR15" t="n">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>1320.08</v>
+        <v>1408.16</v>
       </c>
       <c r="AU15" t="n">
-        <v>1160.08</v>
+        <v>1239.16</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.843713158341048</v>
+        <v>0.8420710042008633</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.006573460733275</v>
+        <v>1.012986238402212</v>
       </c>
       <c r="AX15" t="n">
-        <v>95.89340288502628</v>
+        <v>95.59050526541016</v>
       </c>
       <c r="AY15" t="n">
-        <v>114.200930919761</v>
+        <v>115.2406431323504</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-18.30752803473473</v>
+        <v>-19.65013786694018</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.2963252103298367</v>
+        <v>0.2943490023312808</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.694708203673721</v>
+        <v>0.6901402922954647</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.4869281973932811</v>
+        <v>0.4846641991407081</v>
       </c>
       <c r="BD15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE15" t="n">
         <v>3225</v>
@@ -4380,88 +4380,88 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.068224419335226</v>
+        <v>1.066077707265808</v>
       </c>
       <c r="D16" t="n">
-        <v>0.887690116830567</v>
+        <v>0.8878662483937474</v>
       </c>
       <c r="E16" t="n">
-        <v>120.2707876061511</v>
+        <v>120.0055527422753</v>
       </c>
       <c r="F16" t="n">
-        <v>99.50286999577044</v>
+        <v>99.33988340047138</v>
       </c>
       <c r="G16" t="n">
-        <v>20.76791761038066</v>
+        <v>20.6656693418039</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3265017747829426</v>
+        <v>0.324821321593703</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7123723575062877</v>
+        <v>0.716553029026524</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5273649222365817</v>
+        <v>0.5273042599421123</v>
       </c>
       <c r="K16" t="n">
-        <v>6275</v>
+        <v>6475</v>
       </c>
       <c r="L16" t="n">
-        <v>2860</v>
+        <v>2945</v>
       </c>
       <c r="M16" t="n">
-        <v>681</v>
+        <v>705</v>
       </c>
       <c r="N16" t="n">
-        <v>1163</v>
+        <v>1205</v>
       </c>
       <c r="O16" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="P16" t="n">
-        <v>835</v>
+        <v>863</v>
       </c>
       <c r="Q16" t="n">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="R16" t="n">
-        <v>734</v>
+        <v>750</v>
       </c>
       <c r="S16" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="T16" t="n">
-        <v>719</v>
+        <v>741</v>
       </c>
       <c r="U16" t="n">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="V16" t="n">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="W16" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="X16" t="n">
-        <v>650</v>
+        <v>672</v>
       </c>
       <c r="Y16" t="n">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="Z16" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="n">
-        <v>2352</v>
+        <v>2420</v>
       </c>
       <c r="AB16" t="n">
-        <v>2678.96</v>
+        <v>2764</v>
       </c>
       <c r="AC16" t="n">
-        <v>2381.96</v>
+        <v>2458</v>
       </c>
       <c r="AD16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="n">
         <v>3250</v>
@@ -4542,82 +4542,82 @@
         <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>3025</v>
+        <v>3225</v>
       </c>
       <c r="BF16" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="BG16" t="n">
-        <v>568</v>
+        <v>610</v>
       </c>
       <c r="BH16" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="BI16" t="n">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="BJ16" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="BK16" t="n">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="BL16" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="BM16" t="n">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="BN16" t="n">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="BO16" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="BP16" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="BQ16" t="n">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="BR16" t="n">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="BS16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BT16" t="n">
-        <v>1305.4</v>
+        <v>1390.44</v>
       </c>
       <c r="BU16" t="n">
-        <v>1149.4</v>
+        <v>1225.44</v>
       </c>
       <c r="BV16" t="n">
-        <v>1.061971749265086</v>
+        <v>1.058069117005632</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8522282534441883</v>
+        <v>0.8547968830321977</v>
       </c>
       <c r="BX16" t="n">
-        <v>120.7921071080789</v>
+        <v>120.2290549114568</v>
       </c>
       <c r="BY16" t="n">
-        <v>94.54300566107989</v>
+        <v>94.52702399139994</v>
       </c>
       <c r="BZ16" t="n">
-        <v>26.24910144699898</v>
+        <v>25.70203092005682</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.3409317290832209</v>
+        <v>0.3366689505609742</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.739188087663736</v>
+        <v>0.7458734475693679</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.5462529474158399</v>
+        <v>0.5449511212531973</v>
       </c>
       <c r="CD16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -4632,166 +4632,166 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.01903839489033</v>
+        <v>1.015267110347749</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9603141056122063</v>
+        <v>0.9618162070459789</v>
       </c>
       <c r="E17" t="n">
-        <v>114.0024385783518</v>
+        <v>113.7582786349142</v>
       </c>
       <c r="F17" t="n">
-        <v>108.2652360962009</v>
+        <v>108.4019152856317</v>
       </c>
       <c r="G17" t="n">
-        <v>5.737202482150895</v>
+        <v>5.356363349282503</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2969399888952391</v>
+        <v>0.3001606142422629</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7063667082258202</v>
+        <v>0.7074782324647311</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5090361720154426</v>
+        <v>0.5110591195088124</v>
       </c>
       <c r="K17" t="n">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="L17" t="n">
-        <v>2612</v>
+        <v>2682</v>
       </c>
       <c r="M17" t="n">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="N17" t="n">
-        <v>997</v>
+        <v>1023</v>
       </c>
       <c r="O17" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="P17" t="n">
-        <v>891</v>
+        <v>924</v>
       </c>
       <c r="Q17" t="n">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="R17" t="n">
-        <v>690</v>
+        <v>708</v>
       </c>
       <c r="S17" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="T17" t="n">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="U17" t="n">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="V17" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="W17" t="n">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="X17" t="n">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="Y17" t="n">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="Z17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AA17" t="n">
-        <v>2484</v>
+        <v>2561</v>
       </c>
       <c r="AB17" t="n">
-        <v>2562.6</v>
+        <v>2640.52</v>
       </c>
       <c r="AC17" t="n">
-        <v>2292.6</v>
+        <v>2358.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="AF17" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AG17" t="n">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="AH17" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AI17" t="n">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="AJ17" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="AK17" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="AL17" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="AM17" t="n">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="AN17" t="n">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="AO17" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AP17" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="AQ17" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="AR17" t="n">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="AS17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AT17" t="n">
-        <v>1228.68</v>
+        <v>1306.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1107.68</v>
+        <v>1173.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.002864804508091</v>
+        <v>0.9963330848218177</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.9766604326316545</v>
+        <v>0.9786429900604842</v>
       </c>
       <c r="AX17" t="n">
-        <v>111.2264350797026</v>
+        <v>110.911615411493</v>
       </c>
       <c r="AY17" t="n">
-        <v>110.1620942098723</v>
+        <v>110.3168989566294</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.064340869830321</v>
+        <v>0.5947164548635753</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.2797634275300964</v>
+        <v>0.2872782133094654</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.7096996860168905</v>
+        <v>0.7117144233827704</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.5048446121457768</v>
+        <v>0.5091524796243707</v>
       </c>
       <c r="BD17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE17" t="n">
         <v>3200</v>
@@ -4884,88 +4884,88 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.870390857512733</v>
+        <v>0.8638239766980027</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9553159824473043</v>
+        <v>0.9578083151317248</v>
       </c>
       <c r="E18" t="n">
-        <v>97.90063438127875</v>
+        <v>97.4249699380297</v>
       </c>
       <c r="F18" t="n">
-        <v>109.9505938313866</v>
+        <v>110.1473647982258</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.04995945010781</v>
+        <v>-12.72239486019604</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2697491769747821</v>
+        <v>0.2738195151943201</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6458988698255751</v>
+        <v>0.6465478634768592</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4500887128220807</v>
+        <v>0.4516484405463906</v>
       </c>
       <c r="K18" t="n">
-        <v>6225</v>
+        <v>6425</v>
       </c>
       <c r="L18" t="n">
-        <v>2257</v>
+        <v>2316</v>
       </c>
       <c r="M18" t="n">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="N18" t="n">
-        <v>1091</v>
+        <v>1138</v>
       </c>
       <c r="O18" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="P18" t="n">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="Q18" t="n">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="R18" t="n">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="S18" t="n">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="T18" t="n">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="U18" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="V18" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="W18" t="n">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="X18" t="n">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="Y18" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="Z18" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AA18" t="n">
-        <v>2568</v>
+        <v>2653</v>
       </c>
       <c r="AB18" t="n">
-        <v>2600.88</v>
+        <v>2690.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>2311.88</v>
+        <v>2383.24</v>
       </c>
       <c r="AD18" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE18" t="n">
         <v>3200</v>
@@ -5046,82 +5046,82 @@
         <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>3025</v>
+        <v>3225</v>
       </c>
       <c r="BF18" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="BG18" t="n">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="BH18" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="BI18" t="n">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="BJ18" t="n">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="BK18" t="n">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="BL18" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="BM18" t="n">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="BN18" t="n">
+        <v>215</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP18" t="n">
         <v>208</v>
       </c>
-      <c r="BO18" t="n">
-        <v>104</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>195</v>
-      </c>
       <c r="BQ18" t="n">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="BR18" t="n">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="BS18" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="BT18" t="n">
-        <v>1287.16</v>
+        <v>1376.52</v>
       </c>
       <c r="BU18" t="n">
-        <v>1130.16</v>
+        <v>1201.52</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8489342095684588</v>
+        <v>0.8371414884355152</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9091597191451085</v>
+        <v>0.9170291509703365</v>
       </c>
       <c r="BX18" t="n">
-        <v>96.64984034572326</v>
+        <v>95.7766860864474</v>
       </c>
       <c r="BY18" t="n">
-        <v>104.6256789069867</v>
+        <v>105.3520280234401</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-7.975838561263433</v>
+        <v>-9.575341936992674</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.2959708099840623</v>
+        <v>0.3024726343600584</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.6501243403989243</v>
+        <v>0.6511582357906581</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.4677567643771539</v>
+        <v>0.4697719666035818</v>
       </c>
       <c r="CD18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -5136,88 +5136,88 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9849576124627533</v>
+        <v>0.9888999092955144</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8754339667635122</v>
+        <v>0.8744193816990695</v>
       </c>
       <c r="E19" t="n">
-        <v>111.744736945671</v>
+        <v>112.3645560213819</v>
       </c>
       <c r="F19" t="n">
-        <v>98.78099034872697</v>
+        <v>98.68901868291414</v>
       </c>
       <c r="G19" t="n">
-        <v>12.96374659694402</v>
+        <v>13.67553733846779</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3132206482623495</v>
+        <v>0.3185187099007027</v>
       </c>
       <c r="I19" t="n">
-        <v>0.710756407306438</v>
+        <v>0.7121733183585996</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5182996466520845</v>
+        <v>0.5221920684084925</v>
       </c>
       <c r="K19" t="n">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="L19" t="n">
-        <v>2575</v>
+        <v>2675</v>
       </c>
       <c r="M19" t="n">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="N19" t="n">
-        <v>1166</v>
+        <v>1200</v>
       </c>
       <c r="O19" t="n">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="P19" t="n">
-        <v>856</v>
+        <v>890</v>
       </c>
       <c r="Q19" t="n">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="R19" t="n">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="S19" t="n">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="T19" t="n">
-        <v>723</v>
+        <v>754</v>
       </c>
       <c r="U19" t="n">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="V19" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="W19" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="X19" t="n">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="Y19" t="n">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="Z19" t="n">
         <v>50</v>
       </c>
       <c r="AA19" t="n">
-        <v>2254</v>
+        <v>2324</v>
       </c>
       <c r="AB19" t="n">
-        <v>2619.96</v>
+        <v>2709.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>2303.96</v>
+        <v>2379.96</v>
       </c>
       <c r="AD19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE19" t="n">
         <v>3200</v>
@@ -5298,82 +5298,82 @@
         <v>16</v>
       </c>
       <c r="BE19" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="BF19" t="n">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="BG19" t="n">
-        <v>580</v>
+        <v>614</v>
       </c>
       <c r="BH19" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="BI19" t="n">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="BJ19" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="BK19" t="n">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="BL19" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="BM19" t="n">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="BN19" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="BO19" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="BP19" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="BQ19" t="n">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="BR19" t="n">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="BS19" t="n">
         <v>23</v>
       </c>
       <c r="BT19" t="n">
-        <v>1269.72</v>
+        <v>1359.72</v>
       </c>
       <c r="BU19" t="n">
-        <v>1112.72</v>
+        <v>1188.72</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.9985547260685805</v>
+        <v>1.005589500133739</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.8704555676139751</v>
+        <v>0.868737547431936</v>
       </c>
       <c r="BX19" t="n">
-        <v>113.5190815668361</v>
+        <v>114.6478231794352</v>
       </c>
       <c r="BY19" t="n">
-        <v>99.09188879488417</v>
+        <v>98.88851431037368</v>
       </c>
       <c r="BZ19" t="n">
-        <v>14.42719277195196</v>
+        <v>15.75930886906151</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.3312662916568919</v>
+        <v>0.3407345622214396</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.6928484535275222</v>
+        <v>0.6968015227430276</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.5231864667530209</v>
+        <v>0.5306658840095285</v>
       </c>
       <c r="CD19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
